--- a/src/temp/TEMPLATE.xlsx
+++ b/src/temp/TEMPLATE.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14295"/>
+    <workbookView windowWidth="14340" windowHeight="14115"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -176,10 +176,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="\N\8"/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;₱&quot;* #,##0_-;\-&quot;₱&quot;* #,##0_-;_-&quot;₱&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -202,6 +203,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -228,8 +237,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Cambria"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -244,53 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Cambria"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -303,16 +305,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -325,17 +327,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -392,7 +393,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,19 +447,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,73 +459,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,7 +507,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,43 +531,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -633,9 +634,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399975585192419"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,6 +648,30 @@
       <top/>
       <bottom style="thick">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,21 +687,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -702,93 +714,83 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -804,20 +806,17 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -826,14 +825,17 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note 2" xfId="1"/>
-    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Note 2" xfId="2"/>
     <cellStyle name="60% - Accent6" xfId="3" builtinId="52"/>
     <cellStyle name="40% - Accent6" xfId="4" builtinId="51"/>
     <cellStyle name="60% - Accent5" xfId="5" builtinId="48"/>
@@ -886,6 +888,7 @@
   </cellStyles>
   <dxfs count="1">
     <dxf>
+      <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
       <alignment horizontal="left"/>
     </dxf>
   </dxfs>
@@ -1280,7 +1283,7 @@
     <col min="7" max="7" width="15.2814814814815" customWidth="1"/>
     <col min="8" max="8" width="23.8518518518519" customWidth="1"/>
     <col min="9" max="9" width="8.71111111111111" customWidth="1"/>
-    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="10" max="10" width="24" style="4" customWidth="1"/>
     <col min="11" max="11" width="26.4222222222222" customWidth="1"/>
     <col min="12" max="14" width="8.14074074074074" customWidth="1"/>
     <col min="15" max="15" width="20.1407407407407" customWidth="1"/>
@@ -1294,7 +1297,7 @@
     <col min="27" max="27" width="16.4222222222222" customWidth="1"/>
     <col min="28" max="28" width="14" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="18.7111111111111" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="9.14074074074074" style="4" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="9.14074074074074" style="5" hidden="1" customWidth="1"/>
     <col min="31" max="31" width="23.7111111111111" hidden="1" customWidth="1"/>
     <col min="32" max="32" width="16.4222222222222" hidden="1" customWidth="1"/>
     <col min="33" max="33" width="13.1407407407407" hidden="1" customWidth="1"/>
@@ -1325,91 +1328,91 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:62">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AA1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AC1" s="6" t="s">
         <v>28</v>
       </c>
       <c r="AE1" s="19" t="s">
@@ -1510,49 +1513,49 @@
       </c>
     </row>
     <row r="2" ht="15.75" spans="2:62">
-      <c r="B2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="J2" s="13"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
+      <c r="B2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="J2" s="15"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
       <c r="AE2" s="20"/>
       <c r="AK2" s="26"/>
       <c r="AL2" s="26"/>
-      <c r="AM2" s="13"/>
+      <c r="AM2" s="27"/>
       <c r="AN2" s="26"/>
       <c r="BE2" s="26"/>
       <c r="BF2" s="26"/>
-      <c r="BH2" s="28"/>
+      <c r="BH2" s="29"/>
       <c r="BJ2" s="26"/>
     </row>
     <row r="3" spans="2:62">
-      <c r="B3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="J3" s="13"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
+      <c r="B3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="J3" s="15"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
       <c r="AE3" s="20"/>
       <c r="AK3" s="26"/>
       <c r="AL3" s="26"/>
-      <c r="AM3" s="13"/>
+      <c r="AM3" s="27"/>
       <c r="AN3" s="26"/>
       <c r="BE3" s="26"/>
       <c r="BF3" s="26"/>
-      <c r="BH3" s="28"/>
+      <c r="BH3" s="29"/>
       <c r="BJ3" s="26"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="2:62">
-      <c r="B4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="J4" s="15"/>
+      <c r="B4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="J4" s="17"/>
       <c r="AD4" s="21"/>
       <c r="BE4" s="25"/>
       <c r="BF4" s="25"/>
@@ -1560,32 +1563,32 @@
       <c r="BJ4" s="25"/>
     </row>
     <row r="5" s="2" customFormat="1" spans="2:62">
-      <c r="B5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="J5" s="16"/>
+      <c r="B5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="J5" s="18"/>
       <c r="AD5" s="22"/>
       <c r="AE5" s="23"/>
-      <c r="AK5" s="27"/>
-      <c r="AL5" s="27"/>
-      <c r="AN5" s="27"/>
-      <c r="BE5" s="27"/>
-      <c r="BF5" s="27"/>
-      <c r="BH5" s="29"/>
-      <c r="BJ5" s="27"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BH5" s="30"/>
+      <c r="BJ5" s="28"/>
     </row>
     <row r="6" spans="1:90">
       <c r="A6" s="1"/>
-      <c r="B6" s="7"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="17"/>
+      <c r="J6" s="15"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
@@ -1612,7 +1615,7 @@
       <c r="AS6" s="1"/>
       <c r="BE6" s="26"/>
       <c r="BF6" s="26"/>
-      <c r="BH6" s="28"/>
+      <c r="BH6" s="29"/>
       <c r="BJ6" s="26"/>
       <c r="BK6" s="1"/>
       <c r="BL6" s="1"/>
@@ -1644,12 +1647,11 @@
       <c r="CL6" s="1"/>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="3:90">
-      <c r="C7" s="9"/>
+      <c r="C7" s="10"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="J7" s="18"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
@@ -1714,10 +1716,9 @@
       <c r="CL7" s="1"/>
     </row>
     <row r="8" spans="3:90">
-      <c r="C8" s="9"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="J8" s="18"/>
+      <c r="C8" s="10"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
@@ -1782,10 +1783,9 @@
       <c r="CL8" s="1"/>
     </row>
     <row r="9" spans="3:90">
-      <c r="C9" s="9"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="J9" s="18"/>
+      <c r="C9" s="10"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -1850,10 +1850,9 @@
       <c r="CL9" s="1"/>
     </row>
     <row r="10" spans="3:90">
-      <c r="C10" s="9"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="J10" s="18"/>
+      <c r="C10" s="10"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -1918,10 +1917,9 @@
       <c r="CL10" s="1"/>
     </row>
     <row r="11" spans="3:90">
-      <c r="C11" s="9"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="J11" s="18"/>
+      <c r="C11" s="10"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -1986,10 +1984,9 @@
       <c r="CL11" s="1"/>
     </row>
     <row r="12" spans="3:90">
-      <c r="C12" s="9"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="J12" s="18"/>
+      <c r="C12" s="10"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
@@ -2054,10 +2051,9 @@
       <c r="CL12" s="1"/>
     </row>
     <row r="13" spans="3:90">
-      <c r="C13" s="9"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="J13" s="18"/>
+      <c r="C13" s="10"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
@@ -2124,14 +2120,14 @@
     <row r="14" s="3" customFormat="1" spans="1:90">
       <c r="A14"/>
       <c r="B14"/>
-      <c r="C14" s="9"/>
+      <c r="C14" s="10"/>
       <c r="D14"/>
       <c r="E14"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
       <c r="H14"/>
       <c r="I14"/>
-      <c r="J14" s="18"/>
+      <c r="J14" s="4"/>
       <c r="K14"/>
       <c r="L14"/>
       <c r="M14"/>
@@ -2151,7 +2147,7 @@
       <c r="AA14"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
-      <c r="AD14" s="4"/>
+      <c r="AD14" s="5"/>
       <c r="AE14" s="1"/>
       <c r="AF14" s="1"/>
       <c r="AG14" s="1"/>
@@ -2214,10 +2210,9 @@
       <c r="CL14" s="1"/>
     </row>
     <row r="15" spans="3:90">
-      <c r="C15" s="9"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="J15" s="18"/>
+      <c r="C15" s="10"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
@@ -2282,10 +2277,9 @@
       <c r="CL15" s="1"/>
     </row>
     <row r="16" spans="3:90">
-      <c r="C16" s="9"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="J16" s="18"/>
+      <c r="C16" s="10"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -2350,10 +2344,9 @@
       <c r="CL16" s="1"/>
     </row>
     <row r="17" spans="3:90">
-      <c r="C17" s="9"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="J17" s="18"/>
+      <c r="C17" s="10"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
@@ -2420,14 +2413,14 @@
     <row r="18" s="3" customFormat="1" spans="1:90">
       <c r="A18"/>
       <c r="B18"/>
-      <c r="C18" s="9"/>
+      <c r="C18" s="10"/>
       <c r="D18"/>
       <c r="E18"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
       <c r="H18"/>
       <c r="I18"/>
-      <c r="J18" s="18"/>
+      <c r="J18" s="4"/>
       <c r="K18"/>
       <c r="L18"/>
       <c r="M18"/>
@@ -2447,7 +2440,7 @@
       <c r="AA18"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
-      <c r="AD18" s="4"/>
+      <c r="AD18" s="5"/>
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1"/>
@@ -2510,10 +2503,9 @@
       <c r="CL18" s="1"/>
     </row>
     <row r="19" spans="3:90">
-      <c r="C19" s="9"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="J19" s="18"/>
+      <c r="C19" s="10"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
@@ -2578,10 +2570,9 @@
       <c r="CL19" s="1"/>
     </row>
     <row r="20" spans="3:90">
-      <c r="C20" s="9"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="J20" s="18"/>
+      <c r="C20" s="10"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
@@ -2646,10 +2637,9 @@
       <c r="CL20" s="1"/>
     </row>
     <row r="21" spans="3:90">
-      <c r="C21" s="9"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="J21" s="18"/>
+      <c r="C21" s="10"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
@@ -2714,10 +2704,9 @@
       <c r="CL21" s="1"/>
     </row>
     <row r="22" spans="3:90">
-      <c r="C22" s="9"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="J22" s="18"/>
+      <c r="C22" s="10"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
@@ -2782,10 +2771,9 @@
       <c r="CL22" s="1"/>
     </row>
     <row r="23" spans="3:90">
-      <c r="C23" s="9"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="J23" s="18"/>
+      <c r="C23" s="10"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
@@ -2850,10 +2838,9 @@
       <c r="CL23" s="1"/>
     </row>
     <row r="24" spans="3:90">
-      <c r="C24" s="9"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="J24" s="18"/>
+      <c r="C24" s="10"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
@@ -2918,10 +2905,9 @@
       <c r="CL24" s="1"/>
     </row>
     <row r="25" spans="3:90">
-      <c r="C25" s="9"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="J25" s="18"/>
+      <c r="C25" s="10"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
@@ -2986,10 +2972,9 @@
       <c r="CL25" s="1"/>
     </row>
     <row r="26" spans="3:90">
-      <c r="C26" s="9"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="J26" s="18"/>
+      <c r="C26" s="10"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
@@ -3054,10 +3039,9 @@
       <c r="CL26" s="1"/>
     </row>
     <row r="27" spans="3:90">
-      <c r="C27" s="9"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="J27" s="18"/>
+      <c r="C27" s="10"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
@@ -3122,10 +3106,9 @@
       <c r="CL27" s="1"/>
     </row>
     <row r="28" spans="3:90">
-      <c r="C28" s="9"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="J28" s="18"/>
+      <c r="C28" s="10"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
@@ -3192,14 +3175,14 @@
     <row r="29" s="3" customFormat="1" spans="1:90">
       <c r="A29"/>
       <c r="B29"/>
-      <c r="C29" s="9"/>
+      <c r="C29" s="10"/>
       <c r="D29"/>
       <c r="E29"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
       <c r="H29"/>
       <c r="I29"/>
-      <c r="J29" s="18"/>
+      <c r="J29" s="4"/>
       <c r="K29"/>
       <c r="L29"/>
       <c r="M29"/>
@@ -3219,7 +3202,7 @@
       <c r="AA29"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
-      <c r="AD29" s="4"/>
+      <c r="AD29" s="5"/>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
       <c r="AG29" s="1"/>
@@ -3282,10 +3265,9 @@
       <c r="CL29" s="1"/>
     </row>
     <row r="30" spans="3:90">
-      <c r="C30" s="9"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="J30" s="18"/>
+      <c r="C30" s="10"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
@@ -3350,10 +3332,9 @@
       <c r="CL30" s="1"/>
     </row>
     <row r="31" spans="3:90">
-      <c r="C31" s="9"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="J31" s="18"/>
+      <c r="C31" s="10"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
@@ -3418,10 +3399,9 @@
       <c r="CL31" s="1"/>
     </row>
     <row r="32" spans="3:90">
-      <c r="C32" s="9"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="J32" s="18"/>
+      <c r="C32" s="10"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
@@ -3486,10 +3466,9 @@
       <c r="CL32" s="1"/>
     </row>
     <row r="33" spans="3:90">
-      <c r="C33" s="9"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="J33" s="18"/>
+      <c r="C33" s="10"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
@@ -3554,10 +3533,9 @@
       <c r="CL33" s="1"/>
     </row>
     <row r="34" spans="3:90">
-      <c r="C34" s="9"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="J34" s="18"/>
+      <c r="C34" s="10"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
@@ -3622,10 +3600,9 @@
       <c r="CL34" s="1"/>
     </row>
     <row r="35" spans="3:90">
-      <c r="C35" s="9"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="J35" s="18"/>
+      <c r="C35" s="10"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
@@ -3690,10 +3667,9 @@
       <c r="CL35" s="1"/>
     </row>
     <row r="36" spans="3:90">
-      <c r="C36" s="9"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="J36" s="18"/>
+      <c r="C36" s="10"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
@@ -3758,10 +3734,9 @@
       <c r="CL36" s="1"/>
     </row>
     <row r="37" spans="3:90">
-      <c r="C37" s="9"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="J37" s="18"/>
+      <c r="C37" s="10"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
@@ -3826,10 +3801,9 @@
       <c r="CL37" s="1"/>
     </row>
     <row r="38" spans="3:90">
-      <c r="C38" s="9"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="J38" s="18"/>
+      <c r="C38" s="10"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
@@ -3894,10 +3868,9 @@
       <c r="CL38" s="1"/>
     </row>
     <row r="39" spans="3:90">
-      <c r="C39" s="9"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="J39" s="18"/>
+      <c r="C39" s="10"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
@@ -3962,10 +3935,9 @@
       <c r="CL39" s="1"/>
     </row>
     <row r="40" spans="3:90">
-      <c r="C40" s="9"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="J40" s="18"/>
+      <c r="C40" s="10"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
@@ -4030,10 +4002,9 @@
       <c r="CL40" s="1"/>
     </row>
     <row r="41" spans="3:90">
-      <c r="C41" s="9"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="J41" s="18"/>
+      <c r="C41" s="10"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
@@ -4098,10 +4069,9 @@
       <c r="CL41" s="1"/>
     </row>
     <row r="42" spans="3:90">
-      <c r="C42" s="9"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="J42" s="18"/>
+      <c r="C42" s="10"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
@@ -4166,10 +4136,9 @@
       <c r="CL42" s="1"/>
     </row>
     <row r="43" spans="3:90">
-      <c r="C43" s="9"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="J43" s="18"/>
+      <c r="C43" s="10"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
@@ -4234,10 +4203,9 @@
       <c r="CL43" s="1"/>
     </row>
     <row r="44" spans="3:90">
-      <c r="C44" s="9"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="J44" s="18"/>
+      <c r="C44" s="10"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
@@ -4302,10 +4270,9 @@
       <c r="CL44" s="1"/>
     </row>
     <row r="45" spans="3:90">
-      <c r="C45" s="9"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="J45" s="18"/>
+      <c r="C45" s="10"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
@@ -4370,10 +4337,9 @@
       <c r="CL45" s="1"/>
     </row>
     <row r="46" spans="3:90">
-      <c r="C46" s="9"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="J46" s="18"/>
+      <c r="C46" s="10"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
@@ -4438,10 +4404,9 @@
       <c r="CL46" s="1"/>
     </row>
     <row r="47" spans="3:90">
-      <c r="C47" s="9"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="J47" s="18"/>
+      <c r="C47" s="10"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
@@ -4506,10 +4471,9 @@
       <c r="CL47" s="1"/>
     </row>
     <row r="48" spans="3:90">
-      <c r="C48" s="9"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="J48" s="18"/>
+      <c r="C48" s="10"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
@@ -4574,10 +4538,9 @@
       <c r="CL48" s="1"/>
     </row>
     <row r="49" spans="3:90">
-      <c r="C49" s="9"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="J49" s="18"/>
+      <c r="C49" s="10"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
@@ -4642,10 +4605,9 @@
       <c r="CL49" s="1"/>
     </row>
     <row r="50" spans="3:90">
-      <c r="C50" s="9"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="J50" s="18"/>
+      <c r="C50" s="10"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
@@ -4710,10 +4672,9 @@
       <c r="CL50" s="1"/>
     </row>
     <row r="51" spans="3:90">
-      <c r="C51" s="9"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="J51" s="18"/>
+      <c r="C51" s="10"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
@@ -4778,10 +4739,9 @@
       <c r="CL51" s="1"/>
     </row>
     <row r="52" spans="3:90">
-      <c r="C52" s="9"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="J52" s="18"/>
+      <c r="C52" s="10"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
@@ -4846,10 +4806,9 @@
       <c r="CL52" s="1"/>
     </row>
     <row r="53" spans="3:90">
-      <c r="C53" s="9"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="J53" s="18"/>
+      <c r="C53" s="10"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
@@ -4914,10 +4873,9 @@
       <c r="CL53" s="1"/>
     </row>
     <row r="54" spans="3:90">
-      <c r="C54" s="9"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="J54" s="18"/>
+      <c r="C54" s="10"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
@@ -4982,10 +4940,9 @@
       <c r="CL54" s="1"/>
     </row>
     <row r="55" spans="3:90">
-      <c r="C55" s="9"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="J55" s="18"/>
+      <c r="C55" s="10"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
@@ -5050,10 +5007,9 @@
       <c r="CL55" s="1"/>
     </row>
     <row r="56" spans="3:90">
-      <c r="C56" s="9"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="J56" s="18"/>
+      <c r="C56" s="10"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
@@ -5118,10 +5074,9 @@
       <c r="CL56" s="1"/>
     </row>
     <row r="57" spans="3:90">
-      <c r="C57" s="9"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="J57" s="18"/>
+      <c r="C57" s="10"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
@@ -5186,10 +5141,9 @@
       <c r="CL57" s="1"/>
     </row>
     <row r="58" spans="3:90">
-      <c r="C58" s="9"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="J58" s="18"/>
+      <c r="C58" s="10"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
@@ -5254,10 +5208,9 @@
       <c r="CL58" s="1"/>
     </row>
     <row r="59" spans="3:90">
-      <c r="C59" s="9"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="J59" s="18"/>
+      <c r="C59" s="10"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
@@ -5322,10 +5275,9 @@
       <c r="CL59" s="1"/>
     </row>
     <row r="60" spans="3:90">
-      <c r="C60" s="9"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="J60" s="18"/>
+      <c r="C60" s="10"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
@@ -5390,10 +5342,9 @@
       <c r="CL60" s="1"/>
     </row>
     <row r="61" spans="3:90">
-      <c r="C61" s="9"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="J61" s="18"/>
+      <c r="C61" s="10"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
@@ -5458,10 +5409,9 @@
       <c r="CL61" s="1"/>
     </row>
     <row r="62" spans="3:90">
-      <c r="C62" s="9"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="J62" s="18"/>
+      <c r="C62" s="10"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
@@ -5526,10 +5476,9 @@
       <c r="CL62" s="1"/>
     </row>
     <row r="63" spans="3:90">
-      <c r="C63" s="9"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="J63" s="18"/>
+      <c r="C63" s="10"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
@@ -5594,10 +5543,9 @@
       <c r="CL63" s="1"/>
     </row>
     <row r="64" spans="3:90">
-      <c r="C64" s="9"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
-      <c r="J64" s="18"/>
+      <c r="C64" s="10"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
@@ -5662,10 +5610,9 @@
       <c r="CL64" s="1"/>
     </row>
     <row r="65" spans="3:90">
-      <c r="C65" s="9"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="J65" s="18"/>
+      <c r="C65" s="10"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
@@ -5730,10 +5677,9 @@
       <c r="CL65" s="1"/>
     </row>
     <row r="66" spans="3:90">
-      <c r="C66" s="9"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="J66" s="18"/>
+      <c r="C66" s="10"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
@@ -5798,10 +5744,9 @@
       <c r="CL66" s="1"/>
     </row>
     <row r="67" spans="3:90">
-      <c r="C67" s="9"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="J67" s="18"/>
+      <c r="C67" s="10"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
@@ -5866,10 +5811,9 @@
       <c r="CL67" s="1"/>
     </row>
     <row r="68" spans="3:90">
-      <c r="C68" s="9"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="J68" s="18"/>
+      <c r="C68" s="10"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
       <c r="S68" s="1"/>
@@ -5934,10 +5878,9 @@
       <c r="CL68" s="1"/>
     </row>
     <row r="69" spans="3:90">
-      <c r="C69" s="9"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="J69" s="18"/>
+      <c r="C69" s="10"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
@@ -6002,10 +5945,9 @@
       <c r="CL69" s="1"/>
     </row>
     <row r="70" spans="3:90">
-      <c r="C70" s="9"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="11"/>
-      <c r="J70" s="18"/>
+      <c r="C70" s="10"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
@@ -6070,10 +6012,9 @@
       <c r="CL70" s="1"/>
     </row>
     <row r="71" spans="3:90">
-      <c r="C71" s="9"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="J71" s="18"/>
+      <c r="C71" s="10"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
@@ -6138,10 +6079,9 @@
       <c r="CL71" s="1"/>
     </row>
     <row r="72" spans="3:90">
-      <c r="C72" s="9"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="J72" s="18"/>
+      <c r="C72" s="10"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
@@ -6206,10 +6146,9 @@
       <c r="CL72" s="1"/>
     </row>
     <row r="73" spans="3:90">
-      <c r="C73" s="9"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="J73" s="18"/>
+      <c r="C73" s="10"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
@@ -6274,10 +6213,9 @@
       <c r="CL73" s="1"/>
     </row>
     <row r="74" spans="3:90">
-      <c r="C74" s="9"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="J74" s="18"/>
+      <c r="C74" s="10"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
@@ -6342,10 +6280,9 @@
       <c r="CL74" s="1"/>
     </row>
     <row r="75" spans="3:90">
-      <c r="C75" s="9"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11"/>
-      <c r="J75" s="18"/>
+      <c r="C75" s="10"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
@@ -6410,10 +6347,9 @@
       <c r="CL75" s="1"/>
     </row>
     <row r="76" spans="3:90">
-      <c r="C76" s="9"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
-      <c r="J76" s="18"/>
+      <c r="C76" s="10"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
@@ -6478,13 +6414,13 @@
       <c r="CL76" s="1"/>
     </row>
     <row r="77" spans="3:90">
-      <c r="C77" s="9"/>
+      <c r="C77" s="10"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="11"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
-      <c r="J77" s="18"/>
+      <c r="J77" s="4"/>
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
@@ -6555,13 +6491,13 @@
       <c r="CL77" s="1"/>
     </row>
     <row r="78" spans="3:90">
-      <c r="C78" s="9"/>
+      <c r="C78" s="10"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="11"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
-      <c r="J78" s="18"/>
+      <c r="J78" s="4"/>
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
@@ -6632,13 +6568,13 @@
       <c r="CL78" s="1"/>
     </row>
     <row r="79" spans="3:90">
-      <c r="C79" s="9"/>
+      <c r="C79" s="10"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
-      <c r="J79" s="18"/>
+      <c r="J79" s="4"/>
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
@@ -6709,13 +6645,13 @@
       <c r="CL79" s="1"/>
     </row>
     <row r="80" spans="3:90">
-      <c r="C80" s="9"/>
+      <c r="C80" s="10"/>
       <c r="E80" s="1"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="11"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
-      <c r="J80" s="18"/>
+      <c r="J80" s="4"/>
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
@@ -6786,13 +6722,13 @@
       <c r="CL80" s="1"/>
     </row>
     <row r="81" spans="3:90">
-      <c r="C81" s="9"/>
+      <c r="C81" s="10"/>
       <c r="E81" s="1"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
-      <c r="J81" s="18"/>
+      <c r="J81" s="4"/>
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
@@ -6863,13 +6799,13 @@
       <c r="CL81" s="1"/>
     </row>
     <row r="82" spans="3:90">
-      <c r="C82" s="9"/>
+      <c r="C82" s="10"/>
       <c r="E82" s="1"/>
-      <c r="F82" s="11"/>
-      <c r="G82" s="11"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="18"/>
+      <c r="J82" s="4"/>
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
@@ -6940,13 +6876,13 @@
       <c r="CL82" s="1"/>
     </row>
     <row r="83" spans="3:90">
-      <c r="C83" s="9"/>
+      <c r="C83" s="10"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="11"/>
-      <c r="G83" s="11"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
-      <c r="J83" s="18"/>
+      <c r="J83" s="4"/>
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
@@ -7017,13 +6953,13 @@
       <c r="CL83" s="1"/>
     </row>
     <row r="84" spans="3:90">
-      <c r="C84" s="9"/>
+      <c r="C84" s="10"/>
       <c r="E84" s="1"/>
-      <c r="F84" s="11"/>
-      <c r="G84" s="11"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
-      <c r="J84" s="18"/>
+      <c r="J84" s="4"/>
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
@@ -7094,13 +7030,13 @@
       <c r="CL84" s="1"/>
     </row>
     <row r="85" spans="3:90">
-      <c r="C85" s="9"/>
+      <c r="C85" s="10"/>
       <c r="E85" s="1"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="11"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
-      <c r="J85" s="18"/>
+      <c r="J85" s="4"/>
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
@@ -7171,13 +7107,13 @@
       <c r="CL85" s="1"/>
     </row>
     <row r="86" spans="3:90">
-      <c r="C86" s="9"/>
+      <c r="C86" s="10"/>
       <c r="E86" s="1"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="11"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
-      <c r="J86" s="18"/>
+      <c r="J86" s="4"/>
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
@@ -7248,13 +7184,13 @@
       <c r="CL86" s="1"/>
     </row>
     <row r="87" spans="3:62">
-      <c r="C87" s="9"/>
+      <c r="C87" s="10"/>
       <c r="E87" s="1"/>
-      <c r="F87" s="11"/>
-      <c r="G87" s="11"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
-      <c r="J87" s="18"/>
+      <c r="J87" s="4"/>
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
@@ -7297,13 +7233,13 @@
       <c r="BJ87" s="25"/>
     </row>
     <row r="88" spans="3:62">
-      <c r="C88" s="9"/>
+      <c r="C88" s="10"/>
       <c r="E88" s="1"/>
-      <c r="F88" s="11"/>
-      <c r="G88" s="11"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
-      <c r="J88" s="18"/>
+      <c r="J88" s="4"/>
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
@@ -7346,13 +7282,13 @@
       <c r="BJ88" s="25"/>
     </row>
     <row r="89" spans="3:62">
-      <c r="C89" s="9"/>
+      <c r="C89" s="10"/>
       <c r="E89" s="1"/>
-      <c r="F89" s="11"/>
-      <c r="G89" s="11"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
-      <c r="J89" s="18"/>
+      <c r="J89" s="4"/>
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
@@ -7395,13 +7331,13 @@
       <c r="BJ89" s="25"/>
     </row>
     <row r="90" spans="3:62">
-      <c r="C90" s="9"/>
+      <c r="C90" s="10"/>
       <c r="E90" s="1"/>
-      <c r="F90" s="11"/>
-      <c r="G90" s="11"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
-      <c r="J90" s="18"/>
+      <c r="J90" s="4"/>
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
@@ -7444,13 +7380,13 @@
       <c r="BJ90" s="25"/>
     </row>
     <row r="91" spans="3:62">
-      <c r="C91" s="9"/>
+      <c r="C91" s="10"/>
       <c r="E91" s="1"/>
-      <c r="F91" s="11"/>
-      <c r="G91" s="11"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
-      <c r="J91" s="18"/>
+      <c r="J91" s="4"/>
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
@@ -7493,13 +7429,13 @@
       <c r="BJ91" s="25"/>
     </row>
     <row r="92" spans="3:62">
-      <c r="C92" s="9"/>
+      <c r="C92" s="10"/>
       <c r="E92" s="1"/>
-      <c r="F92" s="11"/>
-      <c r="G92" s="11"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
-      <c r="J92" s="18"/>
+      <c r="J92" s="4"/>
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
@@ -7542,13 +7478,13 @@
       <c r="BJ92" s="25"/>
     </row>
     <row r="93" spans="3:62">
-      <c r="C93" s="9"/>
+      <c r="C93" s="10"/>
       <c r="E93" s="1"/>
-      <c r="F93" s="11"/>
-      <c r="G93" s="11"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
-      <c r="J93" s="18"/>
+      <c r="J93" s="4"/>
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
@@ -7591,13 +7527,13 @@
       <c r="BJ93" s="25"/>
     </row>
     <row r="94" spans="3:62">
-      <c r="C94" s="9"/>
+      <c r="C94" s="10"/>
       <c r="E94" s="1"/>
-      <c r="F94" s="11"/>
-      <c r="G94" s="11"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
-      <c r="J94" s="18"/>
+      <c r="J94" s="4"/>
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
@@ -7640,13 +7576,13 @@
       <c r="BJ94" s="25"/>
     </row>
     <row r="95" spans="3:62">
-      <c r="C95" s="9"/>
+      <c r="C95" s="10"/>
       <c r="E95" s="1"/>
-      <c r="F95" s="11"/>
-      <c r="G95" s="11"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
-      <c r="J95" s="18"/>
+      <c r="J95" s="4"/>
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
@@ -7689,13 +7625,13 @@
       <c r="BJ95" s="25"/>
     </row>
     <row r="96" spans="3:62">
-      <c r="C96" s="9"/>
+      <c r="C96" s="10"/>
       <c r="E96" s="1"/>
-      <c r="F96" s="11"/>
-      <c r="G96" s="11"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
-      <c r="J96" s="18"/>
+      <c r="J96" s="4"/>
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
@@ -7738,13 +7674,13 @@
       <c r="BJ96" s="25"/>
     </row>
     <row r="97" spans="3:62">
-      <c r="C97" s="9"/>
+      <c r="C97" s="10"/>
       <c r="E97" s="1"/>
-      <c r="F97" s="11"/>
-      <c r="G97" s="11"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
-      <c r="J97" s="18"/>
+      <c r="J97" s="4"/>
       <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
@@ -7788,13 +7724,13 @@
       <c r="BJ97" s="25"/>
     </row>
     <row r="98" spans="3:62">
-      <c r="C98" s="9"/>
+      <c r="C98" s="10"/>
       <c r="E98" s="1"/>
-      <c r="F98" s="11"/>
-      <c r="G98" s="11"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
-      <c r="J98" s="18"/>
+      <c r="J98" s="4"/>
       <c r="P98" s="1"/>
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
@@ -7838,13 +7774,13 @@
       <c r="BJ98" s="25"/>
     </row>
     <row r="99" spans="3:62">
-      <c r="C99" s="9"/>
+      <c r="C99" s="10"/>
       <c r="E99" s="1"/>
-      <c r="F99" s="11"/>
-      <c r="G99" s="11"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
-      <c r="J99" s="18"/>
+      <c r="J99" s="4"/>
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
@@ -7888,13 +7824,13 @@
       <c r="BJ99" s="25"/>
     </row>
     <row r="100" spans="3:62">
-      <c r="C100" s="9"/>
+      <c r="C100" s="10"/>
       <c r="E100" s="1"/>
-      <c r="F100" s="11"/>
-      <c r="G100" s="11"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
-      <c r="J100" s="18"/>
+      <c r="J100" s="4"/>
       <c r="P100" s="1"/>
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
@@ -7938,13 +7874,13 @@
       <c r="BJ100" s="25"/>
     </row>
     <row r="101" spans="3:62">
-      <c r="C101" s="9"/>
+      <c r="C101" s="10"/>
       <c r="E101" s="1"/>
-      <c r="F101" s="11"/>
-      <c r="G101" s="11"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
-      <c r="J101" s="18"/>
+      <c r="J101" s="4"/>
       <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
@@ -7988,13 +7924,13 @@
       <c r="BJ101" s="25"/>
     </row>
     <row r="102" spans="3:62">
-      <c r="C102" s="9"/>
+      <c r="C102" s="10"/>
       <c r="E102" s="1"/>
-      <c r="F102" s="11"/>
-      <c r="G102" s="11"/>
+      <c r="F102" s="12"/>
+      <c r="G102" s="12"/>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
-      <c r="J102" s="18"/>
+      <c r="J102" s="4"/>
       <c r="P102" s="1"/>
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
@@ -8038,13 +7974,13 @@
       <c r="BJ102" s="25"/>
     </row>
     <row r="103" spans="3:62">
-      <c r="C103" s="9"/>
+      <c r="C103" s="10"/>
       <c r="E103" s="1"/>
-      <c r="F103" s="11"/>
-      <c r="G103" s="11"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="12"/>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
-      <c r="J103" s="18"/>
+      <c r="J103" s="4"/>
       <c r="P103" s="1"/>
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
@@ -8088,13 +8024,13 @@
       <c r="BJ103" s="25"/>
     </row>
     <row r="104" spans="3:62">
-      <c r="C104" s="9"/>
+      <c r="C104" s="10"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="11"/>
-      <c r="G104" s="11"/>
+      <c r="F104" s="12"/>
+      <c r="G104" s="12"/>
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
-      <c r="J104" s="18"/>
+      <c r="J104" s="4"/>
       <c r="P104" s="1"/>
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
@@ -8138,13 +8074,13 @@
       <c r="BJ104" s="25"/>
     </row>
     <row r="105" spans="3:62">
-      <c r="C105" s="9"/>
+      <c r="C105" s="10"/>
       <c r="E105" s="1"/>
-      <c r="F105" s="11"/>
-      <c r="G105" s="11"/>
+      <c r="F105" s="12"/>
+      <c r="G105" s="12"/>
       <c r="H105" s="1"/>
       <c r="I105" s="1"/>
-      <c r="J105" s="18"/>
+      <c r="J105" s="4"/>
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
@@ -8188,13 +8124,13 @@
       <c r="BJ105" s="25"/>
     </row>
     <row r="106" spans="3:62">
-      <c r="C106" s="9"/>
+      <c r="C106" s="10"/>
       <c r="E106" s="1"/>
-      <c r="F106" s="11"/>
-      <c r="G106" s="11"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
-      <c r="J106" s="18"/>
+      <c r="J106" s="4"/>
       <c r="P106" s="1"/>
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
@@ -8238,13 +8174,13 @@
       <c r="BJ106" s="25"/>
     </row>
     <row r="107" spans="3:62">
-      <c r="C107" s="9"/>
+      <c r="C107" s="10"/>
       <c r="E107" s="1"/>
-      <c r="F107" s="11"/>
-      <c r="G107" s="11"/>
+      <c r="F107" s="12"/>
+      <c r="G107" s="12"/>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
-      <c r="J107" s="18"/>
+      <c r="J107" s="4"/>
       <c r="P107" s="1"/>
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
@@ -8288,13 +8224,13 @@
       <c r="BJ107" s="25"/>
     </row>
     <row r="108" spans="3:62">
-      <c r="C108" s="9"/>
+      <c r="C108" s="10"/>
       <c r="E108" s="1"/>
-      <c r="F108" s="11"/>
-      <c r="G108" s="11"/>
+      <c r="F108" s="12"/>
+      <c r="G108" s="12"/>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
-      <c r="J108" s="18"/>
+      <c r="J108" s="4"/>
       <c r="P108" s="1"/>
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
@@ -8338,13 +8274,13 @@
       <c r="BJ108" s="25"/>
     </row>
     <row r="109" spans="3:62">
-      <c r="C109" s="9"/>
+      <c r="C109" s="10"/>
       <c r="E109" s="1"/>
-      <c r="F109" s="11"/>
-      <c r="G109" s="11"/>
+      <c r="F109" s="12"/>
+      <c r="G109" s="12"/>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
-      <c r="J109" s="18"/>
+      <c r="J109" s="4"/>
       <c r="P109" s="1"/>
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
@@ -8388,13 +8324,13 @@
       <c r="BJ109" s="25"/>
     </row>
     <row r="110" spans="3:62">
-      <c r="C110" s="9"/>
+      <c r="C110" s="10"/>
       <c r="E110" s="1"/>
-      <c r="F110" s="11"/>
-      <c r="G110" s="11"/>
+      <c r="F110" s="12"/>
+      <c r="G110" s="12"/>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
-      <c r="J110" s="18"/>
+      <c r="J110" s="4"/>
       <c r="P110" s="1"/>
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
@@ -8438,13 +8374,13 @@
       <c r="BJ110" s="25"/>
     </row>
     <row r="111" spans="3:62">
-      <c r="C111" s="9"/>
+      <c r="C111" s="10"/>
       <c r="E111" s="1"/>
-      <c r="F111" s="11"/>
-      <c r="G111" s="11"/>
+      <c r="F111" s="12"/>
+      <c r="G111" s="12"/>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
-      <c r="J111" s="18"/>
+      <c r="J111" s="4"/>
       <c r="P111" s="1"/>
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
@@ -8488,13 +8424,13 @@
       <c r="BJ111" s="25"/>
     </row>
     <row r="112" spans="3:62">
-      <c r="C112" s="9"/>
+      <c r="C112" s="10"/>
       <c r="E112" s="1"/>
-      <c r="F112" s="11"/>
-      <c r="G112" s="11"/>
+      <c r="F112" s="12"/>
+      <c r="G112" s="12"/>
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
-      <c r="J112" s="18"/>
+      <c r="J112" s="4"/>
       <c r="P112" s="1"/>
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
@@ -8538,13 +8474,13 @@
       <c r="BJ112" s="25"/>
     </row>
     <row r="113" spans="3:62">
-      <c r="C113" s="9"/>
+      <c r="C113" s="10"/>
       <c r="E113" s="1"/>
-      <c r="F113" s="11"/>
-      <c r="G113" s="11"/>
+      <c r="F113" s="12"/>
+      <c r="G113" s="12"/>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
-      <c r="J113" s="18"/>
+      <c r="J113" s="4"/>
       <c r="P113" s="1"/>
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
@@ -8588,13 +8524,13 @@
       <c r="BJ113" s="25"/>
     </row>
     <row r="114" spans="3:62">
-      <c r="C114" s="9"/>
+      <c r="C114" s="10"/>
       <c r="E114" s="1"/>
-      <c r="F114" s="11"/>
-      <c r="G114" s="11"/>
+      <c r="F114" s="12"/>
+      <c r="G114" s="12"/>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
-      <c r="J114" s="18"/>
+      <c r="J114" s="4"/>
       <c r="P114" s="1"/>
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
@@ -8638,13 +8574,13 @@
       <c r="BJ114" s="25"/>
     </row>
     <row r="115" spans="3:62">
-      <c r="C115" s="9"/>
+      <c r="C115" s="10"/>
       <c r="E115" s="1"/>
-      <c r="F115" s="11"/>
-      <c r="G115" s="11"/>
+      <c r="F115" s="12"/>
+      <c r="G115" s="12"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
-      <c r="J115" s="18"/>
+      <c r="J115" s="4"/>
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
@@ -8688,13 +8624,13 @@
       <c r="BJ115" s="25"/>
     </row>
     <row r="116" spans="3:62">
-      <c r="C116" s="9"/>
+      <c r="C116" s="10"/>
       <c r="E116" s="1"/>
-      <c r="F116" s="11"/>
-      <c r="G116" s="11"/>
+      <c r="F116" s="12"/>
+      <c r="G116" s="12"/>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
-      <c r="J116" s="18"/>
+      <c r="J116" s="4"/>
       <c r="P116" s="1"/>
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
@@ -8738,13 +8674,13 @@
       <c r="BJ116" s="25"/>
     </row>
     <row r="117" spans="3:62">
-      <c r="C117" s="9"/>
+      <c r="C117" s="10"/>
       <c r="E117" s="1"/>
-      <c r="F117" s="11"/>
-      <c r="G117" s="11"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="12"/>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
-      <c r="J117" s="18"/>
+      <c r="J117" s="4"/>
       <c r="P117" s="1"/>
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
@@ -8788,13 +8724,13 @@
       <c r="BJ117" s="25"/>
     </row>
     <row r="118" spans="3:62">
-      <c r="C118" s="9"/>
+      <c r="C118" s="10"/>
       <c r="E118" s="1"/>
-      <c r="F118" s="11"/>
-      <c r="G118" s="11"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
-      <c r="J118" s="18"/>
+      <c r="J118" s="4"/>
       <c r="P118" s="1"/>
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
@@ -8838,13 +8774,13 @@
       <c r="BJ118" s="25"/>
     </row>
     <row r="119" spans="3:62">
-      <c r="C119" s="9"/>
+      <c r="C119" s="10"/>
       <c r="E119" s="1"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="11"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
-      <c r="J119" s="18"/>
+      <c r="J119" s="4"/>
       <c r="P119" s="1"/>
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
@@ -8888,13 +8824,13 @@
       <c r="BJ119" s="25"/>
     </row>
     <row r="120" spans="3:62">
-      <c r="C120" s="9"/>
+      <c r="C120" s="10"/>
       <c r="E120" s="1"/>
-      <c r="F120" s="11"/>
-      <c r="G120" s="11"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="12"/>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
-      <c r="J120" s="18"/>
+      <c r="J120" s="4"/>
       <c r="P120" s="1"/>
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
@@ -8938,13 +8874,13 @@
       <c r="BJ120" s="25"/>
     </row>
     <row r="121" spans="3:62">
-      <c r="C121" s="9"/>
+      <c r="C121" s="10"/>
       <c r="E121" s="1"/>
-      <c r="F121" s="11"/>
-      <c r="G121" s="11"/>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12"/>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
-      <c r="J121" s="18"/>
+      <c r="J121" s="4"/>
       <c r="P121" s="1"/>
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
@@ -8988,13 +8924,13 @@
       <c r="BJ121" s="25"/>
     </row>
     <row r="122" spans="3:62">
-      <c r="C122" s="9"/>
+      <c r="C122" s="10"/>
       <c r="E122" s="1"/>
-      <c r="F122" s="11"/>
-      <c r="G122" s="11"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
-      <c r="J122" s="18"/>
+      <c r="J122" s="4"/>
       <c r="P122" s="1"/>
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
@@ -9038,13 +8974,13 @@
       <c r="BJ122" s="25"/>
     </row>
     <row r="123" spans="3:62">
-      <c r="C123" s="9"/>
+      <c r="C123" s="10"/>
       <c r="E123" s="1"/>
-      <c r="F123" s="11"/>
-      <c r="G123" s="11"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
-      <c r="J123" s="18"/>
+      <c r="J123" s="4"/>
       <c r="P123" s="1"/>
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
@@ -9088,13 +9024,13 @@
       <c r="BJ123" s="25"/>
     </row>
     <row r="124" spans="3:62">
-      <c r="C124" s="9"/>
+      <c r="C124" s="10"/>
       <c r="E124" s="1"/>
-      <c r="F124" s="11"/>
-      <c r="G124" s="11"/>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12"/>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
-      <c r="J124" s="18"/>
+      <c r="J124" s="4"/>
       <c r="P124" s="1"/>
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
@@ -9138,13 +9074,13 @@
       <c r="BJ124" s="25"/>
     </row>
     <row r="125" spans="3:62">
-      <c r="C125" s="9"/>
+      <c r="C125" s="10"/>
       <c r="E125" s="1"/>
-      <c r="F125" s="11"/>
-      <c r="G125" s="11"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="12"/>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
-      <c r="J125" s="18"/>
+      <c r="J125" s="4"/>
       <c r="P125" s="1"/>
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
@@ -9188,13 +9124,13 @@
       <c r="BJ125" s="25"/>
     </row>
     <row r="126" spans="3:62">
-      <c r="C126" s="9"/>
+      <c r="C126" s="10"/>
       <c r="E126" s="1"/>
-      <c r="F126" s="11"/>
-      <c r="G126" s="11"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12"/>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
-      <c r="J126" s="18"/>
+      <c r="J126" s="4"/>
       <c r="P126" s="1"/>
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
@@ -9238,13 +9174,13 @@
       <c r="BJ126" s="25"/>
     </row>
     <row r="127" spans="3:62">
-      <c r="C127" s="9"/>
+      <c r="C127" s="10"/>
       <c r="E127" s="1"/>
-      <c r="F127" s="11"/>
-      <c r="G127" s="11"/>
+      <c r="F127" s="12"/>
+      <c r="G127" s="12"/>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
-      <c r="J127" s="18"/>
+      <c r="J127" s="4"/>
       <c r="P127" s="1"/>
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
@@ -9288,13 +9224,13 @@
       <c r="BJ127" s="25"/>
     </row>
     <row r="128" spans="3:62">
-      <c r="C128" s="9"/>
+      <c r="C128" s="10"/>
       <c r="E128" s="1"/>
-      <c r="F128" s="11"/>
-      <c r="G128" s="11"/>
+      <c r="F128" s="12"/>
+      <c r="G128" s="12"/>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
-      <c r="J128" s="18"/>
+      <c r="J128" s="4"/>
       <c r="P128" s="1"/>
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
@@ -9338,13 +9274,13 @@
       <c r="BJ128" s="25"/>
     </row>
     <row r="129" spans="3:62">
-      <c r="C129" s="9"/>
+      <c r="C129" s="10"/>
       <c r="E129" s="1"/>
-      <c r="F129" s="11"/>
-      <c r="G129" s="11"/>
+      <c r="F129" s="12"/>
+      <c r="G129" s="12"/>
       <c r="H129" s="1"/>
       <c r="I129" s="1"/>
-      <c r="J129" s="18"/>
+      <c r="J129" s="4"/>
       <c r="P129" s="1"/>
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
@@ -9388,13 +9324,13 @@
       <c r="BJ129" s="25"/>
     </row>
     <row r="130" spans="3:62">
-      <c r="C130" s="9"/>
+      <c r="C130" s="10"/>
       <c r="E130" s="1"/>
-      <c r="F130" s="11"/>
-      <c r="G130" s="11"/>
+      <c r="F130" s="12"/>
+      <c r="G130" s="12"/>
       <c r="H130" s="1"/>
       <c r="I130" s="1"/>
-      <c r="J130" s="18"/>
+      <c r="J130" s="4"/>
       <c r="P130" s="1"/>
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
@@ -9438,13 +9374,13 @@
       <c r="BJ130" s="25"/>
     </row>
     <row r="131" spans="3:62">
-      <c r="C131" s="9"/>
+      <c r="C131" s="10"/>
       <c r="E131" s="1"/>
-      <c r="F131" s="11"/>
-      <c r="G131" s="11"/>
+      <c r="F131" s="12"/>
+      <c r="G131" s="12"/>
       <c r="H131" s="1"/>
       <c r="I131" s="1"/>
-      <c r="J131" s="18"/>
+      <c r="J131" s="4"/>
       <c r="P131" s="1"/>
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
@@ -9488,13 +9424,13 @@
       <c r="BJ131" s="25"/>
     </row>
     <row r="132" spans="3:62">
-      <c r="C132" s="9"/>
+      <c r="C132" s="10"/>
       <c r="E132" s="1"/>
-      <c r="F132" s="11"/>
-      <c r="G132" s="11"/>
+      <c r="F132" s="12"/>
+      <c r="G132" s="12"/>
       <c r="H132" s="1"/>
       <c r="I132" s="1"/>
-      <c r="J132" s="18"/>
+      <c r="J132" s="4"/>
       <c r="P132" s="1"/>
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
@@ -9538,13 +9474,13 @@
       <c r="BJ132" s="25"/>
     </row>
     <row r="133" spans="3:62">
-      <c r="C133" s="9"/>
+      <c r="C133" s="10"/>
       <c r="E133" s="1"/>
-      <c r="F133" s="11"/>
-      <c r="G133" s="11"/>
+      <c r="F133" s="12"/>
+      <c r="G133" s="12"/>
       <c r="H133" s="1"/>
       <c r="I133" s="1"/>
-      <c r="J133" s="18"/>
+      <c r="J133" s="4"/>
       <c r="P133" s="1"/>
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
@@ -9588,13 +9524,13 @@
       <c r="BJ133" s="25"/>
     </row>
     <row r="134" spans="3:62">
-      <c r="C134" s="9"/>
+      <c r="C134" s="10"/>
       <c r="E134" s="1"/>
-      <c r="F134" s="11"/>
-      <c r="G134" s="11"/>
+      <c r="F134" s="12"/>
+      <c r="G134" s="12"/>
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
-      <c r="J134" s="18"/>
+      <c r="J134" s="4"/>
       <c r="P134" s="1"/>
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
@@ -9638,13 +9574,13 @@
       <c r="BJ134" s="25"/>
     </row>
     <row r="135" spans="3:62">
-      <c r="C135" s="9"/>
+      <c r="C135" s="10"/>
       <c r="E135" s="1"/>
-      <c r="F135" s="11"/>
-      <c r="G135" s="11"/>
+      <c r="F135" s="12"/>
+      <c r="G135" s="12"/>
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
-      <c r="J135" s="18"/>
+      <c r="J135" s="4"/>
       <c r="P135" s="1"/>
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
@@ -9688,13 +9624,13 @@
       <c r="BJ135" s="25"/>
     </row>
     <row r="136" spans="3:62">
-      <c r="C136" s="9"/>
+      <c r="C136" s="10"/>
       <c r="E136" s="1"/>
-      <c r="F136" s="11"/>
-      <c r="G136" s="11"/>
+      <c r="F136" s="12"/>
+      <c r="G136" s="12"/>
       <c r="H136" s="1"/>
       <c r="I136" s="1"/>
-      <c r="J136" s="18"/>
+      <c r="J136" s="4"/>
       <c r="AA136" s="1"/>
       <c r="AU136" s="1"/>
       <c r="AV136" s="1"/>
@@ -9714,13 +9650,13 @@
       <c r="BJ136" s="25"/>
     </row>
     <row r="137" spans="3:62">
-      <c r="C137" s="9"/>
+      <c r="C137" s="10"/>
       <c r="E137" s="1"/>
-      <c r="F137" s="11"/>
-      <c r="G137" s="11"/>
+      <c r="F137" s="12"/>
+      <c r="G137" s="12"/>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
-      <c r="J137" s="18"/>
+      <c r="J137" s="4"/>
       <c r="AA137" s="1"/>
       <c r="AU137" s="1"/>
       <c r="AV137" s="1"/>
@@ -9740,13 +9676,13 @@
       <c r="BJ137" s="25"/>
     </row>
     <row r="138" spans="3:62">
-      <c r="C138" s="9"/>
+      <c r="C138" s="10"/>
       <c r="E138" s="1"/>
-      <c r="F138" s="11"/>
-      <c r="G138" s="11"/>
+      <c r="F138" s="12"/>
+      <c r="G138" s="12"/>
       <c r="H138" s="1"/>
       <c r="I138" s="1"/>
-      <c r="J138" s="18"/>
+      <c r="J138" s="4"/>
       <c r="AA138" s="1"/>
       <c r="AU138" s="1"/>
       <c r="AV138" s="1"/>
@@ -9766,13 +9702,13 @@
       <c r="BJ138" s="25"/>
     </row>
     <row r="139" spans="3:62">
-      <c r="C139" s="9"/>
+      <c r="C139" s="10"/>
       <c r="E139" s="1"/>
-      <c r="F139" s="11"/>
-      <c r="G139" s="11"/>
+      <c r="F139" s="12"/>
+      <c r="G139" s="12"/>
       <c r="H139" s="1"/>
       <c r="I139" s="1"/>
-      <c r="J139" s="18"/>
+      <c r="J139" s="4"/>
       <c r="AA139" s="1"/>
       <c r="AU139" s="1"/>
       <c r="AV139" s="1"/>
@@ -9792,13 +9728,13 @@
       <c r="BJ139" s="25"/>
     </row>
     <row r="140" spans="3:62">
-      <c r="C140" s="9"/>
+      <c r="C140" s="10"/>
       <c r="E140" s="1"/>
-      <c r="F140" s="11"/>
-      <c r="G140" s="11"/>
+      <c r="F140" s="12"/>
+      <c r="G140" s="12"/>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
-      <c r="J140" s="18"/>
+      <c r="J140" s="4"/>
       <c r="AA140" s="1"/>
       <c r="AU140" s="1"/>
       <c r="AV140" s="1"/>
@@ -9818,13 +9754,13 @@
       <c r="BJ140" s="25"/>
     </row>
     <row r="141" spans="3:62">
-      <c r="C141" s="9"/>
+      <c r="C141" s="10"/>
       <c r="E141" s="1"/>
-      <c r="F141" s="11"/>
-      <c r="G141" s="11"/>
+      <c r="F141" s="12"/>
+      <c r="G141" s="12"/>
       <c r="H141" s="1"/>
       <c r="I141" s="1"/>
-      <c r="J141" s="18"/>
+      <c r="J141" s="4"/>
       <c r="AA141" s="1"/>
       <c r="AU141" s="1"/>
       <c r="AV141" s="1"/>
@@ -9844,13 +9780,13 @@
       <c r="BJ141" s="25"/>
     </row>
     <row r="142" spans="3:62">
-      <c r="C142" s="9"/>
+      <c r="C142" s="10"/>
       <c r="E142" s="1"/>
-      <c r="F142" s="11"/>
-      <c r="G142" s="11"/>
+      <c r="F142" s="12"/>
+      <c r="G142" s="12"/>
       <c r="H142" s="1"/>
       <c r="I142" s="1"/>
-      <c r="J142" s="18"/>
+      <c r="J142" s="4"/>
       <c r="AA142" s="1"/>
       <c r="AU142" s="1"/>
       <c r="AV142" s="1"/>
@@ -9870,13 +9806,13 @@
       <c r="BJ142" s="25"/>
     </row>
     <row r="143" spans="3:62">
-      <c r="C143" s="9"/>
+      <c r="C143" s="10"/>
       <c r="E143" s="1"/>
-      <c r="F143" s="11"/>
-      <c r="G143" s="11"/>
+      <c r="F143" s="12"/>
+      <c r="G143" s="12"/>
       <c r="H143" s="1"/>
       <c r="I143" s="1"/>
-      <c r="J143" s="18"/>
+      <c r="J143" s="4"/>
       <c r="AA143" s="1"/>
       <c r="AU143" s="1"/>
       <c r="AV143" s="1"/>
@@ -9896,13 +9832,13 @@
       <c r="BJ143" s="25"/>
     </row>
     <row r="144" spans="3:62">
-      <c r="C144" s="9"/>
+      <c r="C144" s="10"/>
       <c r="E144" s="1"/>
-      <c r="F144" s="11"/>
-      <c r="G144" s="11"/>
+      <c r="F144" s="12"/>
+      <c r="G144" s="12"/>
       <c r="H144" s="1"/>
       <c r="I144" s="1"/>
-      <c r="J144" s="18"/>
+      <c r="J144" s="4"/>
       <c r="AA144" s="1"/>
       <c r="AU144" s="1"/>
       <c r="AV144" s="1"/>
@@ -9922,13 +9858,13 @@
       <c r="BJ144" s="25"/>
     </row>
     <row r="145" spans="3:62">
-      <c r="C145" s="9"/>
+      <c r="C145" s="10"/>
       <c r="E145" s="1"/>
-      <c r="F145" s="11"/>
-      <c r="G145" s="11"/>
+      <c r="F145" s="12"/>
+      <c r="G145" s="12"/>
       <c r="H145" s="1"/>
       <c r="I145" s="1"/>
-      <c r="J145" s="18"/>
+      <c r="J145" s="4"/>
       <c r="AA145" s="1"/>
       <c r="AU145" s="1"/>
       <c r="AV145" s="1"/>
@@ -9948,13 +9884,13 @@
       <c r="BJ145" s="25"/>
     </row>
     <row r="146" spans="3:62">
-      <c r="C146" s="9"/>
+      <c r="C146" s="10"/>
       <c r="E146" s="1"/>
-      <c r="F146" s="11"/>
-      <c r="G146" s="11"/>
+      <c r="F146" s="12"/>
+      <c r="G146" s="12"/>
       <c r="H146" s="1"/>
       <c r="I146" s="1"/>
-      <c r="J146" s="18"/>
+      <c r="J146" s="4"/>
       <c r="AA146" s="1"/>
       <c r="AU146" s="1"/>
       <c r="AV146" s="1"/>
@@ -9974,13 +9910,13 @@
       <c r="BJ146" s="25"/>
     </row>
     <row r="147" spans="3:62">
-      <c r="C147" s="9"/>
+      <c r="C147" s="10"/>
       <c r="E147" s="1"/>
-      <c r="F147" s="11"/>
-      <c r="G147" s="11"/>
+      <c r="F147" s="12"/>
+      <c r="G147" s="12"/>
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
-      <c r="J147" s="18"/>
+      <c r="J147" s="4"/>
       <c r="AA147" s="1"/>
       <c r="AU147" s="1"/>
       <c r="AV147" s="1"/>
@@ -10000,13 +9936,13 @@
       <c r="BJ147" s="25"/>
     </row>
     <row r="148" spans="3:62">
-      <c r="C148" s="9"/>
+      <c r="C148" s="10"/>
       <c r="E148" s="1"/>
-      <c r="F148" s="11"/>
-      <c r="G148" s="11"/>
+      <c r="F148" s="12"/>
+      <c r="G148" s="12"/>
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
-      <c r="J148" s="18"/>
+      <c r="J148" s="4"/>
       <c r="AA148" s="1"/>
       <c r="AU148" s="1"/>
       <c r="AV148" s="1"/>
@@ -10026,13 +9962,13 @@
       <c r="BJ148" s="25"/>
     </row>
     <row r="149" spans="3:62">
-      <c r="C149" s="9"/>
+      <c r="C149" s="10"/>
       <c r="E149" s="1"/>
-      <c r="F149" s="11"/>
-      <c r="G149" s="11"/>
+      <c r="F149" s="12"/>
+      <c r="G149" s="12"/>
       <c r="H149" s="1"/>
       <c r="I149" s="1"/>
-      <c r="J149" s="18"/>
+      <c r="J149" s="4"/>
       <c r="AA149" s="1"/>
       <c r="AU149" s="1"/>
       <c r="AV149" s="1"/>
@@ -10052,13 +9988,13 @@
       <c r="BJ149" s="25"/>
     </row>
     <row r="150" spans="3:62">
-      <c r="C150" s="9"/>
+      <c r="C150" s="10"/>
       <c r="E150" s="1"/>
-      <c r="F150" s="11"/>
-      <c r="G150" s="11"/>
+      <c r="F150" s="12"/>
+      <c r="G150" s="12"/>
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
-      <c r="J150" s="18"/>
+      <c r="J150" s="4"/>
       <c r="AA150" s="1"/>
       <c r="AU150" s="1"/>
       <c r="AV150" s="1"/>
@@ -10078,13 +10014,13 @@
       <c r="BJ150" s="25"/>
     </row>
     <row r="151" spans="3:62">
-      <c r="C151" s="9"/>
+      <c r="C151" s="10"/>
       <c r="E151" s="1"/>
-      <c r="F151" s="11"/>
-      <c r="G151" s="11"/>
+      <c r="F151" s="12"/>
+      <c r="G151" s="12"/>
       <c r="H151" s="1"/>
       <c r="I151" s="1"/>
-      <c r="J151" s="18"/>
+      <c r="J151" s="4"/>
       <c r="AA151" s="1"/>
       <c r="AU151" s="1"/>
       <c r="AV151" s="1"/>
@@ -10104,13 +10040,13 @@
       <c r="BJ151" s="25"/>
     </row>
     <row r="152" spans="3:62">
-      <c r="C152" s="9"/>
+      <c r="C152" s="10"/>
       <c r="E152" s="1"/>
-      <c r="F152" s="11"/>
-      <c r="G152" s="11"/>
+      <c r="F152" s="12"/>
+      <c r="G152" s="12"/>
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
-      <c r="J152" s="18"/>
+      <c r="J152" s="4"/>
       <c r="AA152" s="1"/>
       <c r="AU152" s="1"/>
       <c r="AV152" s="1"/>
@@ -10130,13 +10066,13 @@
       <c r="BJ152" s="25"/>
     </row>
     <row r="153" spans="3:62">
-      <c r="C153" s="9"/>
+      <c r="C153" s="10"/>
       <c r="E153" s="1"/>
-      <c r="F153" s="11"/>
-      <c r="G153" s="11"/>
+      <c r="F153" s="12"/>
+      <c r="G153" s="12"/>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
-      <c r="J153" s="18"/>
+      <c r="J153" s="4"/>
       <c r="AA153" s="1"/>
       <c r="AU153" s="1"/>
       <c r="AV153" s="1"/>
@@ -10156,13 +10092,13 @@
       <c r="BJ153" s="25"/>
     </row>
     <row r="154" spans="3:62">
-      <c r="C154" s="9"/>
+      <c r="C154" s="10"/>
       <c r="E154" s="1"/>
-      <c r="F154" s="11"/>
-      <c r="G154" s="11"/>
+      <c r="F154" s="12"/>
+      <c r="G154" s="12"/>
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
-      <c r="J154" s="18"/>
+      <c r="J154" s="4"/>
       <c r="AA154" s="1"/>
       <c r="AU154" s="1"/>
       <c r="AV154" s="1"/>
@@ -10182,13 +10118,13 @@
       <c r="BJ154" s="25"/>
     </row>
     <row r="155" spans="3:62">
-      <c r="C155" s="9"/>
+      <c r="C155" s="10"/>
       <c r="E155" s="1"/>
-      <c r="F155" s="11"/>
-      <c r="G155" s="11"/>
+      <c r="F155" s="12"/>
+      <c r="G155" s="12"/>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
-      <c r="J155" s="18"/>
+      <c r="J155" s="4"/>
       <c r="AA155" s="1"/>
       <c r="AU155" s="1"/>
       <c r="AV155" s="1"/>
@@ -10208,13 +10144,13 @@
       <c r="BJ155" s="25"/>
     </row>
     <row r="156" spans="3:62">
-      <c r="C156" s="9"/>
+      <c r="C156" s="10"/>
       <c r="E156" s="1"/>
-      <c r="F156" s="11"/>
-      <c r="G156" s="11"/>
+      <c r="F156" s="12"/>
+      <c r="G156" s="12"/>
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
-      <c r="J156" s="18"/>
+      <c r="J156" s="4"/>
       <c r="AA156" s="1"/>
       <c r="AU156" s="1"/>
       <c r="AV156" s="1"/>
@@ -10234,13 +10170,13 @@
       <c r="BJ156" s="25"/>
     </row>
     <row r="157" ht="14.25" customHeight="1" spans="3:62">
-      <c r="C157" s="9"/>
+      <c r="C157" s="10"/>
       <c r="E157" s="1"/>
-      <c r="F157" s="11"/>
-      <c r="G157" s="11"/>
+      <c r="F157" s="12"/>
+      <c r="G157" s="12"/>
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
-      <c r="J157" s="18"/>
+      <c r="J157" s="4"/>
       <c r="AA157" s="1"/>
       <c r="AU157" s="1"/>
       <c r="AV157" s="1"/>
@@ -10260,13 +10196,13 @@
       <c r="BJ157" s="25"/>
     </row>
     <row r="158" spans="3:62">
-      <c r="C158" s="9"/>
+      <c r="C158" s="10"/>
       <c r="E158" s="1"/>
-      <c r="F158" s="11"/>
-      <c r="G158" s="11"/>
+      <c r="F158" s="12"/>
+      <c r="G158" s="12"/>
       <c r="H158" s="1"/>
       <c r="I158" s="1"/>
-      <c r="J158" s="18"/>
+      <c r="J158" s="4"/>
       <c r="AA158" s="1"/>
       <c r="AU158" s="1"/>
       <c r="AV158" s="1"/>
@@ -10286,13 +10222,13 @@
       <c r="BJ158" s="25"/>
     </row>
     <row r="159" spans="3:62">
-      <c r="C159" s="9"/>
+      <c r="C159" s="10"/>
       <c r="E159" s="1"/>
-      <c r="F159" s="11"/>
-      <c r="G159" s="11"/>
+      <c r="F159" s="12"/>
+      <c r="G159" s="12"/>
       <c r="H159" s="1"/>
       <c r="I159" s="1"/>
-      <c r="J159" s="18"/>
+      <c r="J159" s="4"/>
       <c r="AA159" s="1"/>
       <c r="AU159" s="1"/>
       <c r="AV159" s="1"/>
@@ -10312,13 +10248,13 @@
       <c r="BJ159" s="25"/>
     </row>
     <row r="160" spans="3:62">
-      <c r="C160" s="9"/>
+      <c r="C160" s="10"/>
       <c r="E160" s="1"/>
-      <c r="F160" s="11"/>
-      <c r="G160" s="11"/>
+      <c r="F160" s="12"/>
+      <c r="G160" s="12"/>
       <c r="H160" s="1"/>
       <c r="I160" s="1"/>
-      <c r="J160" s="18"/>
+      <c r="J160" s="4"/>
       <c r="AA160" s="1"/>
       <c r="AU160" s="1"/>
       <c r="AV160" s="1"/>
@@ -10338,13 +10274,13 @@
       <c r="BJ160" s="25"/>
     </row>
     <row r="161" spans="3:62">
-      <c r="C161" s="9"/>
+      <c r="C161" s="10"/>
       <c r="E161" s="1"/>
-      <c r="F161" s="11"/>
-      <c r="G161" s="11"/>
+      <c r="F161" s="12"/>
+      <c r="G161" s="12"/>
       <c r="H161" s="1"/>
       <c r="I161" s="1"/>
-      <c r="J161" s="18"/>
+      <c r="J161" s="4"/>
       <c r="AA161" s="1"/>
       <c r="AU161" s="1"/>
       <c r="AV161" s="1"/>
@@ -10364,13 +10300,13 @@
       <c r="BJ161" s="25"/>
     </row>
     <row r="162" ht="15.75" customHeight="1" spans="3:62">
-      <c r="C162" s="9"/>
+      <c r="C162" s="10"/>
       <c r="E162" s="1"/>
-      <c r="F162" s="11"/>
-      <c r="G162" s="11"/>
+      <c r="F162" s="12"/>
+      <c r="G162" s="12"/>
       <c r="H162" s="1"/>
       <c r="I162" s="1"/>
-      <c r="J162" s="18"/>
+      <c r="J162" s="4"/>
       <c r="AA162" s="1"/>
       <c r="AU162" s="1"/>
       <c r="AV162" s="1"/>
@@ -10390,13 +10326,13 @@
       <c r="BJ162" s="25"/>
     </row>
     <row r="163" ht="14.25" customHeight="1" spans="3:62">
-      <c r="C163" s="9"/>
+      <c r="C163" s="10"/>
       <c r="E163" s="1"/>
-      <c r="F163" s="11"/>
-      <c r="G163" s="11"/>
+      <c r="F163" s="12"/>
+      <c r="G163" s="12"/>
       <c r="H163" s="1"/>
       <c r="I163" s="1"/>
-      <c r="J163" s="18"/>
+      <c r="J163" s="4"/>
       <c r="AA163" s="1"/>
       <c r="AU163" s="1"/>
       <c r="AV163" s="1"/>
@@ -10416,13 +10352,13 @@
       <c r="BJ163" s="25"/>
     </row>
     <row r="164" spans="3:62">
-      <c r="C164" s="9"/>
+      <c r="C164" s="10"/>
       <c r="E164" s="1"/>
-      <c r="F164" s="11"/>
-      <c r="G164" s="11"/>
+      <c r="F164" s="12"/>
+      <c r="G164" s="12"/>
       <c r="H164" s="1"/>
       <c r="I164" s="1"/>
-      <c r="J164" s="18"/>
+      <c r="J164" s="4"/>
       <c r="AA164" s="1"/>
       <c r="AU164" s="1"/>
       <c r="AV164" s="1"/>
@@ -10442,13 +10378,13 @@
       <c r="BJ164" s="25"/>
     </row>
     <row r="165" spans="3:62">
-      <c r="C165" s="9"/>
+      <c r="C165" s="10"/>
       <c r="E165" s="1"/>
-      <c r="F165" s="11"/>
-      <c r="G165" s="11"/>
+      <c r="F165" s="12"/>
+      <c r="G165" s="12"/>
       <c r="H165" s="1"/>
       <c r="I165" s="1"/>
-      <c r="J165" s="18"/>
+      <c r="J165" s="4"/>
       <c r="AA165" s="1"/>
       <c r="AU165" s="1"/>
       <c r="AV165" s="1"/>
@@ -10469,15 +10405,15 @@
     </row>
     <row r="166" spans="1:62">
       <c r="A166" s="1"/>
-      <c r="B166" s="7"/>
+      <c r="B166" s="8"/>
       <c r="C166" s="1"/>
-      <c r="D166" s="7"/>
+      <c r="D166" s="8"/>
       <c r="E166" s="1"/>
-      <c r="F166" s="11"/>
-      <c r="G166" s="11"/>
+      <c r="F166" s="12"/>
+      <c r="G166" s="12"/>
       <c r="H166" s="1"/>
       <c r="I166" s="1"/>
-      <c r="J166" s="17"/>
+      <c r="J166" s="15"/>
       <c r="AO166" s="1"/>
       <c r="AP166" s="1"/>
       <c r="AU166" s="1"/>
@@ -10499,15 +10435,15 @@
     </row>
     <row r="167" spans="1:62">
       <c r="A167" s="1"/>
-      <c r="B167" s="7"/>
+      <c r="B167" s="8"/>
       <c r="C167" s="1"/>
-      <c r="D167" s="7"/>
+      <c r="D167" s="8"/>
       <c r="E167" s="1"/>
-      <c r="F167" s="11"/>
-      <c r="G167" s="11"/>
+      <c r="F167" s="12"/>
+      <c r="G167" s="12"/>
       <c r="H167" s="1"/>
       <c r="I167" s="1"/>
-      <c r="J167" s="17"/>
+      <c r="J167" s="15"/>
       <c r="AO167" s="1"/>
       <c r="AP167" s="1"/>
       <c r="AU167" s="1"/>
@@ -10528,15 +10464,15 @@
       <c r="BJ167" s="25"/>
     </row>
     <row r="168" spans="2:62">
-      <c r="B168" s="7"/>
+      <c r="B168" s="8"/>
       <c r="C168" s="1"/>
-      <c r="D168" s="7"/>
+      <c r="D168" s="8"/>
       <c r="E168" s="1"/>
-      <c r="F168" s="11"/>
-      <c r="G168" s="11"/>
+      <c r="F168" s="12"/>
+      <c r="G168" s="12"/>
       <c r="H168" s="1"/>
       <c r="I168" s="1"/>
-      <c r="J168" s="17"/>
+      <c r="J168" s="15"/>
       <c r="AO168" s="1"/>
       <c r="AP168" s="1"/>
       <c r="AU168" s="1"/>
@@ -10558,15 +10494,15 @@
     </row>
     <row r="169" spans="1:62">
       <c r="A169" s="1"/>
-      <c r="B169" s="7"/>
+      <c r="B169" s="8"/>
       <c r="C169" s="1"/>
-      <c r="D169" s="7"/>
+      <c r="D169" s="8"/>
       <c r="E169" s="1"/>
-      <c r="F169" s="11"/>
-      <c r="G169" s="11"/>
+      <c r="F169" s="12"/>
+      <c r="G169" s="12"/>
       <c r="H169" s="1"/>
       <c r="I169" s="1"/>
-      <c r="J169" s="17"/>
+      <c r="J169" s="15"/>
       <c r="AO169" s="1"/>
       <c r="AP169" s="1"/>
       <c r="AU169" s="1"/>
@@ -10588,15 +10524,15 @@
     </row>
     <row r="170" spans="1:62">
       <c r="A170" s="1"/>
-      <c r="B170" s="7"/>
+      <c r="B170" s="8"/>
       <c r="C170" s="1"/>
-      <c r="D170" s="7"/>
+      <c r="D170" s="8"/>
       <c r="E170" s="1"/>
-      <c r="F170" s="11"/>
-      <c r="G170" s="11"/>
+      <c r="F170" s="12"/>
+      <c r="G170" s="12"/>
       <c r="H170" s="1"/>
       <c r="I170" s="1"/>
-      <c r="J170" s="17"/>
+      <c r="J170" s="15"/>
       <c r="AO170" s="1"/>
       <c r="AP170" s="1"/>
       <c r="AU170" s="1"/>
@@ -10618,15 +10554,15 @@
     </row>
     <row r="171" spans="1:62">
       <c r="A171" s="1"/>
-      <c r="B171" s="7"/>
+      <c r="B171" s="8"/>
       <c r="C171" s="1"/>
-      <c r="D171" s="7"/>
+      <c r="D171" s="8"/>
       <c r="E171" s="1"/>
-      <c r="F171" s="11"/>
-      <c r="G171" s="11"/>
+      <c r="F171" s="12"/>
+      <c r="G171" s="12"/>
       <c r="H171" s="1"/>
       <c r="I171" s="1"/>
-      <c r="J171" s="17"/>
+      <c r="J171" s="15"/>
       <c r="AO171" s="1"/>
       <c r="AP171" s="1"/>
       <c r="AU171" s="1"/>
@@ -10648,15 +10584,15 @@
     </row>
     <row r="172" spans="1:62">
       <c r="A172" s="1"/>
-      <c r="B172" s="7"/>
+      <c r="B172" s="8"/>
       <c r="C172" s="1"/>
-      <c r="D172" s="7"/>
+      <c r="D172" s="8"/>
       <c r="E172" s="1"/>
-      <c r="F172" s="11"/>
-      <c r="G172" s="11"/>
+      <c r="F172" s="12"/>
+      <c r="G172" s="12"/>
       <c r="H172" s="1"/>
       <c r="I172" s="1"/>
-      <c r="J172" s="17"/>
+      <c r="J172" s="15"/>
       <c r="AO172" s="1"/>
       <c r="AP172" s="1"/>
       <c r="AU172" s="1"/>
@@ -10678,15 +10614,15 @@
     </row>
     <row r="173" spans="1:62">
       <c r="A173" s="1"/>
-      <c r="B173" s="7"/>
+      <c r="B173" s="8"/>
       <c r="C173" s="1"/>
-      <c r="D173" s="7"/>
+      <c r="D173" s="8"/>
       <c r="E173" s="1"/>
-      <c r="F173" s="11"/>
-      <c r="G173" s="11"/>
+      <c r="F173" s="12"/>
+      <c r="G173" s="12"/>
       <c r="H173" s="1"/>
       <c r="I173" s="1"/>
-      <c r="J173" s="17"/>
+      <c r="J173" s="15"/>
       <c r="AO173" s="1"/>
       <c r="AP173" s="1"/>
       <c r="AU173" s="1"/>
@@ -10708,15 +10644,15 @@
     </row>
     <row r="174" spans="1:62">
       <c r="A174" s="1"/>
-      <c r="B174" s="7"/>
+      <c r="B174" s="8"/>
       <c r="C174" s="1"/>
-      <c r="D174" s="7"/>
+      <c r="D174" s="8"/>
       <c r="E174" s="1"/>
-      <c r="F174" s="11"/>
-      <c r="G174" s="11"/>
+      <c r="F174" s="12"/>
+      <c r="G174" s="12"/>
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
-      <c r="J174" s="17"/>
+      <c r="J174" s="15"/>
       <c r="AO174" s="1"/>
       <c r="AP174" s="1"/>
       <c r="AU174" s="1"/>
@@ -10738,15 +10674,15 @@
     </row>
     <row r="175" spans="1:62">
       <c r="A175" s="1"/>
-      <c r="B175" s="7"/>
+      <c r="B175" s="8"/>
       <c r="C175" s="1"/>
-      <c r="D175" s="7"/>
+      <c r="D175" s="8"/>
       <c r="E175" s="1"/>
-      <c r="F175" s="11"/>
-      <c r="G175" s="11"/>
+      <c r="F175" s="12"/>
+      <c r="G175" s="12"/>
       <c r="H175" s="1"/>
       <c r="I175" s="1"/>
-      <c r="J175" s="17"/>
+      <c r="J175" s="15"/>
       <c r="AO175" s="1"/>
       <c r="AP175" s="1"/>
       <c r="AU175" s="1"/>
@@ -10768,15 +10704,15 @@
     </row>
     <row r="176" spans="1:62">
       <c r="A176" s="1"/>
-      <c r="B176" s="7"/>
+      <c r="B176" s="8"/>
       <c r="C176" s="1"/>
-      <c r="D176" s="7"/>
+      <c r="D176" s="8"/>
       <c r="E176" s="1"/>
-      <c r="F176" s="11"/>
-      <c r="G176" s="11"/>
+      <c r="F176" s="12"/>
+      <c r="G176" s="12"/>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
-      <c r="J176" s="17"/>
+      <c r="J176" s="15"/>
       <c r="AO176" s="1"/>
       <c r="AP176" s="1"/>
       <c r="AU176" s="1"/>
@@ -10798,15 +10734,15 @@
     </row>
     <row r="177" spans="1:62">
       <c r="A177" s="1"/>
-      <c r="B177" s="7"/>
+      <c r="B177" s="8"/>
       <c r="C177" s="1"/>
-      <c r="D177" s="7"/>
+      <c r="D177" s="8"/>
       <c r="E177" s="1"/>
-      <c r="F177" s="11"/>
-      <c r="G177" s="11"/>
+      <c r="F177" s="12"/>
+      <c r="G177" s="12"/>
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
-      <c r="J177" s="17"/>
+      <c r="J177" s="15"/>
       <c r="AO177" s="1"/>
       <c r="AP177" s="1"/>
       <c r="AU177" s="1"/>
@@ -10828,15 +10764,15 @@
     </row>
     <row r="178" spans="1:62">
       <c r="A178" s="1"/>
-      <c r="B178" s="7"/>
+      <c r="B178" s="8"/>
       <c r="C178" s="1"/>
-      <c r="D178" s="7"/>
+      <c r="D178" s="8"/>
       <c r="E178" s="1"/>
-      <c r="F178" s="11"/>
-      <c r="G178" s="11"/>
+      <c r="F178" s="12"/>
+      <c r="G178" s="12"/>
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
-      <c r="J178" s="17"/>
+      <c r="J178" s="15"/>
       <c r="AO178" s="1"/>
       <c r="AP178" s="1"/>
       <c r="AU178" s="1"/>
@@ -10858,15 +10794,15 @@
     </row>
     <row r="179" spans="1:62">
       <c r="A179" s="1"/>
-      <c r="B179" s="7"/>
+      <c r="B179" s="8"/>
       <c r="C179" s="1"/>
-      <c r="D179" s="7"/>
+      <c r="D179" s="8"/>
       <c r="E179" s="1"/>
-      <c r="F179" s="11"/>
-      <c r="G179" s="11"/>
+      <c r="F179" s="12"/>
+      <c r="G179" s="12"/>
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
-      <c r="J179" s="17"/>
+      <c r="J179" s="15"/>
       <c r="AO179" s="1"/>
       <c r="AP179" s="1"/>
       <c r="AU179" s="1"/>
@@ -10888,15 +10824,15 @@
     </row>
     <row r="180" spans="1:62">
       <c r="A180" s="1"/>
-      <c r="B180" s="7"/>
+      <c r="B180" s="8"/>
       <c r="C180" s="1"/>
-      <c r="D180" s="7"/>
+      <c r="D180" s="8"/>
       <c r="E180" s="1"/>
-      <c r="F180" s="11"/>
-      <c r="G180" s="11"/>
+      <c r="F180" s="12"/>
+      <c r="G180" s="12"/>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
-      <c r="J180" s="17"/>
+      <c r="J180" s="15"/>
       <c r="AO180" s="1"/>
       <c r="AP180" s="1"/>
       <c r="AU180" s="1"/>
@@ -10918,15 +10854,15 @@
     </row>
     <row r="181" spans="1:62">
       <c r="A181" s="1"/>
-      <c r="B181" s="7"/>
+      <c r="B181" s="8"/>
       <c r="C181" s="1"/>
-      <c r="D181" s="7"/>
+      <c r="D181" s="8"/>
       <c r="E181" s="1"/>
-      <c r="F181" s="11"/>
-      <c r="G181" s="11"/>
+      <c r="F181" s="12"/>
+      <c r="G181" s="12"/>
       <c r="H181" s="1"/>
       <c r="I181" s="1"/>
-      <c r="J181" s="17"/>
+      <c r="J181" s="15"/>
       <c r="AO181" s="1"/>
       <c r="AP181" s="1"/>
       <c r="AU181" s="1"/>
@@ -10948,15 +10884,15 @@
     </row>
     <row r="182" spans="1:62">
       <c r="A182" s="1"/>
-      <c r="B182" s="7"/>
+      <c r="B182" s="8"/>
       <c r="C182" s="1"/>
-      <c r="D182" s="7"/>
+      <c r="D182" s="8"/>
       <c r="E182" s="1"/>
-      <c r="F182" s="11"/>
-      <c r="G182" s="11"/>
+      <c r="F182" s="12"/>
+      <c r="G182" s="12"/>
       <c r="H182" s="1"/>
       <c r="I182" s="1"/>
-      <c r="J182" s="17"/>
+      <c r="J182" s="15"/>
       <c r="AO182" s="1"/>
       <c r="AP182" s="1"/>
       <c r="AU182" s="1"/>
@@ -10978,15 +10914,15 @@
     </row>
     <row r="183" spans="1:62">
       <c r="A183" s="1"/>
-      <c r="B183" s="7"/>
+      <c r="B183" s="8"/>
       <c r="C183" s="1"/>
-      <c r="D183" s="7"/>
+      <c r="D183" s="8"/>
       <c r="E183" s="1"/>
-      <c r="F183" s="11"/>
-      <c r="G183" s="11"/>
+      <c r="F183" s="12"/>
+      <c r="G183" s="12"/>
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
-      <c r="J183" s="17"/>
+      <c r="J183" s="15"/>
       <c r="AO183" s="1"/>
       <c r="AP183" s="1"/>
       <c r="AU183" s="1"/>
@@ -11008,15 +10944,15 @@
     </row>
     <row r="184" spans="1:62">
       <c r="A184" s="1"/>
-      <c r="B184" s="7"/>
+      <c r="B184" s="8"/>
       <c r="C184" s="1"/>
-      <c r="D184" s="7"/>
+      <c r="D184" s="8"/>
       <c r="E184" s="1"/>
-      <c r="F184" s="11"/>
-      <c r="G184" s="11"/>
+      <c r="F184" s="12"/>
+      <c r="G184" s="12"/>
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
-      <c r="J184" s="17"/>
+      <c r="J184" s="15"/>
       <c r="AO184" s="1"/>
       <c r="AP184" s="1"/>
       <c r="AU184" s="1"/>
@@ -11038,15 +10974,15 @@
     </row>
     <row r="185" spans="1:62">
       <c r="A185" s="1"/>
-      <c r="B185" s="7"/>
+      <c r="B185" s="8"/>
       <c r="C185" s="1"/>
-      <c r="D185" s="7"/>
+      <c r="D185" s="8"/>
       <c r="E185" s="1"/>
-      <c r="F185" s="11"/>
-      <c r="G185" s="11"/>
+      <c r="F185" s="12"/>
+      <c r="G185" s="12"/>
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
-      <c r="J185" s="17"/>
+      <c r="J185" s="15"/>
       <c r="AO185" s="1"/>
       <c r="AP185" s="1"/>
       <c r="AU185" s="1"/>
@@ -11068,15 +11004,15 @@
     </row>
     <row r="186" spans="1:62">
       <c r="A186" s="1"/>
-      <c r="B186" s="7"/>
+      <c r="B186" s="8"/>
       <c r="C186" s="1"/>
-      <c r="D186" s="7"/>
+      <c r="D186" s="8"/>
       <c r="E186" s="1"/>
-      <c r="F186" s="11"/>
-      <c r="G186" s="11"/>
+      <c r="F186" s="12"/>
+      <c r="G186" s="12"/>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
-      <c r="J186" s="17"/>
+      <c r="J186" s="15"/>
       <c r="AO186" s="1"/>
       <c r="AP186" s="1"/>
       <c r="AU186" s="1"/>
@@ -11098,15 +11034,15 @@
     </row>
     <row r="187" spans="1:62">
       <c r="A187" s="1"/>
-      <c r="B187" s="7"/>
+      <c r="B187" s="8"/>
       <c r="C187" s="1"/>
-      <c r="D187" s="7"/>
+      <c r="D187" s="8"/>
       <c r="E187" s="1"/>
-      <c r="F187" s="11"/>
-      <c r="G187" s="11"/>
+      <c r="F187" s="12"/>
+      <c r="G187" s="12"/>
       <c r="H187" s="1"/>
       <c r="I187" s="1"/>
-      <c r="J187" s="17"/>
+      <c r="J187" s="15"/>
       <c r="AO187" s="1"/>
       <c r="AP187" s="1"/>
       <c r="AU187" s="1"/>
@@ -11128,15 +11064,15 @@
     </row>
     <row r="188" spans="1:62">
       <c r="A188" s="1"/>
-      <c r="B188" s="7"/>
+      <c r="B188" s="8"/>
       <c r="C188" s="1"/>
-      <c r="D188" s="7"/>
+      <c r="D188" s="8"/>
       <c r="E188" s="1"/>
-      <c r="F188" s="11"/>
-      <c r="G188" s="11"/>
+      <c r="F188" s="12"/>
+      <c r="G188" s="12"/>
       <c r="H188" s="1"/>
       <c r="I188" s="1"/>
-      <c r="J188" s="17"/>
+      <c r="J188" s="15"/>
       <c r="AO188" s="1"/>
       <c r="AP188" s="1"/>
       <c r="AU188" s="1"/>
@@ -11158,15 +11094,15 @@
     </row>
     <row r="189" spans="1:62">
       <c r="A189" s="1"/>
-      <c r="B189" s="7"/>
+      <c r="B189" s="8"/>
       <c r="C189" s="1"/>
-      <c r="D189" s="7"/>
+      <c r="D189" s="8"/>
       <c r="E189" s="1"/>
-      <c r="F189" s="11"/>
-      <c r="G189" s="11"/>
+      <c r="F189" s="12"/>
+      <c r="G189" s="12"/>
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
-      <c r="J189" s="17"/>
+      <c r="J189" s="15"/>
       <c r="AO189" s="1"/>
       <c r="AP189" s="1"/>
       <c r="AU189" s="1"/>
@@ -11188,15 +11124,15 @@
     </row>
     <row r="190" spans="1:62">
       <c r="A190" s="1"/>
-      <c r="B190" s="7"/>
+      <c r="B190" s="8"/>
       <c r="C190" s="1"/>
-      <c r="D190" s="7"/>
+      <c r="D190" s="8"/>
       <c r="E190" s="1"/>
-      <c r="F190" s="11"/>
-      <c r="G190" s="11"/>
+      <c r="F190" s="12"/>
+      <c r="G190" s="12"/>
       <c r="H190" s="1"/>
       <c r="I190" s="1"/>
-      <c r="J190" s="17"/>
+      <c r="J190" s="15"/>
       <c r="AO190" s="1"/>
       <c r="AP190" s="1"/>
       <c r="AU190" s="1"/>
@@ -11218,15 +11154,15 @@
     </row>
     <row r="191" spans="1:62">
       <c r="A191" s="1"/>
-      <c r="B191" s="7"/>
+      <c r="B191" s="8"/>
       <c r="C191" s="1"/>
-      <c r="D191" s="7"/>
+      <c r="D191" s="8"/>
       <c r="E191" s="1"/>
-      <c r="F191" s="11"/>
-      <c r="G191" s="11"/>
+      <c r="F191" s="12"/>
+      <c r="G191" s="12"/>
       <c r="H191" s="1"/>
       <c r="I191" s="1"/>
-      <c r="J191" s="17"/>
+      <c r="J191" s="15"/>
       <c r="AO191" s="1"/>
       <c r="AP191" s="1"/>
       <c r="AU191" s="1"/>
@@ -11248,15 +11184,15 @@
     </row>
     <row r="192" spans="1:62">
       <c r="A192" s="1"/>
-      <c r="B192" s="7"/>
+      <c r="B192" s="8"/>
       <c r="C192" s="1"/>
-      <c r="D192" s="7"/>
+      <c r="D192" s="8"/>
       <c r="E192" s="1"/>
-      <c r="F192" s="11"/>
-      <c r="G192" s="11"/>
+      <c r="F192" s="12"/>
+      <c r="G192" s="12"/>
       <c r="H192" s="1"/>
       <c r="I192" s="1"/>
-      <c r="J192" s="17"/>
+      <c r="J192" s="15"/>
       <c r="AO192" s="1"/>
       <c r="AP192" s="1"/>
       <c r="AU192" s="1"/>
@@ -11278,15 +11214,15 @@
     </row>
     <row r="193" spans="1:62">
       <c r="A193" s="1"/>
-      <c r="B193" s="7"/>
+      <c r="B193" s="8"/>
       <c r="C193" s="1"/>
-      <c r="D193" s="7"/>
+      <c r="D193" s="8"/>
       <c r="E193" s="1"/>
-      <c r="F193" s="11"/>
-      <c r="G193" s="11"/>
+      <c r="F193" s="12"/>
+      <c r="G193" s="12"/>
       <c r="H193" s="1"/>
       <c r="I193" s="1"/>
-      <c r="J193" s="17"/>
+      <c r="J193" s="15"/>
       <c r="AO193" s="1"/>
       <c r="AP193" s="1"/>
       <c r="AU193" s="1"/>
@@ -11308,15 +11244,15 @@
     </row>
     <row r="194" spans="1:62">
       <c r="A194" s="1"/>
-      <c r="B194" s="7"/>
+      <c r="B194" s="8"/>
       <c r="C194" s="1"/>
-      <c r="D194" s="7"/>
+      <c r="D194" s="8"/>
       <c r="E194" s="1"/>
-      <c r="F194" s="11"/>
-      <c r="G194" s="11"/>
+      <c r="F194" s="12"/>
+      <c r="G194" s="12"/>
       <c r="H194" s="1"/>
       <c r="I194" s="1"/>
-      <c r="J194" s="17"/>
+      <c r="J194" s="15"/>
       <c r="AO194" s="1"/>
       <c r="AP194" s="1"/>
       <c r="AU194" s="1"/>
@@ -11338,15 +11274,15 @@
     </row>
     <row r="195" spans="1:62">
       <c r="A195" s="1"/>
-      <c r="B195" s="7"/>
+      <c r="B195" s="8"/>
       <c r="C195" s="1"/>
-      <c r="D195" s="7"/>
+      <c r="D195" s="8"/>
       <c r="E195" s="1"/>
-      <c r="F195" s="11"/>
-      <c r="G195" s="11"/>
+      <c r="F195" s="12"/>
+      <c r="G195" s="12"/>
       <c r="H195" s="1"/>
       <c r="I195" s="1"/>
-      <c r="J195" s="17"/>
+      <c r="J195" s="15"/>
       <c r="AO195" s="1"/>
       <c r="AP195" s="1"/>
       <c r="AU195" s="1"/>
@@ -11368,15 +11304,15 @@
     </row>
     <row r="196" spans="1:62">
       <c r="A196" s="1"/>
-      <c r="B196" s="7"/>
+      <c r="B196" s="8"/>
       <c r="C196" s="1"/>
-      <c r="D196" s="7"/>
+      <c r="D196" s="8"/>
       <c r="E196" s="1"/>
-      <c r="F196" s="11"/>
-      <c r="G196" s="11"/>
+      <c r="F196" s="12"/>
+      <c r="G196" s="12"/>
       <c r="H196" s="1"/>
       <c r="I196" s="1"/>
-      <c r="J196" s="17"/>
+      <c r="J196" s="15"/>
       <c r="AO196" s="1"/>
       <c r="AP196" s="1"/>
       <c r="AU196" s="1"/>
@@ -11398,15 +11334,15 @@
     </row>
     <row r="197" spans="1:62">
       <c r="A197" s="1"/>
-      <c r="B197" s="7"/>
+      <c r="B197" s="8"/>
       <c r="C197" s="1"/>
-      <c r="D197" s="7"/>
+      <c r="D197" s="8"/>
       <c r="E197" s="1"/>
-      <c r="F197" s="11"/>
-      <c r="G197" s="11"/>
+      <c r="F197" s="12"/>
+      <c r="G197" s="12"/>
       <c r="H197" s="1"/>
       <c r="I197" s="1"/>
-      <c r="J197" s="17"/>
+      <c r="J197" s="15"/>
       <c r="AO197" s="1"/>
       <c r="AP197" s="1"/>
       <c r="AU197" s="1"/>
@@ -11428,15 +11364,15 @@
     </row>
     <row r="198" spans="1:62">
       <c r="A198" s="1"/>
-      <c r="B198" s="7"/>
+      <c r="B198" s="8"/>
       <c r="C198" s="1"/>
-      <c r="D198" s="7"/>
+      <c r="D198" s="8"/>
       <c r="E198" s="1"/>
-      <c r="F198" s="11"/>
-      <c r="G198" s="11"/>
+      <c r="F198" s="12"/>
+      <c r="G198" s="12"/>
       <c r="H198" s="1"/>
       <c r="I198" s="1"/>
-      <c r="J198" s="17"/>
+      <c r="J198" s="15"/>
       <c r="AO198" s="1"/>
       <c r="AP198" s="1"/>
       <c r="AU198" s="1"/>
@@ -11457,15 +11393,15 @@
       <c r="BJ198" s="25"/>
     </row>
     <row r="199" spans="2:62">
-      <c r="B199" s="7"/>
+      <c r="B199" s="8"/>
       <c r="C199" s="1"/>
-      <c r="D199" s="7"/>
+      <c r="D199" s="8"/>
       <c r="E199" s="1"/>
-      <c r="F199" s="11"/>
-      <c r="G199" s="11"/>
+      <c r="F199" s="12"/>
+      <c r="G199" s="12"/>
       <c r="H199" s="1"/>
       <c r="I199" s="1"/>
-      <c r="J199" s="17"/>
+      <c r="J199" s="15"/>
       <c r="AO199" s="1"/>
       <c r="AP199" s="1"/>
       <c r="AU199" s="1"/>
@@ -11486,310 +11422,310 @@
       <c r="BJ199" s="25"/>
     </row>
     <row r="200" spans="10:10">
-      <c r="J200" s="13"/>
+      <c r="J200" s="15"/>
     </row>
     <row r="201" spans="10:10">
-      <c r="J201" s="13"/>
+      <c r="J201" s="15"/>
     </row>
     <row r="202" spans="10:10">
-      <c r="J202" s="13"/>
+      <c r="J202" s="15"/>
     </row>
     <row r="203" spans="10:10">
-      <c r="J203" s="13"/>
+      <c r="J203" s="15"/>
     </row>
     <row r="204" spans="10:10">
-      <c r="J204" s="13"/>
+      <c r="J204" s="15"/>
     </row>
     <row r="205" spans="10:10">
-      <c r="J205" s="13"/>
+      <c r="J205" s="15"/>
     </row>
     <row r="206" spans="10:10">
-      <c r="J206" s="13"/>
+      <c r="J206" s="15"/>
     </row>
     <row r="207" spans="10:10">
-      <c r="J207" s="13"/>
+      <c r="J207" s="15"/>
     </row>
     <row r="208" spans="10:10">
-      <c r="J208" s="13"/>
+      <c r="J208" s="15"/>
     </row>
     <row r="209" spans="10:10">
-      <c r="J209" s="13"/>
+      <c r="J209" s="15"/>
     </row>
     <row r="210" spans="10:10">
-      <c r="J210" s="13"/>
+      <c r="J210" s="15"/>
     </row>
     <row r="211" spans="10:10">
-      <c r="J211" s="13"/>
+      <c r="J211" s="15"/>
     </row>
     <row r="212" spans="10:10">
-      <c r="J212" s="13"/>
+      <c r="J212" s="15"/>
     </row>
     <row r="213" spans="10:10">
-      <c r="J213" s="13"/>
+      <c r="J213" s="15"/>
     </row>
     <row r="214" spans="10:10">
-      <c r="J214" s="13"/>
+      <c r="J214" s="15"/>
     </row>
     <row r="215" spans="10:10">
-      <c r="J215" s="13"/>
+      <c r="J215" s="15"/>
     </row>
     <row r="216" spans="10:10">
-      <c r="J216" s="13"/>
+      <c r="J216" s="15"/>
     </row>
     <row r="217" spans="10:10">
-      <c r="J217" s="13"/>
+      <c r="J217" s="15"/>
     </row>
     <row r="218" spans="10:10">
-      <c r="J218" s="13"/>
+      <c r="J218" s="15"/>
     </row>
     <row r="219" spans="10:10">
-      <c r="J219" s="13"/>
+      <c r="J219" s="15"/>
     </row>
     <row r="220" spans="10:10">
-      <c r="J220" s="13"/>
+      <c r="J220" s="15"/>
     </row>
     <row r="221" spans="10:10">
-      <c r="J221" s="13"/>
+      <c r="J221" s="15"/>
     </row>
     <row r="222" spans="10:10">
-      <c r="J222" s="13"/>
+      <c r="J222" s="15"/>
     </row>
     <row r="223" spans="10:10">
-      <c r="J223" s="13"/>
+      <c r="J223" s="15"/>
     </row>
     <row r="224" spans="10:10">
-      <c r="J224" s="13"/>
+      <c r="J224" s="15"/>
     </row>
     <row r="225" spans="10:10">
-      <c r="J225" s="13"/>
+      <c r="J225" s="15"/>
     </row>
     <row r="226" spans="10:10">
-      <c r="J226" s="13"/>
+      <c r="J226" s="15"/>
     </row>
     <row r="227" spans="10:10">
-      <c r="J227" s="13"/>
+      <c r="J227" s="15"/>
     </row>
     <row r="228" spans="10:10">
-      <c r="J228" s="13"/>
+      <c r="J228" s="15"/>
     </row>
     <row r="229" spans="10:10">
-      <c r="J229" s="13"/>
+      <c r="J229" s="15"/>
     </row>
     <row r="230" spans="10:10">
-      <c r="J230" s="13"/>
+      <c r="J230" s="15"/>
     </row>
     <row r="231" spans="10:10">
-      <c r="J231" s="13"/>
+      <c r="J231" s="15"/>
     </row>
     <row r="232" spans="10:10">
-      <c r="J232" s="13"/>
+      <c r="J232" s="15"/>
     </row>
     <row r="233" spans="10:10">
-      <c r="J233" s="13"/>
+      <c r="J233" s="15"/>
     </row>
     <row r="234" spans="10:10">
-      <c r="J234" s="13"/>
+      <c r="J234" s="15"/>
     </row>
     <row r="235" spans="10:10">
-      <c r="J235" s="13"/>
+      <c r="J235" s="15"/>
     </row>
     <row r="236" spans="10:10">
-      <c r="J236" s="13"/>
+      <c r="J236" s="15"/>
     </row>
     <row r="237" spans="10:10">
-      <c r="J237" s="13"/>
+      <c r="J237" s="15"/>
     </row>
     <row r="238" spans="10:10">
-      <c r="J238" s="13"/>
+      <c r="J238" s="15"/>
     </row>
     <row r="239" spans="10:10">
-      <c r="J239" s="13"/>
+      <c r="J239" s="15"/>
     </row>
     <row r="240" spans="10:10">
-      <c r="J240" s="13"/>
+      <c r="J240" s="15"/>
     </row>
     <row r="241" spans="10:10">
-      <c r="J241" s="13"/>
+      <c r="J241" s="15"/>
     </row>
     <row r="242" spans="10:10">
-      <c r="J242" s="13"/>
+      <c r="J242" s="15"/>
     </row>
     <row r="243" spans="10:10">
-      <c r="J243" s="13"/>
+      <c r="J243" s="15"/>
     </row>
     <row r="244" spans="10:10">
-      <c r="J244" s="13"/>
+      <c r="J244" s="15"/>
     </row>
     <row r="245" spans="10:10">
-      <c r="J245" s="13"/>
+      <c r="J245" s="15"/>
     </row>
     <row r="246" spans="10:10">
-      <c r="J246" s="13"/>
+      <c r="J246" s="15"/>
     </row>
     <row r="247" spans="10:10">
-      <c r="J247" s="13"/>
+      <c r="J247" s="15"/>
     </row>
     <row r="248" spans="10:10">
-      <c r="J248" s="13"/>
+      <c r="J248" s="15"/>
     </row>
     <row r="249" spans="10:10">
-      <c r="J249" s="13"/>
+      <c r="J249" s="15"/>
     </row>
     <row r="250" spans="10:10">
-      <c r="J250" s="13"/>
+      <c r="J250" s="15"/>
     </row>
     <row r="251" spans="10:10">
-      <c r="J251" s="13"/>
+      <c r="J251" s="15"/>
     </row>
     <row r="252" spans="10:10">
-      <c r="J252" s="13"/>
+      <c r="J252" s="15"/>
     </row>
     <row r="253" spans="10:10">
-      <c r="J253" s="13"/>
+      <c r="J253" s="15"/>
     </row>
     <row r="254" spans="10:10">
-      <c r="J254" s="13"/>
+      <c r="J254" s="15"/>
     </row>
     <row r="255" spans="10:10">
-      <c r="J255" s="13"/>
+      <c r="J255" s="15"/>
     </row>
     <row r="256" spans="10:10">
-      <c r="J256" s="13"/>
+      <c r="J256" s="15"/>
     </row>
     <row r="257" spans="10:10">
-      <c r="J257" s="13"/>
+      <c r="J257" s="15"/>
     </row>
     <row r="258" spans="10:10">
-      <c r="J258" s="13"/>
+      <c r="J258" s="15"/>
     </row>
     <row r="259" spans="10:10">
-      <c r="J259" s="13"/>
+      <c r="J259" s="15"/>
     </row>
     <row r="260" spans="10:10">
-      <c r="J260" s="13"/>
+      <c r="J260" s="15"/>
     </row>
     <row r="261" spans="10:10">
-      <c r="J261" s="13"/>
+      <c r="J261" s="15"/>
     </row>
     <row r="262" spans="10:10">
-      <c r="J262" s="13"/>
+      <c r="J262" s="15"/>
     </row>
     <row r="263" spans="10:10">
-      <c r="J263" s="13"/>
+      <c r="J263" s="15"/>
     </row>
     <row r="264" spans="10:10">
-      <c r="J264" s="13"/>
+      <c r="J264" s="15"/>
     </row>
     <row r="265" spans="10:10">
-      <c r="J265" s="13"/>
+      <c r="J265" s="15"/>
     </row>
     <row r="266" spans="10:10">
-      <c r="J266" s="13"/>
+      <c r="J266" s="15"/>
     </row>
     <row r="267" spans="10:10">
-      <c r="J267" s="13"/>
+      <c r="J267" s="15"/>
     </row>
     <row r="268" spans="10:10">
-      <c r="J268" s="13"/>
+      <c r="J268" s="15"/>
     </row>
     <row r="269" spans="10:10">
-      <c r="J269" s="13"/>
+      <c r="J269" s="15"/>
     </row>
     <row r="270" spans="10:10">
-      <c r="J270" s="13"/>
+      <c r="J270" s="15"/>
     </row>
     <row r="271" spans="10:10">
-      <c r="J271" s="13"/>
+      <c r="J271" s="15"/>
     </row>
     <row r="272" spans="10:10">
-      <c r="J272" s="13"/>
+      <c r="J272" s="15"/>
     </row>
     <row r="273" spans="10:10">
-      <c r="J273" s="13"/>
+      <c r="J273" s="15"/>
     </row>
     <row r="274" spans="10:10">
-      <c r="J274" s="13"/>
+      <c r="J274" s="15"/>
     </row>
     <row r="275" spans="10:10">
-      <c r="J275" s="13"/>
+      <c r="J275" s="15"/>
     </row>
     <row r="276" spans="10:10">
-      <c r="J276" s="13"/>
+      <c r="J276" s="15"/>
     </row>
     <row r="277" spans="10:10">
-      <c r="J277" s="13"/>
+      <c r="J277" s="15"/>
     </row>
     <row r="278" spans="10:10">
-      <c r="J278" s="13"/>
+      <c r="J278" s="15"/>
     </row>
     <row r="279" spans="10:10">
-      <c r="J279" s="13"/>
+      <c r="J279" s="15"/>
     </row>
     <row r="280" spans="10:10">
-      <c r="J280" s="13"/>
+      <c r="J280" s="15"/>
     </row>
     <row r="281" spans="10:10">
-      <c r="J281" s="13"/>
+      <c r="J281" s="15"/>
     </row>
     <row r="282" spans="10:10">
-      <c r="J282" s="13"/>
+      <c r="J282" s="15"/>
     </row>
     <row r="283" spans="10:10">
-      <c r="J283" s="13"/>
+      <c r="J283" s="15"/>
     </row>
     <row r="284" spans="10:10">
-      <c r="J284" s="13"/>
+      <c r="J284" s="15"/>
     </row>
     <row r="285" spans="10:10">
-      <c r="J285" s="13"/>
+      <c r="J285" s="15"/>
     </row>
     <row r="286" spans="10:10">
-      <c r="J286" s="13"/>
+      <c r="J286" s="15"/>
     </row>
     <row r="287" spans="10:10">
-      <c r="J287" s="13"/>
+      <c r="J287" s="15"/>
     </row>
     <row r="288" spans="10:10">
-      <c r="J288" s="13"/>
+      <c r="J288" s="15"/>
     </row>
     <row r="289" spans="10:10">
-      <c r="J289" s="13"/>
+      <c r="J289" s="15"/>
     </row>
     <row r="290" spans="10:10">
-      <c r="J290" s="13"/>
+      <c r="J290" s="15"/>
     </row>
     <row r="291" spans="10:10">
-      <c r="J291" s="13"/>
+      <c r="J291" s="15"/>
     </row>
     <row r="292" spans="10:10">
-      <c r="J292" s="13"/>
+      <c r="J292" s="15"/>
     </row>
     <row r="293" spans="10:10">
-      <c r="J293" s="13"/>
+      <c r="J293" s="15"/>
     </row>
     <row r="294" spans="10:10">
-      <c r="J294" s="13"/>
+      <c r="J294" s="15"/>
     </row>
     <row r="295" spans="10:10">
-      <c r="J295" s="13"/>
+      <c r="J295" s="15"/>
     </row>
     <row r="296" spans="10:10">
-      <c r="J296" s="13"/>
+      <c r="J296" s="15"/>
     </row>
     <row r="297" spans="10:10">
-      <c r="J297" s="13"/>
+      <c r="J297" s="15"/>
     </row>
     <row r="298" spans="10:10">
-      <c r="J298" s="13"/>
+      <c r="J298" s="15"/>
     </row>
     <row r="299" spans="10:10">
-      <c r="J299" s="13"/>
+      <c r="J299" s="15"/>
     </row>
     <row r="300" spans="10:10">
-      <c r="J300" s="13"/>
+      <c r="J300" s="15"/>
     </row>
     <row r="301" spans="10:10">
-      <c r="J301" s="13"/>
+      <c r="J301" s="15"/>
     </row>
   </sheetData>
   <protectedRanges>

--- a/src/temp/TEMPLATE.xlsx
+++ b/src/temp/TEMPLATE.xlsx
@@ -176,13 +176,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="\N\8"/>
-    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;₱&quot;* #,##0_-;\-&quot;₱&quot;* #,##0_-;_-&quot;₱&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -215,33 +214,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -252,9 +234,8 @@
       <scheme val="major"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -270,14 +251,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -285,28 +258,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -320,15 +272,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -337,6 +290,52 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -381,37 +380,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,6 +416,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -441,7 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,7 +458,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,7 +482,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -477,13 +512,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -495,73 +560,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -608,50 +607,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -663,6 +618,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -691,6 +655,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -709,75 +693,90 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -785,12 +784,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -803,20 +801,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -825,17 +831,14 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="Note 2" xfId="2"/>
+    <cellStyle name="Note 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="2"/>
     <cellStyle name="60% - Accent6" xfId="3" builtinId="52"/>
     <cellStyle name="40% - Accent6" xfId="4" builtinId="51"/>
     <cellStyle name="60% - Accent5" xfId="5" builtinId="48"/>
@@ -888,7 +891,6 @@
   </cellStyles>
   <dxfs count="1">
     <dxf>
-      <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
       <alignment horizontal="left"/>
     </dxf>
   </dxfs>
@@ -1283,7 +1285,7 @@
     <col min="7" max="7" width="15.2814814814815" customWidth="1"/>
     <col min="8" max="8" width="23.8518518518519" customWidth="1"/>
     <col min="9" max="9" width="8.71111111111111" customWidth="1"/>
-    <col min="10" max="10" width="24" style="4" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
     <col min="11" max="11" width="26.4222222222222" customWidth="1"/>
     <col min="12" max="14" width="8.14074074074074" customWidth="1"/>
     <col min="15" max="15" width="20.1407407407407" customWidth="1"/>
@@ -1297,7 +1299,7 @@
     <col min="27" max="27" width="16.4222222222222" customWidth="1"/>
     <col min="28" max="28" width="14" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="18.7111111111111" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="9.14074074074074" style="5" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="9.14074074074074" style="4" hidden="1" customWidth="1"/>
     <col min="31" max="31" width="23.7111111111111" hidden="1" customWidth="1"/>
     <col min="32" max="32" width="16.4222222222222" hidden="1" customWidth="1"/>
     <col min="33" max="33" width="13.1407407407407" hidden="1" customWidth="1"/>
@@ -1328,267 +1330,267 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:62">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AA1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AB1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="19" t="s">
+      <c r="AE1" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="19" t="s">
+      <c r="AF1" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="19" t="s">
+      <c r="AG1" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="19" t="s">
+      <c r="AH1" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="19" t="s">
+      <c r="AI1" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="19" t="s">
+      <c r="AJ1" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="19" t="s">
+      <c r="AK1" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="19" t="s">
+      <c r="AL1" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="19" t="s">
+      <c r="AM1" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="19" t="s">
+      <c r="AN1" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="AO1" s="19" t="s">
+      <c r="AO1" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="AP1" s="19" t="s">
+      <c r="AP1" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="AQ1" s="19" t="s">
+      <c r="AQ1" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="AR1" s="19" t="s">
+      <c r="AR1" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="AS1" s="19" t="s">
+      <c r="AS1" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="AT1" s="19" t="s">
+      <c r="AT1" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="AU1" s="19" t="s">
+      <c r="AU1" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="AV1" s="19" t="s">
+      <c r="AV1" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="AW1" s="19" t="s">
+      <c r="AW1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="AX1" s="19" t="s">
+      <c r="AX1" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="AY1" s="19" t="s">
+      <c r="AY1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="AZ1" s="19" t="s">
+      <c r="AZ1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="BA1" s="19" t="s">
+      <c r="BA1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="BB1" s="19" t="s">
+      <c r="BB1" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="BC1" s="19" t="s">
+      <c r="BC1" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="BD1" s="19" t="s">
+      <c r="BD1" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="BE1" s="19" t="s">
+      <c r="BE1" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="BF1" s="19" t="s">
+      <c r="BF1" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="BG1" s="19" t="s">
+      <c r="BG1" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="BH1" s="19" t="s">
+      <c r="BH1" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="BI1" s="19" t="s">
+      <c r="BI1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="BJ1" s="19" t="s">
+      <c r="BJ1" s="22" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="2:62">
-      <c r="B2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="J2" s="15"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="AE2" s="20"/>
-      <c r="AK2" s="26"/>
-      <c r="AL2" s="26"/>
-      <c r="AM2" s="27"/>
-      <c r="AN2" s="26"/>
-      <c r="BE2" s="26"/>
-      <c r="BF2" s="26"/>
-      <c r="BH2" s="29"/>
-      <c r="BJ2" s="26"/>
+      <c r="B2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="J2" s="16"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="AE2" s="23"/>
+      <c r="AK2" s="29"/>
+      <c r="AL2" s="29"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="29"/>
+      <c r="BE2" s="29"/>
+      <c r="BF2" s="29"/>
+      <c r="BH2" s="31"/>
+      <c r="BJ2" s="29"/>
     </row>
     <row r="3" spans="2:62">
-      <c r="B3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="J3" s="15"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
-      <c r="AE3" s="20"/>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="27"/>
-      <c r="AN3" s="26"/>
-      <c r="BE3" s="26"/>
-      <c r="BF3" s="26"/>
-      <c r="BH3" s="29"/>
-      <c r="BJ3" s="26"/>
+      <c r="B3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="J3" s="16"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="AE3" s="23"/>
+      <c r="AK3" s="29"/>
+      <c r="AL3" s="29"/>
+      <c r="AM3" s="16"/>
+      <c r="AN3" s="29"/>
+      <c r="BE3" s="29"/>
+      <c r="BF3" s="29"/>
+      <c r="BH3" s="31"/>
+      <c r="BJ3" s="29"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="2:62">
-      <c r="B4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="J4" s="17"/>
-      <c r="AD4" s="21"/>
-      <c r="BE4" s="25"/>
-      <c r="BF4" s="25"/>
-      <c r="BH4" s="24"/>
-      <c r="BJ4" s="25"/>
+      <c r="B4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="J4" s="18"/>
+      <c r="AD4" s="24"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BH4" s="27"/>
+      <c r="BJ4" s="28"/>
     </row>
     <row r="5" s="2" customFormat="1" spans="2:62">
-      <c r="B5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="J5" s="18"/>
-      <c r="AD5" s="22"/>
-      <c r="AE5" s="23"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="BE5" s="28"/>
-      <c r="BF5" s="28"/>
-      <c r="BH5" s="30"/>
-      <c r="BJ5" s="28"/>
+      <c r="B5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="J5" s="19"/>
+      <c r="AD5" s="25"/>
+      <c r="AE5" s="26"/>
+      <c r="AK5" s="30"/>
+      <c r="AL5" s="30"/>
+      <c r="AN5" s="30"/>
+      <c r="BE5" s="30"/>
+      <c r="BF5" s="30"/>
+      <c r="BH5" s="32"/>
+      <c r="BJ5" s="30"/>
     </row>
     <row r="6" spans="1:90">
       <c r="A6" s="1"/>
-      <c r="B6" s="8"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="8"/>
+      <c r="D6" s="7"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="15"/>
+      <c r="J6" s="20"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
@@ -1613,10 +1615,10 @@
       <c r="AN6" s="1"/>
       <c r="AR6" s="1"/>
       <c r="AS6" s="1"/>
-      <c r="BE6" s="26"/>
-      <c r="BF6" s="26"/>
-      <c r="BH6" s="29"/>
-      <c r="BJ6" s="26"/>
+      <c r="BE6" s="29"/>
+      <c r="BF6" s="29"/>
+      <c r="BH6" s="31"/>
+      <c r="BJ6" s="29"/>
       <c r="BK6" s="1"/>
       <c r="BL6" s="1"/>
       <c r="BM6" s="1"/>
@@ -1647,11 +1649,19 @@
       <c r="CL6" s="1"/>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="3:90">
-      <c r="C7" s="10"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="13"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7" s="21"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
@@ -1662,6 +1672,7 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
+      <c r="AA7"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AE7" s="1"/>
@@ -1672,8 +1683,11 @@
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
       <c r="AL7" s="1"/>
+      <c r="AM7"/>
       <c r="AR7" s="1"/>
       <c r="AS7" s="1"/>
+      <c r="AT7"/>
+      <c r="AU7"/>
       <c r="AV7" s="1"/>
       <c r="AW7" s="1"/>
       <c r="AX7" s="1"/>
@@ -1683,9 +1697,12 @@
       <c r="BB7" s="1"/>
       <c r="BC7" s="1"/>
       <c r="BD7" s="1"/>
-      <c r="BE7" s="25"/>
-      <c r="BF7" s="25"/>
-      <c r="BH7" s="24"/>
+      <c r="BE7" s="28"/>
+      <c r="BF7" s="28"/>
+      <c r="BG7"/>
+      <c r="BH7" s="27"/>
+      <c r="BI7"/>
+      <c r="BJ7"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
       <c r="BM7" s="1"/>
@@ -1716,9 +1733,19 @@
       <c r="CL7" s="1"/>
     </row>
     <row r="8" spans="3:90">
-      <c r="C8" s="10"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="C8" s="11"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8" s="21"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
@@ -1729,6 +1756,7 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
+      <c r="AA8"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AE8" s="1"/>
@@ -1739,8 +1767,11 @@
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
+      <c r="AM8"/>
       <c r="AR8" s="1"/>
       <c r="AS8" s="1"/>
+      <c r="AT8"/>
+      <c r="AU8"/>
       <c r="AV8" s="1"/>
       <c r="AW8" s="1"/>
       <c r="AX8" s="1"/>
@@ -1750,9 +1781,12 @@
       <c r="BB8" s="1"/>
       <c r="BC8" s="1"/>
       <c r="BD8" s="1"/>
-      <c r="BE8" s="25"/>
-      <c r="BF8" s="25"/>
-      <c r="BH8" s="24"/>
+      <c r="BE8" s="28"/>
+      <c r="BF8" s="28"/>
+      <c r="BG8"/>
+      <c r="BH8" s="27"/>
+      <c r="BI8"/>
+      <c r="BJ8"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
       <c r="BM8" s="1"/>
@@ -1783,9 +1817,19 @@
       <c r="CL8" s="1"/>
     </row>
     <row r="9" spans="3:90">
-      <c r="C9" s="10"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
+      <c r="C9" s="11"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9" s="21"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -1796,6 +1840,7 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
+      <c r="AA9"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AE9" s="1"/>
@@ -1806,8 +1851,11 @@
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
+      <c r="AM9"/>
       <c r="AR9" s="1"/>
       <c r="AS9" s="1"/>
+      <c r="AT9"/>
+      <c r="AU9"/>
       <c r="AV9" s="1"/>
       <c r="AW9" s="1"/>
       <c r="AX9" s="1"/>
@@ -1817,9 +1865,12 @@
       <c r="BB9" s="1"/>
       <c r="BC9" s="1"/>
       <c r="BD9" s="1"/>
-      <c r="BE9" s="25"/>
-      <c r="BF9" s="25"/>
-      <c r="BH9" s="24"/>
+      <c r="BE9" s="28"/>
+      <c r="BF9" s="28"/>
+      <c r="BG9"/>
+      <c r="BH9" s="27"/>
+      <c r="BI9"/>
+      <c r="BJ9"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
       <c r="BM9" s="1"/>
@@ -1850,9 +1901,19 @@
       <c r="CL9" s="1"/>
     </row>
     <row r="10" spans="3:90">
-      <c r="C10" s="10"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="C10" s="11"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10" s="21"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -1863,6 +1924,7 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
+      <c r="AA10"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AE10" s="1"/>
@@ -1873,8 +1935,11 @@
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
       <c r="AL10" s="1"/>
+      <c r="AM10"/>
       <c r="AR10" s="1"/>
       <c r="AS10" s="1"/>
+      <c r="AT10"/>
+      <c r="AU10"/>
       <c r="AV10" s="1"/>
       <c r="AW10" s="1"/>
       <c r="AX10" s="1"/>
@@ -1884,9 +1949,12 @@
       <c r="BB10" s="1"/>
       <c r="BC10" s="1"/>
       <c r="BD10" s="1"/>
-      <c r="BE10" s="25"/>
-      <c r="BF10" s="25"/>
-      <c r="BH10" s="24"/>
+      <c r="BE10" s="28"/>
+      <c r="BF10" s="28"/>
+      <c r="BG10"/>
+      <c r="BH10" s="27"/>
+      <c r="BI10"/>
+      <c r="BJ10"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
       <c r="BM10" s="1"/>
@@ -1917,9 +1985,19 @@
       <c r="CL10" s="1"/>
     </row>
     <row r="11" spans="3:90">
-      <c r="C11" s="10"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="C11" s="11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11" s="21"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -1930,18 +2008,22 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
+      <c r="AA11"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AE11" s="1"/>
-      <c r="AF11" s="24"/>
+      <c r="AF11" s="27"/>
       <c r="AG11" s="1"/>
-      <c r="AH11" s="25"/>
+      <c r="AH11" s="28"/>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
+      <c r="AM11"/>
       <c r="AR11" s="1"/>
       <c r="AS11" s="1"/>
+      <c r="AT11"/>
+      <c r="AU11"/>
       <c r="AV11" s="1"/>
       <c r="AW11" s="1"/>
       <c r="AX11" s="1"/>
@@ -1951,9 +2033,12 @@
       <c r="BB11" s="1"/>
       <c r="BC11" s="1"/>
       <c r="BD11" s="1"/>
-      <c r="BE11" s="25"/>
-      <c r="BF11" s="25"/>
-      <c r="BH11" s="24"/>
+      <c r="BE11" s="28"/>
+      <c r="BF11" s="28"/>
+      <c r="BG11"/>
+      <c r="BH11" s="27"/>
+      <c r="BI11"/>
+      <c r="BJ11"/>
       <c r="BK11" s="1"/>
       <c r="BL11" s="1"/>
       <c r="BM11" s="1"/>
@@ -1984,9 +2069,19 @@
       <c r="CL11" s="1"/>
     </row>
     <row r="12" spans="3:90">
-      <c r="C12" s="10"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
+      <c r="C12" s="11"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12" s="21"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
@@ -1997,18 +2092,22 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
+      <c r="AA12"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AE12" s="1"/>
-      <c r="AF12" s="24"/>
+      <c r="AF12" s="27"/>
       <c r="AG12" s="1"/>
-      <c r="AH12" s="25"/>
+      <c r="AH12" s="28"/>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
       <c r="AL12" s="1"/>
+      <c r="AM12"/>
       <c r="AR12" s="1"/>
       <c r="AS12" s="1"/>
+      <c r="AT12"/>
+      <c r="AU12"/>
       <c r="AV12" s="1"/>
       <c r="AW12" s="1"/>
       <c r="AX12" s="1"/>
@@ -2018,9 +2117,12 @@
       <c r="BB12" s="1"/>
       <c r="BC12" s="1"/>
       <c r="BD12" s="1"/>
-      <c r="BE12" s="25"/>
-      <c r="BF12" s="25"/>
-      <c r="BH12" s="24"/>
+      <c r="BE12" s="28"/>
+      <c r="BF12" s="28"/>
+      <c r="BG12"/>
+      <c r="BH12" s="27"/>
+      <c r="BI12"/>
+      <c r="BJ12"/>
       <c r="BK12" s="1"/>
       <c r="BL12" s="1"/>
       <c r="BM12" s="1"/>
@@ -2051,9 +2153,10 @@
       <c r="CL12" s="1"/>
     </row>
     <row r="13" spans="3:90">
-      <c r="C13" s="10"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
+      <c r="C13" s="11"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="J13" s="21"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
@@ -2074,8 +2177,11 @@
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
       <c r="AL13" s="1"/>
+      <c r="AM13"/>
       <c r="AR13" s="1"/>
       <c r="AS13" s="1"/>
+      <c r="AT13"/>
+      <c r="AU13"/>
       <c r="AV13" s="1"/>
       <c r="AW13" s="1"/>
       <c r="AX13" s="1"/>
@@ -2085,9 +2191,12 @@
       <c r="BB13" s="1"/>
       <c r="BC13" s="1"/>
       <c r="BD13" s="1"/>
-      <c r="BE13" s="25"/>
-      <c r="BF13" s="25"/>
-      <c r="BH13" s="24"/>
+      <c r="BE13" s="28"/>
+      <c r="BF13" s="28"/>
+      <c r="BG13"/>
+      <c r="BH13" s="27"/>
+      <c r="BI13"/>
+      <c r="BJ13"/>
       <c r="BK13" s="1"/>
       <c r="BL13" s="1"/>
       <c r="BM13" s="1"/>
@@ -2120,14 +2229,14 @@
     <row r="14" s="3" customFormat="1" spans="1:90">
       <c r="A14"/>
       <c r="B14"/>
-      <c r="C14" s="10"/>
+      <c r="C14" s="11"/>
       <c r="D14"/>
       <c r="E14"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
       <c r="H14"/>
       <c r="I14"/>
-      <c r="J14" s="4"/>
+      <c r="J14" s="21"/>
       <c r="K14"/>
       <c r="L14"/>
       <c r="M14"/>
@@ -2147,7 +2256,7 @@
       <c r="AA14"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
-      <c r="AD14" s="5"/>
+      <c r="AD14" s="4"/>
       <c r="AE14" s="1"/>
       <c r="AF14" s="1"/>
       <c r="AG14" s="1"/>
@@ -2174,10 +2283,10 @@
       <c r="BB14" s="1"/>
       <c r="BC14" s="1"/>
       <c r="BD14" s="1"/>
-      <c r="BE14" s="25"/>
-      <c r="BF14" s="25"/>
+      <c r="BE14" s="28"/>
+      <c r="BF14" s="28"/>
       <c r="BG14"/>
-      <c r="BH14" s="24"/>
+      <c r="BH14" s="27"/>
       <c r="BI14"/>
       <c r="BJ14"/>
       <c r="BK14" s="1"/>
@@ -2210,9 +2319,19 @@
       <c r="CL14" s="1"/>
     </row>
     <row r="15" spans="3:90">
-      <c r="C15" s="10"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
+      <c r="C15" s="11"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15" s="21"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
@@ -2223,6 +2342,7 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
+      <c r="AA15"/>
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AE15" s="1"/>
@@ -2233,8 +2353,11 @@
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
       <c r="AL15" s="1"/>
+      <c r="AM15"/>
       <c r="AR15" s="1"/>
       <c r="AS15" s="1"/>
+      <c r="AT15"/>
+      <c r="AU15"/>
       <c r="AV15" s="1"/>
       <c r="AW15" s="1"/>
       <c r="AX15" s="1"/>
@@ -2244,9 +2367,12 @@
       <c r="BB15" s="1"/>
       <c r="BC15" s="1"/>
       <c r="BD15" s="1"/>
-      <c r="BE15" s="25"/>
-      <c r="BF15" s="25"/>
-      <c r="BH15" s="24"/>
+      <c r="BE15" s="28"/>
+      <c r="BF15" s="28"/>
+      <c r="BG15"/>
+      <c r="BH15" s="27"/>
+      <c r="BI15"/>
+      <c r="BJ15"/>
       <c r="BK15" s="1"/>
       <c r="BL15" s="1"/>
       <c r="BM15" s="1"/>
@@ -2277,9 +2403,19 @@
       <c r="CL15" s="1"/>
     </row>
     <row r="16" spans="3:90">
-      <c r="C16" s="10"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
+      <c r="C16" s="11"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16" s="21"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -2290,6 +2426,7 @@
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
+      <c r="AA16"/>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AE16" s="1"/>
@@ -2300,8 +2437,11 @@
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
       <c r="AL16" s="1"/>
+      <c r="AM16"/>
       <c r="AR16" s="1"/>
       <c r="AS16" s="1"/>
+      <c r="AT16"/>
+      <c r="AU16"/>
       <c r="AV16" s="1"/>
       <c r="AW16" s="1"/>
       <c r="AX16" s="1"/>
@@ -2311,9 +2451,12 @@
       <c r="BB16" s="1"/>
       <c r="BC16" s="1"/>
       <c r="BD16" s="1"/>
-      <c r="BE16" s="25"/>
-      <c r="BF16" s="25"/>
-      <c r="BH16" s="24"/>
+      <c r="BE16" s="28"/>
+      <c r="BF16" s="28"/>
+      <c r="BG16"/>
+      <c r="BH16" s="27"/>
+      <c r="BI16"/>
+      <c r="BJ16"/>
       <c r="BK16" s="1"/>
       <c r="BL16" s="1"/>
       <c r="BM16" s="1"/>
@@ -2344,9 +2487,19 @@
       <c r="CL16" s="1"/>
     </row>
     <row r="17" spans="3:90">
-      <c r="C17" s="10"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
+      <c r="C17" s="11"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17" s="21"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
@@ -2357,6 +2510,7 @@
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
+      <c r="AA17"/>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AE17" s="1"/>
@@ -2367,8 +2521,11 @@
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
       <c r="AL17" s="1"/>
+      <c r="AM17"/>
       <c r="AR17" s="1"/>
       <c r="AS17" s="1"/>
+      <c r="AT17"/>
+      <c r="AU17"/>
       <c r="AV17" s="1"/>
       <c r="AW17" s="1"/>
       <c r="AX17" s="1"/>
@@ -2378,9 +2535,12 @@
       <c r="BB17" s="1"/>
       <c r="BC17" s="1"/>
       <c r="BD17" s="1"/>
-      <c r="BE17" s="25"/>
-      <c r="BF17" s="25"/>
-      <c r="BH17" s="24"/>
+      <c r="BE17" s="28"/>
+      <c r="BF17" s="28"/>
+      <c r="BG17"/>
+      <c r="BH17" s="27"/>
+      <c r="BI17"/>
+      <c r="BJ17"/>
       <c r="BK17" s="1"/>
       <c r="BL17" s="1"/>
       <c r="BM17" s="1"/>
@@ -2413,14 +2573,14 @@
     <row r="18" s="3" customFormat="1" spans="1:90">
       <c r="A18"/>
       <c r="B18"/>
-      <c r="C18" s="10"/>
+      <c r="C18" s="11"/>
       <c r="D18"/>
       <c r="E18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
       <c r="H18"/>
       <c r="I18"/>
-      <c r="J18" s="4"/>
+      <c r="J18" s="21"/>
       <c r="K18"/>
       <c r="L18"/>
       <c r="M18"/>
@@ -2440,7 +2600,7 @@
       <c r="AA18"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
-      <c r="AD18" s="5"/>
+      <c r="AD18" s="4"/>
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1"/>
@@ -2467,10 +2627,10 @@
       <c r="BB18" s="1"/>
       <c r="BC18" s="1"/>
       <c r="BD18" s="1"/>
-      <c r="BE18" s="25"/>
-      <c r="BF18" s="25"/>
+      <c r="BE18" s="28"/>
+      <c r="BF18" s="28"/>
       <c r="BG18"/>
-      <c r="BH18" s="24"/>
+      <c r="BH18" s="27"/>
       <c r="BI18"/>
       <c r="BJ18"/>
       <c r="BK18" s="1"/>
@@ -2503,9 +2663,19 @@
       <c r="CL18" s="1"/>
     </row>
     <row r="19" spans="3:90">
-      <c r="C19" s="10"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
+      <c r="C19" s="11"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19" s="21"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
@@ -2516,6 +2686,7 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
+      <c r="AA19"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AE19" s="1"/>
@@ -2526,8 +2697,11 @@
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
+      <c r="AM19"/>
       <c r="AR19" s="1"/>
       <c r="AS19" s="1"/>
+      <c r="AT19"/>
+      <c r="AU19"/>
       <c r="AV19" s="1"/>
       <c r="AW19" s="1"/>
       <c r="AX19" s="1"/>
@@ -2537,9 +2711,12 @@
       <c r="BB19" s="1"/>
       <c r="BC19" s="1"/>
       <c r="BD19" s="1"/>
-      <c r="BE19" s="25"/>
-      <c r="BF19" s="25"/>
-      <c r="BH19" s="24"/>
+      <c r="BE19" s="28"/>
+      <c r="BF19" s="28"/>
+      <c r="BG19"/>
+      <c r="BH19" s="27"/>
+      <c r="BI19"/>
+      <c r="BJ19"/>
       <c r="BK19" s="1"/>
       <c r="BL19" s="1"/>
       <c r="BM19" s="1"/>
@@ -2570,9 +2747,19 @@
       <c r="CL19" s="1"/>
     </row>
     <row r="20" spans="3:90">
-      <c r="C20" s="10"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="C20" s="11"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20" s="21"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
@@ -2583,6 +2770,7 @@
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
+      <c r="AA20"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AE20" s="1"/>
@@ -2593,8 +2781,11 @@
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
       <c r="AL20" s="1"/>
+      <c r="AM20"/>
       <c r="AR20" s="1"/>
       <c r="AS20" s="1"/>
+      <c r="AT20"/>
+      <c r="AU20"/>
       <c r="AV20" s="1"/>
       <c r="AW20" s="1"/>
       <c r="AX20" s="1"/>
@@ -2604,9 +2795,12 @@
       <c r="BB20" s="1"/>
       <c r="BC20" s="1"/>
       <c r="BD20" s="1"/>
-      <c r="BE20" s="25"/>
-      <c r="BF20" s="25"/>
-      <c r="BH20" s="24"/>
+      <c r="BE20" s="28"/>
+      <c r="BF20" s="28"/>
+      <c r="BG20"/>
+      <c r="BH20" s="27"/>
+      <c r="BI20"/>
+      <c r="BJ20"/>
       <c r="BK20" s="1"/>
       <c r="BL20" s="1"/>
       <c r="BM20" s="1"/>
@@ -2637,9 +2831,19 @@
       <c r="CL20" s="1"/>
     </row>
     <row r="21" spans="3:90">
-      <c r="C21" s="10"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
+      <c r="C21" s="11"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21" s="21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
@@ -2650,6 +2854,7 @@
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
+      <c r="AA21"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AE21" s="1"/>
@@ -2660,8 +2865,11 @@
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
       <c r="AL21" s="1"/>
+      <c r="AM21"/>
       <c r="AR21" s="1"/>
       <c r="AS21" s="1"/>
+      <c r="AT21"/>
+      <c r="AU21"/>
       <c r="AV21" s="1"/>
       <c r="AW21" s="1"/>
       <c r="AX21" s="1"/>
@@ -2671,9 +2879,12 @@
       <c r="BB21" s="1"/>
       <c r="BC21" s="1"/>
       <c r="BD21" s="1"/>
-      <c r="BE21" s="25"/>
-      <c r="BF21" s="25"/>
-      <c r="BH21" s="24"/>
+      <c r="BE21" s="28"/>
+      <c r="BF21" s="28"/>
+      <c r="BG21"/>
+      <c r="BH21" s="27"/>
+      <c r="BI21"/>
+      <c r="BJ21"/>
       <c r="BK21" s="1"/>
       <c r="BL21" s="1"/>
       <c r="BM21" s="1"/>
@@ -2704,9 +2915,19 @@
       <c r="CL21" s="1"/>
     </row>
     <row r="22" spans="3:90">
-      <c r="C22" s="10"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+      <c r="C22" s="11"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22" s="21"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
@@ -2717,6 +2938,7 @@
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
+      <c r="AA22"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AE22" s="1"/>
@@ -2727,8 +2949,11 @@
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
       <c r="AL22" s="1"/>
+      <c r="AM22"/>
       <c r="AR22" s="1"/>
       <c r="AS22" s="1"/>
+      <c r="AT22"/>
+      <c r="AU22"/>
       <c r="AV22" s="1"/>
       <c r="AW22" s="1"/>
       <c r="AX22" s="1"/>
@@ -2738,9 +2963,12 @@
       <c r="BB22" s="1"/>
       <c r="BC22" s="1"/>
       <c r="BD22" s="1"/>
-      <c r="BE22" s="25"/>
-      <c r="BF22" s="25"/>
-      <c r="BH22" s="24"/>
+      <c r="BE22" s="28"/>
+      <c r="BF22" s="28"/>
+      <c r="BG22"/>
+      <c r="BH22" s="27"/>
+      <c r="BI22"/>
+      <c r="BJ22"/>
       <c r="BK22" s="1"/>
       <c r="BL22" s="1"/>
       <c r="BM22" s="1"/>
@@ -2771,9 +2999,19 @@
       <c r="CL22" s="1"/>
     </row>
     <row r="23" spans="3:90">
-      <c r="C23" s="10"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
+      <c r="C23" s="11"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23" s="21"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
@@ -2784,6 +3022,7 @@
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
+      <c r="AA23"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AE23" s="1"/>
@@ -2794,8 +3033,11 @@
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
       <c r="AL23" s="1"/>
+      <c r="AM23"/>
       <c r="AR23" s="1"/>
       <c r="AS23" s="1"/>
+      <c r="AT23"/>
+      <c r="AU23"/>
       <c r="AV23" s="1"/>
       <c r="AW23" s="1"/>
       <c r="AX23" s="1"/>
@@ -2805,9 +3047,12 @@
       <c r="BB23" s="1"/>
       <c r="BC23" s="1"/>
       <c r="BD23" s="1"/>
-      <c r="BE23" s="25"/>
-      <c r="BF23" s="25"/>
-      <c r="BH23" s="24"/>
+      <c r="BE23" s="28"/>
+      <c r="BF23" s="28"/>
+      <c r="BG23"/>
+      <c r="BH23" s="27"/>
+      <c r="BI23"/>
+      <c r="BJ23"/>
       <c r="BK23" s="1"/>
       <c r="BL23" s="1"/>
       <c r="BM23" s="1"/>
@@ -2838,9 +3083,10 @@
       <c r="CL23" s="1"/>
     </row>
     <row r="24" spans="3:90">
-      <c r="C24" s="10"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
+      <c r="C24" s="11"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="J24" s="21"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
@@ -2851,6 +3097,7 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
+      <c r="AA24"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AE24" s="1"/>
@@ -2861,8 +3108,11 @@
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
       <c r="AL24" s="1"/>
+      <c r="AM24"/>
       <c r="AR24" s="1"/>
       <c r="AS24" s="1"/>
+      <c r="AT24"/>
+      <c r="AU24"/>
       <c r="AV24" s="1"/>
       <c r="AW24" s="1"/>
       <c r="AX24" s="1"/>
@@ -2872,9 +3122,12 @@
       <c r="BB24" s="1"/>
       <c r="BC24" s="1"/>
       <c r="BD24" s="1"/>
-      <c r="BE24" s="25"/>
-      <c r="BF24" s="25"/>
-      <c r="BH24" s="24"/>
+      <c r="BE24" s="28"/>
+      <c r="BF24" s="28"/>
+      <c r="BG24"/>
+      <c r="BH24" s="27"/>
+      <c r="BI24"/>
+      <c r="BJ24"/>
       <c r="BK24" s="1"/>
       <c r="BL24" s="1"/>
       <c r="BM24" s="1"/>
@@ -2905,9 +3158,10 @@
       <c r="CL24" s="1"/>
     </row>
     <row r="25" spans="3:90">
-      <c r="C25" s="10"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
+      <c r="C25" s="11"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="J25" s="21"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
@@ -2918,6 +3172,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
+      <c r="AA25"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AE25" s="1"/>
@@ -2928,8 +3183,11 @@
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
       <c r="AL25" s="1"/>
+      <c r="AM25"/>
       <c r="AR25" s="1"/>
       <c r="AS25" s="1"/>
+      <c r="AT25"/>
+      <c r="AU25"/>
       <c r="AV25" s="1"/>
       <c r="AW25" s="1"/>
       <c r="AX25" s="1"/>
@@ -2939,9 +3197,12 @@
       <c r="BB25" s="1"/>
       <c r="BC25" s="1"/>
       <c r="BD25" s="1"/>
-      <c r="BE25" s="25"/>
-      <c r="BF25" s="25"/>
-      <c r="BH25" s="24"/>
+      <c r="BE25" s="28"/>
+      <c r="BF25" s="28"/>
+      <c r="BG25"/>
+      <c r="BH25" s="27"/>
+      <c r="BI25"/>
+      <c r="BJ25"/>
       <c r="BK25" s="1"/>
       <c r="BL25" s="1"/>
       <c r="BM25" s="1"/>
@@ -2972,9 +3233,10 @@
       <c r="CL25" s="1"/>
     </row>
     <row r="26" spans="3:90">
-      <c r="C26" s="10"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
+      <c r="C26" s="11"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="J26" s="21"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
@@ -2985,6 +3247,7 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
+      <c r="AA26"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AE26" s="1"/>
@@ -2995,8 +3258,11 @@
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
       <c r="AL26" s="1"/>
+      <c r="AM26"/>
       <c r="AR26" s="1"/>
       <c r="AS26" s="1"/>
+      <c r="AT26"/>
+      <c r="AU26"/>
       <c r="AV26" s="1"/>
       <c r="AW26" s="1"/>
       <c r="AX26" s="1"/>
@@ -3006,9 +3272,12 @@
       <c r="BB26" s="1"/>
       <c r="BC26" s="1"/>
       <c r="BD26" s="1"/>
-      <c r="BE26" s="25"/>
-      <c r="BF26" s="25"/>
-      <c r="BH26" s="24"/>
+      <c r="BE26" s="28"/>
+      <c r="BF26" s="28"/>
+      <c r="BG26"/>
+      <c r="BH26" s="27"/>
+      <c r="BI26"/>
+      <c r="BJ26"/>
       <c r="BK26" s="1"/>
       <c r="BL26" s="1"/>
       <c r="BM26" s="1"/>
@@ -3039,9 +3308,10 @@
       <c r="CL26" s="1"/>
     </row>
     <row r="27" spans="3:90">
-      <c r="C27" s="10"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
+      <c r="C27" s="11"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="J27" s="21"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
@@ -3052,6 +3322,7 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
+      <c r="AA27"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AE27" s="1"/>
@@ -3062,8 +3333,11 @@
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
       <c r="AL27" s="1"/>
+      <c r="AM27"/>
       <c r="AR27" s="1"/>
       <c r="AS27" s="1"/>
+      <c r="AT27"/>
+      <c r="AU27"/>
       <c r="AV27" s="1"/>
       <c r="AW27" s="1"/>
       <c r="AX27" s="1"/>
@@ -3073,9 +3347,12 @@
       <c r="BB27" s="1"/>
       <c r="BC27" s="1"/>
       <c r="BD27" s="1"/>
-      <c r="BE27" s="25"/>
-      <c r="BF27" s="25"/>
-      <c r="BH27" s="24"/>
+      <c r="BE27" s="28"/>
+      <c r="BF27" s="28"/>
+      <c r="BG27"/>
+      <c r="BH27" s="27"/>
+      <c r="BI27"/>
+      <c r="BJ27"/>
       <c r="BK27" s="1"/>
       <c r="BL27" s="1"/>
       <c r="BM27" s="1"/>
@@ -3106,9 +3383,10 @@
       <c r="CL27" s="1"/>
     </row>
     <row r="28" spans="3:90">
-      <c r="C28" s="10"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
+      <c r="C28" s="11"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="J28" s="21"/>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
@@ -3119,6 +3397,7 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
+      <c r="AA28"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
       <c r="AE28" s="1"/>
@@ -3129,8 +3408,11 @@
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
       <c r="AL28" s="1"/>
+      <c r="AM28"/>
       <c r="AR28" s="1"/>
       <c r="AS28" s="1"/>
+      <c r="AT28"/>
+      <c r="AU28"/>
       <c r="AV28" s="1"/>
       <c r="AW28" s="1"/>
       <c r="AX28" s="1"/>
@@ -3140,9 +3422,12 @@
       <c r="BB28" s="1"/>
       <c r="BC28" s="1"/>
       <c r="BD28" s="1"/>
-      <c r="BE28" s="25"/>
-      <c r="BF28" s="25"/>
-      <c r="BH28" s="24"/>
+      <c r="BE28" s="28"/>
+      <c r="BF28" s="28"/>
+      <c r="BG28"/>
+      <c r="BH28" s="27"/>
+      <c r="BI28"/>
+      <c r="BJ28"/>
       <c r="BK28" s="1"/>
       <c r="BL28" s="1"/>
       <c r="BM28" s="1"/>
@@ -3175,14 +3460,14 @@
     <row r="29" s="3" customFormat="1" spans="1:90">
       <c r="A29"/>
       <c r="B29"/>
-      <c r="C29" s="10"/>
+      <c r="C29" s="11"/>
       <c r="D29"/>
       <c r="E29"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
       <c r="H29"/>
       <c r="I29"/>
-      <c r="J29" s="4"/>
+      <c r="J29" s="21"/>
       <c r="K29"/>
       <c r="L29"/>
       <c r="M29"/>
@@ -3202,7 +3487,7 @@
       <c r="AA29"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
-      <c r="AD29" s="5"/>
+      <c r="AD29" s="4"/>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
       <c r="AG29" s="1"/>
@@ -3229,10 +3514,10 @@
       <c r="BB29" s="1"/>
       <c r="BC29" s="1"/>
       <c r="BD29" s="1"/>
-      <c r="BE29" s="25"/>
-      <c r="BF29" s="25"/>
+      <c r="BE29" s="28"/>
+      <c r="BF29" s="28"/>
       <c r="BG29"/>
-      <c r="BH29" s="24"/>
+      <c r="BH29" s="27"/>
       <c r="BI29"/>
       <c r="BJ29"/>
       <c r="BK29" s="1"/>
@@ -3265,9 +3550,10 @@
       <c r="CL29" s="1"/>
     </row>
     <row r="30" spans="3:90">
-      <c r="C30" s="10"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
+      <c r="C30" s="11"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="J30" s="21"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
@@ -3278,6 +3564,7 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
+      <c r="AA30"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AE30" s="1"/>
@@ -3288,8 +3575,11 @@
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
       <c r="AL30" s="1"/>
+      <c r="AM30"/>
       <c r="AR30" s="1"/>
       <c r="AS30" s="1"/>
+      <c r="AT30"/>
+      <c r="AU30"/>
       <c r="AV30" s="1"/>
       <c r="AW30" s="1"/>
       <c r="AX30" s="1"/>
@@ -3299,9 +3589,12 @@
       <c r="BB30" s="1"/>
       <c r="BC30" s="1"/>
       <c r="BD30" s="1"/>
-      <c r="BE30" s="25"/>
-      <c r="BF30" s="25"/>
-      <c r="BH30" s="24"/>
+      <c r="BE30" s="28"/>
+      <c r="BF30" s="28"/>
+      <c r="BG30"/>
+      <c r="BH30" s="27"/>
+      <c r="BI30"/>
+      <c r="BJ30"/>
       <c r="BK30" s="1"/>
       <c r="BL30" s="1"/>
       <c r="BM30" s="1"/>
@@ -3332,9 +3625,10 @@
       <c r="CL30" s="1"/>
     </row>
     <row r="31" spans="3:90">
-      <c r="C31" s="10"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
+      <c r="C31" s="11"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="J31" s="21"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
@@ -3345,6 +3639,7 @@
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
+      <c r="AA31"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AE31" s="1"/>
@@ -3355,8 +3650,11 @@
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
       <c r="AL31" s="1"/>
+      <c r="AM31"/>
       <c r="AR31" s="1"/>
       <c r="AS31" s="1"/>
+      <c r="AT31"/>
+      <c r="AU31"/>
       <c r="AV31" s="1"/>
       <c r="AW31" s="1"/>
       <c r="AX31" s="1"/>
@@ -3366,9 +3664,12 @@
       <c r="BB31" s="1"/>
       <c r="BC31" s="1"/>
       <c r="BD31" s="1"/>
-      <c r="BE31" s="25"/>
-      <c r="BF31" s="25"/>
-      <c r="BH31" s="24"/>
+      <c r="BE31" s="28"/>
+      <c r="BF31" s="28"/>
+      <c r="BG31"/>
+      <c r="BH31" s="27"/>
+      <c r="BI31"/>
+      <c r="BJ31"/>
       <c r="BK31" s="1"/>
       <c r="BL31" s="1"/>
       <c r="BM31" s="1"/>
@@ -3399,9 +3700,10 @@
       <c r="CL31" s="1"/>
     </row>
     <row r="32" spans="3:90">
-      <c r="C32" s="10"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
+      <c r="C32" s="11"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="J32" s="21"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
@@ -3412,6 +3714,7 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
+      <c r="AA32"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AE32" s="1"/>
@@ -3422,8 +3725,11 @@
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
       <c r="AL32" s="1"/>
+      <c r="AM32"/>
       <c r="AR32" s="1"/>
       <c r="AS32" s="1"/>
+      <c r="AT32"/>
+      <c r="AU32"/>
       <c r="AV32" s="1"/>
       <c r="AW32" s="1"/>
       <c r="AX32" s="1"/>
@@ -3433,9 +3739,12 @@
       <c r="BB32" s="1"/>
       <c r="BC32" s="1"/>
       <c r="BD32" s="1"/>
-      <c r="BE32" s="25"/>
-      <c r="BF32" s="25"/>
-      <c r="BH32" s="24"/>
+      <c r="BE32" s="28"/>
+      <c r="BF32" s="28"/>
+      <c r="BG32"/>
+      <c r="BH32" s="27"/>
+      <c r="BI32"/>
+      <c r="BJ32"/>
       <c r="BK32" s="1"/>
       <c r="BL32" s="1"/>
       <c r="BM32" s="1"/>
@@ -3466,9 +3775,10 @@
       <c r="CL32" s="1"/>
     </row>
     <row r="33" spans="3:90">
-      <c r="C33" s="10"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
+      <c r="C33" s="11"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="J33" s="21"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
@@ -3479,6 +3789,7 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
+      <c r="AA33"/>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AE33" s="1"/>
@@ -3489,8 +3800,11 @@
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
       <c r="AL33" s="1"/>
+      <c r="AM33"/>
       <c r="AR33" s="1"/>
       <c r="AS33" s="1"/>
+      <c r="AT33"/>
+      <c r="AU33"/>
       <c r="AV33" s="1"/>
       <c r="AW33" s="1"/>
       <c r="AX33" s="1"/>
@@ -3500,9 +3814,12 @@
       <c r="BB33" s="1"/>
       <c r="BC33" s="1"/>
       <c r="BD33" s="1"/>
-      <c r="BE33" s="25"/>
-      <c r="BF33" s="25"/>
-      <c r="BH33" s="24"/>
+      <c r="BE33" s="28"/>
+      <c r="BF33" s="28"/>
+      <c r="BG33"/>
+      <c r="BH33" s="27"/>
+      <c r="BI33"/>
+      <c r="BJ33"/>
       <c r="BK33" s="1"/>
       <c r="BL33" s="1"/>
       <c r="BM33" s="1"/>
@@ -3533,9 +3850,10 @@
       <c r="CL33" s="1"/>
     </row>
     <row r="34" spans="3:90">
-      <c r="C34" s="10"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
+      <c r="C34" s="11"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="J34" s="21"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
@@ -3546,6 +3864,7 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
+      <c r="AA34"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AE34" s="1"/>
@@ -3556,8 +3875,11 @@
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
       <c r="AL34" s="1"/>
+      <c r="AM34"/>
       <c r="AR34" s="1"/>
       <c r="AS34" s="1"/>
+      <c r="AT34"/>
+      <c r="AU34"/>
       <c r="AV34" s="1"/>
       <c r="AW34" s="1"/>
       <c r="AX34" s="1"/>
@@ -3567,9 +3889,12 @@
       <c r="BB34" s="1"/>
       <c r="BC34" s="1"/>
       <c r="BD34" s="1"/>
-      <c r="BE34" s="25"/>
-      <c r="BF34" s="25"/>
-      <c r="BH34" s="24"/>
+      <c r="BE34" s="28"/>
+      <c r="BF34" s="28"/>
+      <c r="BG34"/>
+      <c r="BH34" s="27"/>
+      <c r="BI34"/>
+      <c r="BJ34"/>
       <c r="BK34" s="1"/>
       <c r="BL34" s="1"/>
       <c r="BM34" s="1"/>
@@ -3600,9 +3925,10 @@
       <c r="CL34" s="1"/>
     </row>
     <row r="35" spans="3:90">
-      <c r="C35" s="10"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
+      <c r="C35" s="11"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="J35" s="21"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
@@ -3613,6 +3939,7 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
+      <c r="AA35"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AE35" s="1"/>
@@ -3623,8 +3950,11 @@
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
       <c r="AL35" s="1"/>
+      <c r="AM35"/>
       <c r="AR35" s="1"/>
       <c r="AS35" s="1"/>
+      <c r="AT35"/>
+      <c r="AU35"/>
       <c r="AV35" s="1"/>
       <c r="AW35" s="1"/>
       <c r="AX35" s="1"/>
@@ -3634,9 +3964,12 @@
       <c r="BB35" s="1"/>
       <c r="BC35" s="1"/>
       <c r="BD35" s="1"/>
-      <c r="BE35" s="25"/>
-      <c r="BF35" s="25"/>
-      <c r="BH35" s="24"/>
+      <c r="BE35" s="28"/>
+      <c r="BF35" s="28"/>
+      <c r="BG35"/>
+      <c r="BH35" s="27"/>
+      <c r="BI35"/>
+      <c r="BJ35"/>
       <c r="BK35" s="1"/>
       <c r="BL35" s="1"/>
       <c r="BM35" s="1"/>
@@ -3667,9 +4000,10 @@
       <c r="CL35" s="1"/>
     </row>
     <row r="36" spans="3:90">
-      <c r="C36" s="10"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
+      <c r="C36" s="11"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="J36" s="21"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
@@ -3680,6 +4014,7 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
+      <c r="AA36"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AE36" s="1"/>
@@ -3690,8 +4025,11 @@
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
       <c r="AL36" s="1"/>
+      <c r="AM36"/>
       <c r="AR36" s="1"/>
       <c r="AS36" s="1"/>
+      <c r="AT36"/>
+      <c r="AU36"/>
       <c r="AV36" s="1"/>
       <c r="AW36" s="1"/>
       <c r="AX36" s="1"/>
@@ -3701,9 +4039,12 @@
       <c r="BB36" s="1"/>
       <c r="BC36" s="1"/>
       <c r="BD36" s="1"/>
-      <c r="BE36" s="25"/>
-      <c r="BF36" s="25"/>
-      <c r="BH36" s="24"/>
+      <c r="BE36" s="28"/>
+      <c r="BF36" s="28"/>
+      <c r="BG36"/>
+      <c r="BH36" s="27"/>
+      <c r="BI36"/>
+      <c r="BJ36"/>
       <c r="BK36" s="1"/>
       <c r="BL36" s="1"/>
       <c r="BM36" s="1"/>
@@ -3734,9 +4075,10 @@
       <c r="CL36" s="1"/>
     </row>
     <row r="37" spans="3:90">
-      <c r="C37" s="10"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
+      <c r="C37" s="11"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="J37" s="21"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
@@ -3747,6 +4089,7 @@
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
+      <c r="AA37"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AE37" s="1"/>
@@ -3757,8 +4100,11 @@
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
       <c r="AL37" s="1"/>
+      <c r="AM37"/>
       <c r="AR37" s="1"/>
       <c r="AS37" s="1"/>
+      <c r="AT37"/>
+      <c r="AU37"/>
       <c r="AV37" s="1"/>
       <c r="AW37" s="1"/>
       <c r="AX37" s="1"/>
@@ -3768,9 +4114,12 @@
       <c r="BB37" s="1"/>
       <c r="BC37" s="1"/>
       <c r="BD37" s="1"/>
-      <c r="BE37" s="25"/>
-      <c r="BF37" s="25"/>
-      <c r="BH37" s="24"/>
+      <c r="BE37" s="28"/>
+      <c r="BF37" s="28"/>
+      <c r="BG37"/>
+      <c r="BH37" s="27"/>
+      <c r="BI37"/>
+      <c r="BJ37"/>
       <c r="BK37" s="1"/>
       <c r="BL37" s="1"/>
       <c r="BM37" s="1"/>
@@ -3801,9 +4150,19 @@
       <c r="CL37" s="1"/>
     </row>
     <row r="38" spans="3:90">
-      <c r="C38" s="10"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
+      <c r="C38" s="11"/>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38" s="21"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
@@ -3814,6 +4173,7 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
+      <c r="AA38"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AE38" s="1"/>
@@ -3824,8 +4184,11 @@
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
       <c r="AL38" s="1"/>
+      <c r="AM38"/>
       <c r="AR38" s="1"/>
       <c r="AS38" s="1"/>
+      <c r="AT38"/>
+      <c r="AU38"/>
       <c r="AV38" s="1"/>
       <c r="AW38" s="1"/>
       <c r="AX38" s="1"/>
@@ -3835,9 +4198,12 @@
       <c r="BB38" s="1"/>
       <c r="BC38" s="1"/>
       <c r="BD38" s="1"/>
-      <c r="BE38" s="25"/>
-      <c r="BF38" s="25"/>
-      <c r="BH38" s="24"/>
+      <c r="BE38" s="28"/>
+      <c r="BF38" s="28"/>
+      <c r="BG38"/>
+      <c r="BH38" s="27"/>
+      <c r="BI38"/>
+      <c r="BJ38"/>
       <c r="BK38" s="1"/>
       <c r="BL38" s="1"/>
       <c r="BM38" s="1"/>
@@ -3868,9 +4234,19 @@
       <c r="CL38" s="1"/>
     </row>
     <row r="39" spans="3:90">
-      <c r="C39" s="10"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
+      <c r="C39" s="11"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39" s="21"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
@@ -3881,6 +4257,7 @@
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
+      <c r="AA39"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AE39" s="1"/>
@@ -3891,8 +4268,11 @@
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
       <c r="AL39" s="1"/>
+      <c r="AM39"/>
       <c r="AR39" s="1"/>
       <c r="AS39" s="1"/>
+      <c r="AT39"/>
+      <c r="AU39"/>
       <c r="AV39" s="1"/>
       <c r="AW39" s="1"/>
       <c r="AX39" s="1"/>
@@ -3902,9 +4282,12 @@
       <c r="BB39" s="1"/>
       <c r="BC39" s="1"/>
       <c r="BD39" s="1"/>
-      <c r="BE39" s="25"/>
-      <c r="BF39" s="25"/>
-      <c r="BH39" s="24"/>
+      <c r="BE39" s="28"/>
+      <c r="BF39" s="28"/>
+      <c r="BG39"/>
+      <c r="BH39" s="27"/>
+      <c r="BI39"/>
+      <c r="BJ39"/>
       <c r="BK39" s="1"/>
       <c r="BL39" s="1"/>
       <c r="BM39" s="1"/>
@@ -3935,9 +4318,19 @@
       <c r="CL39" s="1"/>
     </row>
     <row r="40" spans="3:90">
-      <c r="C40" s="10"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
+      <c r="C40" s="11"/>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40" s="21"/>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
@@ -3948,6 +4341,7 @@
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
+      <c r="AA40"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AE40" s="1"/>
@@ -3958,8 +4352,11 @@
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
       <c r="AL40" s="1"/>
+      <c r="AM40"/>
       <c r="AR40" s="1"/>
       <c r="AS40" s="1"/>
+      <c r="AT40"/>
+      <c r="AU40"/>
       <c r="AV40" s="1"/>
       <c r="AW40" s="1"/>
       <c r="AX40" s="1"/>
@@ -3969,9 +4366,12 @@
       <c r="BB40" s="1"/>
       <c r="BC40" s="1"/>
       <c r="BD40" s="1"/>
-      <c r="BE40" s="25"/>
-      <c r="BF40" s="25"/>
-      <c r="BH40" s="24"/>
+      <c r="BE40" s="28"/>
+      <c r="BF40" s="28"/>
+      <c r="BG40"/>
+      <c r="BH40" s="27"/>
+      <c r="BI40"/>
+      <c r="BJ40"/>
       <c r="BK40" s="1"/>
       <c r="BL40" s="1"/>
       <c r="BM40" s="1"/>
@@ -4002,9 +4402,10 @@
       <c r="CL40" s="1"/>
     </row>
     <row r="41" spans="3:90">
-      <c r="C41" s="10"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
+      <c r="C41" s="11"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="J41" s="21"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
@@ -4015,6 +4416,7 @@
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
+      <c r="AA41"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AE41" s="1"/>
@@ -4025,8 +4427,11 @@
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
       <c r="AL41" s="1"/>
+      <c r="AM41"/>
       <c r="AR41" s="1"/>
       <c r="AS41" s="1"/>
+      <c r="AT41"/>
+      <c r="AU41"/>
       <c r="AV41" s="1"/>
       <c r="AW41" s="1"/>
       <c r="AX41" s="1"/>
@@ -4036,9 +4441,12 @@
       <c r="BB41" s="1"/>
       <c r="BC41" s="1"/>
       <c r="BD41" s="1"/>
-      <c r="BE41" s="25"/>
-      <c r="BF41" s="25"/>
-      <c r="BH41" s="24"/>
+      <c r="BE41" s="28"/>
+      <c r="BF41" s="28"/>
+      <c r="BG41"/>
+      <c r="BH41" s="27"/>
+      <c r="BI41"/>
+      <c r="BJ41"/>
       <c r="BK41" s="1"/>
       <c r="BL41" s="1"/>
       <c r="BM41" s="1"/>
@@ -4069,9 +4477,19 @@
       <c r="CL41" s="1"/>
     </row>
     <row r="42" spans="3:90">
-      <c r="C42" s="10"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
+      <c r="C42" s="11"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42" s="21"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
@@ -4082,6 +4500,7 @@
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
+      <c r="AA42"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AE42" s="1"/>
@@ -4092,8 +4511,11 @@
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
       <c r="AL42" s="1"/>
+      <c r="AM42"/>
       <c r="AR42" s="1"/>
       <c r="AS42" s="1"/>
+      <c r="AT42"/>
+      <c r="AU42"/>
       <c r="AV42" s="1"/>
       <c r="AW42" s="1"/>
       <c r="AX42" s="1"/>
@@ -4103,9 +4525,12 @@
       <c r="BB42" s="1"/>
       <c r="BC42" s="1"/>
       <c r="BD42" s="1"/>
-      <c r="BE42" s="25"/>
-      <c r="BF42" s="25"/>
-      <c r="BH42" s="24"/>
+      <c r="BE42" s="28"/>
+      <c r="BF42" s="28"/>
+      <c r="BG42"/>
+      <c r="BH42" s="27"/>
+      <c r="BI42"/>
+      <c r="BJ42"/>
       <c r="BK42" s="1"/>
       <c r="BL42" s="1"/>
       <c r="BM42" s="1"/>
@@ -4136,9 +4561,19 @@
       <c r="CL42" s="1"/>
     </row>
     <row r="43" spans="3:90">
-      <c r="C43" s="10"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
+      <c r="C43" s="11"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43" s="21"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
@@ -4149,6 +4584,7 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
+      <c r="AA43"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
       <c r="AE43" s="1"/>
@@ -4159,8 +4595,11 @@
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
       <c r="AL43" s="1"/>
+      <c r="AM43"/>
       <c r="AR43" s="1"/>
       <c r="AS43" s="1"/>
+      <c r="AT43"/>
+      <c r="AU43"/>
       <c r="AV43" s="1"/>
       <c r="AW43" s="1"/>
       <c r="AX43" s="1"/>
@@ -4170,9 +4609,12 @@
       <c r="BB43" s="1"/>
       <c r="BC43" s="1"/>
       <c r="BD43" s="1"/>
-      <c r="BE43" s="25"/>
-      <c r="BF43" s="25"/>
-      <c r="BH43" s="24"/>
+      <c r="BE43" s="28"/>
+      <c r="BF43" s="28"/>
+      <c r="BG43"/>
+      <c r="BH43" s="27"/>
+      <c r="BI43"/>
+      <c r="BJ43"/>
       <c r="BK43" s="1"/>
       <c r="BL43" s="1"/>
       <c r="BM43" s="1"/>
@@ -4203,9 +4645,10 @@
       <c r="CL43" s="1"/>
     </row>
     <row r="44" spans="3:90">
-      <c r="C44" s="10"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
+      <c r="C44" s="11"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="J44" s="21"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
@@ -4216,6 +4659,7 @@
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
+      <c r="AA44"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AE44" s="1"/>
@@ -4226,8 +4670,11 @@
       <c r="AJ44" s="1"/>
       <c r="AK44" s="1"/>
       <c r="AL44" s="1"/>
+      <c r="AM44"/>
       <c r="AR44" s="1"/>
       <c r="AS44" s="1"/>
+      <c r="AT44"/>
+      <c r="AU44"/>
       <c r="AV44" s="1"/>
       <c r="AW44" s="1"/>
       <c r="AX44" s="1"/>
@@ -4237,9 +4684,12 @@
       <c r="BB44" s="1"/>
       <c r="BC44" s="1"/>
       <c r="BD44" s="1"/>
-      <c r="BE44" s="25"/>
-      <c r="BF44" s="25"/>
-      <c r="BH44" s="24"/>
+      <c r="BE44" s="28"/>
+      <c r="BF44" s="28"/>
+      <c r="BG44"/>
+      <c r="BH44" s="27"/>
+      <c r="BI44"/>
+      <c r="BJ44"/>
       <c r="BK44" s="1"/>
       <c r="BL44" s="1"/>
       <c r="BM44" s="1"/>
@@ -4270,9 +4720,19 @@
       <c r="CL44" s="1"/>
     </row>
     <row r="45" spans="3:90">
-      <c r="C45" s="10"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
+      <c r="C45" s="11"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45" s="21"/>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
@@ -4283,6 +4743,7 @@
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
+      <c r="AA45"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
       <c r="AE45" s="1"/>
@@ -4293,8 +4754,11 @@
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
       <c r="AL45" s="1"/>
+      <c r="AM45"/>
       <c r="AR45" s="1"/>
       <c r="AS45" s="1"/>
+      <c r="AT45"/>
+      <c r="AU45"/>
       <c r="AV45" s="1"/>
       <c r="AW45" s="1"/>
       <c r="AX45" s="1"/>
@@ -4304,9 +4768,12 @@
       <c r="BB45" s="1"/>
       <c r="BC45" s="1"/>
       <c r="BD45" s="1"/>
-      <c r="BE45" s="25"/>
-      <c r="BF45" s="25"/>
-      <c r="BH45" s="24"/>
+      <c r="BE45" s="28"/>
+      <c r="BF45" s="28"/>
+      <c r="BG45"/>
+      <c r="BH45" s="27"/>
+      <c r="BI45"/>
+      <c r="BJ45"/>
       <c r="BK45" s="1"/>
       <c r="BL45" s="1"/>
       <c r="BM45" s="1"/>
@@ -4337,9 +4804,19 @@
       <c r="CL45" s="1"/>
     </row>
     <row r="46" spans="3:90">
-      <c r="C46" s="10"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
+      <c r="C46" s="11"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46" s="21"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
@@ -4350,6 +4827,7 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
+      <c r="AA46"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
       <c r="AE46" s="1"/>
@@ -4360,8 +4838,11 @@
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
       <c r="AL46" s="1"/>
+      <c r="AM46"/>
       <c r="AR46" s="1"/>
       <c r="AS46" s="1"/>
+      <c r="AT46"/>
+      <c r="AU46"/>
       <c r="AV46" s="1"/>
       <c r="AW46" s="1"/>
       <c r="AX46" s="1"/>
@@ -4371,9 +4852,12 @@
       <c r="BB46" s="1"/>
       <c r="BC46" s="1"/>
       <c r="BD46" s="1"/>
-      <c r="BE46" s="25"/>
-      <c r="BF46" s="25"/>
-      <c r="BH46" s="24"/>
+      <c r="BE46" s="28"/>
+      <c r="BF46" s="28"/>
+      <c r="BG46"/>
+      <c r="BH46" s="27"/>
+      <c r="BI46"/>
+      <c r="BJ46"/>
       <c r="BK46" s="1"/>
       <c r="BL46" s="1"/>
       <c r="BM46" s="1"/>
@@ -4404,9 +4888,19 @@
       <c r="CL46" s="1"/>
     </row>
     <row r="47" spans="3:90">
-      <c r="C47" s="10"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
+      <c r="C47" s="11"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47" s="21"/>
+      <c r="K47"/>
+      <c r="L47"/>
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="O47"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
@@ -4417,6 +4911,7 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
+      <c r="AA47"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
       <c r="AE47" s="1"/>
@@ -4427,8 +4922,11 @@
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
       <c r="AL47" s="1"/>
+      <c r="AM47"/>
       <c r="AR47" s="1"/>
       <c r="AS47" s="1"/>
+      <c r="AT47"/>
+      <c r="AU47"/>
       <c r="AV47" s="1"/>
       <c r="AW47" s="1"/>
       <c r="AX47" s="1"/>
@@ -4438,9 +4936,12 @@
       <c r="BB47" s="1"/>
       <c r="BC47" s="1"/>
       <c r="BD47" s="1"/>
-      <c r="BE47" s="25"/>
-      <c r="BF47" s="25"/>
-      <c r="BH47" s="24"/>
+      <c r="BE47" s="28"/>
+      <c r="BF47" s="28"/>
+      <c r="BG47"/>
+      <c r="BH47" s="27"/>
+      <c r="BI47"/>
+      <c r="BJ47"/>
       <c r="BK47" s="1"/>
       <c r="BL47" s="1"/>
       <c r="BM47" s="1"/>
@@ -4471,9 +4972,19 @@
       <c r="CL47" s="1"/>
     </row>
     <row r="48" spans="3:90">
-      <c r="C48" s="10"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
+      <c r="C48" s="11"/>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48"/>
+      <c r="I48"/>
+      <c r="J48" s="21"/>
+      <c r="K48"/>
+      <c r="L48"/>
+      <c r="M48"/>
+      <c r="N48"/>
+      <c r="O48"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
@@ -4484,6 +4995,7 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
+      <c r="AA48"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AE48" s="1"/>
@@ -4494,8 +5006,11 @@
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
       <c r="AL48" s="1"/>
+      <c r="AM48"/>
       <c r="AR48" s="1"/>
       <c r="AS48" s="1"/>
+      <c r="AT48"/>
+      <c r="AU48"/>
       <c r="AV48" s="1"/>
       <c r="AW48" s="1"/>
       <c r="AX48" s="1"/>
@@ -4505,9 +5020,12 @@
       <c r="BB48" s="1"/>
       <c r="BC48" s="1"/>
       <c r="BD48" s="1"/>
-      <c r="BE48" s="25"/>
-      <c r="BF48" s="25"/>
-      <c r="BH48" s="24"/>
+      <c r="BE48" s="28"/>
+      <c r="BF48" s="28"/>
+      <c r="BG48"/>
+      <c r="BH48" s="27"/>
+      <c r="BI48"/>
+      <c r="BJ48"/>
       <c r="BK48" s="1"/>
       <c r="BL48" s="1"/>
       <c r="BM48" s="1"/>
@@ -4538,9 +5056,19 @@
       <c r="CL48" s="1"/>
     </row>
     <row r="49" spans="3:90">
-      <c r="C49" s="10"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
+      <c r="C49" s="11"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49" s="21"/>
+      <c r="K49"/>
+      <c r="L49"/>
+      <c r="M49"/>
+      <c r="N49"/>
+      <c r="O49"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
@@ -4551,6 +5079,7 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
+      <c r="AA49"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AE49" s="1"/>
@@ -4561,8 +5090,11 @@
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
       <c r="AL49" s="1"/>
+      <c r="AM49"/>
       <c r="AR49" s="1"/>
       <c r="AS49" s="1"/>
+      <c r="AT49"/>
+      <c r="AU49"/>
       <c r="AV49" s="1"/>
       <c r="AW49" s="1"/>
       <c r="AX49" s="1"/>
@@ -4572,9 +5104,12 @@
       <c r="BB49" s="1"/>
       <c r="BC49" s="1"/>
       <c r="BD49" s="1"/>
-      <c r="BE49" s="25"/>
-      <c r="BF49" s="25"/>
-      <c r="BH49" s="24"/>
+      <c r="BE49" s="28"/>
+      <c r="BF49" s="28"/>
+      <c r="BG49"/>
+      <c r="BH49" s="27"/>
+      <c r="BI49"/>
+      <c r="BJ49"/>
       <c r="BK49" s="1"/>
       <c r="BL49" s="1"/>
       <c r="BM49" s="1"/>
@@ -4605,9 +5140,10 @@
       <c r="CL49" s="1"/>
     </row>
     <row r="50" spans="3:90">
-      <c r="C50" s="10"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
+      <c r="C50" s="11"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="J50" s="21"/>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
@@ -4618,6 +5154,7 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
+      <c r="AA50"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
       <c r="AE50" s="1"/>
@@ -4628,8 +5165,11 @@
       <c r="AJ50" s="1"/>
       <c r="AK50" s="1"/>
       <c r="AL50" s="1"/>
+      <c r="AM50"/>
       <c r="AR50" s="1"/>
       <c r="AS50" s="1"/>
+      <c r="AT50"/>
+      <c r="AU50"/>
       <c r="AV50" s="1"/>
       <c r="AW50" s="1"/>
       <c r="AX50" s="1"/>
@@ -4639,9 +5179,12 @@
       <c r="BB50" s="1"/>
       <c r="BC50" s="1"/>
       <c r="BD50" s="1"/>
-      <c r="BE50" s="25"/>
-      <c r="BF50" s="25"/>
-      <c r="BH50" s="24"/>
+      <c r="BE50" s="28"/>
+      <c r="BF50" s="28"/>
+      <c r="BG50"/>
+      <c r="BH50" s="27"/>
+      <c r="BI50"/>
+      <c r="BJ50"/>
       <c r="BK50" s="1"/>
       <c r="BL50" s="1"/>
       <c r="BM50" s="1"/>
@@ -4672,9 +5215,19 @@
       <c r="CL50" s="1"/>
     </row>
     <row r="51" spans="3:90">
-      <c r="C51" s="10"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
+      <c r="C51" s="11"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51" s="21"/>
+      <c r="K51"/>
+      <c r="L51"/>
+      <c r="M51"/>
+      <c r="N51"/>
+      <c r="O51"/>
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
@@ -4685,6 +5238,7 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
+      <c r="AA51"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AE51" s="1"/>
@@ -4695,8 +5249,11 @@
       <c r="AJ51" s="1"/>
       <c r="AK51" s="1"/>
       <c r="AL51" s="1"/>
+      <c r="AM51"/>
       <c r="AR51" s="1"/>
       <c r="AS51" s="1"/>
+      <c r="AT51"/>
+      <c r="AU51"/>
       <c r="AV51" s="1"/>
       <c r="AW51" s="1"/>
       <c r="AX51" s="1"/>
@@ -4706,9 +5263,12 @@
       <c r="BB51" s="1"/>
       <c r="BC51" s="1"/>
       <c r="BD51" s="1"/>
-      <c r="BE51" s="25"/>
-      <c r="BF51" s="25"/>
-      <c r="BH51" s="24"/>
+      <c r="BE51" s="28"/>
+      <c r="BF51" s="28"/>
+      <c r="BG51"/>
+      <c r="BH51" s="27"/>
+      <c r="BI51"/>
+      <c r="BJ51"/>
       <c r="BK51" s="1"/>
       <c r="BL51" s="1"/>
       <c r="BM51" s="1"/>
@@ -4739,9 +5299,19 @@
       <c r="CL51" s="1"/>
     </row>
     <row r="52" spans="3:90">
-      <c r="C52" s="10"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
+      <c r="C52" s="11"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52" s="21"/>
+      <c r="K52"/>
+      <c r="L52"/>
+      <c r="M52"/>
+      <c r="N52"/>
+      <c r="O52"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
@@ -4752,6 +5322,7 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
+      <c r="AA52"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AE52" s="1"/>
@@ -4762,8 +5333,11 @@
       <c r="AJ52" s="1"/>
       <c r="AK52" s="1"/>
       <c r="AL52" s="1"/>
+      <c r="AM52"/>
       <c r="AR52" s="1"/>
       <c r="AS52" s="1"/>
+      <c r="AT52"/>
+      <c r="AU52"/>
       <c r="AV52" s="1"/>
       <c r="AW52" s="1"/>
       <c r="AX52" s="1"/>
@@ -4773,9 +5347,12 @@
       <c r="BB52" s="1"/>
       <c r="BC52" s="1"/>
       <c r="BD52" s="1"/>
-      <c r="BE52" s="25"/>
-      <c r="BF52" s="25"/>
-      <c r="BH52" s="24"/>
+      <c r="BE52" s="28"/>
+      <c r="BF52" s="28"/>
+      <c r="BG52"/>
+      <c r="BH52" s="27"/>
+      <c r="BI52"/>
+      <c r="BJ52"/>
       <c r="BK52" s="1"/>
       <c r="BL52" s="1"/>
       <c r="BM52" s="1"/>
@@ -4806,9 +5383,19 @@
       <c r="CL52" s="1"/>
     </row>
     <row r="53" spans="3:90">
-      <c r="C53" s="10"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
+      <c r="C53" s="11"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53" s="21"/>
+      <c r="K53"/>
+      <c r="L53"/>
+      <c r="M53"/>
+      <c r="N53"/>
+      <c r="O53"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
@@ -4819,6 +5406,7 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
+      <c r="AA53"/>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
       <c r="AE53" s="1"/>
@@ -4829,8 +5417,11 @@
       <c r="AJ53" s="1"/>
       <c r="AK53" s="1"/>
       <c r="AL53" s="1"/>
+      <c r="AM53"/>
       <c r="AR53" s="1"/>
       <c r="AS53" s="1"/>
+      <c r="AT53"/>
+      <c r="AU53"/>
       <c r="AV53" s="1"/>
       <c r="AW53" s="1"/>
       <c r="AX53" s="1"/>
@@ -4840,9 +5431,12 @@
       <c r="BB53" s="1"/>
       <c r="BC53" s="1"/>
       <c r="BD53" s="1"/>
-      <c r="BE53" s="25"/>
-      <c r="BF53" s="25"/>
-      <c r="BH53" s="24"/>
+      <c r="BE53" s="28"/>
+      <c r="BF53" s="28"/>
+      <c r="BG53"/>
+      <c r="BH53" s="27"/>
+      <c r="BI53"/>
+      <c r="BJ53"/>
       <c r="BK53" s="1"/>
       <c r="BL53" s="1"/>
       <c r="BM53" s="1"/>
@@ -4873,9 +5467,19 @@
       <c r="CL53" s="1"/>
     </row>
     <row r="54" spans="3:90">
-      <c r="C54" s="10"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
+      <c r="C54" s="11"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54" s="21"/>
+      <c r="K54"/>
+      <c r="L54"/>
+      <c r="M54"/>
+      <c r="N54"/>
+      <c r="O54"/>
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
@@ -4886,6 +5490,7 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
+      <c r="AA54"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AE54" s="1"/>
@@ -4896,8 +5501,11 @@
       <c r="AJ54" s="1"/>
       <c r="AK54" s="1"/>
       <c r="AL54" s="1"/>
+      <c r="AM54"/>
       <c r="AR54" s="1"/>
       <c r="AS54" s="1"/>
+      <c r="AT54"/>
+      <c r="AU54"/>
       <c r="AV54" s="1"/>
       <c r="AW54" s="1"/>
       <c r="AX54" s="1"/>
@@ -4907,9 +5515,12 @@
       <c r="BB54" s="1"/>
       <c r="BC54" s="1"/>
       <c r="BD54" s="1"/>
-      <c r="BE54" s="25"/>
-      <c r="BF54" s="25"/>
-      <c r="BH54" s="24"/>
+      <c r="BE54" s="28"/>
+      <c r="BF54" s="28"/>
+      <c r="BG54"/>
+      <c r="BH54" s="27"/>
+      <c r="BI54"/>
+      <c r="BJ54"/>
       <c r="BK54" s="1"/>
       <c r="BL54" s="1"/>
       <c r="BM54" s="1"/>
@@ -4940,9 +5551,19 @@
       <c r="CL54" s="1"/>
     </row>
     <row r="55" spans="3:90">
-      <c r="C55" s="10"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
+      <c r="C55" s="11"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55" s="21"/>
+      <c r="K55"/>
+      <c r="L55"/>
+      <c r="M55"/>
+      <c r="N55"/>
+      <c r="O55"/>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
@@ -4953,6 +5574,7 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
+      <c r="AA55"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AE55" s="1"/>
@@ -4963,8 +5585,11 @@
       <c r="AJ55" s="1"/>
       <c r="AK55" s="1"/>
       <c r="AL55" s="1"/>
+      <c r="AM55"/>
       <c r="AR55" s="1"/>
       <c r="AS55" s="1"/>
+      <c r="AT55"/>
+      <c r="AU55"/>
       <c r="AV55" s="1"/>
       <c r="AW55" s="1"/>
       <c r="AX55" s="1"/>
@@ -4974,9 +5599,12 @@
       <c r="BB55" s="1"/>
       <c r="BC55" s="1"/>
       <c r="BD55" s="1"/>
-      <c r="BE55" s="25"/>
-      <c r="BF55" s="25"/>
-      <c r="BH55" s="24"/>
+      <c r="BE55" s="28"/>
+      <c r="BF55" s="28"/>
+      <c r="BG55"/>
+      <c r="BH55" s="27"/>
+      <c r="BI55"/>
+      <c r="BJ55"/>
       <c r="BK55" s="1"/>
       <c r="BL55" s="1"/>
       <c r="BM55" s="1"/>
@@ -5007,9 +5635,19 @@
       <c r="CL55" s="1"/>
     </row>
     <row r="56" spans="3:90">
-      <c r="C56" s="10"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
+      <c r="C56" s="11"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56" s="21"/>
+      <c r="K56"/>
+      <c r="L56"/>
+      <c r="M56"/>
+      <c r="N56"/>
+      <c r="O56"/>
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
@@ -5020,6 +5658,7 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
+      <c r="AA56"/>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
       <c r="AE56" s="1"/>
@@ -5030,8 +5669,11 @@
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
       <c r="AL56" s="1"/>
+      <c r="AM56"/>
       <c r="AR56" s="1"/>
       <c r="AS56" s="1"/>
+      <c r="AT56"/>
+      <c r="AU56"/>
       <c r="AV56" s="1"/>
       <c r="AW56" s="1"/>
       <c r="AX56" s="1"/>
@@ -5041,9 +5683,12 @@
       <c r="BB56" s="1"/>
       <c r="BC56" s="1"/>
       <c r="BD56" s="1"/>
-      <c r="BE56" s="25"/>
-      <c r="BF56" s="25"/>
-      <c r="BH56" s="24"/>
+      <c r="BE56" s="28"/>
+      <c r="BF56" s="28"/>
+      <c r="BG56"/>
+      <c r="BH56" s="27"/>
+      <c r="BI56"/>
+      <c r="BJ56"/>
       <c r="BK56" s="1"/>
       <c r="BL56" s="1"/>
       <c r="BM56" s="1"/>
@@ -5074,9 +5719,10 @@
       <c r="CL56" s="1"/>
     </row>
     <row r="57" spans="3:90">
-      <c r="C57" s="10"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
+      <c r="C57" s="11"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="J57" s="21"/>
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
@@ -5087,6 +5733,7 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
+      <c r="AA57"/>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
       <c r="AE57" s="1"/>
@@ -5097,8 +5744,11 @@
       <c r="AJ57" s="1"/>
       <c r="AK57" s="1"/>
       <c r="AL57" s="1"/>
+      <c r="AM57"/>
       <c r="AR57" s="1"/>
       <c r="AS57" s="1"/>
+      <c r="AT57"/>
+      <c r="AU57"/>
       <c r="AV57" s="1"/>
       <c r="AW57" s="1"/>
       <c r="AX57" s="1"/>
@@ -5108,9 +5758,12 @@
       <c r="BB57" s="1"/>
       <c r="BC57" s="1"/>
       <c r="BD57" s="1"/>
-      <c r="BE57" s="25"/>
-      <c r="BF57" s="25"/>
-      <c r="BH57" s="24"/>
+      <c r="BE57" s="28"/>
+      <c r="BF57" s="28"/>
+      <c r="BG57"/>
+      <c r="BH57" s="27"/>
+      <c r="BI57"/>
+      <c r="BJ57"/>
       <c r="BK57" s="1"/>
       <c r="BL57" s="1"/>
       <c r="BM57" s="1"/>
@@ -5141,9 +5794,19 @@
       <c r="CL57" s="1"/>
     </row>
     <row r="58" spans="3:90">
-      <c r="C58" s="10"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
+      <c r="C58" s="11"/>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58"/>
+      <c r="I58"/>
+      <c r="J58" s="21"/>
+      <c r="K58"/>
+      <c r="L58"/>
+      <c r="M58"/>
+      <c r="N58"/>
+      <c r="O58"/>
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
@@ -5154,6 +5817,7 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
+      <c r="AA58"/>
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
       <c r="AE58" s="1"/>
@@ -5164,8 +5828,11 @@
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
       <c r="AL58" s="1"/>
+      <c r="AM58"/>
       <c r="AR58" s="1"/>
       <c r="AS58" s="1"/>
+      <c r="AT58"/>
+      <c r="AU58"/>
       <c r="AV58" s="1"/>
       <c r="AW58" s="1"/>
       <c r="AX58" s="1"/>
@@ -5175,9 +5842,12 @@
       <c r="BB58" s="1"/>
       <c r="BC58" s="1"/>
       <c r="BD58" s="1"/>
-      <c r="BE58" s="25"/>
-      <c r="BF58" s="25"/>
-      <c r="BH58" s="24"/>
+      <c r="BE58" s="28"/>
+      <c r="BF58" s="28"/>
+      <c r="BG58"/>
+      <c r="BH58" s="27"/>
+      <c r="BI58"/>
+      <c r="BJ58"/>
       <c r="BK58" s="1"/>
       <c r="BL58" s="1"/>
       <c r="BM58" s="1"/>
@@ -5208,9 +5878,19 @@
       <c r="CL58" s="1"/>
     </row>
     <row r="59" spans="3:90">
-      <c r="C59" s="10"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
+      <c r="C59" s="11"/>
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59" s="21"/>
+      <c r="K59"/>
+      <c r="L59"/>
+      <c r="M59"/>
+      <c r="N59"/>
+      <c r="O59"/>
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
@@ -5221,6 +5901,7 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
+      <c r="AA59"/>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
       <c r="AE59" s="1"/>
@@ -5231,8 +5912,11 @@
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
       <c r="AL59" s="1"/>
+      <c r="AM59"/>
       <c r="AR59" s="1"/>
       <c r="AS59" s="1"/>
+      <c r="AT59"/>
+      <c r="AU59"/>
       <c r="AV59" s="1"/>
       <c r="AW59" s="1"/>
       <c r="AX59" s="1"/>
@@ -5242,9 +5926,12 @@
       <c r="BB59" s="1"/>
       <c r="BC59" s="1"/>
       <c r="BD59" s="1"/>
-      <c r="BE59" s="25"/>
-      <c r="BF59" s="25"/>
-      <c r="BH59" s="24"/>
+      <c r="BE59" s="28"/>
+      <c r="BF59" s="28"/>
+      <c r="BG59"/>
+      <c r="BH59" s="27"/>
+      <c r="BI59"/>
+      <c r="BJ59"/>
       <c r="BK59" s="1"/>
       <c r="BL59" s="1"/>
       <c r="BM59" s="1"/>
@@ -5275,9 +5962,19 @@
       <c r="CL59" s="1"/>
     </row>
     <row r="60" spans="3:90">
-      <c r="C60" s="10"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
+      <c r="C60" s="11"/>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60"/>
+      <c r="I60"/>
+      <c r="J60" s="21"/>
+      <c r="K60"/>
+      <c r="L60"/>
+      <c r="M60"/>
+      <c r="N60"/>
+      <c r="O60"/>
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
@@ -5288,6 +5985,7 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
+      <c r="AA60"/>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
       <c r="AE60" s="1"/>
@@ -5298,8 +5996,11 @@
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
       <c r="AL60" s="1"/>
+      <c r="AM60"/>
       <c r="AR60" s="1"/>
       <c r="AS60" s="1"/>
+      <c r="AT60"/>
+      <c r="AU60"/>
       <c r="AV60" s="1"/>
       <c r="AW60" s="1"/>
       <c r="AX60" s="1"/>
@@ -5309,9 +6010,12 @@
       <c r="BB60" s="1"/>
       <c r="BC60" s="1"/>
       <c r="BD60" s="1"/>
-      <c r="BE60" s="25"/>
-      <c r="BF60" s="25"/>
-      <c r="BH60" s="24"/>
+      <c r="BE60" s="28"/>
+      <c r="BF60" s="28"/>
+      <c r="BG60"/>
+      <c r="BH60" s="27"/>
+      <c r="BI60"/>
+      <c r="BJ60"/>
       <c r="BK60" s="1"/>
       <c r="BL60" s="1"/>
       <c r="BM60" s="1"/>
@@ -5342,9 +6046,19 @@
       <c r="CL60" s="1"/>
     </row>
     <row r="61" spans="3:90">
-      <c r="C61" s="10"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
+      <c r="C61" s="11"/>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61" s="21"/>
+      <c r="K61"/>
+      <c r="L61"/>
+      <c r="M61"/>
+      <c r="N61"/>
+      <c r="O61"/>
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
@@ -5355,6 +6069,7 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
+      <c r="AA61"/>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
       <c r="AE61" s="1"/>
@@ -5365,8 +6080,11 @@
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
       <c r="AL61" s="1"/>
+      <c r="AM61"/>
       <c r="AR61" s="1"/>
       <c r="AS61" s="1"/>
+      <c r="AT61"/>
+      <c r="AU61"/>
       <c r="AV61" s="1"/>
       <c r="AW61" s="1"/>
       <c r="AX61" s="1"/>
@@ -5376,9 +6094,12 @@
       <c r="BB61" s="1"/>
       <c r="BC61" s="1"/>
       <c r="BD61" s="1"/>
-      <c r="BE61" s="25"/>
-      <c r="BF61" s="25"/>
-      <c r="BH61" s="24"/>
+      <c r="BE61" s="28"/>
+      <c r="BF61" s="28"/>
+      <c r="BG61"/>
+      <c r="BH61" s="27"/>
+      <c r="BI61"/>
+      <c r="BJ61"/>
       <c r="BK61" s="1"/>
       <c r="BL61" s="1"/>
       <c r="BM61" s="1"/>
@@ -5409,9 +6130,19 @@
       <c r="CL61" s="1"/>
     </row>
     <row r="62" spans="3:90">
-      <c r="C62" s="10"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
+      <c r="C62" s="11"/>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62"/>
+      <c r="I62"/>
+      <c r="J62" s="21"/>
+      <c r="K62"/>
+      <c r="L62"/>
+      <c r="M62"/>
+      <c r="N62"/>
+      <c r="O62"/>
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
@@ -5422,6 +6153,7 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
+      <c r="AA62"/>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
       <c r="AE62" s="1"/>
@@ -5432,8 +6164,11 @@
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
       <c r="AL62" s="1"/>
+      <c r="AM62"/>
       <c r="AR62" s="1"/>
       <c r="AS62" s="1"/>
+      <c r="AT62"/>
+      <c r="AU62"/>
       <c r="AV62" s="1"/>
       <c r="AW62" s="1"/>
       <c r="AX62" s="1"/>
@@ -5443,9 +6178,12 @@
       <c r="BB62" s="1"/>
       <c r="BC62" s="1"/>
       <c r="BD62" s="1"/>
-      <c r="BE62" s="25"/>
-      <c r="BF62" s="25"/>
-      <c r="BH62" s="24"/>
+      <c r="BE62" s="28"/>
+      <c r="BF62" s="28"/>
+      <c r="BG62"/>
+      <c r="BH62" s="27"/>
+      <c r="BI62"/>
+      <c r="BJ62"/>
       <c r="BK62" s="1"/>
       <c r="BL62" s="1"/>
       <c r="BM62" s="1"/>
@@ -5476,9 +6214,19 @@
       <c r="CL62" s="1"/>
     </row>
     <row r="63" spans="3:90">
-      <c r="C63" s="10"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
+      <c r="C63" s="11"/>
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63"/>
+      <c r="I63"/>
+      <c r="J63" s="21"/>
+      <c r="K63"/>
+      <c r="L63"/>
+      <c r="M63"/>
+      <c r="N63"/>
+      <c r="O63"/>
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
@@ -5489,6 +6237,7 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
+      <c r="AA63"/>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
       <c r="AE63" s="1"/>
@@ -5499,8 +6248,11 @@
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
       <c r="AL63" s="1"/>
+      <c r="AM63"/>
       <c r="AR63" s="1"/>
       <c r="AS63" s="1"/>
+      <c r="AT63"/>
+      <c r="AU63"/>
       <c r="AV63" s="1"/>
       <c r="AW63" s="1"/>
       <c r="AX63" s="1"/>
@@ -5510,9 +6262,12 @@
       <c r="BB63" s="1"/>
       <c r="BC63" s="1"/>
       <c r="BD63" s="1"/>
-      <c r="BE63" s="25"/>
-      <c r="BF63" s="25"/>
-      <c r="BH63" s="24"/>
+      <c r="BE63" s="28"/>
+      <c r="BF63" s="28"/>
+      <c r="BG63"/>
+      <c r="BH63" s="27"/>
+      <c r="BI63"/>
+      <c r="BJ63"/>
       <c r="BK63" s="1"/>
       <c r="BL63" s="1"/>
       <c r="BM63" s="1"/>
@@ -5543,9 +6298,19 @@
       <c r="CL63" s="1"/>
     </row>
     <row r="64" spans="3:90">
-      <c r="C64" s="10"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
+      <c r="C64" s="11"/>
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
+      <c r="H64"/>
+      <c r="I64"/>
+      <c r="J64" s="21"/>
+      <c r="K64"/>
+      <c r="L64"/>
+      <c r="M64"/>
+      <c r="N64"/>
+      <c r="O64"/>
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
@@ -5556,6 +6321,7 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
+      <c r="AA64"/>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
       <c r="AE64" s="1"/>
@@ -5566,8 +6332,11 @@
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
       <c r="AL64" s="1"/>
+      <c r="AM64"/>
       <c r="AR64" s="1"/>
       <c r="AS64" s="1"/>
+      <c r="AT64"/>
+      <c r="AU64"/>
       <c r="AV64" s="1"/>
       <c r="AW64" s="1"/>
       <c r="AX64" s="1"/>
@@ -5577,9 +6346,12 @@
       <c r="BB64" s="1"/>
       <c r="BC64" s="1"/>
       <c r="BD64" s="1"/>
-      <c r="BE64" s="25"/>
-      <c r="BF64" s="25"/>
-      <c r="BH64" s="24"/>
+      <c r="BE64" s="28"/>
+      <c r="BF64" s="28"/>
+      <c r="BG64"/>
+      <c r="BH64" s="27"/>
+      <c r="BI64"/>
+      <c r="BJ64"/>
       <c r="BK64" s="1"/>
       <c r="BL64" s="1"/>
       <c r="BM64" s="1"/>
@@ -5610,9 +6382,19 @@
       <c r="CL64" s="1"/>
     </row>
     <row r="65" spans="3:90">
-      <c r="C65" s="10"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
+      <c r="C65" s="11"/>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65"/>
+      <c r="I65"/>
+      <c r="J65" s="21"/>
+      <c r="K65"/>
+      <c r="L65"/>
+      <c r="M65"/>
+      <c r="N65"/>
+      <c r="O65"/>
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
@@ -5623,6 +6405,7 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
+      <c r="AA65"/>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
       <c r="AE65" s="1"/>
@@ -5633,8 +6416,11 @@
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
       <c r="AL65" s="1"/>
+      <c r="AM65"/>
       <c r="AR65" s="1"/>
       <c r="AS65" s="1"/>
+      <c r="AT65"/>
+      <c r="AU65"/>
       <c r="AV65" s="1"/>
       <c r="AW65" s="1"/>
       <c r="AX65" s="1"/>
@@ -5644,9 +6430,12 @@
       <c r="BB65" s="1"/>
       <c r="BC65" s="1"/>
       <c r="BD65" s="1"/>
-      <c r="BE65" s="25"/>
-      <c r="BF65" s="25"/>
-      <c r="BH65" s="24"/>
+      <c r="BE65" s="28"/>
+      <c r="BF65" s="28"/>
+      <c r="BG65"/>
+      <c r="BH65" s="27"/>
+      <c r="BI65"/>
+      <c r="BJ65"/>
       <c r="BK65" s="1"/>
       <c r="BL65" s="1"/>
       <c r="BM65" s="1"/>
@@ -5677,9 +6466,10 @@
       <c r="CL65" s="1"/>
     </row>
     <row r="66" spans="3:90">
-      <c r="C66" s="10"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
+      <c r="C66" s="11"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="J66" s="21"/>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
@@ -5690,6 +6480,7 @@
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
+      <c r="AA66"/>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
       <c r="AE66" s="1"/>
@@ -5700,8 +6491,11 @@
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
       <c r="AL66" s="1"/>
+      <c r="AM66"/>
       <c r="AR66" s="1"/>
       <c r="AS66" s="1"/>
+      <c r="AT66"/>
+      <c r="AU66"/>
       <c r="AV66" s="1"/>
       <c r="AW66" s="1"/>
       <c r="AX66" s="1"/>
@@ -5711,9 +6505,12 @@
       <c r="BB66" s="1"/>
       <c r="BC66" s="1"/>
       <c r="BD66" s="1"/>
-      <c r="BE66" s="25"/>
-      <c r="BF66" s="25"/>
-      <c r="BH66" s="24"/>
+      <c r="BE66" s="28"/>
+      <c r="BF66" s="28"/>
+      <c r="BG66"/>
+      <c r="BH66" s="27"/>
+      <c r="BI66"/>
+      <c r="BJ66"/>
       <c r="BK66" s="1"/>
       <c r="BL66" s="1"/>
       <c r="BM66" s="1"/>
@@ -5744,9 +6541,19 @@
       <c r="CL66" s="1"/>
     </row>
     <row r="67" spans="3:90">
-      <c r="C67" s="10"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
+      <c r="C67" s="11"/>
+      <c r="D67"/>
+      <c r="E67"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67"/>
+      <c r="I67"/>
+      <c r="J67" s="21"/>
+      <c r="K67"/>
+      <c r="L67"/>
+      <c r="M67"/>
+      <c r="N67"/>
+      <c r="O67"/>
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
@@ -5757,6 +6564,7 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
+      <c r="AA67"/>
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
       <c r="AE67" s="1"/>
@@ -5767,8 +6575,11 @@
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
       <c r="AL67" s="1"/>
+      <c r="AM67"/>
       <c r="AR67" s="1"/>
       <c r="AS67" s="1"/>
+      <c r="AT67"/>
+      <c r="AU67"/>
       <c r="AV67" s="1"/>
       <c r="AW67" s="1"/>
       <c r="AX67" s="1"/>
@@ -5778,9 +6589,12 @@
       <c r="BB67" s="1"/>
       <c r="BC67" s="1"/>
       <c r="BD67" s="1"/>
-      <c r="BE67" s="25"/>
-      <c r="BF67" s="25"/>
-      <c r="BH67" s="24"/>
+      <c r="BE67" s="28"/>
+      <c r="BF67" s="28"/>
+      <c r="BG67"/>
+      <c r="BH67" s="27"/>
+      <c r="BI67"/>
+      <c r="BJ67"/>
       <c r="BK67" s="1"/>
       <c r="BL67" s="1"/>
       <c r="BM67" s="1"/>
@@ -5811,9 +6625,19 @@
       <c r="CL67" s="1"/>
     </row>
     <row r="68" spans="3:90">
-      <c r="C68" s="10"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
+      <c r="C68" s="11"/>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68"/>
+      <c r="I68"/>
+      <c r="J68" s="21"/>
+      <c r="K68"/>
+      <c r="L68"/>
+      <c r="M68"/>
+      <c r="N68"/>
+      <c r="O68"/>
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
       <c r="S68" s="1"/>
@@ -5824,6 +6648,7 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
+      <c r="AA68"/>
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
       <c r="AE68" s="1"/>
@@ -5834,8 +6659,11 @@
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
       <c r="AL68" s="1"/>
+      <c r="AM68"/>
       <c r="AR68" s="1"/>
       <c r="AS68" s="1"/>
+      <c r="AT68"/>
+      <c r="AU68"/>
       <c r="AV68" s="1"/>
       <c r="AW68" s="1"/>
       <c r="AX68" s="1"/>
@@ -5845,9 +6673,12 @@
       <c r="BB68" s="1"/>
       <c r="BC68" s="1"/>
       <c r="BD68" s="1"/>
-      <c r="BE68" s="25"/>
-      <c r="BF68" s="25"/>
-      <c r="BH68" s="24"/>
+      <c r="BE68" s="28"/>
+      <c r="BF68" s="28"/>
+      <c r="BG68"/>
+      <c r="BH68" s="27"/>
+      <c r="BI68"/>
+      <c r="BJ68"/>
       <c r="BK68" s="1"/>
       <c r="BL68" s="1"/>
       <c r="BM68" s="1"/>
@@ -5878,9 +6709,19 @@
       <c r="CL68" s="1"/>
     </row>
     <row r="69" spans="3:90">
-      <c r="C69" s="10"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
+      <c r="C69" s="11"/>
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69"/>
+      <c r="I69"/>
+      <c r="J69" s="21"/>
+      <c r="K69"/>
+      <c r="L69"/>
+      <c r="M69"/>
+      <c r="N69"/>
+      <c r="O69"/>
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
@@ -5891,6 +6732,7 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
+      <c r="AA69"/>
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
       <c r="AE69" s="1"/>
@@ -5901,8 +6743,11 @@
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
       <c r="AL69" s="1"/>
+      <c r="AM69"/>
       <c r="AR69" s="1"/>
       <c r="AS69" s="1"/>
+      <c r="AT69"/>
+      <c r="AU69"/>
       <c r="AV69" s="1"/>
       <c r="AW69" s="1"/>
       <c r="AX69" s="1"/>
@@ -5912,9 +6757,12 @@
       <c r="BB69" s="1"/>
       <c r="BC69" s="1"/>
       <c r="BD69" s="1"/>
-      <c r="BE69" s="25"/>
-      <c r="BF69" s="25"/>
-      <c r="BH69" s="24"/>
+      <c r="BE69" s="28"/>
+      <c r="BF69" s="28"/>
+      <c r="BG69"/>
+      <c r="BH69" s="27"/>
+      <c r="BI69"/>
+      <c r="BJ69"/>
       <c r="BK69" s="1"/>
       <c r="BL69" s="1"/>
       <c r="BM69" s="1"/>
@@ -5945,9 +6793,19 @@
       <c r="CL69" s="1"/>
     </row>
     <row r="70" spans="3:90">
-      <c r="C70" s="10"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
+      <c r="C70" s="11"/>
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70"/>
+      <c r="I70"/>
+      <c r="J70" s="21"/>
+      <c r="K70"/>
+      <c r="L70"/>
+      <c r="M70"/>
+      <c r="N70"/>
+      <c r="O70"/>
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
@@ -5958,6 +6816,7 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
+      <c r="AA70"/>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
       <c r="AE70" s="1"/>
@@ -5968,8 +6827,11 @@
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
       <c r="AL70" s="1"/>
+      <c r="AM70"/>
       <c r="AR70" s="1"/>
       <c r="AS70" s="1"/>
+      <c r="AT70"/>
+      <c r="AU70"/>
       <c r="AV70" s="1"/>
       <c r="AW70" s="1"/>
       <c r="AX70" s="1"/>
@@ -5979,9 +6841,12 @@
       <c r="BB70" s="1"/>
       <c r="BC70" s="1"/>
       <c r="BD70" s="1"/>
-      <c r="BE70" s="25"/>
-      <c r="BF70" s="25"/>
-      <c r="BH70" s="24"/>
+      <c r="BE70" s="28"/>
+      <c r="BF70" s="28"/>
+      <c r="BG70"/>
+      <c r="BH70" s="27"/>
+      <c r="BI70"/>
+      <c r="BJ70"/>
       <c r="BK70" s="1"/>
       <c r="BL70" s="1"/>
       <c r="BM70" s="1"/>
@@ -6012,9 +6877,19 @@
       <c r="CL70" s="1"/>
     </row>
     <row r="71" spans="3:90">
-      <c r="C71" s="10"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="12"/>
+      <c r="C71" s="11"/>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71"/>
+      <c r="I71"/>
+      <c r="J71" s="21"/>
+      <c r="K71"/>
+      <c r="L71"/>
+      <c r="M71"/>
+      <c r="N71"/>
+      <c r="O71"/>
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
@@ -6025,6 +6900,7 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
+      <c r="AA71"/>
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
       <c r="AE71" s="1"/>
@@ -6035,8 +6911,11 @@
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
       <c r="AL71" s="1"/>
+      <c r="AM71"/>
       <c r="AR71" s="1"/>
       <c r="AS71" s="1"/>
+      <c r="AT71"/>
+      <c r="AU71"/>
       <c r="AV71" s="1"/>
       <c r="AW71" s="1"/>
       <c r="AX71" s="1"/>
@@ -6046,9 +6925,12 @@
       <c r="BB71" s="1"/>
       <c r="BC71" s="1"/>
       <c r="BD71" s="1"/>
-      <c r="BE71" s="25"/>
-      <c r="BF71" s="25"/>
-      <c r="BH71" s="24"/>
+      <c r="BE71" s="28"/>
+      <c r="BF71" s="28"/>
+      <c r="BG71"/>
+      <c r="BH71" s="27"/>
+      <c r="BI71"/>
+      <c r="BJ71"/>
       <c r="BK71" s="1"/>
       <c r="BL71" s="1"/>
       <c r="BM71" s="1"/>
@@ -6079,9 +6961,11 @@
       <c r="CL71" s="1"/>
     </row>
     <row r="72" spans="3:90">
-      <c r="C72" s="10"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="12"/>
+      <c r="C72" s="11"/>
+      <c r="D72"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13"/>
+      <c r="J72" s="21"/>
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
@@ -6092,6 +6976,7 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
+      <c r="AA72"/>
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
       <c r="AE72" s="1"/>
@@ -6102,8 +6987,11 @@
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
       <c r="AL72" s="1"/>
+      <c r="AM72"/>
       <c r="AR72" s="1"/>
       <c r="AS72" s="1"/>
+      <c r="AT72"/>
+      <c r="AU72"/>
       <c r="AV72" s="1"/>
       <c r="AW72" s="1"/>
       <c r="AX72" s="1"/>
@@ -6113,9 +7001,12 @@
       <c r="BB72" s="1"/>
       <c r="BC72" s="1"/>
       <c r="BD72" s="1"/>
-      <c r="BE72" s="25"/>
-      <c r="BF72" s="25"/>
-      <c r="BH72" s="24"/>
+      <c r="BE72" s="28"/>
+      <c r="BF72" s="28"/>
+      <c r="BG72"/>
+      <c r="BH72" s="27"/>
+      <c r="BI72"/>
+      <c r="BJ72"/>
       <c r="BK72" s="1"/>
       <c r="BL72" s="1"/>
       <c r="BM72" s="1"/>
@@ -6146,9 +7037,19 @@
       <c r="CL72" s="1"/>
     </row>
     <row r="73" spans="3:90">
-      <c r="C73" s="10"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="12"/>
+      <c r="C73" s="11"/>
+      <c r="D73"/>
+      <c r="E73"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73"/>
+      <c r="I73"/>
+      <c r="J73" s="21"/>
+      <c r="K73"/>
+      <c r="L73"/>
+      <c r="M73"/>
+      <c r="N73"/>
+      <c r="O73"/>
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
@@ -6159,6 +7060,7 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
+      <c r="AA73"/>
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
       <c r="AE73" s="1"/>
@@ -6169,8 +7071,11 @@
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
       <c r="AL73" s="1"/>
+      <c r="AM73"/>
       <c r="AR73" s="1"/>
       <c r="AS73" s="1"/>
+      <c r="AT73"/>
+      <c r="AU73"/>
       <c r="AV73" s="1"/>
       <c r="AW73" s="1"/>
       <c r="AX73" s="1"/>
@@ -6180,9 +7085,12 @@
       <c r="BB73" s="1"/>
       <c r="BC73" s="1"/>
       <c r="BD73" s="1"/>
-      <c r="BE73" s="25"/>
-      <c r="BF73" s="25"/>
-      <c r="BH73" s="24"/>
+      <c r="BE73" s="28"/>
+      <c r="BF73" s="28"/>
+      <c r="BG73"/>
+      <c r="BH73" s="27"/>
+      <c r="BI73"/>
+      <c r="BJ73"/>
       <c r="BK73" s="1"/>
       <c r="BL73" s="1"/>
       <c r="BM73" s="1"/>
@@ -6213,9 +7121,19 @@
       <c r="CL73" s="1"/>
     </row>
     <row r="74" spans="3:90">
-      <c r="C74" s="10"/>
-      <c r="F74" s="12"/>
-      <c r="G74" s="12"/>
+      <c r="C74" s="11"/>
+      <c r="D74"/>
+      <c r="E74"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74"/>
+      <c r="I74"/>
+      <c r="J74" s="21"/>
+      <c r="K74"/>
+      <c r="L74"/>
+      <c r="M74"/>
+      <c r="N74"/>
+      <c r="O74"/>
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
@@ -6226,6 +7144,7 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
+      <c r="AA74"/>
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
       <c r="AE74" s="1"/>
@@ -6236,8 +7155,11 @@
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
       <c r="AL74" s="1"/>
+      <c r="AM74"/>
       <c r="AR74" s="1"/>
       <c r="AS74" s="1"/>
+      <c r="AT74"/>
+      <c r="AU74"/>
       <c r="AV74" s="1"/>
       <c r="AW74" s="1"/>
       <c r="AX74" s="1"/>
@@ -6247,9 +7169,12 @@
       <c r="BB74" s="1"/>
       <c r="BC74" s="1"/>
       <c r="BD74" s="1"/>
-      <c r="BE74" s="25"/>
-      <c r="BF74" s="25"/>
-      <c r="BH74" s="24"/>
+      <c r="BE74" s="28"/>
+      <c r="BF74" s="28"/>
+      <c r="BG74"/>
+      <c r="BH74" s="27"/>
+      <c r="BI74"/>
+      <c r="BJ74"/>
       <c r="BK74" s="1"/>
       <c r="BL74" s="1"/>
       <c r="BM74" s="1"/>
@@ -6280,9 +7205,19 @@
       <c r="CL74" s="1"/>
     </row>
     <row r="75" spans="3:90">
-      <c r="C75" s="10"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="12"/>
+      <c r="C75" s="11"/>
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75"/>
+      <c r="I75"/>
+      <c r="J75" s="21"/>
+      <c r="K75"/>
+      <c r="L75"/>
+      <c r="M75"/>
+      <c r="N75"/>
+      <c r="O75"/>
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
@@ -6293,6 +7228,7 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
+      <c r="AA75"/>
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
       <c r="AE75" s="1"/>
@@ -6303,8 +7239,11 @@
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
       <c r="AL75" s="1"/>
+      <c r="AM75"/>
       <c r="AR75" s="1"/>
       <c r="AS75" s="1"/>
+      <c r="AT75"/>
+      <c r="AU75"/>
       <c r="AV75" s="1"/>
       <c r="AW75" s="1"/>
       <c r="AX75" s="1"/>
@@ -6314,9 +7253,12 @@
       <c r="BB75" s="1"/>
       <c r="BC75" s="1"/>
       <c r="BD75" s="1"/>
-      <c r="BE75" s="25"/>
-      <c r="BF75" s="25"/>
-      <c r="BH75" s="24"/>
+      <c r="BE75" s="28"/>
+      <c r="BF75" s="28"/>
+      <c r="BG75"/>
+      <c r="BH75" s="27"/>
+      <c r="BI75"/>
+      <c r="BJ75"/>
       <c r="BK75" s="1"/>
       <c r="BL75" s="1"/>
       <c r="BM75" s="1"/>
@@ -6347,9 +7289,19 @@
       <c r="CL75" s="1"/>
     </row>
     <row r="76" spans="3:90">
-      <c r="C76" s="10"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="12"/>
+      <c r="C76" s="11"/>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76"/>
+      <c r="I76"/>
+      <c r="J76" s="21"/>
+      <c r="K76"/>
+      <c r="L76"/>
+      <c r="M76"/>
+      <c r="N76"/>
+      <c r="O76"/>
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
@@ -6360,6 +7312,7 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
+      <c r="AA76"/>
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
       <c r="AE76" s="1"/>
@@ -6370,8 +7323,11 @@
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
       <c r="AL76" s="1"/>
+      <c r="AM76"/>
       <c r="AR76" s="1"/>
       <c r="AS76" s="1"/>
+      <c r="AT76"/>
+      <c r="AU76"/>
       <c r="AV76" s="1"/>
       <c r="AW76" s="1"/>
       <c r="AX76" s="1"/>
@@ -6381,9 +7337,12 @@
       <c r="BB76" s="1"/>
       <c r="BC76" s="1"/>
       <c r="BD76" s="1"/>
-      <c r="BE76" s="25"/>
-      <c r="BF76" s="25"/>
-      <c r="BH76" s="24"/>
+      <c r="BE76" s="28"/>
+      <c r="BF76" s="28"/>
+      <c r="BG76"/>
+      <c r="BH76" s="27"/>
+      <c r="BI76"/>
+      <c r="BJ76"/>
       <c r="BK76" s="1"/>
       <c r="BL76" s="1"/>
       <c r="BM76" s="1"/>
@@ -6414,13 +7373,13 @@
       <c r="CL76" s="1"/>
     </row>
     <row r="77" spans="3:90">
-      <c r="C77" s="10"/>
+      <c r="C77" s="11"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="12"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
-      <c r="J77" s="4"/>
+      <c r="J77" s="21"/>
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
@@ -6455,12 +7414,12 @@
       <c r="BB77" s="1"/>
       <c r="BC77" s="1"/>
       <c r="BD77" s="1"/>
-      <c r="BE77" s="25"/>
-      <c r="BF77" s="25"/>
+      <c r="BE77" s="28"/>
+      <c r="BF77" s="28"/>
       <c r="BG77" s="1"/>
-      <c r="BH77" s="24"/>
+      <c r="BH77" s="27"/>
       <c r="BI77" s="1"/>
-      <c r="BJ77" s="25"/>
+      <c r="BJ77" s="28"/>
       <c r="BK77" s="1"/>
       <c r="BL77" s="1"/>
       <c r="BM77" s="1"/>
@@ -6491,13 +7450,13 @@
       <c r="CL77" s="1"/>
     </row>
     <row r="78" spans="3:90">
-      <c r="C78" s="10"/>
+      <c r="C78" s="11"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="12"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
-      <c r="J78" s="4"/>
+      <c r="J78" s="21"/>
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
@@ -6532,12 +7491,12 @@
       <c r="BB78" s="1"/>
       <c r="BC78" s="1"/>
       <c r="BD78" s="1"/>
-      <c r="BE78" s="25"/>
-      <c r="BF78" s="25"/>
+      <c r="BE78" s="28"/>
+      <c r="BF78" s="28"/>
       <c r="BG78" s="1"/>
-      <c r="BH78" s="24"/>
+      <c r="BH78" s="27"/>
       <c r="BI78" s="1"/>
-      <c r="BJ78" s="25"/>
+      <c r="BJ78" s="28"/>
       <c r="BK78" s="1"/>
       <c r="BL78" s="1"/>
       <c r="BM78" s="1"/>
@@ -6568,13 +7527,13 @@
       <c r="CL78" s="1"/>
     </row>
     <row r="79" spans="3:90">
-      <c r="C79" s="10"/>
+      <c r="C79" s="11"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
-      <c r="J79" s="4"/>
+      <c r="J79" s="21"/>
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
@@ -6609,12 +7568,12 @@
       <c r="BB79" s="1"/>
       <c r="BC79" s="1"/>
       <c r="BD79" s="1"/>
-      <c r="BE79" s="25"/>
-      <c r="BF79" s="25"/>
+      <c r="BE79" s="28"/>
+      <c r="BF79" s="28"/>
       <c r="BG79" s="1"/>
-      <c r="BH79" s="24"/>
+      <c r="BH79" s="27"/>
       <c r="BI79" s="1"/>
-      <c r="BJ79" s="25"/>
+      <c r="BJ79" s="28"/>
       <c r="BK79" s="1"/>
       <c r="BL79" s="1"/>
       <c r="BM79" s="1"/>
@@ -6645,13 +7604,13 @@
       <c r="CL79" s="1"/>
     </row>
     <row r="80" spans="3:90">
-      <c r="C80" s="10"/>
+      <c r="C80" s="11"/>
       <c r="E80" s="1"/>
-      <c r="F80" s="12"/>
-      <c r="G80" s="12"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
-      <c r="J80" s="4"/>
+      <c r="J80" s="21"/>
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
@@ -6686,12 +7645,12 @@
       <c r="BB80" s="1"/>
       <c r="BC80" s="1"/>
       <c r="BD80" s="1"/>
-      <c r="BE80" s="25"/>
-      <c r="BF80" s="25"/>
+      <c r="BE80" s="28"/>
+      <c r="BF80" s="28"/>
       <c r="BG80" s="1"/>
-      <c r="BH80" s="24"/>
+      <c r="BH80" s="27"/>
       <c r="BI80" s="1"/>
-      <c r="BJ80" s="25"/>
+      <c r="BJ80" s="28"/>
       <c r="BK80" s="1"/>
       <c r="BL80" s="1"/>
       <c r="BM80" s="1"/>
@@ -6722,13 +7681,13 @@
       <c r="CL80" s="1"/>
     </row>
     <row r="81" spans="3:90">
-      <c r="C81" s="10"/>
+      <c r="C81" s="11"/>
       <c r="E81" s="1"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
-      <c r="J81" s="4"/>
+      <c r="J81" s="21"/>
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
@@ -6763,12 +7722,12 @@
       <c r="BB81" s="1"/>
       <c r="BC81" s="1"/>
       <c r="BD81" s="1"/>
-      <c r="BE81" s="25"/>
-      <c r="BF81" s="25"/>
+      <c r="BE81" s="28"/>
+      <c r="BF81" s="28"/>
       <c r="BG81" s="1"/>
-      <c r="BH81" s="24"/>
+      <c r="BH81" s="27"/>
       <c r="BI81" s="1"/>
-      <c r="BJ81" s="25"/>
+      <c r="BJ81" s="28"/>
       <c r="BK81" s="1"/>
       <c r="BL81" s="1"/>
       <c r="BM81" s="1"/>
@@ -6799,13 +7758,13 @@
       <c r="CL81" s="1"/>
     </row>
     <row r="82" spans="3:90">
-      <c r="C82" s="10"/>
+      <c r="C82" s="11"/>
       <c r="E82" s="1"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="4"/>
+      <c r="J82" s="21"/>
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
@@ -6840,12 +7799,12 @@
       <c r="BB82" s="1"/>
       <c r="BC82" s="1"/>
       <c r="BD82" s="1"/>
-      <c r="BE82" s="25"/>
-      <c r="BF82" s="25"/>
+      <c r="BE82" s="28"/>
+      <c r="BF82" s="28"/>
       <c r="BG82" s="1"/>
-      <c r="BH82" s="24"/>
+      <c r="BH82" s="27"/>
       <c r="BI82" s="1"/>
-      <c r="BJ82" s="25"/>
+      <c r="BJ82" s="28"/>
       <c r="BK82" s="1"/>
       <c r="BL82" s="1"/>
       <c r="BM82" s="1"/>
@@ -6876,13 +7835,13 @@
       <c r="CL82" s="1"/>
     </row>
     <row r="83" spans="3:90">
-      <c r="C83" s="10"/>
+      <c r="C83" s="11"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="12"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="13"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
-      <c r="J83" s="4"/>
+      <c r="J83" s="21"/>
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
@@ -6917,12 +7876,12 @@
       <c r="BB83" s="1"/>
       <c r="BC83" s="1"/>
       <c r="BD83" s="1"/>
-      <c r="BE83" s="25"/>
-      <c r="BF83" s="25"/>
+      <c r="BE83" s="28"/>
+      <c r="BF83" s="28"/>
       <c r="BG83" s="1"/>
-      <c r="BH83" s="24"/>
+      <c r="BH83" s="27"/>
       <c r="BI83" s="1"/>
-      <c r="BJ83" s="25"/>
+      <c r="BJ83" s="28"/>
       <c r="BK83" s="1"/>
       <c r="BL83" s="1"/>
       <c r="BM83" s="1"/>
@@ -6953,13 +7912,13 @@
       <c r="CL83" s="1"/>
     </row>
     <row r="84" spans="3:90">
-      <c r="C84" s="10"/>
+      <c r="C84" s="11"/>
       <c r="E84" s="1"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="13"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
-      <c r="J84" s="4"/>
+      <c r="J84" s="21"/>
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
@@ -6994,12 +7953,12 @@
       <c r="BB84" s="1"/>
       <c r="BC84" s="1"/>
       <c r="BD84" s="1"/>
-      <c r="BE84" s="25"/>
-      <c r="BF84" s="25"/>
+      <c r="BE84" s="28"/>
+      <c r="BF84" s="28"/>
       <c r="BG84" s="1"/>
-      <c r="BH84" s="24"/>
+      <c r="BH84" s="27"/>
       <c r="BI84" s="1"/>
-      <c r="BJ84" s="25"/>
+      <c r="BJ84" s="28"/>
       <c r="BK84" s="1"/>
       <c r="BL84" s="1"/>
       <c r="BM84" s="1"/>
@@ -7030,13 +7989,13 @@
       <c r="CL84" s="1"/>
     </row>
     <row r="85" spans="3:90">
-      <c r="C85" s="10"/>
+      <c r="C85" s="11"/>
       <c r="E85" s="1"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="12"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="13"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
-      <c r="J85" s="4"/>
+      <c r="J85" s="21"/>
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
@@ -7071,12 +8030,12 @@
       <c r="BB85" s="1"/>
       <c r="BC85" s="1"/>
       <c r="BD85" s="1"/>
-      <c r="BE85" s="25"/>
-      <c r="BF85" s="25"/>
+      <c r="BE85" s="28"/>
+      <c r="BF85" s="28"/>
       <c r="BG85" s="1"/>
-      <c r="BH85" s="24"/>
+      <c r="BH85" s="27"/>
       <c r="BI85" s="1"/>
-      <c r="BJ85" s="25"/>
+      <c r="BJ85" s="28"/>
       <c r="BK85" s="1"/>
       <c r="BL85" s="1"/>
       <c r="BM85" s="1"/>
@@ -7107,13 +8066,13 @@
       <c r="CL85" s="1"/>
     </row>
     <row r="86" spans="3:90">
-      <c r="C86" s="10"/>
+      <c r="C86" s="11"/>
       <c r="E86" s="1"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="12"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
-      <c r="J86" s="4"/>
+      <c r="J86" s="21"/>
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
@@ -7148,12 +8107,12 @@
       <c r="BB86" s="1"/>
       <c r="BC86" s="1"/>
       <c r="BD86" s="1"/>
-      <c r="BE86" s="25"/>
-      <c r="BF86" s="25"/>
+      <c r="BE86" s="28"/>
+      <c r="BF86" s="28"/>
       <c r="BG86" s="1"/>
-      <c r="BH86" s="24"/>
+      <c r="BH86" s="27"/>
       <c r="BI86" s="1"/>
-      <c r="BJ86" s="25"/>
+      <c r="BJ86" s="28"/>
       <c r="BK86" s="1"/>
       <c r="BL86" s="1"/>
       <c r="BM86" s="1"/>
@@ -7184,13 +8143,13 @@
       <c r="CL86" s="1"/>
     </row>
     <row r="87" spans="3:62">
-      <c r="C87" s="10"/>
+      <c r="C87" s="11"/>
       <c r="E87" s="1"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="12"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="13"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
-      <c r="J87" s="4"/>
+      <c r="J87" s="21"/>
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
@@ -7225,21 +8184,21 @@
       <c r="BB87" s="1"/>
       <c r="BC87" s="1"/>
       <c r="BD87" s="1"/>
-      <c r="BE87" s="25"/>
-      <c r="BF87" s="25"/>
+      <c r="BE87" s="28"/>
+      <c r="BF87" s="28"/>
       <c r="BG87" s="1"/>
-      <c r="BH87" s="24"/>
+      <c r="BH87" s="27"/>
       <c r="BI87" s="1"/>
-      <c r="BJ87" s="25"/>
+      <c r="BJ87" s="28"/>
     </row>
     <row r="88" spans="3:62">
-      <c r="C88" s="10"/>
+      <c r="C88" s="11"/>
       <c r="E88" s="1"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="12"/>
+      <c r="F88" s="13"/>
+      <c r="G88" s="13"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
-      <c r="J88" s="4"/>
+      <c r="J88" s="21"/>
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
@@ -7274,21 +8233,21 @@
       <c r="BB88" s="1"/>
       <c r="BC88" s="1"/>
       <c r="BD88" s="1"/>
-      <c r="BE88" s="25"/>
-      <c r="BF88" s="25"/>
+      <c r="BE88" s="28"/>
+      <c r="BF88" s="28"/>
       <c r="BG88" s="1"/>
-      <c r="BH88" s="24"/>
+      <c r="BH88" s="27"/>
       <c r="BI88" s="1"/>
-      <c r="BJ88" s="25"/>
+      <c r="BJ88" s="28"/>
     </row>
     <row r="89" spans="3:62">
-      <c r="C89" s="10"/>
+      <c r="C89" s="11"/>
       <c r="E89" s="1"/>
-      <c r="F89" s="12"/>
-      <c r="G89" s="12"/>
+      <c r="F89" s="13"/>
+      <c r="G89" s="13"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
-      <c r="J89" s="4"/>
+      <c r="J89" s="21"/>
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
@@ -7323,21 +8282,21 @@
       <c r="BB89" s="1"/>
       <c r="BC89" s="1"/>
       <c r="BD89" s="1"/>
-      <c r="BE89" s="25"/>
-      <c r="BF89" s="25"/>
+      <c r="BE89" s="28"/>
+      <c r="BF89" s="28"/>
       <c r="BG89" s="1"/>
-      <c r="BH89" s="24"/>
+      <c r="BH89" s="27"/>
       <c r="BI89" s="1"/>
-      <c r="BJ89" s="25"/>
+      <c r="BJ89" s="28"/>
     </row>
     <row r="90" spans="3:62">
-      <c r="C90" s="10"/>
+      <c r="C90" s="11"/>
       <c r="E90" s="1"/>
-      <c r="F90" s="12"/>
-      <c r="G90" s="12"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="13"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
-      <c r="J90" s="4"/>
+      <c r="J90" s="21"/>
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
@@ -7372,21 +8331,21 @@
       <c r="BB90" s="1"/>
       <c r="BC90" s="1"/>
       <c r="BD90" s="1"/>
-      <c r="BE90" s="25"/>
-      <c r="BF90" s="25"/>
+      <c r="BE90" s="28"/>
+      <c r="BF90" s="28"/>
       <c r="BG90" s="1"/>
-      <c r="BH90" s="24"/>
+      <c r="BH90" s="27"/>
       <c r="BI90" s="1"/>
-      <c r="BJ90" s="25"/>
+      <c r="BJ90" s="28"/>
     </row>
     <row r="91" spans="3:62">
-      <c r="C91" s="10"/>
+      <c r="C91" s="11"/>
       <c r="E91" s="1"/>
-      <c r="F91" s="12"/>
-      <c r="G91" s="12"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="13"/>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
-      <c r="J91" s="4"/>
+      <c r="J91" s="21"/>
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
@@ -7421,21 +8380,21 @@
       <c r="BB91" s="1"/>
       <c r="BC91" s="1"/>
       <c r="BD91" s="1"/>
-      <c r="BE91" s="25"/>
-      <c r="BF91" s="25"/>
+      <c r="BE91" s="28"/>
+      <c r="BF91" s="28"/>
       <c r="BG91" s="1"/>
-      <c r="BH91" s="24"/>
+      <c r="BH91" s="27"/>
       <c r="BI91" s="1"/>
-      <c r="BJ91" s="25"/>
+      <c r="BJ91" s="28"/>
     </row>
     <row r="92" spans="3:62">
-      <c r="C92" s="10"/>
+      <c r="C92" s="11"/>
       <c r="E92" s="1"/>
-      <c r="F92" s="12"/>
-      <c r="G92" s="12"/>
+      <c r="F92" s="13"/>
+      <c r="G92" s="13"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
-      <c r="J92" s="4"/>
+      <c r="J92" s="21"/>
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
@@ -7470,21 +8429,21 @@
       <c r="BB92" s="1"/>
       <c r="BC92" s="1"/>
       <c r="BD92" s="1"/>
-      <c r="BE92" s="25"/>
-      <c r="BF92" s="25"/>
+      <c r="BE92" s="28"/>
+      <c r="BF92" s="28"/>
       <c r="BG92" s="1"/>
-      <c r="BH92" s="24"/>
+      <c r="BH92" s="27"/>
       <c r="BI92" s="1"/>
-      <c r="BJ92" s="25"/>
+      <c r="BJ92" s="28"/>
     </row>
     <row r="93" spans="3:62">
-      <c r="C93" s="10"/>
+      <c r="C93" s="11"/>
       <c r="E93" s="1"/>
-      <c r="F93" s="12"/>
-      <c r="G93" s="12"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
-      <c r="J93" s="4"/>
+      <c r="J93" s="21"/>
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
@@ -7519,21 +8478,21 @@
       <c r="BB93" s="1"/>
       <c r="BC93" s="1"/>
       <c r="BD93" s="1"/>
-      <c r="BE93" s="25"/>
-      <c r="BF93" s="25"/>
+      <c r="BE93" s="28"/>
+      <c r="BF93" s="28"/>
       <c r="BG93" s="1"/>
-      <c r="BH93" s="24"/>
+      <c r="BH93" s="27"/>
       <c r="BI93" s="1"/>
-      <c r="BJ93" s="25"/>
+      <c r="BJ93" s="28"/>
     </row>
     <row r="94" spans="3:62">
-      <c r="C94" s="10"/>
+      <c r="C94" s="11"/>
       <c r="E94" s="1"/>
-      <c r="F94" s="12"/>
-      <c r="G94" s="12"/>
+      <c r="F94" s="13"/>
+      <c r="G94" s="13"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
-      <c r="J94" s="4"/>
+      <c r="J94" s="21"/>
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
@@ -7568,21 +8527,21 @@
       <c r="BB94" s="1"/>
       <c r="BC94" s="1"/>
       <c r="BD94" s="1"/>
-      <c r="BE94" s="25"/>
-      <c r="BF94" s="25"/>
+      <c r="BE94" s="28"/>
+      <c r="BF94" s="28"/>
       <c r="BG94" s="1"/>
-      <c r="BH94" s="24"/>
+      <c r="BH94" s="27"/>
       <c r="BI94" s="1"/>
-      <c r="BJ94" s="25"/>
+      <c r="BJ94" s="28"/>
     </row>
     <row r="95" spans="3:62">
-      <c r="C95" s="10"/>
+      <c r="C95" s="11"/>
       <c r="E95" s="1"/>
-      <c r="F95" s="12"/>
-      <c r="G95" s="12"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="13"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
-      <c r="J95" s="4"/>
+      <c r="J95" s="21"/>
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
@@ -7617,21 +8576,21 @@
       <c r="BB95" s="1"/>
       <c r="BC95" s="1"/>
       <c r="BD95" s="1"/>
-      <c r="BE95" s="25"/>
-      <c r="BF95" s="25"/>
+      <c r="BE95" s="28"/>
+      <c r="BF95" s="28"/>
       <c r="BG95" s="1"/>
-      <c r="BH95" s="24"/>
+      <c r="BH95" s="27"/>
       <c r="BI95" s="1"/>
-      <c r="BJ95" s="25"/>
+      <c r="BJ95" s="28"/>
     </row>
     <row r="96" spans="3:62">
-      <c r="C96" s="10"/>
+      <c r="C96" s="11"/>
       <c r="E96" s="1"/>
-      <c r="F96" s="12"/>
-      <c r="G96" s="12"/>
+      <c r="F96" s="13"/>
+      <c r="G96" s="13"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
-      <c r="J96" s="4"/>
+      <c r="J96" s="21"/>
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
@@ -7666,21 +8625,21 @@
       <c r="BB96" s="1"/>
       <c r="BC96" s="1"/>
       <c r="BD96" s="1"/>
-      <c r="BE96" s="25"/>
-      <c r="BF96" s="25"/>
+      <c r="BE96" s="28"/>
+      <c r="BF96" s="28"/>
       <c r="BG96" s="1"/>
-      <c r="BH96" s="24"/>
+      <c r="BH96" s="27"/>
       <c r="BI96" s="1"/>
-      <c r="BJ96" s="25"/>
+      <c r="BJ96" s="28"/>
     </row>
     <row r="97" spans="3:62">
-      <c r="C97" s="10"/>
+      <c r="C97" s="11"/>
       <c r="E97" s="1"/>
-      <c r="F97" s="12"/>
-      <c r="G97" s="12"/>
+      <c r="F97" s="13"/>
+      <c r="G97" s="13"/>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
-      <c r="J97" s="4"/>
+      <c r="J97" s="21"/>
       <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
@@ -7716,21 +8675,21 @@
       <c r="BB97" s="1"/>
       <c r="BC97" s="1"/>
       <c r="BD97" s="1"/>
-      <c r="BE97" s="25"/>
-      <c r="BF97" s="25"/>
+      <c r="BE97" s="28"/>
+      <c r="BF97" s="28"/>
       <c r="BG97" s="1"/>
-      <c r="BH97" s="24"/>
+      <c r="BH97" s="27"/>
       <c r="BI97" s="1"/>
-      <c r="BJ97" s="25"/>
+      <c r="BJ97" s="28"/>
     </row>
     <row r="98" spans="3:62">
-      <c r="C98" s="10"/>
+      <c r="C98" s="11"/>
       <c r="E98" s="1"/>
-      <c r="F98" s="12"/>
-      <c r="G98" s="12"/>
+      <c r="F98" s="13"/>
+      <c r="G98" s="13"/>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
-      <c r="J98" s="4"/>
+      <c r="J98" s="21"/>
       <c r="P98" s="1"/>
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
@@ -7766,21 +8725,21 @@
       <c r="BB98" s="1"/>
       <c r="BC98" s="1"/>
       <c r="BD98" s="1"/>
-      <c r="BE98" s="25"/>
-      <c r="BF98" s="25"/>
+      <c r="BE98" s="28"/>
+      <c r="BF98" s="28"/>
       <c r="BG98" s="1"/>
-      <c r="BH98" s="24"/>
+      <c r="BH98" s="27"/>
       <c r="BI98" s="1"/>
-      <c r="BJ98" s="25"/>
+      <c r="BJ98" s="28"/>
     </row>
     <row r="99" spans="3:62">
-      <c r="C99" s="10"/>
+      <c r="C99" s="11"/>
       <c r="E99" s="1"/>
-      <c r="F99" s="12"/>
-      <c r="G99" s="12"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="13"/>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
-      <c r="J99" s="4"/>
+      <c r="J99" s="21"/>
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
@@ -7816,21 +8775,21 @@
       <c r="BB99" s="1"/>
       <c r="BC99" s="1"/>
       <c r="BD99" s="1"/>
-      <c r="BE99" s="25"/>
-      <c r="BF99" s="25"/>
+      <c r="BE99" s="28"/>
+      <c r="BF99" s="28"/>
       <c r="BG99" s="1"/>
-      <c r="BH99" s="24"/>
+      <c r="BH99" s="27"/>
       <c r="BI99" s="1"/>
-      <c r="BJ99" s="25"/>
+      <c r="BJ99" s="28"/>
     </row>
     <row r="100" spans="3:62">
-      <c r="C100" s="10"/>
+      <c r="C100" s="11"/>
       <c r="E100" s="1"/>
-      <c r="F100" s="12"/>
-      <c r="G100" s="12"/>
+      <c r="F100" s="13"/>
+      <c r="G100" s="13"/>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
-      <c r="J100" s="4"/>
+      <c r="J100" s="21"/>
       <c r="P100" s="1"/>
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
@@ -7866,21 +8825,21 @@
       <c r="BB100" s="1"/>
       <c r="BC100" s="1"/>
       <c r="BD100" s="1"/>
-      <c r="BE100" s="25"/>
-      <c r="BF100" s="25"/>
+      <c r="BE100" s="28"/>
+      <c r="BF100" s="28"/>
       <c r="BG100" s="1"/>
-      <c r="BH100" s="24"/>
+      <c r="BH100" s="27"/>
       <c r="BI100" s="1"/>
-      <c r="BJ100" s="25"/>
+      <c r="BJ100" s="28"/>
     </row>
     <row r="101" spans="3:62">
-      <c r="C101" s="10"/>
+      <c r="C101" s="11"/>
       <c r="E101" s="1"/>
-      <c r="F101" s="12"/>
-      <c r="G101" s="12"/>
+      <c r="F101" s="13"/>
+      <c r="G101" s="13"/>
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
-      <c r="J101" s="4"/>
+      <c r="J101" s="21"/>
       <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
@@ -7916,21 +8875,21 @@
       <c r="BB101" s="1"/>
       <c r="BC101" s="1"/>
       <c r="BD101" s="1"/>
-      <c r="BE101" s="25"/>
-      <c r="BF101" s="25"/>
+      <c r="BE101" s="28"/>
+      <c r="BF101" s="28"/>
       <c r="BG101" s="1"/>
-      <c r="BH101" s="24"/>
+      <c r="BH101" s="27"/>
       <c r="BI101" s="1"/>
-      <c r="BJ101" s="25"/>
+      <c r="BJ101" s="28"/>
     </row>
     <row r="102" spans="3:62">
-      <c r="C102" s="10"/>
+      <c r="C102" s="11"/>
       <c r="E102" s="1"/>
-      <c r="F102" s="12"/>
-      <c r="G102" s="12"/>
+      <c r="F102" s="13"/>
+      <c r="G102" s="13"/>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
-      <c r="J102" s="4"/>
+      <c r="J102" s="21"/>
       <c r="P102" s="1"/>
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
@@ -7966,21 +8925,21 @@
       <c r="BB102" s="1"/>
       <c r="BC102" s="1"/>
       <c r="BD102" s="1"/>
-      <c r="BE102" s="25"/>
-      <c r="BF102" s="25"/>
+      <c r="BE102" s="28"/>
+      <c r="BF102" s="28"/>
       <c r="BG102" s="1"/>
-      <c r="BH102" s="24"/>
+      <c r="BH102" s="27"/>
       <c r="BI102" s="1"/>
-      <c r="BJ102" s="25"/>
+      <c r="BJ102" s="28"/>
     </row>
     <row r="103" spans="3:62">
-      <c r="C103" s="10"/>
+      <c r="C103" s="11"/>
       <c r="E103" s="1"/>
-      <c r="F103" s="12"/>
-      <c r="G103" s="12"/>
+      <c r="F103" s="13"/>
+      <c r="G103" s="13"/>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
-      <c r="J103" s="4"/>
+      <c r="J103" s="21"/>
       <c r="P103" s="1"/>
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
@@ -8016,21 +8975,21 @@
       <c r="BB103" s="1"/>
       <c r="BC103" s="1"/>
       <c r="BD103" s="1"/>
-      <c r="BE103" s="25"/>
-      <c r="BF103" s="25"/>
+      <c r="BE103" s="28"/>
+      <c r="BF103" s="28"/>
       <c r="BG103" s="1"/>
-      <c r="BH103" s="24"/>
+      <c r="BH103" s="27"/>
       <c r="BI103" s="1"/>
-      <c r="BJ103" s="25"/>
+      <c r="BJ103" s="28"/>
     </row>
     <row r="104" spans="3:62">
-      <c r="C104" s="10"/>
+      <c r="C104" s="11"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="12"/>
-      <c r="G104" s="12"/>
+      <c r="F104" s="13"/>
+      <c r="G104" s="13"/>
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
-      <c r="J104" s="4"/>
+      <c r="J104" s="21"/>
       <c r="P104" s="1"/>
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
@@ -8066,21 +9025,21 @@
       <c r="BB104" s="1"/>
       <c r="BC104" s="1"/>
       <c r="BD104" s="1"/>
-      <c r="BE104" s="25"/>
-      <c r="BF104" s="25"/>
+      <c r="BE104" s="28"/>
+      <c r="BF104" s="28"/>
       <c r="BG104" s="1"/>
-      <c r="BH104" s="24"/>
+      <c r="BH104" s="27"/>
       <c r="BI104" s="1"/>
-      <c r="BJ104" s="25"/>
+      <c r="BJ104" s="28"/>
     </row>
     <row r="105" spans="3:62">
-      <c r="C105" s="10"/>
+      <c r="C105" s="11"/>
       <c r="E105" s="1"/>
-      <c r="F105" s="12"/>
-      <c r="G105" s="12"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="13"/>
       <c r="H105" s="1"/>
       <c r="I105" s="1"/>
-      <c r="J105" s="4"/>
+      <c r="J105" s="21"/>
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
@@ -8116,21 +9075,21 @@
       <c r="BB105" s="1"/>
       <c r="BC105" s="1"/>
       <c r="BD105" s="1"/>
-      <c r="BE105" s="25"/>
-      <c r="BF105" s="25"/>
+      <c r="BE105" s="28"/>
+      <c r="BF105" s="28"/>
       <c r="BG105" s="1"/>
-      <c r="BH105" s="24"/>
+      <c r="BH105" s="27"/>
       <c r="BI105" s="1"/>
-      <c r="BJ105" s="25"/>
+      <c r="BJ105" s="28"/>
     </row>
     <row r="106" spans="3:62">
-      <c r="C106" s="10"/>
+      <c r="C106" s="11"/>
       <c r="E106" s="1"/>
-      <c r="F106" s="12"/>
-      <c r="G106" s="12"/>
+      <c r="F106" s="13"/>
+      <c r="G106" s="13"/>
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
-      <c r="J106" s="4"/>
+      <c r="J106" s="21"/>
       <c r="P106" s="1"/>
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
@@ -8166,21 +9125,21 @@
       <c r="BB106" s="1"/>
       <c r="BC106" s="1"/>
       <c r="BD106" s="1"/>
-      <c r="BE106" s="25"/>
-      <c r="BF106" s="25"/>
+      <c r="BE106" s="28"/>
+      <c r="BF106" s="28"/>
       <c r="BG106" s="1"/>
-      <c r="BH106" s="24"/>
+      <c r="BH106" s="27"/>
       <c r="BI106" s="1"/>
-      <c r="BJ106" s="25"/>
+      <c r="BJ106" s="28"/>
     </row>
     <row r="107" spans="3:62">
-      <c r="C107" s="10"/>
+      <c r="C107" s="11"/>
       <c r="E107" s="1"/>
-      <c r="F107" s="12"/>
-      <c r="G107" s="12"/>
+      <c r="F107" s="13"/>
+      <c r="G107" s="13"/>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
-      <c r="J107" s="4"/>
+      <c r="J107" s="21"/>
       <c r="P107" s="1"/>
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
@@ -8216,21 +9175,21 @@
       <c r="BB107" s="1"/>
       <c r="BC107" s="1"/>
       <c r="BD107" s="1"/>
-      <c r="BE107" s="25"/>
-      <c r="BF107" s="25"/>
+      <c r="BE107" s="28"/>
+      <c r="BF107" s="28"/>
       <c r="BG107" s="1"/>
-      <c r="BH107" s="24"/>
+      <c r="BH107" s="27"/>
       <c r="BI107" s="1"/>
-      <c r="BJ107" s="25"/>
+      <c r="BJ107" s="28"/>
     </row>
     <row r="108" spans="3:62">
-      <c r="C108" s="10"/>
+      <c r="C108" s="11"/>
       <c r="E108" s="1"/>
-      <c r="F108" s="12"/>
-      <c r="G108" s="12"/>
+      <c r="F108" s="13"/>
+      <c r="G108" s="13"/>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
-      <c r="J108" s="4"/>
+      <c r="J108" s="21"/>
       <c r="P108" s="1"/>
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
@@ -8266,21 +9225,21 @@
       <c r="BB108" s="1"/>
       <c r="BC108" s="1"/>
       <c r="BD108" s="1"/>
-      <c r="BE108" s="25"/>
-      <c r="BF108" s="25"/>
+      <c r="BE108" s="28"/>
+      <c r="BF108" s="28"/>
       <c r="BG108" s="1"/>
-      <c r="BH108" s="24"/>
+      <c r="BH108" s="27"/>
       <c r="BI108" s="1"/>
-      <c r="BJ108" s="25"/>
+      <c r="BJ108" s="28"/>
     </row>
     <row r="109" spans="3:62">
-      <c r="C109" s="10"/>
+      <c r="C109" s="11"/>
       <c r="E109" s="1"/>
-      <c r="F109" s="12"/>
-      <c r="G109" s="12"/>
+      <c r="F109" s="13"/>
+      <c r="G109" s="13"/>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
-      <c r="J109" s="4"/>
+      <c r="J109" s="21"/>
       <c r="P109" s="1"/>
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
@@ -8316,21 +9275,21 @@
       <c r="BB109" s="1"/>
       <c r="BC109" s="1"/>
       <c r="BD109" s="1"/>
-      <c r="BE109" s="25"/>
-      <c r="BF109" s="25"/>
+      <c r="BE109" s="28"/>
+      <c r="BF109" s="28"/>
       <c r="BG109" s="1"/>
-      <c r="BH109" s="24"/>
+      <c r="BH109" s="27"/>
       <c r="BI109" s="1"/>
-      <c r="BJ109" s="25"/>
+      <c r="BJ109" s="28"/>
     </row>
     <row r="110" spans="3:62">
-      <c r="C110" s="10"/>
+      <c r="C110" s="11"/>
       <c r="E110" s="1"/>
-      <c r="F110" s="12"/>
-      <c r="G110" s="12"/>
+      <c r="F110" s="13"/>
+      <c r="G110" s="13"/>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
-      <c r="J110" s="4"/>
+      <c r="J110" s="21"/>
       <c r="P110" s="1"/>
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
@@ -8366,21 +9325,21 @@
       <c r="BB110" s="1"/>
       <c r="BC110" s="1"/>
       <c r="BD110" s="1"/>
-      <c r="BE110" s="25"/>
-      <c r="BF110" s="25"/>
+      <c r="BE110" s="28"/>
+      <c r="BF110" s="28"/>
       <c r="BG110" s="1"/>
-      <c r="BH110" s="24"/>
+      <c r="BH110" s="27"/>
       <c r="BI110" s="1"/>
-      <c r="BJ110" s="25"/>
+      <c r="BJ110" s="28"/>
     </row>
     <row r="111" spans="3:62">
-      <c r="C111" s="10"/>
+      <c r="C111" s="11"/>
       <c r="E111" s="1"/>
-      <c r="F111" s="12"/>
-      <c r="G111" s="12"/>
+      <c r="F111" s="13"/>
+      <c r="G111" s="13"/>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
-      <c r="J111" s="4"/>
+      <c r="J111" s="21"/>
       <c r="P111" s="1"/>
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
@@ -8416,21 +9375,21 @@
       <c r="BB111" s="1"/>
       <c r="BC111" s="1"/>
       <c r="BD111" s="1"/>
-      <c r="BE111" s="25"/>
-      <c r="BF111" s="25"/>
+      <c r="BE111" s="28"/>
+      <c r="BF111" s="28"/>
       <c r="BG111" s="1"/>
-      <c r="BH111" s="24"/>
+      <c r="BH111" s="27"/>
       <c r="BI111" s="1"/>
-      <c r="BJ111" s="25"/>
+      <c r="BJ111" s="28"/>
     </row>
     <row r="112" spans="3:62">
-      <c r="C112" s="10"/>
+      <c r="C112" s="11"/>
       <c r="E112" s="1"/>
-      <c r="F112" s="12"/>
-      <c r="G112" s="12"/>
+      <c r="F112" s="13"/>
+      <c r="G112" s="13"/>
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
-      <c r="J112" s="4"/>
+      <c r="J112" s="21"/>
       <c r="P112" s="1"/>
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
@@ -8466,21 +9425,21 @@
       <c r="BB112" s="1"/>
       <c r="BC112" s="1"/>
       <c r="BD112" s="1"/>
-      <c r="BE112" s="25"/>
-      <c r="BF112" s="25"/>
+      <c r="BE112" s="28"/>
+      <c r="BF112" s="28"/>
       <c r="BG112" s="1"/>
-      <c r="BH112" s="24"/>
+      <c r="BH112" s="27"/>
       <c r="BI112" s="1"/>
-      <c r="BJ112" s="25"/>
+      <c r="BJ112" s="28"/>
     </row>
     <row r="113" spans="3:62">
-      <c r="C113" s="10"/>
+      <c r="C113" s="11"/>
       <c r="E113" s="1"/>
-      <c r="F113" s="12"/>
-      <c r="G113" s="12"/>
+      <c r="F113" s="13"/>
+      <c r="G113" s="13"/>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
-      <c r="J113" s="4"/>
+      <c r="J113" s="21"/>
       <c r="P113" s="1"/>
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
@@ -8516,21 +9475,21 @@
       <c r="BB113" s="1"/>
       <c r="BC113" s="1"/>
       <c r="BD113" s="1"/>
-      <c r="BE113" s="25"/>
-      <c r="BF113" s="25"/>
+      <c r="BE113" s="28"/>
+      <c r="BF113" s="28"/>
       <c r="BG113" s="1"/>
-      <c r="BH113" s="24"/>
+      <c r="BH113" s="27"/>
       <c r="BI113" s="1"/>
-      <c r="BJ113" s="25"/>
+      <c r="BJ113" s="28"/>
     </row>
     <row r="114" spans="3:62">
-      <c r="C114" s="10"/>
+      <c r="C114" s="11"/>
       <c r="E114" s="1"/>
-      <c r="F114" s="12"/>
-      <c r="G114" s="12"/>
+      <c r="F114" s="13"/>
+      <c r="G114" s="13"/>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
-      <c r="J114" s="4"/>
+      <c r="J114" s="21"/>
       <c r="P114" s="1"/>
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
@@ -8566,21 +9525,21 @@
       <c r="BB114" s="1"/>
       <c r="BC114" s="1"/>
       <c r="BD114" s="1"/>
-      <c r="BE114" s="25"/>
-      <c r="BF114" s="25"/>
+      <c r="BE114" s="28"/>
+      <c r="BF114" s="28"/>
       <c r="BG114" s="1"/>
-      <c r="BH114" s="24"/>
+      <c r="BH114" s="27"/>
       <c r="BI114" s="1"/>
-      <c r="BJ114" s="25"/>
+      <c r="BJ114" s="28"/>
     </row>
     <row r="115" spans="3:62">
-      <c r="C115" s="10"/>
+      <c r="C115" s="11"/>
       <c r="E115" s="1"/>
-      <c r="F115" s="12"/>
-      <c r="G115" s="12"/>
+      <c r="F115" s="13"/>
+      <c r="G115" s="13"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
-      <c r="J115" s="4"/>
+      <c r="J115" s="21"/>
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
@@ -8616,21 +9575,21 @@
       <c r="BB115" s="1"/>
       <c r="BC115" s="1"/>
       <c r="BD115" s="1"/>
-      <c r="BE115" s="25"/>
-      <c r="BF115" s="25"/>
+      <c r="BE115" s="28"/>
+      <c r="BF115" s="28"/>
       <c r="BG115" s="1"/>
-      <c r="BH115" s="24"/>
+      <c r="BH115" s="27"/>
       <c r="BI115" s="1"/>
-      <c r="BJ115" s="25"/>
+      <c r="BJ115" s="28"/>
     </row>
     <row r="116" spans="3:62">
-      <c r="C116" s="10"/>
+      <c r="C116" s="11"/>
       <c r="E116" s="1"/>
-      <c r="F116" s="12"/>
-      <c r="G116" s="12"/>
+      <c r="F116" s="13"/>
+      <c r="G116" s="13"/>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
-      <c r="J116" s="4"/>
+      <c r="J116" s="21"/>
       <c r="P116" s="1"/>
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
@@ -8666,21 +9625,21 @@
       <c r="BB116" s="1"/>
       <c r="BC116" s="1"/>
       <c r="BD116" s="1"/>
-      <c r="BE116" s="25"/>
-      <c r="BF116" s="25"/>
+      <c r="BE116" s="28"/>
+      <c r="BF116" s="28"/>
       <c r="BG116" s="1"/>
-      <c r="BH116" s="24"/>
+      <c r="BH116" s="27"/>
       <c r="BI116" s="1"/>
-      <c r="BJ116" s="25"/>
+      <c r="BJ116" s="28"/>
     </row>
     <row r="117" spans="3:62">
-      <c r="C117" s="10"/>
+      <c r="C117" s="11"/>
       <c r="E117" s="1"/>
-      <c r="F117" s="12"/>
-      <c r="G117" s="12"/>
+      <c r="F117" s="13"/>
+      <c r="G117" s="13"/>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
-      <c r="J117" s="4"/>
+      <c r="J117" s="21"/>
       <c r="P117" s="1"/>
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
@@ -8716,21 +9675,21 @@
       <c r="BB117" s="1"/>
       <c r="BC117" s="1"/>
       <c r="BD117" s="1"/>
-      <c r="BE117" s="25"/>
-      <c r="BF117" s="25"/>
+      <c r="BE117" s="28"/>
+      <c r="BF117" s="28"/>
       <c r="BG117" s="1"/>
-      <c r="BH117" s="24"/>
+      <c r="BH117" s="27"/>
       <c r="BI117" s="1"/>
-      <c r="BJ117" s="25"/>
+      <c r="BJ117" s="28"/>
     </row>
     <row r="118" spans="3:62">
-      <c r="C118" s="10"/>
+      <c r="C118" s="11"/>
       <c r="E118" s="1"/>
-      <c r="F118" s="12"/>
-      <c r="G118" s="12"/>
+      <c r="F118" s="13"/>
+      <c r="G118" s="13"/>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
-      <c r="J118" s="4"/>
+      <c r="J118" s="21"/>
       <c r="P118" s="1"/>
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
@@ -8766,21 +9725,21 @@
       <c r="BB118" s="1"/>
       <c r="BC118" s="1"/>
       <c r="BD118" s="1"/>
-      <c r="BE118" s="25"/>
-      <c r="BF118" s="25"/>
+      <c r="BE118" s="28"/>
+      <c r="BF118" s="28"/>
       <c r="BG118" s="1"/>
-      <c r="BH118" s="24"/>
+      <c r="BH118" s="27"/>
       <c r="BI118" s="1"/>
-      <c r="BJ118" s="25"/>
+      <c r="BJ118" s="28"/>
     </row>
     <row r="119" spans="3:62">
-      <c r="C119" s="10"/>
+      <c r="C119" s="11"/>
       <c r="E119" s="1"/>
-      <c r="F119" s="12"/>
-      <c r="G119" s="12"/>
+      <c r="F119" s="13"/>
+      <c r="G119" s="13"/>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
-      <c r="J119" s="4"/>
+      <c r="J119" s="21"/>
       <c r="P119" s="1"/>
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
@@ -8816,21 +9775,21 @@
       <c r="BB119" s="1"/>
       <c r="BC119" s="1"/>
       <c r="BD119" s="1"/>
-      <c r="BE119" s="25"/>
-      <c r="BF119" s="25"/>
+      <c r="BE119" s="28"/>
+      <c r="BF119" s="28"/>
       <c r="BG119" s="1"/>
-      <c r="BH119" s="24"/>
+      <c r="BH119" s="27"/>
       <c r="BI119" s="1"/>
-      <c r="BJ119" s="25"/>
+      <c r="BJ119" s="28"/>
     </row>
     <row r="120" spans="3:62">
-      <c r="C120" s="10"/>
+      <c r="C120" s="11"/>
       <c r="E120" s="1"/>
-      <c r="F120" s="12"/>
-      <c r="G120" s="12"/>
+      <c r="F120" s="13"/>
+      <c r="G120" s="13"/>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
-      <c r="J120" s="4"/>
+      <c r="J120" s="21"/>
       <c r="P120" s="1"/>
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
@@ -8866,21 +9825,21 @@
       <c r="BB120" s="1"/>
       <c r="BC120" s="1"/>
       <c r="BD120" s="1"/>
-      <c r="BE120" s="25"/>
-      <c r="BF120" s="25"/>
+      <c r="BE120" s="28"/>
+      <c r="BF120" s="28"/>
       <c r="BG120" s="1"/>
-      <c r="BH120" s="24"/>
+      <c r="BH120" s="27"/>
       <c r="BI120" s="1"/>
-      <c r="BJ120" s="25"/>
+      <c r="BJ120" s="28"/>
     </row>
     <row r="121" spans="3:62">
-      <c r="C121" s="10"/>
+      <c r="C121" s="11"/>
       <c r="E121" s="1"/>
-      <c r="F121" s="12"/>
-      <c r="G121" s="12"/>
+      <c r="F121" s="13"/>
+      <c r="G121" s="13"/>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
-      <c r="J121" s="4"/>
+      <c r="J121" s="21"/>
       <c r="P121" s="1"/>
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
@@ -8916,21 +9875,21 @@
       <c r="BB121" s="1"/>
       <c r="BC121" s="1"/>
       <c r="BD121" s="1"/>
-      <c r="BE121" s="25"/>
-      <c r="BF121" s="25"/>
+      <c r="BE121" s="28"/>
+      <c r="BF121" s="28"/>
       <c r="BG121" s="1"/>
-      <c r="BH121" s="24"/>
+      <c r="BH121" s="27"/>
       <c r="BI121" s="1"/>
-      <c r="BJ121" s="25"/>
+      <c r="BJ121" s="28"/>
     </row>
     <row r="122" spans="3:62">
-      <c r="C122" s="10"/>
+      <c r="C122" s="11"/>
       <c r="E122" s="1"/>
-      <c r="F122" s="12"/>
-      <c r="G122" s="12"/>
+      <c r="F122" s="13"/>
+      <c r="G122" s="13"/>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
-      <c r="J122" s="4"/>
+      <c r="J122" s="21"/>
       <c r="P122" s="1"/>
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
@@ -8966,21 +9925,21 @@
       <c r="BB122" s="1"/>
       <c r="BC122" s="1"/>
       <c r="BD122" s="1"/>
-      <c r="BE122" s="25"/>
-      <c r="BF122" s="25"/>
+      <c r="BE122" s="28"/>
+      <c r="BF122" s="28"/>
       <c r="BG122" s="1"/>
-      <c r="BH122" s="24"/>
+      <c r="BH122" s="27"/>
       <c r="BI122" s="1"/>
-      <c r="BJ122" s="25"/>
+      <c r="BJ122" s="28"/>
     </row>
     <row r="123" spans="3:62">
-      <c r="C123" s="10"/>
+      <c r="C123" s="11"/>
       <c r="E123" s="1"/>
-      <c r="F123" s="12"/>
-      <c r="G123" s="12"/>
+      <c r="F123" s="13"/>
+      <c r="G123" s="13"/>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
-      <c r="J123" s="4"/>
+      <c r="J123" s="21"/>
       <c r="P123" s="1"/>
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
@@ -9016,21 +9975,21 @@
       <c r="BB123" s="1"/>
       <c r="BC123" s="1"/>
       <c r="BD123" s="1"/>
-      <c r="BE123" s="25"/>
-      <c r="BF123" s="25"/>
+      <c r="BE123" s="28"/>
+      <c r="BF123" s="28"/>
       <c r="BG123" s="1"/>
-      <c r="BH123" s="24"/>
+      <c r="BH123" s="27"/>
       <c r="BI123" s="1"/>
-      <c r="BJ123" s="25"/>
+      <c r="BJ123" s="28"/>
     </row>
     <row r="124" spans="3:62">
-      <c r="C124" s="10"/>
+      <c r="C124" s="11"/>
       <c r="E124" s="1"/>
-      <c r="F124" s="12"/>
-      <c r="G124" s="12"/>
+      <c r="F124" s="13"/>
+      <c r="G124" s="13"/>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
-      <c r="J124" s="4"/>
+      <c r="J124" s="21"/>
       <c r="P124" s="1"/>
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
@@ -9066,21 +10025,21 @@
       <c r="BB124" s="1"/>
       <c r="BC124" s="1"/>
       <c r="BD124" s="1"/>
-      <c r="BE124" s="25"/>
-      <c r="BF124" s="25"/>
+      <c r="BE124" s="28"/>
+      <c r="BF124" s="28"/>
       <c r="BG124" s="1"/>
-      <c r="BH124" s="24"/>
+      <c r="BH124" s="27"/>
       <c r="BI124" s="1"/>
-      <c r="BJ124" s="25"/>
+      <c r="BJ124" s="28"/>
     </row>
     <row r="125" spans="3:62">
-      <c r="C125" s="10"/>
+      <c r="C125" s="11"/>
       <c r="E125" s="1"/>
-      <c r="F125" s="12"/>
-      <c r="G125" s="12"/>
+      <c r="F125" s="13"/>
+      <c r="G125" s="13"/>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
-      <c r="J125" s="4"/>
+      <c r="J125" s="21"/>
       <c r="P125" s="1"/>
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
@@ -9116,21 +10075,21 @@
       <c r="BB125" s="1"/>
       <c r="BC125" s="1"/>
       <c r="BD125" s="1"/>
-      <c r="BE125" s="25"/>
-      <c r="BF125" s="25"/>
+      <c r="BE125" s="28"/>
+      <c r="BF125" s="28"/>
       <c r="BG125" s="1"/>
-      <c r="BH125" s="24"/>
+      <c r="BH125" s="27"/>
       <c r="BI125" s="1"/>
-      <c r="BJ125" s="25"/>
+      <c r="BJ125" s="28"/>
     </row>
     <row r="126" spans="3:62">
-      <c r="C126" s="10"/>
+      <c r="C126" s="11"/>
       <c r="E126" s="1"/>
-      <c r="F126" s="12"/>
-      <c r="G126" s="12"/>
+      <c r="F126" s="13"/>
+      <c r="G126" s="13"/>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
-      <c r="J126" s="4"/>
+      <c r="J126" s="21"/>
       <c r="P126" s="1"/>
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
@@ -9166,21 +10125,21 @@
       <c r="BB126" s="1"/>
       <c r="BC126" s="1"/>
       <c r="BD126" s="1"/>
-      <c r="BE126" s="25"/>
-      <c r="BF126" s="25"/>
+      <c r="BE126" s="28"/>
+      <c r="BF126" s="28"/>
       <c r="BG126" s="1"/>
-      <c r="BH126" s="24"/>
+      <c r="BH126" s="27"/>
       <c r="BI126" s="1"/>
-      <c r="BJ126" s="25"/>
+      <c r="BJ126" s="28"/>
     </row>
     <row r="127" spans="3:62">
-      <c r="C127" s="10"/>
+      <c r="C127" s="11"/>
       <c r="E127" s="1"/>
-      <c r="F127" s="12"/>
-      <c r="G127" s="12"/>
+      <c r="F127" s="13"/>
+      <c r="G127" s="13"/>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
-      <c r="J127" s="4"/>
+      <c r="J127" s="21"/>
       <c r="P127" s="1"/>
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
@@ -9216,21 +10175,21 @@
       <c r="BB127" s="1"/>
       <c r="BC127" s="1"/>
       <c r="BD127" s="1"/>
-      <c r="BE127" s="25"/>
-      <c r="BF127" s="25"/>
+      <c r="BE127" s="28"/>
+      <c r="BF127" s="28"/>
       <c r="BG127" s="1"/>
-      <c r="BH127" s="24"/>
+      <c r="BH127" s="27"/>
       <c r="BI127" s="1"/>
-      <c r="BJ127" s="25"/>
+      <c r="BJ127" s="28"/>
     </row>
     <row r="128" spans="3:62">
-      <c r="C128" s="10"/>
+      <c r="C128" s="11"/>
       <c r="E128" s="1"/>
-      <c r="F128" s="12"/>
-      <c r="G128" s="12"/>
+      <c r="F128" s="13"/>
+      <c r="G128" s="13"/>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
-      <c r="J128" s="4"/>
+      <c r="J128" s="21"/>
       <c r="P128" s="1"/>
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
@@ -9266,21 +10225,21 @@
       <c r="BB128" s="1"/>
       <c r="BC128" s="1"/>
       <c r="BD128" s="1"/>
-      <c r="BE128" s="25"/>
-      <c r="BF128" s="25"/>
+      <c r="BE128" s="28"/>
+      <c r="BF128" s="28"/>
       <c r="BG128" s="1"/>
-      <c r="BH128" s="24"/>
+      <c r="BH128" s="27"/>
       <c r="BI128" s="1"/>
-      <c r="BJ128" s="25"/>
+      <c r="BJ128" s="28"/>
     </row>
     <row r="129" spans="3:62">
-      <c r="C129" s="10"/>
+      <c r="C129" s="11"/>
       <c r="E129" s="1"/>
-      <c r="F129" s="12"/>
-      <c r="G129" s="12"/>
+      <c r="F129" s="13"/>
+      <c r="G129" s="13"/>
       <c r="H129" s="1"/>
       <c r="I129" s="1"/>
-      <c r="J129" s="4"/>
+      <c r="J129" s="21"/>
       <c r="P129" s="1"/>
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
@@ -9316,21 +10275,21 @@
       <c r="BB129" s="1"/>
       <c r="BC129" s="1"/>
       <c r="BD129" s="1"/>
-      <c r="BE129" s="25"/>
-      <c r="BF129" s="25"/>
+      <c r="BE129" s="28"/>
+      <c r="BF129" s="28"/>
       <c r="BG129" s="1"/>
-      <c r="BH129" s="24"/>
+      <c r="BH129" s="27"/>
       <c r="BI129" s="1"/>
-      <c r="BJ129" s="25"/>
+      <c r="BJ129" s="28"/>
     </row>
     <row r="130" spans="3:62">
-      <c r="C130" s="10"/>
+      <c r="C130" s="11"/>
       <c r="E130" s="1"/>
-      <c r="F130" s="12"/>
-      <c r="G130" s="12"/>
+      <c r="F130" s="13"/>
+      <c r="G130" s="13"/>
       <c r="H130" s="1"/>
       <c r="I130" s="1"/>
-      <c r="J130" s="4"/>
+      <c r="J130" s="21"/>
       <c r="P130" s="1"/>
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
@@ -9366,21 +10325,21 @@
       <c r="BB130" s="1"/>
       <c r="BC130" s="1"/>
       <c r="BD130" s="1"/>
-      <c r="BE130" s="25"/>
-      <c r="BF130" s="25"/>
+      <c r="BE130" s="28"/>
+      <c r="BF130" s="28"/>
       <c r="BG130" s="1"/>
-      <c r="BH130" s="24"/>
+      <c r="BH130" s="27"/>
       <c r="BI130" s="1"/>
-      <c r="BJ130" s="25"/>
+      <c r="BJ130" s="28"/>
     </row>
     <row r="131" spans="3:62">
-      <c r="C131" s="10"/>
+      <c r="C131" s="11"/>
       <c r="E131" s="1"/>
-      <c r="F131" s="12"/>
-      <c r="G131" s="12"/>
+      <c r="F131" s="13"/>
+      <c r="G131" s="13"/>
       <c r="H131" s="1"/>
       <c r="I131" s="1"/>
-      <c r="J131" s="4"/>
+      <c r="J131" s="21"/>
       <c r="P131" s="1"/>
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
@@ -9416,21 +10375,21 @@
       <c r="BB131" s="1"/>
       <c r="BC131" s="1"/>
       <c r="BD131" s="1"/>
-      <c r="BE131" s="25"/>
-      <c r="BF131" s="25"/>
+      <c r="BE131" s="28"/>
+      <c r="BF131" s="28"/>
       <c r="BG131" s="1"/>
-      <c r="BH131" s="24"/>
+      <c r="BH131" s="27"/>
       <c r="BI131" s="1"/>
-      <c r="BJ131" s="25"/>
+      <c r="BJ131" s="28"/>
     </row>
     <row r="132" spans="3:62">
-      <c r="C132" s="10"/>
+      <c r="C132" s="11"/>
       <c r="E132" s="1"/>
-      <c r="F132" s="12"/>
-      <c r="G132" s="12"/>
+      <c r="F132" s="13"/>
+      <c r="G132" s="13"/>
       <c r="H132" s="1"/>
       <c r="I132" s="1"/>
-      <c r="J132" s="4"/>
+      <c r="J132" s="21"/>
       <c r="P132" s="1"/>
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
@@ -9466,21 +10425,21 @@
       <c r="BB132" s="1"/>
       <c r="BC132" s="1"/>
       <c r="BD132" s="1"/>
-      <c r="BE132" s="25"/>
-      <c r="BF132" s="25"/>
+      <c r="BE132" s="28"/>
+      <c r="BF132" s="28"/>
       <c r="BG132" s="1"/>
-      <c r="BH132" s="24"/>
+      <c r="BH132" s="27"/>
       <c r="BI132" s="1"/>
-      <c r="BJ132" s="25"/>
+      <c r="BJ132" s="28"/>
     </row>
     <row r="133" spans="3:62">
-      <c r="C133" s="10"/>
+      <c r="C133" s="11"/>
       <c r="E133" s="1"/>
-      <c r="F133" s="12"/>
-      <c r="G133" s="12"/>
+      <c r="F133" s="13"/>
+      <c r="G133" s="13"/>
       <c r="H133" s="1"/>
       <c r="I133" s="1"/>
-      <c r="J133" s="4"/>
+      <c r="J133" s="21"/>
       <c r="P133" s="1"/>
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
@@ -9516,21 +10475,21 @@
       <c r="BB133" s="1"/>
       <c r="BC133" s="1"/>
       <c r="BD133" s="1"/>
-      <c r="BE133" s="25"/>
-      <c r="BF133" s="25"/>
+      <c r="BE133" s="28"/>
+      <c r="BF133" s="28"/>
       <c r="BG133" s="1"/>
-      <c r="BH133" s="24"/>
+      <c r="BH133" s="27"/>
       <c r="BI133" s="1"/>
-      <c r="BJ133" s="25"/>
+      <c r="BJ133" s="28"/>
     </row>
     <row r="134" spans="3:62">
-      <c r="C134" s="10"/>
+      <c r="C134" s="11"/>
       <c r="E134" s="1"/>
-      <c r="F134" s="12"/>
-      <c r="G134" s="12"/>
+      <c r="F134" s="13"/>
+      <c r="G134" s="13"/>
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
-      <c r="J134" s="4"/>
+      <c r="J134" s="21"/>
       <c r="P134" s="1"/>
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
@@ -9566,21 +10525,21 @@
       <c r="BB134" s="1"/>
       <c r="BC134" s="1"/>
       <c r="BD134" s="1"/>
-      <c r="BE134" s="25"/>
-      <c r="BF134" s="25"/>
+      <c r="BE134" s="28"/>
+      <c r="BF134" s="28"/>
       <c r="BG134" s="1"/>
-      <c r="BH134" s="24"/>
+      <c r="BH134" s="27"/>
       <c r="BI134" s="1"/>
-      <c r="BJ134" s="25"/>
+      <c r="BJ134" s="28"/>
     </row>
     <row r="135" spans="3:62">
-      <c r="C135" s="10"/>
+      <c r="C135" s="11"/>
       <c r="E135" s="1"/>
-      <c r="F135" s="12"/>
-      <c r="G135" s="12"/>
+      <c r="F135" s="13"/>
+      <c r="G135" s="13"/>
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
-      <c r="J135" s="4"/>
+      <c r="J135" s="21"/>
       <c r="P135" s="1"/>
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
@@ -9616,21 +10575,21 @@
       <c r="BB135" s="1"/>
       <c r="BC135" s="1"/>
       <c r="BD135" s="1"/>
-      <c r="BE135" s="25"/>
-      <c r="BF135" s="25"/>
+      <c r="BE135" s="28"/>
+      <c r="BF135" s="28"/>
       <c r="BG135" s="1"/>
-      <c r="BH135" s="24"/>
+      <c r="BH135" s="27"/>
       <c r="BI135" s="1"/>
-      <c r="BJ135" s="25"/>
+      <c r="BJ135" s="28"/>
     </row>
     <row r="136" spans="3:62">
-      <c r="C136" s="10"/>
+      <c r="C136" s="11"/>
       <c r="E136" s="1"/>
-      <c r="F136" s="12"/>
-      <c r="G136" s="12"/>
+      <c r="F136" s="13"/>
+      <c r="G136" s="13"/>
       <c r="H136" s="1"/>
       <c r="I136" s="1"/>
-      <c r="J136" s="4"/>
+      <c r="J136" s="21"/>
       <c r="AA136" s="1"/>
       <c r="AU136" s="1"/>
       <c r="AV136" s="1"/>
@@ -9642,21 +10601,21 @@
       <c r="BB136" s="1"/>
       <c r="BC136" s="1"/>
       <c r="BD136" s="1"/>
-      <c r="BE136" s="25"/>
-      <c r="BF136" s="25"/>
+      <c r="BE136" s="28"/>
+      <c r="BF136" s="28"/>
       <c r="BG136" s="1"/>
-      <c r="BH136" s="24"/>
+      <c r="BH136" s="27"/>
       <c r="BI136" s="1"/>
-      <c r="BJ136" s="25"/>
+      <c r="BJ136" s="28"/>
     </row>
     <row r="137" spans="3:62">
-      <c r="C137" s="10"/>
+      <c r="C137" s="11"/>
       <c r="E137" s="1"/>
-      <c r="F137" s="12"/>
-      <c r="G137" s="12"/>
+      <c r="F137" s="13"/>
+      <c r="G137" s="13"/>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
-      <c r="J137" s="4"/>
+      <c r="J137" s="21"/>
       <c r="AA137" s="1"/>
       <c r="AU137" s="1"/>
       <c r="AV137" s="1"/>
@@ -9668,21 +10627,21 @@
       <c r="BB137" s="1"/>
       <c r="BC137" s="1"/>
       <c r="BD137" s="1"/>
-      <c r="BE137" s="25"/>
-      <c r="BF137" s="25"/>
+      <c r="BE137" s="28"/>
+      <c r="BF137" s="28"/>
       <c r="BG137" s="1"/>
-      <c r="BH137" s="24"/>
+      <c r="BH137" s="27"/>
       <c r="BI137" s="1"/>
-      <c r="BJ137" s="25"/>
+      <c r="BJ137" s="28"/>
     </row>
     <row r="138" spans="3:62">
-      <c r="C138" s="10"/>
+      <c r="C138" s="11"/>
       <c r="E138" s="1"/>
-      <c r="F138" s="12"/>
-      <c r="G138" s="12"/>
+      <c r="F138" s="13"/>
+      <c r="G138" s="13"/>
       <c r="H138" s="1"/>
       <c r="I138" s="1"/>
-      <c r="J138" s="4"/>
+      <c r="J138" s="21"/>
       <c r="AA138" s="1"/>
       <c r="AU138" s="1"/>
       <c r="AV138" s="1"/>
@@ -9694,21 +10653,21 @@
       <c r="BB138" s="1"/>
       <c r="BC138" s="1"/>
       <c r="BD138" s="1"/>
-      <c r="BE138" s="25"/>
-      <c r="BF138" s="25"/>
+      <c r="BE138" s="28"/>
+      <c r="BF138" s="28"/>
       <c r="BG138" s="1"/>
-      <c r="BH138" s="24"/>
+      <c r="BH138" s="27"/>
       <c r="BI138" s="1"/>
-      <c r="BJ138" s="25"/>
+      <c r="BJ138" s="28"/>
     </row>
     <row r="139" spans="3:62">
-      <c r="C139" s="10"/>
+      <c r="C139" s="11"/>
       <c r="E139" s="1"/>
-      <c r="F139" s="12"/>
-      <c r="G139" s="12"/>
+      <c r="F139" s="13"/>
+      <c r="G139" s="13"/>
       <c r="H139" s="1"/>
       <c r="I139" s="1"/>
-      <c r="J139" s="4"/>
+      <c r="J139" s="21"/>
       <c r="AA139" s="1"/>
       <c r="AU139" s="1"/>
       <c r="AV139" s="1"/>
@@ -9720,21 +10679,21 @@
       <c r="BB139" s="1"/>
       <c r="BC139" s="1"/>
       <c r="BD139" s="1"/>
-      <c r="BE139" s="25"/>
-      <c r="BF139" s="25"/>
+      <c r="BE139" s="28"/>
+      <c r="BF139" s="28"/>
       <c r="BG139" s="1"/>
-      <c r="BH139" s="24"/>
+      <c r="BH139" s="27"/>
       <c r="BI139" s="1"/>
-      <c r="BJ139" s="25"/>
+      <c r="BJ139" s="28"/>
     </row>
     <row r="140" spans="3:62">
-      <c r="C140" s="10"/>
+      <c r="C140" s="11"/>
       <c r="E140" s="1"/>
-      <c r="F140" s="12"/>
-      <c r="G140" s="12"/>
+      <c r="F140" s="13"/>
+      <c r="G140" s="13"/>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
-      <c r="J140" s="4"/>
+      <c r="J140" s="21"/>
       <c r="AA140" s="1"/>
       <c r="AU140" s="1"/>
       <c r="AV140" s="1"/>
@@ -9746,21 +10705,21 @@
       <c r="BB140" s="1"/>
       <c r="BC140" s="1"/>
       <c r="BD140" s="1"/>
-      <c r="BE140" s="25"/>
-      <c r="BF140" s="25"/>
+      <c r="BE140" s="28"/>
+      <c r="BF140" s="28"/>
       <c r="BG140" s="1"/>
-      <c r="BH140" s="24"/>
+      <c r="BH140" s="27"/>
       <c r="BI140" s="1"/>
-      <c r="BJ140" s="25"/>
+      <c r="BJ140" s="28"/>
     </row>
     <row r="141" spans="3:62">
-      <c r="C141" s="10"/>
+      <c r="C141" s="11"/>
       <c r="E141" s="1"/>
-      <c r="F141" s="12"/>
-      <c r="G141" s="12"/>
+      <c r="F141" s="13"/>
+      <c r="G141" s="13"/>
       <c r="H141" s="1"/>
       <c r="I141" s="1"/>
-      <c r="J141" s="4"/>
+      <c r="J141" s="21"/>
       <c r="AA141" s="1"/>
       <c r="AU141" s="1"/>
       <c r="AV141" s="1"/>
@@ -9772,21 +10731,21 @@
       <c r="BB141" s="1"/>
       <c r="BC141" s="1"/>
       <c r="BD141" s="1"/>
-      <c r="BE141" s="25"/>
-      <c r="BF141" s="25"/>
+      <c r="BE141" s="28"/>
+      <c r="BF141" s="28"/>
       <c r="BG141" s="1"/>
-      <c r="BH141" s="24"/>
+      <c r="BH141" s="27"/>
       <c r="BI141" s="1"/>
-      <c r="BJ141" s="25"/>
+      <c r="BJ141" s="28"/>
     </row>
     <row r="142" spans="3:62">
-      <c r="C142" s="10"/>
+      <c r="C142" s="11"/>
       <c r="E142" s="1"/>
-      <c r="F142" s="12"/>
-      <c r="G142" s="12"/>
+      <c r="F142" s="13"/>
+      <c r="G142" s="13"/>
       <c r="H142" s="1"/>
       <c r="I142" s="1"/>
-      <c r="J142" s="4"/>
+      <c r="J142" s="21"/>
       <c r="AA142" s="1"/>
       <c r="AU142" s="1"/>
       <c r="AV142" s="1"/>
@@ -9798,21 +10757,21 @@
       <c r="BB142" s="1"/>
       <c r="BC142" s="1"/>
       <c r="BD142" s="1"/>
-      <c r="BE142" s="25"/>
-      <c r="BF142" s="25"/>
+      <c r="BE142" s="28"/>
+      <c r="BF142" s="28"/>
       <c r="BG142" s="1"/>
-      <c r="BH142" s="24"/>
+      <c r="BH142" s="27"/>
       <c r="BI142" s="1"/>
-      <c r="BJ142" s="25"/>
+      <c r="BJ142" s="28"/>
     </row>
     <row r="143" spans="3:62">
-      <c r="C143" s="10"/>
+      <c r="C143" s="11"/>
       <c r="E143" s="1"/>
-      <c r="F143" s="12"/>
-      <c r="G143" s="12"/>
+      <c r="F143" s="13"/>
+      <c r="G143" s="13"/>
       <c r="H143" s="1"/>
       <c r="I143" s="1"/>
-      <c r="J143" s="4"/>
+      <c r="J143" s="21"/>
       <c r="AA143" s="1"/>
       <c r="AU143" s="1"/>
       <c r="AV143" s="1"/>
@@ -9824,21 +10783,21 @@
       <c r="BB143" s="1"/>
       <c r="BC143" s="1"/>
       <c r="BD143" s="1"/>
-      <c r="BE143" s="25"/>
-      <c r="BF143" s="25"/>
+      <c r="BE143" s="28"/>
+      <c r="BF143" s="28"/>
       <c r="BG143" s="1"/>
-      <c r="BH143" s="24"/>
+      <c r="BH143" s="27"/>
       <c r="BI143" s="1"/>
-      <c r="BJ143" s="25"/>
+      <c r="BJ143" s="28"/>
     </row>
     <row r="144" spans="3:62">
-      <c r="C144" s="10"/>
+      <c r="C144" s="11"/>
       <c r="E144" s="1"/>
-      <c r="F144" s="12"/>
-      <c r="G144" s="12"/>
+      <c r="F144" s="13"/>
+      <c r="G144" s="13"/>
       <c r="H144" s="1"/>
       <c r="I144" s="1"/>
-      <c r="J144" s="4"/>
+      <c r="J144" s="21"/>
       <c r="AA144" s="1"/>
       <c r="AU144" s="1"/>
       <c r="AV144" s="1"/>
@@ -9850,21 +10809,21 @@
       <c r="BB144" s="1"/>
       <c r="BC144" s="1"/>
       <c r="BD144" s="1"/>
-      <c r="BE144" s="25"/>
-      <c r="BF144" s="25"/>
+      <c r="BE144" s="28"/>
+      <c r="BF144" s="28"/>
       <c r="BG144" s="1"/>
-      <c r="BH144" s="24"/>
+      <c r="BH144" s="27"/>
       <c r="BI144" s="1"/>
-      <c r="BJ144" s="25"/>
+      <c r="BJ144" s="28"/>
     </row>
     <row r="145" spans="3:62">
-      <c r="C145" s="10"/>
+      <c r="C145" s="11"/>
       <c r="E145" s="1"/>
-      <c r="F145" s="12"/>
-      <c r="G145" s="12"/>
+      <c r="F145" s="13"/>
+      <c r="G145" s="13"/>
       <c r="H145" s="1"/>
       <c r="I145" s="1"/>
-      <c r="J145" s="4"/>
+      <c r="J145" s="21"/>
       <c r="AA145" s="1"/>
       <c r="AU145" s="1"/>
       <c r="AV145" s="1"/>
@@ -9876,21 +10835,21 @@
       <c r="BB145" s="1"/>
       <c r="BC145" s="1"/>
       <c r="BD145" s="1"/>
-      <c r="BE145" s="25"/>
-      <c r="BF145" s="25"/>
+      <c r="BE145" s="28"/>
+      <c r="BF145" s="28"/>
       <c r="BG145" s="1"/>
-      <c r="BH145" s="24"/>
+      <c r="BH145" s="27"/>
       <c r="BI145" s="1"/>
-      <c r="BJ145" s="25"/>
+      <c r="BJ145" s="28"/>
     </row>
     <row r="146" spans="3:62">
-      <c r="C146" s="10"/>
+      <c r="C146" s="11"/>
       <c r="E146" s="1"/>
-      <c r="F146" s="12"/>
-      <c r="G146" s="12"/>
+      <c r="F146" s="13"/>
+      <c r="G146" s="13"/>
       <c r="H146" s="1"/>
       <c r="I146" s="1"/>
-      <c r="J146" s="4"/>
+      <c r="J146" s="21"/>
       <c r="AA146" s="1"/>
       <c r="AU146" s="1"/>
       <c r="AV146" s="1"/>
@@ -9902,21 +10861,21 @@
       <c r="BB146" s="1"/>
       <c r="BC146" s="1"/>
       <c r="BD146" s="1"/>
-      <c r="BE146" s="25"/>
-      <c r="BF146" s="25"/>
+      <c r="BE146" s="28"/>
+      <c r="BF146" s="28"/>
       <c r="BG146" s="1"/>
-      <c r="BH146" s="24"/>
+      <c r="BH146" s="27"/>
       <c r="BI146" s="1"/>
-      <c r="BJ146" s="25"/>
+      <c r="BJ146" s="28"/>
     </row>
     <row r="147" spans="3:62">
-      <c r="C147" s="10"/>
+      <c r="C147" s="11"/>
       <c r="E147" s="1"/>
-      <c r="F147" s="12"/>
-      <c r="G147" s="12"/>
+      <c r="F147" s="13"/>
+      <c r="G147" s="13"/>
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
-      <c r="J147" s="4"/>
+      <c r="J147" s="21"/>
       <c r="AA147" s="1"/>
       <c r="AU147" s="1"/>
       <c r="AV147" s="1"/>
@@ -9928,21 +10887,21 @@
       <c r="BB147" s="1"/>
       <c r="BC147" s="1"/>
       <c r="BD147" s="1"/>
-      <c r="BE147" s="25"/>
-      <c r="BF147" s="25"/>
+      <c r="BE147" s="28"/>
+      <c r="BF147" s="28"/>
       <c r="BG147" s="1"/>
-      <c r="BH147" s="24"/>
+      <c r="BH147" s="27"/>
       <c r="BI147" s="1"/>
-      <c r="BJ147" s="25"/>
+      <c r="BJ147" s="28"/>
     </row>
     <row r="148" spans="3:62">
-      <c r="C148" s="10"/>
+      <c r="C148" s="11"/>
       <c r="E148" s="1"/>
-      <c r="F148" s="12"/>
-      <c r="G148" s="12"/>
+      <c r="F148" s="13"/>
+      <c r="G148" s="13"/>
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
-      <c r="J148" s="4"/>
+      <c r="J148" s="21"/>
       <c r="AA148" s="1"/>
       <c r="AU148" s="1"/>
       <c r="AV148" s="1"/>
@@ -9954,21 +10913,21 @@
       <c r="BB148" s="1"/>
       <c r="BC148" s="1"/>
       <c r="BD148" s="1"/>
-      <c r="BE148" s="25"/>
-      <c r="BF148" s="25"/>
+      <c r="BE148" s="28"/>
+      <c r="BF148" s="28"/>
       <c r="BG148" s="1"/>
-      <c r="BH148" s="24"/>
+      <c r="BH148" s="27"/>
       <c r="BI148" s="1"/>
-      <c r="BJ148" s="25"/>
+      <c r="BJ148" s="28"/>
     </row>
     <row r="149" spans="3:62">
-      <c r="C149" s="10"/>
+      <c r="C149" s="11"/>
       <c r="E149" s="1"/>
-      <c r="F149" s="12"/>
-      <c r="G149" s="12"/>
+      <c r="F149" s="13"/>
+      <c r="G149" s="13"/>
       <c r="H149" s="1"/>
       <c r="I149" s="1"/>
-      <c r="J149" s="4"/>
+      <c r="J149" s="21"/>
       <c r="AA149" s="1"/>
       <c r="AU149" s="1"/>
       <c r="AV149" s="1"/>
@@ -9980,21 +10939,21 @@
       <c r="BB149" s="1"/>
       <c r="BC149" s="1"/>
       <c r="BD149" s="1"/>
-      <c r="BE149" s="25"/>
-      <c r="BF149" s="25"/>
+      <c r="BE149" s="28"/>
+      <c r="BF149" s="28"/>
       <c r="BG149" s="1"/>
-      <c r="BH149" s="24"/>
+      <c r="BH149" s="27"/>
       <c r="BI149" s="1"/>
-      <c r="BJ149" s="25"/>
+      <c r="BJ149" s="28"/>
     </row>
     <row r="150" spans="3:62">
-      <c r="C150" s="10"/>
+      <c r="C150" s="11"/>
       <c r="E150" s="1"/>
-      <c r="F150" s="12"/>
-      <c r="G150" s="12"/>
+      <c r="F150" s="13"/>
+      <c r="G150" s="13"/>
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
-      <c r="J150" s="4"/>
+      <c r="J150" s="21"/>
       <c r="AA150" s="1"/>
       <c r="AU150" s="1"/>
       <c r="AV150" s="1"/>
@@ -10006,21 +10965,21 @@
       <c r="BB150" s="1"/>
       <c r="BC150" s="1"/>
       <c r="BD150" s="1"/>
-      <c r="BE150" s="25"/>
-      <c r="BF150" s="25"/>
+      <c r="BE150" s="28"/>
+      <c r="BF150" s="28"/>
       <c r="BG150" s="1"/>
-      <c r="BH150" s="24"/>
+      <c r="BH150" s="27"/>
       <c r="BI150" s="1"/>
-      <c r="BJ150" s="25"/>
+      <c r="BJ150" s="28"/>
     </row>
     <row r="151" spans="3:62">
-      <c r="C151" s="10"/>
+      <c r="C151" s="11"/>
       <c r="E151" s="1"/>
-      <c r="F151" s="12"/>
-      <c r="G151" s="12"/>
+      <c r="F151" s="13"/>
+      <c r="G151" s="13"/>
       <c r="H151" s="1"/>
       <c r="I151" s="1"/>
-      <c r="J151" s="4"/>
+      <c r="J151" s="21"/>
       <c r="AA151" s="1"/>
       <c r="AU151" s="1"/>
       <c r="AV151" s="1"/>
@@ -10032,21 +10991,21 @@
       <c r="BB151" s="1"/>
       <c r="BC151" s="1"/>
       <c r="BD151" s="1"/>
-      <c r="BE151" s="25"/>
-      <c r="BF151" s="25"/>
+      <c r="BE151" s="28"/>
+      <c r="BF151" s="28"/>
       <c r="BG151" s="1"/>
-      <c r="BH151" s="24"/>
+      <c r="BH151" s="27"/>
       <c r="BI151" s="1"/>
-      <c r="BJ151" s="25"/>
+      <c r="BJ151" s="28"/>
     </row>
     <row r="152" spans="3:62">
-      <c r="C152" s="10"/>
+      <c r="C152" s="11"/>
       <c r="E152" s="1"/>
-      <c r="F152" s="12"/>
-      <c r="G152" s="12"/>
+      <c r="F152" s="13"/>
+      <c r="G152" s="13"/>
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
-      <c r="J152" s="4"/>
+      <c r="J152" s="21"/>
       <c r="AA152" s="1"/>
       <c r="AU152" s="1"/>
       <c r="AV152" s="1"/>
@@ -10058,21 +11017,21 @@
       <c r="BB152" s="1"/>
       <c r="BC152" s="1"/>
       <c r="BD152" s="1"/>
-      <c r="BE152" s="25"/>
-      <c r="BF152" s="25"/>
+      <c r="BE152" s="28"/>
+      <c r="BF152" s="28"/>
       <c r="BG152" s="1"/>
-      <c r="BH152" s="24"/>
+      <c r="BH152" s="27"/>
       <c r="BI152" s="1"/>
-      <c r="BJ152" s="25"/>
+      <c r="BJ152" s="28"/>
     </row>
     <row r="153" spans="3:62">
-      <c r="C153" s="10"/>
+      <c r="C153" s="11"/>
       <c r="E153" s="1"/>
-      <c r="F153" s="12"/>
-      <c r="G153" s="12"/>
+      <c r="F153" s="13"/>
+      <c r="G153" s="13"/>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
-      <c r="J153" s="4"/>
+      <c r="J153" s="21"/>
       <c r="AA153" s="1"/>
       <c r="AU153" s="1"/>
       <c r="AV153" s="1"/>
@@ -10084,21 +11043,21 @@
       <c r="BB153" s="1"/>
       <c r="BC153" s="1"/>
       <c r="BD153" s="1"/>
-      <c r="BE153" s="25"/>
-      <c r="BF153" s="25"/>
+      <c r="BE153" s="28"/>
+      <c r="BF153" s="28"/>
       <c r="BG153" s="1"/>
-      <c r="BH153" s="24"/>
+      <c r="BH153" s="27"/>
       <c r="BI153" s="1"/>
-      <c r="BJ153" s="25"/>
+      <c r="BJ153" s="28"/>
     </row>
     <row r="154" spans="3:62">
-      <c r="C154" s="10"/>
+      <c r="C154" s="11"/>
       <c r="E154" s="1"/>
-      <c r="F154" s="12"/>
-      <c r="G154" s="12"/>
+      <c r="F154" s="13"/>
+      <c r="G154" s="13"/>
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
-      <c r="J154" s="4"/>
+      <c r="J154" s="21"/>
       <c r="AA154" s="1"/>
       <c r="AU154" s="1"/>
       <c r="AV154" s="1"/>
@@ -10110,21 +11069,21 @@
       <c r="BB154" s="1"/>
       <c r="BC154" s="1"/>
       <c r="BD154" s="1"/>
-      <c r="BE154" s="25"/>
-      <c r="BF154" s="25"/>
+      <c r="BE154" s="28"/>
+      <c r="BF154" s="28"/>
       <c r="BG154" s="1"/>
-      <c r="BH154" s="24"/>
+      <c r="BH154" s="27"/>
       <c r="BI154" s="1"/>
-      <c r="BJ154" s="25"/>
+      <c r="BJ154" s="28"/>
     </row>
     <row r="155" spans="3:62">
-      <c r="C155" s="10"/>
+      <c r="C155" s="11"/>
       <c r="E155" s="1"/>
-      <c r="F155" s="12"/>
-      <c r="G155" s="12"/>
+      <c r="F155" s="13"/>
+      <c r="G155" s="13"/>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
-      <c r="J155" s="4"/>
+      <c r="J155" s="21"/>
       <c r="AA155" s="1"/>
       <c r="AU155" s="1"/>
       <c r="AV155" s="1"/>
@@ -10136,21 +11095,21 @@
       <c r="BB155" s="1"/>
       <c r="BC155" s="1"/>
       <c r="BD155" s="1"/>
-      <c r="BE155" s="25"/>
-      <c r="BF155" s="25"/>
+      <c r="BE155" s="28"/>
+      <c r="BF155" s="28"/>
       <c r="BG155" s="1"/>
-      <c r="BH155" s="24"/>
+      <c r="BH155" s="27"/>
       <c r="BI155" s="1"/>
-      <c r="BJ155" s="25"/>
+      <c r="BJ155" s="28"/>
     </row>
     <row r="156" spans="3:62">
-      <c r="C156" s="10"/>
+      <c r="C156" s="11"/>
       <c r="E156" s="1"/>
-      <c r="F156" s="12"/>
-      <c r="G156" s="12"/>
+      <c r="F156" s="13"/>
+      <c r="G156" s="13"/>
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
-      <c r="J156" s="4"/>
+      <c r="J156" s="21"/>
       <c r="AA156" s="1"/>
       <c r="AU156" s="1"/>
       <c r="AV156" s="1"/>
@@ -10162,21 +11121,21 @@
       <c r="BB156" s="1"/>
       <c r="BC156" s="1"/>
       <c r="BD156" s="1"/>
-      <c r="BE156" s="25"/>
-      <c r="BF156" s="25"/>
+      <c r="BE156" s="28"/>
+      <c r="BF156" s="28"/>
       <c r="BG156" s="1"/>
-      <c r="BH156" s="24"/>
+      <c r="BH156" s="27"/>
       <c r="BI156" s="1"/>
-      <c r="BJ156" s="25"/>
+      <c r="BJ156" s="28"/>
     </row>
     <row r="157" ht="14.25" customHeight="1" spans="3:62">
-      <c r="C157" s="10"/>
+      <c r="C157" s="11"/>
       <c r="E157" s="1"/>
-      <c r="F157" s="12"/>
-      <c r="G157" s="12"/>
+      <c r="F157" s="13"/>
+      <c r="G157" s="13"/>
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
-      <c r="J157" s="4"/>
+      <c r="J157" s="21"/>
       <c r="AA157" s="1"/>
       <c r="AU157" s="1"/>
       <c r="AV157" s="1"/>
@@ -10188,21 +11147,21 @@
       <c r="BB157" s="1"/>
       <c r="BC157" s="1"/>
       <c r="BD157" s="1"/>
-      <c r="BE157" s="25"/>
-      <c r="BF157" s="25"/>
+      <c r="BE157" s="28"/>
+      <c r="BF157" s="28"/>
       <c r="BG157" s="1"/>
-      <c r="BH157" s="24"/>
+      <c r="BH157" s="27"/>
       <c r="BI157" s="1"/>
-      <c r="BJ157" s="25"/>
+      <c r="BJ157" s="28"/>
     </row>
     <row r="158" spans="3:62">
-      <c r="C158" s="10"/>
+      <c r="C158" s="11"/>
       <c r="E158" s="1"/>
-      <c r="F158" s="12"/>
-      <c r="G158" s="12"/>
+      <c r="F158" s="13"/>
+      <c r="G158" s="13"/>
       <c r="H158" s="1"/>
       <c r="I158" s="1"/>
-      <c r="J158" s="4"/>
+      <c r="J158" s="21"/>
       <c r="AA158" s="1"/>
       <c r="AU158" s="1"/>
       <c r="AV158" s="1"/>
@@ -10214,21 +11173,21 @@
       <c r="BB158" s="1"/>
       <c r="BC158" s="1"/>
       <c r="BD158" s="1"/>
-      <c r="BE158" s="25"/>
-      <c r="BF158" s="25"/>
+      <c r="BE158" s="28"/>
+      <c r="BF158" s="28"/>
       <c r="BG158" s="1"/>
-      <c r="BH158" s="24"/>
+      <c r="BH158" s="27"/>
       <c r="BI158" s="1"/>
-      <c r="BJ158" s="25"/>
+      <c r="BJ158" s="28"/>
     </row>
     <row r="159" spans="3:62">
-      <c r="C159" s="10"/>
+      <c r="C159" s="11"/>
       <c r="E159" s="1"/>
-      <c r="F159" s="12"/>
-      <c r="G159" s="12"/>
+      <c r="F159" s="13"/>
+      <c r="G159" s="13"/>
       <c r="H159" s="1"/>
       <c r="I159" s="1"/>
-      <c r="J159" s="4"/>
+      <c r="J159" s="21"/>
       <c r="AA159" s="1"/>
       <c r="AU159" s="1"/>
       <c r="AV159" s="1"/>
@@ -10240,21 +11199,21 @@
       <c r="BB159" s="1"/>
       <c r="BC159" s="1"/>
       <c r="BD159" s="1"/>
-      <c r="BE159" s="25"/>
-      <c r="BF159" s="25"/>
+      <c r="BE159" s="28"/>
+      <c r="BF159" s="28"/>
       <c r="BG159" s="1"/>
-      <c r="BH159" s="24"/>
+      <c r="BH159" s="27"/>
       <c r="BI159" s="1"/>
-      <c r="BJ159" s="25"/>
+      <c r="BJ159" s="28"/>
     </row>
     <row r="160" spans="3:62">
-      <c r="C160" s="10"/>
+      <c r="C160" s="11"/>
       <c r="E160" s="1"/>
-      <c r="F160" s="12"/>
-      <c r="G160" s="12"/>
+      <c r="F160" s="13"/>
+      <c r="G160" s="13"/>
       <c r="H160" s="1"/>
       <c r="I160" s="1"/>
-      <c r="J160" s="4"/>
+      <c r="J160" s="21"/>
       <c r="AA160" s="1"/>
       <c r="AU160" s="1"/>
       <c r="AV160" s="1"/>
@@ -10266,21 +11225,21 @@
       <c r="BB160" s="1"/>
       <c r="BC160" s="1"/>
       <c r="BD160" s="1"/>
-      <c r="BE160" s="25"/>
-      <c r="BF160" s="25"/>
+      <c r="BE160" s="28"/>
+      <c r="BF160" s="28"/>
       <c r="BG160" s="1"/>
-      <c r="BH160" s="24"/>
+      <c r="BH160" s="27"/>
       <c r="BI160" s="1"/>
-      <c r="BJ160" s="25"/>
+      <c r="BJ160" s="28"/>
     </row>
     <row r="161" spans="3:62">
-      <c r="C161" s="10"/>
+      <c r="C161" s="11"/>
       <c r="E161" s="1"/>
-      <c r="F161" s="12"/>
-      <c r="G161" s="12"/>
+      <c r="F161" s="13"/>
+      <c r="G161" s="13"/>
       <c r="H161" s="1"/>
       <c r="I161" s="1"/>
-      <c r="J161" s="4"/>
+      <c r="J161" s="21"/>
       <c r="AA161" s="1"/>
       <c r="AU161" s="1"/>
       <c r="AV161" s="1"/>
@@ -10292,21 +11251,21 @@
       <c r="BB161" s="1"/>
       <c r="BC161" s="1"/>
       <c r="BD161" s="1"/>
-      <c r="BE161" s="25"/>
-      <c r="BF161" s="25"/>
+      <c r="BE161" s="28"/>
+      <c r="BF161" s="28"/>
       <c r="BG161" s="1"/>
-      <c r="BH161" s="24"/>
+      <c r="BH161" s="27"/>
       <c r="BI161" s="1"/>
-      <c r="BJ161" s="25"/>
+      <c r="BJ161" s="28"/>
     </row>
     <row r="162" ht="15.75" customHeight="1" spans="3:62">
-      <c r="C162" s="10"/>
+      <c r="C162" s="11"/>
       <c r="E162" s="1"/>
-      <c r="F162" s="12"/>
-      <c r="G162" s="12"/>
+      <c r="F162" s="13"/>
+      <c r="G162" s="13"/>
       <c r="H162" s="1"/>
       <c r="I162" s="1"/>
-      <c r="J162" s="4"/>
+      <c r="J162" s="21"/>
       <c r="AA162" s="1"/>
       <c r="AU162" s="1"/>
       <c r="AV162" s="1"/>
@@ -10318,21 +11277,21 @@
       <c r="BB162" s="1"/>
       <c r="BC162" s="1"/>
       <c r="BD162" s="1"/>
-      <c r="BE162" s="25"/>
-      <c r="BF162" s="25"/>
+      <c r="BE162" s="28"/>
+      <c r="BF162" s="28"/>
       <c r="BG162" s="1"/>
-      <c r="BH162" s="24"/>
+      <c r="BH162" s="27"/>
       <c r="BI162" s="1"/>
-      <c r="BJ162" s="25"/>
+      <c r="BJ162" s="28"/>
     </row>
     <row r="163" ht="14.25" customHeight="1" spans="3:62">
-      <c r="C163" s="10"/>
+      <c r="C163" s="11"/>
       <c r="E163" s="1"/>
-      <c r="F163" s="12"/>
-      <c r="G163" s="12"/>
+      <c r="F163" s="13"/>
+      <c r="G163" s="13"/>
       <c r="H163" s="1"/>
       <c r="I163" s="1"/>
-      <c r="J163" s="4"/>
+      <c r="J163" s="21"/>
       <c r="AA163" s="1"/>
       <c r="AU163" s="1"/>
       <c r="AV163" s="1"/>
@@ -10344,21 +11303,21 @@
       <c r="BB163" s="1"/>
       <c r="BC163" s="1"/>
       <c r="BD163" s="1"/>
-      <c r="BE163" s="25"/>
-      <c r="BF163" s="25"/>
+      <c r="BE163" s="28"/>
+      <c r="BF163" s="28"/>
       <c r="BG163" s="1"/>
-      <c r="BH163" s="24"/>
+      <c r="BH163" s="27"/>
       <c r="BI163" s="1"/>
-      <c r="BJ163" s="25"/>
+      <c r="BJ163" s="28"/>
     </row>
     <row r="164" spans="3:62">
-      <c r="C164" s="10"/>
+      <c r="C164" s="11"/>
       <c r="E164" s="1"/>
-      <c r="F164" s="12"/>
-      <c r="G164" s="12"/>
+      <c r="F164" s="13"/>
+      <c r="G164" s="13"/>
       <c r="H164" s="1"/>
       <c r="I164" s="1"/>
-      <c r="J164" s="4"/>
+      <c r="J164" s="21"/>
       <c r="AA164" s="1"/>
       <c r="AU164" s="1"/>
       <c r="AV164" s="1"/>
@@ -10370,21 +11329,21 @@
       <c r="BB164" s="1"/>
       <c r="BC164" s="1"/>
       <c r="BD164" s="1"/>
-      <c r="BE164" s="25"/>
-      <c r="BF164" s="25"/>
+      <c r="BE164" s="28"/>
+      <c r="BF164" s="28"/>
       <c r="BG164" s="1"/>
-      <c r="BH164" s="24"/>
+      <c r="BH164" s="27"/>
       <c r="BI164" s="1"/>
-      <c r="BJ164" s="25"/>
+      <c r="BJ164" s="28"/>
     </row>
     <row r="165" spans="3:62">
-      <c r="C165" s="10"/>
+      <c r="C165" s="11"/>
       <c r="E165" s="1"/>
-      <c r="F165" s="12"/>
-      <c r="G165" s="12"/>
+      <c r="F165" s="13"/>
+      <c r="G165" s="13"/>
       <c r="H165" s="1"/>
       <c r="I165" s="1"/>
-      <c r="J165" s="4"/>
+      <c r="J165" s="21"/>
       <c r="AA165" s="1"/>
       <c r="AU165" s="1"/>
       <c r="AV165" s="1"/>
@@ -10396,24 +11355,24 @@
       <c r="BB165" s="1"/>
       <c r="BC165" s="1"/>
       <c r="BD165" s="1"/>
-      <c r="BE165" s="25"/>
-      <c r="BF165" s="25"/>
+      <c r="BE165" s="28"/>
+      <c r="BF165" s="28"/>
       <c r="BG165" s="1"/>
-      <c r="BH165" s="24"/>
+      <c r="BH165" s="27"/>
       <c r="BI165" s="1"/>
-      <c r="BJ165" s="25"/>
+      <c r="BJ165" s="28"/>
     </row>
     <row r="166" spans="1:62">
       <c r="A166" s="1"/>
-      <c r="B166" s="8"/>
+      <c r="B166" s="7"/>
       <c r="C166" s="1"/>
-      <c r="D166" s="8"/>
+      <c r="D166" s="7"/>
       <c r="E166" s="1"/>
-      <c r="F166" s="12"/>
-      <c r="G166" s="12"/>
+      <c r="F166" s="13"/>
+      <c r="G166" s="13"/>
       <c r="H166" s="1"/>
       <c r="I166" s="1"/>
-      <c r="J166" s="15"/>
+      <c r="J166" s="20"/>
       <c r="AO166" s="1"/>
       <c r="AP166" s="1"/>
       <c r="AU166" s="1"/>
@@ -10426,24 +11385,24 @@
       <c r="BB166" s="1"/>
       <c r="BC166" s="1"/>
       <c r="BD166" s="1"/>
-      <c r="BE166" s="25"/>
-      <c r="BF166" s="25"/>
+      <c r="BE166" s="28"/>
+      <c r="BF166" s="28"/>
       <c r="BG166" s="1"/>
-      <c r="BH166" s="24"/>
+      <c r="BH166" s="27"/>
       <c r="BI166" s="1"/>
-      <c r="BJ166" s="25"/>
+      <c r="BJ166" s="28"/>
     </row>
     <row r="167" spans="1:62">
       <c r="A167" s="1"/>
-      <c r="B167" s="8"/>
+      <c r="B167" s="7"/>
       <c r="C167" s="1"/>
-      <c r="D167" s="8"/>
+      <c r="D167" s="7"/>
       <c r="E167" s="1"/>
-      <c r="F167" s="12"/>
-      <c r="G167" s="12"/>
+      <c r="F167" s="13"/>
+      <c r="G167" s="13"/>
       <c r="H167" s="1"/>
       <c r="I167" s="1"/>
-      <c r="J167" s="15"/>
+      <c r="J167" s="20"/>
       <c r="AO167" s="1"/>
       <c r="AP167" s="1"/>
       <c r="AU167" s="1"/>
@@ -10456,23 +11415,23 @@
       <c r="BB167" s="1"/>
       <c r="BC167" s="1"/>
       <c r="BD167" s="1"/>
-      <c r="BE167" s="25"/>
-      <c r="BF167" s="25"/>
+      <c r="BE167" s="28"/>
+      <c r="BF167" s="28"/>
       <c r="BG167" s="1"/>
-      <c r="BH167" s="24"/>
+      <c r="BH167" s="27"/>
       <c r="BI167" s="1"/>
-      <c r="BJ167" s="25"/>
+      <c r="BJ167" s="28"/>
     </row>
     <row r="168" spans="2:62">
-      <c r="B168" s="8"/>
+      <c r="B168" s="7"/>
       <c r="C168" s="1"/>
-      <c r="D168" s="8"/>
+      <c r="D168" s="7"/>
       <c r="E168" s="1"/>
-      <c r="F168" s="12"/>
-      <c r="G168" s="12"/>
+      <c r="F168" s="13"/>
+      <c r="G168" s="13"/>
       <c r="H168" s="1"/>
       <c r="I168" s="1"/>
-      <c r="J168" s="15"/>
+      <c r="J168" s="20"/>
       <c r="AO168" s="1"/>
       <c r="AP168" s="1"/>
       <c r="AU168" s="1"/>
@@ -10485,24 +11444,24 @@
       <c r="BB168" s="1"/>
       <c r="BC168" s="1"/>
       <c r="BD168" s="1"/>
-      <c r="BE168" s="25"/>
-      <c r="BF168" s="25"/>
+      <c r="BE168" s="28"/>
+      <c r="BF168" s="28"/>
       <c r="BG168" s="1"/>
-      <c r="BH168" s="24"/>
+      <c r="BH168" s="27"/>
       <c r="BI168" s="1"/>
-      <c r="BJ168" s="25"/>
+      <c r="BJ168" s="28"/>
     </row>
     <row r="169" spans="1:62">
       <c r="A169" s="1"/>
-      <c r="B169" s="8"/>
+      <c r="B169" s="7"/>
       <c r="C169" s="1"/>
-      <c r="D169" s="8"/>
+      <c r="D169" s="7"/>
       <c r="E169" s="1"/>
-      <c r="F169" s="12"/>
-      <c r="G169" s="12"/>
+      <c r="F169" s="13"/>
+      <c r="G169" s="13"/>
       <c r="H169" s="1"/>
       <c r="I169" s="1"/>
-      <c r="J169" s="15"/>
+      <c r="J169" s="20"/>
       <c r="AO169" s="1"/>
       <c r="AP169" s="1"/>
       <c r="AU169" s="1"/>
@@ -10515,24 +11474,24 @@
       <c r="BB169" s="1"/>
       <c r="BC169" s="1"/>
       <c r="BD169" s="1"/>
-      <c r="BE169" s="25"/>
-      <c r="BF169" s="25"/>
+      <c r="BE169" s="28"/>
+      <c r="BF169" s="28"/>
       <c r="BG169" s="1"/>
-      <c r="BH169" s="24"/>
+      <c r="BH169" s="27"/>
       <c r="BI169" s="1"/>
-      <c r="BJ169" s="25"/>
+      <c r="BJ169" s="28"/>
     </row>
     <row r="170" spans="1:62">
       <c r="A170" s="1"/>
-      <c r="B170" s="8"/>
+      <c r="B170" s="7"/>
       <c r="C170" s="1"/>
-      <c r="D170" s="8"/>
+      <c r="D170" s="7"/>
       <c r="E170" s="1"/>
-      <c r="F170" s="12"/>
-      <c r="G170" s="12"/>
+      <c r="F170" s="13"/>
+      <c r="G170" s="13"/>
       <c r="H170" s="1"/>
       <c r="I170" s="1"/>
-      <c r="J170" s="15"/>
+      <c r="J170" s="20"/>
       <c r="AO170" s="1"/>
       <c r="AP170" s="1"/>
       <c r="AU170" s="1"/>
@@ -10545,24 +11504,24 @@
       <c r="BB170" s="1"/>
       <c r="BC170" s="1"/>
       <c r="BD170" s="1"/>
-      <c r="BE170" s="25"/>
-      <c r="BF170" s="25"/>
+      <c r="BE170" s="28"/>
+      <c r="BF170" s="28"/>
       <c r="BG170" s="1"/>
-      <c r="BH170" s="24"/>
+      <c r="BH170" s="27"/>
       <c r="BI170" s="1"/>
-      <c r="BJ170" s="25"/>
+      <c r="BJ170" s="28"/>
     </row>
     <row r="171" spans="1:62">
       <c r="A171" s="1"/>
-      <c r="B171" s="8"/>
+      <c r="B171" s="7"/>
       <c r="C171" s="1"/>
-      <c r="D171" s="8"/>
+      <c r="D171" s="7"/>
       <c r="E171" s="1"/>
-      <c r="F171" s="12"/>
-      <c r="G171" s="12"/>
+      <c r="F171" s="13"/>
+      <c r="G171" s="13"/>
       <c r="H171" s="1"/>
       <c r="I171" s="1"/>
-      <c r="J171" s="15"/>
+      <c r="J171" s="20"/>
       <c r="AO171" s="1"/>
       <c r="AP171" s="1"/>
       <c r="AU171" s="1"/>
@@ -10575,24 +11534,24 @@
       <c r="BB171" s="1"/>
       <c r="BC171" s="1"/>
       <c r="BD171" s="1"/>
-      <c r="BE171" s="25"/>
-      <c r="BF171" s="25"/>
+      <c r="BE171" s="28"/>
+      <c r="BF171" s="28"/>
       <c r="BG171" s="1"/>
-      <c r="BH171" s="24"/>
+      <c r="BH171" s="27"/>
       <c r="BI171" s="1"/>
-      <c r="BJ171" s="25"/>
+      <c r="BJ171" s="28"/>
     </row>
     <row r="172" spans="1:62">
       <c r="A172" s="1"/>
-      <c r="B172" s="8"/>
+      <c r="B172" s="7"/>
       <c r="C172" s="1"/>
-      <c r="D172" s="8"/>
+      <c r="D172" s="7"/>
       <c r="E172" s="1"/>
-      <c r="F172" s="12"/>
-      <c r="G172" s="12"/>
+      <c r="F172" s="13"/>
+      <c r="G172" s="13"/>
       <c r="H172" s="1"/>
       <c r="I172" s="1"/>
-      <c r="J172" s="15"/>
+      <c r="J172" s="20"/>
       <c r="AO172" s="1"/>
       <c r="AP172" s="1"/>
       <c r="AU172" s="1"/>
@@ -10605,24 +11564,24 @@
       <c r="BB172" s="1"/>
       <c r="BC172" s="1"/>
       <c r="BD172" s="1"/>
-      <c r="BE172" s="25"/>
-      <c r="BF172" s="25"/>
+      <c r="BE172" s="28"/>
+      <c r="BF172" s="28"/>
       <c r="BG172" s="1"/>
-      <c r="BH172" s="24"/>
+      <c r="BH172" s="27"/>
       <c r="BI172" s="1"/>
-      <c r="BJ172" s="25"/>
+      <c r="BJ172" s="28"/>
     </row>
     <row r="173" spans="1:62">
       <c r="A173" s="1"/>
-      <c r="B173" s="8"/>
+      <c r="B173" s="7"/>
       <c r="C173" s="1"/>
-      <c r="D173" s="8"/>
+      <c r="D173" s="7"/>
       <c r="E173" s="1"/>
-      <c r="F173" s="12"/>
-      <c r="G173" s="12"/>
+      <c r="F173" s="13"/>
+      <c r="G173" s="13"/>
       <c r="H173" s="1"/>
       <c r="I173" s="1"/>
-      <c r="J173" s="15"/>
+      <c r="J173" s="20"/>
       <c r="AO173" s="1"/>
       <c r="AP173" s="1"/>
       <c r="AU173" s="1"/>
@@ -10635,24 +11594,24 @@
       <c r="BB173" s="1"/>
       <c r="BC173" s="1"/>
       <c r="BD173" s="1"/>
-      <c r="BE173" s="25"/>
-      <c r="BF173" s="25"/>
+      <c r="BE173" s="28"/>
+      <c r="BF173" s="28"/>
       <c r="BG173" s="1"/>
-      <c r="BH173" s="24"/>
+      <c r="BH173" s="27"/>
       <c r="BI173" s="1"/>
-      <c r="BJ173" s="25"/>
+      <c r="BJ173" s="28"/>
     </row>
     <row r="174" spans="1:62">
       <c r="A174" s="1"/>
-      <c r="B174" s="8"/>
+      <c r="B174" s="7"/>
       <c r="C174" s="1"/>
-      <c r="D174" s="8"/>
+      <c r="D174" s="7"/>
       <c r="E174" s="1"/>
-      <c r="F174" s="12"/>
-      <c r="G174" s="12"/>
+      <c r="F174" s="13"/>
+      <c r="G174" s="13"/>
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
-      <c r="J174" s="15"/>
+      <c r="J174" s="20"/>
       <c r="AO174" s="1"/>
       <c r="AP174" s="1"/>
       <c r="AU174" s="1"/>
@@ -10665,24 +11624,24 @@
       <c r="BB174" s="1"/>
       <c r="BC174" s="1"/>
       <c r="BD174" s="1"/>
-      <c r="BE174" s="25"/>
-      <c r="BF174" s="25"/>
+      <c r="BE174" s="28"/>
+      <c r="BF174" s="28"/>
       <c r="BG174" s="1"/>
-      <c r="BH174" s="24"/>
+      <c r="BH174" s="27"/>
       <c r="BI174" s="1"/>
-      <c r="BJ174" s="25"/>
+      <c r="BJ174" s="28"/>
     </row>
     <row r="175" spans="1:62">
       <c r="A175" s="1"/>
-      <c r="B175" s="8"/>
+      <c r="B175" s="7"/>
       <c r="C175" s="1"/>
-      <c r="D175" s="8"/>
+      <c r="D175" s="7"/>
       <c r="E175" s="1"/>
-      <c r="F175" s="12"/>
-      <c r="G175" s="12"/>
+      <c r="F175" s="13"/>
+      <c r="G175" s="13"/>
       <c r="H175" s="1"/>
       <c r="I175" s="1"/>
-      <c r="J175" s="15"/>
+      <c r="J175" s="20"/>
       <c r="AO175" s="1"/>
       <c r="AP175" s="1"/>
       <c r="AU175" s="1"/>
@@ -10695,24 +11654,24 @@
       <c r="BB175" s="1"/>
       <c r="BC175" s="1"/>
       <c r="BD175" s="1"/>
-      <c r="BE175" s="25"/>
-      <c r="BF175" s="25"/>
+      <c r="BE175" s="28"/>
+      <c r="BF175" s="28"/>
       <c r="BG175" s="1"/>
-      <c r="BH175" s="24"/>
+      <c r="BH175" s="27"/>
       <c r="BI175" s="1"/>
-      <c r="BJ175" s="25"/>
+      <c r="BJ175" s="28"/>
     </row>
     <row r="176" spans="1:62">
       <c r="A176" s="1"/>
-      <c r="B176" s="8"/>
+      <c r="B176" s="7"/>
       <c r="C176" s="1"/>
-      <c r="D176" s="8"/>
+      <c r="D176" s="7"/>
       <c r="E176" s="1"/>
-      <c r="F176" s="12"/>
-      <c r="G176" s="12"/>
+      <c r="F176" s="13"/>
+      <c r="G176" s="13"/>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
-      <c r="J176" s="15"/>
+      <c r="J176" s="20"/>
       <c r="AO176" s="1"/>
       <c r="AP176" s="1"/>
       <c r="AU176" s="1"/>
@@ -10725,24 +11684,24 @@
       <c r="BB176" s="1"/>
       <c r="BC176" s="1"/>
       <c r="BD176" s="1"/>
-      <c r="BE176" s="25"/>
-      <c r="BF176" s="25"/>
+      <c r="BE176" s="28"/>
+      <c r="BF176" s="28"/>
       <c r="BG176" s="1"/>
-      <c r="BH176" s="24"/>
+      <c r="BH176" s="27"/>
       <c r="BI176" s="1"/>
-      <c r="BJ176" s="25"/>
+      <c r="BJ176" s="28"/>
     </row>
     <row r="177" spans="1:62">
       <c r="A177" s="1"/>
-      <c r="B177" s="8"/>
+      <c r="B177" s="7"/>
       <c r="C177" s="1"/>
-      <c r="D177" s="8"/>
+      <c r="D177" s="7"/>
       <c r="E177" s="1"/>
-      <c r="F177" s="12"/>
-      <c r="G177" s="12"/>
+      <c r="F177" s="13"/>
+      <c r="G177" s="13"/>
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
-      <c r="J177" s="15"/>
+      <c r="J177" s="20"/>
       <c r="AO177" s="1"/>
       <c r="AP177" s="1"/>
       <c r="AU177" s="1"/>
@@ -10755,24 +11714,24 @@
       <c r="BB177" s="1"/>
       <c r="BC177" s="1"/>
       <c r="BD177" s="1"/>
-      <c r="BE177" s="25"/>
-      <c r="BF177" s="25"/>
+      <c r="BE177" s="28"/>
+      <c r="BF177" s="28"/>
       <c r="BG177" s="1"/>
-      <c r="BH177" s="24"/>
+      <c r="BH177" s="27"/>
       <c r="BI177" s="1"/>
-      <c r="BJ177" s="25"/>
+      <c r="BJ177" s="28"/>
     </row>
     <row r="178" spans="1:62">
       <c r="A178" s="1"/>
-      <c r="B178" s="8"/>
+      <c r="B178" s="7"/>
       <c r="C178" s="1"/>
-      <c r="D178" s="8"/>
+      <c r="D178" s="7"/>
       <c r="E178" s="1"/>
-      <c r="F178" s="12"/>
-      <c r="G178" s="12"/>
+      <c r="F178" s="13"/>
+      <c r="G178" s="13"/>
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
-      <c r="J178" s="15"/>
+      <c r="J178" s="20"/>
       <c r="AO178" s="1"/>
       <c r="AP178" s="1"/>
       <c r="AU178" s="1"/>
@@ -10785,24 +11744,24 @@
       <c r="BB178" s="1"/>
       <c r="BC178" s="1"/>
       <c r="BD178" s="1"/>
-      <c r="BE178" s="25"/>
-      <c r="BF178" s="25"/>
+      <c r="BE178" s="28"/>
+      <c r="BF178" s="28"/>
       <c r="BG178" s="1"/>
-      <c r="BH178" s="24"/>
+      <c r="BH178" s="27"/>
       <c r="BI178" s="1"/>
-      <c r="BJ178" s="25"/>
+      <c r="BJ178" s="28"/>
     </row>
     <row r="179" spans="1:62">
       <c r="A179" s="1"/>
-      <c r="B179" s="8"/>
+      <c r="B179" s="7"/>
       <c r="C179" s="1"/>
-      <c r="D179" s="8"/>
+      <c r="D179" s="7"/>
       <c r="E179" s="1"/>
-      <c r="F179" s="12"/>
-      <c r="G179" s="12"/>
+      <c r="F179" s="13"/>
+      <c r="G179" s="13"/>
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
-      <c r="J179" s="15"/>
+      <c r="J179" s="20"/>
       <c r="AO179" s="1"/>
       <c r="AP179" s="1"/>
       <c r="AU179" s="1"/>
@@ -10815,24 +11774,24 @@
       <c r="BB179" s="1"/>
       <c r="BC179" s="1"/>
       <c r="BD179" s="1"/>
-      <c r="BE179" s="25"/>
-      <c r="BF179" s="25"/>
+      <c r="BE179" s="28"/>
+      <c r="BF179" s="28"/>
       <c r="BG179" s="1"/>
-      <c r="BH179" s="24"/>
+      <c r="BH179" s="27"/>
       <c r="BI179" s="1"/>
-      <c r="BJ179" s="25"/>
+      <c r="BJ179" s="28"/>
     </row>
     <row r="180" spans="1:62">
       <c r="A180" s="1"/>
-      <c r="B180" s="8"/>
+      <c r="B180" s="7"/>
       <c r="C180" s="1"/>
-      <c r="D180" s="8"/>
+      <c r="D180" s="7"/>
       <c r="E180" s="1"/>
-      <c r="F180" s="12"/>
-      <c r="G180" s="12"/>
+      <c r="F180" s="13"/>
+      <c r="G180" s="13"/>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
-      <c r="J180" s="15"/>
+      <c r="J180" s="20"/>
       <c r="AO180" s="1"/>
       <c r="AP180" s="1"/>
       <c r="AU180" s="1"/>
@@ -10845,24 +11804,24 @@
       <c r="BB180" s="1"/>
       <c r="BC180" s="1"/>
       <c r="BD180" s="1"/>
-      <c r="BE180" s="25"/>
-      <c r="BF180" s="25"/>
+      <c r="BE180" s="28"/>
+      <c r="BF180" s="28"/>
       <c r="BG180" s="1"/>
-      <c r="BH180" s="24"/>
+      <c r="BH180" s="27"/>
       <c r="BI180" s="1"/>
-      <c r="BJ180" s="25"/>
+      <c r="BJ180" s="28"/>
     </row>
     <row r="181" spans="1:62">
       <c r="A181" s="1"/>
-      <c r="B181" s="8"/>
+      <c r="B181" s="7"/>
       <c r="C181" s="1"/>
-      <c r="D181" s="8"/>
+      <c r="D181" s="7"/>
       <c r="E181" s="1"/>
-      <c r="F181" s="12"/>
-      <c r="G181" s="12"/>
+      <c r="F181" s="13"/>
+      <c r="G181" s="13"/>
       <c r="H181" s="1"/>
       <c r="I181" s="1"/>
-      <c r="J181" s="15"/>
+      <c r="J181" s="20"/>
       <c r="AO181" s="1"/>
       <c r="AP181" s="1"/>
       <c r="AU181" s="1"/>
@@ -10875,24 +11834,24 @@
       <c r="BB181" s="1"/>
       <c r="BC181" s="1"/>
       <c r="BD181" s="1"/>
-      <c r="BE181" s="25"/>
-      <c r="BF181" s="25"/>
+      <c r="BE181" s="28"/>
+      <c r="BF181" s="28"/>
       <c r="BG181" s="1"/>
-      <c r="BH181" s="24"/>
+      <c r="BH181" s="27"/>
       <c r="BI181" s="1"/>
-      <c r="BJ181" s="25"/>
+      <c r="BJ181" s="28"/>
     </row>
     <row r="182" spans="1:62">
       <c r="A182" s="1"/>
-      <c r="B182" s="8"/>
+      <c r="B182" s="7"/>
       <c r="C182" s="1"/>
-      <c r="D182" s="8"/>
+      <c r="D182" s="7"/>
       <c r="E182" s="1"/>
-      <c r="F182" s="12"/>
-      <c r="G182" s="12"/>
+      <c r="F182" s="13"/>
+      <c r="G182" s="13"/>
       <c r="H182" s="1"/>
       <c r="I182" s="1"/>
-      <c r="J182" s="15"/>
+      <c r="J182" s="20"/>
       <c r="AO182" s="1"/>
       <c r="AP182" s="1"/>
       <c r="AU182" s="1"/>
@@ -10905,24 +11864,24 @@
       <c r="BB182" s="1"/>
       <c r="BC182" s="1"/>
       <c r="BD182" s="1"/>
-      <c r="BE182" s="25"/>
-      <c r="BF182" s="25"/>
+      <c r="BE182" s="28"/>
+      <c r="BF182" s="28"/>
       <c r="BG182" s="1"/>
-      <c r="BH182" s="24"/>
+      <c r="BH182" s="27"/>
       <c r="BI182" s="1"/>
-      <c r="BJ182" s="25"/>
+      <c r="BJ182" s="28"/>
     </row>
     <row r="183" spans="1:62">
       <c r="A183" s="1"/>
-      <c r="B183" s="8"/>
+      <c r="B183" s="7"/>
       <c r="C183" s="1"/>
-      <c r="D183" s="8"/>
+      <c r="D183" s="7"/>
       <c r="E183" s="1"/>
-      <c r="F183" s="12"/>
-      <c r="G183" s="12"/>
+      <c r="F183" s="13"/>
+      <c r="G183" s="13"/>
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
-      <c r="J183" s="15"/>
+      <c r="J183" s="20"/>
       <c r="AO183" s="1"/>
       <c r="AP183" s="1"/>
       <c r="AU183" s="1"/>
@@ -10935,24 +11894,24 @@
       <c r="BB183" s="1"/>
       <c r="BC183" s="1"/>
       <c r="BD183" s="1"/>
-      <c r="BE183" s="25"/>
-      <c r="BF183" s="25"/>
+      <c r="BE183" s="28"/>
+      <c r="BF183" s="28"/>
       <c r="BG183" s="1"/>
-      <c r="BH183" s="24"/>
+      <c r="BH183" s="27"/>
       <c r="BI183" s="1"/>
-      <c r="BJ183" s="25"/>
+      <c r="BJ183" s="28"/>
     </row>
     <row r="184" spans="1:62">
       <c r="A184" s="1"/>
-      <c r="B184" s="8"/>
+      <c r="B184" s="7"/>
       <c r="C184" s="1"/>
-      <c r="D184" s="8"/>
+      <c r="D184" s="7"/>
       <c r="E184" s="1"/>
-      <c r="F184" s="12"/>
-      <c r="G184" s="12"/>
+      <c r="F184" s="13"/>
+      <c r="G184" s="13"/>
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
-      <c r="J184" s="15"/>
+      <c r="J184" s="20"/>
       <c r="AO184" s="1"/>
       <c r="AP184" s="1"/>
       <c r="AU184" s="1"/>
@@ -10965,24 +11924,24 @@
       <c r="BB184" s="1"/>
       <c r="BC184" s="1"/>
       <c r="BD184" s="1"/>
-      <c r="BE184" s="25"/>
-      <c r="BF184" s="25"/>
+      <c r="BE184" s="28"/>
+      <c r="BF184" s="28"/>
       <c r="BG184" s="1"/>
-      <c r="BH184" s="24"/>
+      <c r="BH184" s="27"/>
       <c r="BI184" s="1"/>
-      <c r="BJ184" s="25"/>
+      <c r="BJ184" s="28"/>
     </row>
     <row r="185" spans="1:62">
       <c r="A185" s="1"/>
-      <c r="B185" s="8"/>
+      <c r="B185" s="7"/>
       <c r="C185" s="1"/>
-      <c r="D185" s="8"/>
+      <c r="D185" s="7"/>
       <c r="E185" s="1"/>
-      <c r="F185" s="12"/>
-      <c r="G185" s="12"/>
+      <c r="F185" s="13"/>
+      <c r="G185" s="13"/>
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
-      <c r="J185" s="15"/>
+      <c r="J185" s="20"/>
       <c r="AO185" s="1"/>
       <c r="AP185" s="1"/>
       <c r="AU185" s="1"/>
@@ -10995,24 +11954,24 @@
       <c r="BB185" s="1"/>
       <c r="BC185" s="1"/>
       <c r="BD185" s="1"/>
-      <c r="BE185" s="25"/>
-      <c r="BF185" s="25"/>
+      <c r="BE185" s="28"/>
+      <c r="BF185" s="28"/>
       <c r="BG185" s="1"/>
-      <c r="BH185" s="24"/>
+      <c r="BH185" s="27"/>
       <c r="BI185" s="1"/>
-      <c r="BJ185" s="25"/>
+      <c r="BJ185" s="28"/>
     </row>
     <row r="186" spans="1:62">
       <c r="A186" s="1"/>
-      <c r="B186" s="8"/>
+      <c r="B186" s="7"/>
       <c r="C186" s="1"/>
-      <c r="D186" s="8"/>
+      <c r="D186" s="7"/>
       <c r="E186" s="1"/>
-      <c r="F186" s="12"/>
-      <c r="G186" s="12"/>
+      <c r="F186" s="13"/>
+      <c r="G186" s="13"/>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
-      <c r="J186" s="15"/>
+      <c r="J186" s="20"/>
       <c r="AO186" s="1"/>
       <c r="AP186" s="1"/>
       <c r="AU186" s="1"/>
@@ -11025,24 +11984,24 @@
       <c r="BB186" s="1"/>
       <c r="BC186" s="1"/>
       <c r="BD186" s="1"/>
-      <c r="BE186" s="25"/>
-      <c r="BF186" s="25"/>
+      <c r="BE186" s="28"/>
+      <c r="BF186" s="28"/>
       <c r="BG186" s="1"/>
-      <c r="BH186" s="24"/>
+      <c r="BH186" s="27"/>
       <c r="BI186" s="1"/>
-      <c r="BJ186" s="25"/>
+      <c r="BJ186" s="28"/>
     </row>
     <row r="187" spans="1:62">
       <c r="A187" s="1"/>
-      <c r="B187" s="8"/>
+      <c r="B187" s="7"/>
       <c r="C187" s="1"/>
-      <c r="D187" s="8"/>
+      <c r="D187" s="7"/>
       <c r="E187" s="1"/>
-      <c r="F187" s="12"/>
-      <c r="G187" s="12"/>
+      <c r="F187" s="13"/>
+      <c r="G187" s="13"/>
       <c r="H187" s="1"/>
       <c r="I187" s="1"/>
-      <c r="J187" s="15"/>
+      <c r="J187" s="20"/>
       <c r="AO187" s="1"/>
       <c r="AP187" s="1"/>
       <c r="AU187" s="1"/>
@@ -11055,24 +12014,24 @@
       <c r="BB187" s="1"/>
       <c r="BC187" s="1"/>
       <c r="BD187" s="1"/>
-      <c r="BE187" s="25"/>
-      <c r="BF187" s="25"/>
+      <c r="BE187" s="28"/>
+      <c r="BF187" s="28"/>
       <c r="BG187" s="1"/>
-      <c r="BH187" s="24"/>
+      <c r="BH187" s="27"/>
       <c r="BI187" s="1"/>
-      <c r="BJ187" s="25"/>
+      <c r="BJ187" s="28"/>
     </row>
     <row r="188" spans="1:62">
       <c r="A188" s="1"/>
-      <c r="B188" s="8"/>
+      <c r="B188" s="7"/>
       <c r="C188" s="1"/>
-      <c r="D188" s="8"/>
+      <c r="D188" s="7"/>
       <c r="E188" s="1"/>
-      <c r="F188" s="12"/>
-      <c r="G188" s="12"/>
+      <c r="F188" s="13"/>
+      <c r="G188" s="13"/>
       <c r="H188" s="1"/>
       <c r="I188" s="1"/>
-      <c r="J188" s="15"/>
+      <c r="J188" s="20"/>
       <c r="AO188" s="1"/>
       <c r="AP188" s="1"/>
       <c r="AU188" s="1"/>
@@ -11085,24 +12044,24 @@
       <c r="BB188" s="1"/>
       <c r="BC188" s="1"/>
       <c r="BD188" s="1"/>
-      <c r="BE188" s="25"/>
-      <c r="BF188" s="25"/>
+      <c r="BE188" s="28"/>
+      <c r="BF188" s="28"/>
       <c r="BG188" s="1"/>
-      <c r="BH188" s="24"/>
+      <c r="BH188" s="27"/>
       <c r="BI188" s="1"/>
-      <c r="BJ188" s="25"/>
+      <c r="BJ188" s="28"/>
     </row>
     <row r="189" spans="1:62">
       <c r="A189" s="1"/>
-      <c r="B189" s="8"/>
+      <c r="B189" s="7"/>
       <c r="C189" s="1"/>
-      <c r="D189" s="8"/>
+      <c r="D189" s="7"/>
       <c r="E189" s="1"/>
-      <c r="F189" s="12"/>
-      <c r="G189" s="12"/>
+      <c r="F189" s="13"/>
+      <c r="G189" s="13"/>
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
-      <c r="J189" s="15"/>
+      <c r="J189" s="20"/>
       <c r="AO189" s="1"/>
       <c r="AP189" s="1"/>
       <c r="AU189" s="1"/>
@@ -11115,24 +12074,24 @@
       <c r="BB189" s="1"/>
       <c r="BC189" s="1"/>
       <c r="BD189" s="1"/>
-      <c r="BE189" s="25"/>
-      <c r="BF189" s="25"/>
+      <c r="BE189" s="28"/>
+      <c r="BF189" s="28"/>
       <c r="BG189" s="1"/>
-      <c r="BH189" s="24"/>
+      <c r="BH189" s="27"/>
       <c r="BI189" s="1"/>
-      <c r="BJ189" s="25"/>
+      <c r="BJ189" s="28"/>
     </row>
     <row r="190" spans="1:62">
       <c r="A190" s="1"/>
-      <c r="B190" s="8"/>
+      <c r="B190" s="7"/>
       <c r="C190" s="1"/>
-      <c r="D190" s="8"/>
+      <c r="D190" s="7"/>
       <c r="E190" s="1"/>
-      <c r="F190" s="12"/>
-      <c r="G190" s="12"/>
+      <c r="F190" s="13"/>
+      <c r="G190" s="13"/>
       <c r="H190" s="1"/>
       <c r="I190" s="1"/>
-      <c r="J190" s="15"/>
+      <c r="J190" s="20"/>
       <c r="AO190" s="1"/>
       <c r="AP190" s="1"/>
       <c r="AU190" s="1"/>
@@ -11145,24 +12104,24 @@
       <c r="BB190" s="1"/>
       <c r="BC190" s="1"/>
       <c r="BD190" s="1"/>
-      <c r="BE190" s="25"/>
-      <c r="BF190" s="25"/>
+      <c r="BE190" s="28"/>
+      <c r="BF190" s="28"/>
       <c r="BG190" s="1"/>
-      <c r="BH190" s="24"/>
+      <c r="BH190" s="27"/>
       <c r="BI190" s="1"/>
-      <c r="BJ190" s="25"/>
+      <c r="BJ190" s="28"/>
     </row>
     <row r="191" spans="1:62">
       <c r="A191" s="1"/>
-      <c r="B191" s="8"/>
+      <c r="B191" s="7"/>
       <c r="C191" s="1"/>
-      <c r="D191" s="8"/>
+      <c r="D191" s="7"/>
       <c r="E191" s="1"/>
-      <c r="F191" s="12"/>
-      <c r="G191" s="12"/>
+      <c r="F191" s="13"/>
+      <c r="G191" s="13"/>
       <c r="H191" s="1"/>
       <c r="I191" s="1"/>
-      <c r="J191" s="15"/>
+      <c r="J191" s="20"/>
       <c r="AO191" s="1"/>
       <c r="AP191" s="1"/>
       <c r="AU191" s="1"/>
@@ -11175,24 +12134,24 @@
       <c r="BB191" s="1"/>
       <c r="BC191" s="1"/>
       <c r="BD191" s="1"/>
-      <c r="BE191" s="25"/>
-      <c r="BF191" s="25"/>
+      <c r="BE191" s="28"/>
+      <c r="BF191" s="28"/>
       <c r="BG191" s="1"/>
-      <c r="BH191" s="24"/>
+      <c r="BH191" s="27"/>
       <c r="BI191" s="1"/>
-      <c r="BJ191" s="25"/>
+      <c r="BJ191" s="28"/>
     </row>
     <row r="192" spans="1:62">
       <c r="A192" s="1"/>
-      <c r="B192" s="8"/>
+      <c r="B192" s="7"/>
       <c r="C192" s="1"/>
-      <c r="D192" s="8"/>
+      <c r="D192" s="7"/>
       <c r="E192" s="1"/>
-      <c r="F192" s="12"/>
-      <c r="G192" s="12"/>
+      <c r="F192" s="13"/>
+      <c r="G192" s="13"/>
       <c r="H192" s="1"/>
       <c r="I192" s="1"/>
-      <c r="J192" s="15"/>
+      <c r="J192" s="20"/>
       <c r="AO192" s="1"/>
       <c r="AP192" s="1"/>
       <c r="AU192" s="1"/>
@@ -11205,24 +12164,24 @@
       <c r="BB192" s="1"/>
       <c r="BC192" s="1"/>
       <c r="BD192" s="1"/>
-      <c r="BE192" s="25"/>
-      <c r="BF192" s="25"/>
+      <c r="BE192" s="28"/>
+      <c r="BF192" s="28"/>
       <c r="BG192" s="1"/>
-      <c r="BH192" s="24"/>
+      <c r="BH192" s="27"/>
       <c r="BI192" s="1"/>
-      <c r="BJ192" s="25"/>
+      <c r="BJ192" s="28"/>
     </row>
     <row r="193" spans="1:62">
       <c r="A193" s="1"/>
-      <c r="B193" s="8"/>
+      <c r="B193" s="7"/>
       <c r="C193" s="1"/>
-      <c r="D193" s="8"/>
+      <c r="D193" s="7"/>
       <c r="E193" s="1"/>
-      <c r="F193" s="12"/>
-      <c r="G193" s="12"/>
+      <c r="F193" s="13"/>
+      <c r="G193" s="13"/>
       <c r="H193" s="1"/>
       <c r="I193" s="1"/>
-      <c r="J193" s="15"/>
+      <c r="J193" s="20"/>
       <c r="AO193" s="1"/>
       <c r="AP193" s="1"/>
       <c r="AU193" s="1"/>
@@ -11235,24 +12194,24 @@
       <c r="BB193" s="1"/>
       <c r="BC193" s="1"/>
       <c r="BD193" s="1"/>
-      <c r="BE193" s="25"/>
-      <c r="BF193" s="25"/>
+      <c r="BE193" s="28"/>
+      <c r="BF193" s="28"/>
       <c r="BG193" s="1"/>
-      <c r="BH193" s="24"/>
+      <c r="BH193" s="27"/>
       <c r="BI193" s="1"/>
-      <c r="BJ193" s="25"/>
+      <c r="BJ193" s="28"/>
     </row>
     <row r="194" spans="1:62">
       <c r="A194" s="1"/>
-      <c r="B194" s="8"/>
+      <c r="B194" s="7"/>
       <c r="C194" s="1"/>
-      <c r="D194" s="8"/>
+      <c r="D194" s="7"/>
       <c r="E194" s="1"/>
-      <c r="F194" s="12"/>
-      <c r="G194" s="12"/>
+      <c r="F194" s="13"/>
+      <c r="G194" s="13"/>
       <c r="H194" s="1"/>
       <c r="I194" s="1"/>
-      <c r="J194" s="15"/>
+      <c r="J194" s="20"/>
       <c r="AO194" s="1"/>
       <c r="AP194" s="1"/>
       <c r="AU194" s="1"/>
@@ -11265,24 +12224,24 @@
       <c r="BB194" s="1"/>
       <c r="BC194" s="1"/>
       <c r="BD194" s="1"/>
-      <c r="BE194" s="25"/>
-      <c r="BF194" s="25"/>
+      <c r="BE194" s="28"/>
+      <c r="BF194" s="28"/>
       <c r="BG194" s="1"/>
-      <c r="BH194" s="24"/>
+      <c r="BH194" s="27"/>
       <c r="BI194" s="1"/>
-      <c r="BJ194" s="25"/>
+      <c r="BJ194" s="28"/>
     </row>
     <row r="195" spans="1:62">
       <c r="A195" s="1"/>
-      <c r="B195" s="8"/>
+      <c r="B195" s="7"/>
       <c r="C195" s="1"/>
-      <c r="D195" s="8"/>
+      <c r="D195" s="7"/>
       <c r="E195" s="1"/>
-      <c r="F195" s="12"/>
-      <c r="G195" s="12"/>
+      <c r="F195" s="13"/>
+      <c r="G195" s="13"/>
       <c r="H195" s="1"/>
       <c r="I195" s="1"/>
-      <c r="J195" s="15"/>
+      <c r="J195" s="20"/>
       <c r="AO195" s="1"/>
       <c r="AP195" s="1"/>
       <c r="AU195" s="1"/>
@@ -11295,24 +12254,24 @@
       <c r="BB195" s="1"/>
       <c r="BC195" s="1"/>
       <c r="BD195" s="1"/>
-      <c r="BE195" s="25"/>
-      <c r="BF195" s="25"/>
+      <c r="BE195" s="28"/>
+      <c r="BF195" s="28"/>
       <c r="BG195" s="1"/>
-      <c r="BH195" s="24"/>
+      <c r="BH195" s="27"/>
       <c r="BI195" s="1"/>
-      <c r="BJ195" s="25"/>
+      <c r="BJ195" s="28"/>
     </row>
     <row r="196" spans="1:62">
       <c r="A196" s="1"/>
-      <c r="B196" s="8"/>
+      <c r="B196" s="7"/>
       <c r="C196" s="1"/>
-      <c r="D196" s="8"/>
+      <c r="D196" s="7"/>
       <c r="E196" s="1"/>
-      <c r="F196" s="12"/>
-      <c r="G196" s="12"/>
+      <c r="F196" s="13"/>
+      <c r="G196" s="13"/>
       <c r="H196" s="1"/>
       <c r="I196" s="1"/>
-      <c r="J196" s="15"/>
+      <c r="J196" s="20"/>
       <c r="AO196" s="1"/>
       <c r="AP196" s="1"/>
       <c r="AU196" s="1"/>
@@ -11325,24 +12284,24 @@
       <c r="BB196" s="1"/>
       <c r="BC196" s="1"/>
       <c r="BD196" s="1"/>
-      <c r="BE196" s="25"/>
-      <c r="BF196" s="25"/>
+      <c r="BE196" s="28"/>
+      <c r="BF196" s="28"/>
       <c r="BG196" s="1"/>
-      <c r="BH196" s="24"/>
+      <c r="BH196" s="27"/>
       <c r="BI196" s="1"/>
-      <c r="BJ196" s="25"/>
+      <c r="BJ196" s="28"/>
     </row>
     <row r="197" spans="1:62">
       <c r="A197" s="1"/>
-      <c r="B197" s="8"/>
+      <c r="B197" s="7"/>
       <c r="C197" s="1"/>
-      <c r="D197" s="8"/>
+      <c r="D197" s="7"/>
       <c r="E197" s="1"/>
-      <c r="F197" s="12"/>
-      <c r="G197" s="12"/>
+      <c r="F197" s="13"/>
+      <c r="G197" s="13"/>
       <c r="H197" s="1"/>
       <c r="I197" s="1"/>
-      <c r="J197" s="15"/>
+      <c r="J197" s="20"/>
       <c r="AO197" s="1"/>
       <c r="AP197" s="1"/>
       <c r="AU197" s="1"/>
@@ -11355,24 +12314,24 @@
       <c r="BB197" s="1"/>
       <c r="BC197" s="1"/>
       <c r="BD197" s="1"/>
-      <c r="BE197" s="25"/>
-      <c r="BF197" s="25"/>
+      <c r="BE197" s="28"/>
+      <c r="BF197" s="28"/>
       <c r="BG197" s="1"/>
-      <c r="BH197" s="24"/>
+      <c r="BH197" s="27"/>
       <c r="BI197" s="1"/>
-      <c r="BJ197" s="25"/>
+      <c r="BJ197" s="28"/>
     </row>
     <row r="198" spans="1:62">
       <c r="A198" s="1"/>
-      <c r="B198" s="8"/>
+      <c r="B198" s="7"/>
       <c r="C198" s="1"/>
-      <c r="D198" s="8"/>
+      <c r="D198" s="7"/>
       <c r="E198" s="1"/>
-      <c r="F198" s="12"/>
-      <c r="G198" s="12"/>
+      <c r="F198" s="13"/>
+      <c r="G198" s="13"/>
       <c r="H198" s="1"/>
       <c r="I198" s="1"/>
-      <c r="J198" s="15"/>
+      <c r="J198" s="20"/>
       <c r="AO198" s="1"/>
       <c r="AP198" s="1"/>
       <c r="AU198" s="1"/>
@@ -11385,23 +12344,23 @@
       <c r="BB198" s="1"/>
       <c r="BC198" s="1"/>
       <c r="BD198" s="1"/>
-      <c r="BE198" s="25"/>
-      <c r="BF198" s="25"/>
+      <c r="BE198" s="28"/>
+      <c r="BF198" s="28"/>
       <c r="BG198" s="1"/>
-      <c r="BH198" s="24"/>
+      <c r="BH198" s="27"/>
       <c r="BI198" s="1"/>
-      <c r="BJ198" s="25"/>
+      <c r="BJ198" s="28"/>
     </row>
     <row r="199" spans="2:62">
-      <c r="B199" s="8"/>
+      <c r="B199" s="7"/>
       <c r="C199" s="1"/>
-      <c r="D199" s="8"/>
+      <c r="D199" s="7"/>
       <c r="E199" s="1"/>
-      <c r="F199" s="12"/>
-      <c r="G199" s="12"/>
+      <c r="F199" s="13"/>
+      <c r="G199" s="13"/>
       <c r="H199" s="1"/>
       <c r="I199" s="1"/>
-      <c r="J199" s="15"/>
+      <c r="J199" s="20"/>
       <c r="AO199" s="1"/>
       <c r="AP199" s="1"/>
       <c r="AU199" s="1"/>
@@ -11414,318 +12373,318 @@
       <c r="BB199" s="1"/>
       <c r="BC199" s="1"/>
       <c r="BD199" s="1"/>
-      <c r="BE199" s="25"/>
-      <c r="BF199" s="25"/>
+      <c r="BE199" s="28"/>
+      <c r="BF199" s="28"/>
       <c r="BG199" s="1"/>
-      <c r="BH199" s="24"/>
+      <c r="BH199" s="27"/>
       <c r="BI199" s="1"/>
-      <c r="BJ199" s="25"/>
+      <c r="BJ199" s="28"/>
     </row>
     <row r="200" spans="10:10">
-      <c r="J200" s="15"/>
+      <c r="J200" s="16"/>
     </row>
     <row r="201" spans="10:10">
-      <c r="J201" s="15"/>
+      <c r="J201" s="16"/>
     </row>
     <row r="202" spans="10:10">
-      <c r="J202" s="15"/>
+      <c r="J202" s="16"/>
     </row>
     <row r="203" spans="10:10">
-      <c r="J203" s="15"/>
+      <c r="J203" s="16"/>
     </row>
     <row r="204" spans="10:10">
-      <c r="J204" s="15"/>
+      <c r="J204" s="16"/>
     </row>
     <row r="205" spans="10:10">
-      <c r="J205" s="15"/>
+      <c r="J205" s="16"/>
     </row>
     <row r="206" spans="10:10">
-      <c r="J206" s="15"/>
+      <c r="J206" s="16"/>
     </row>
     <row r="207" spans="10:10">
-      <c r="J207" s="15"/>
+      <c r="J207" s="16"/>
     </row>
     <row r="208" spans="10:10">
-      <c r="J208" s="15"/>
+      <c r="J208" s="16"/>
     </row>
     <row r="209" spans="10:10">
-      <c r="J209" s="15"/>
+      <c r="J209" s="16"/>
     </row>
     <row r="210" spans="10:10">
-      <c r="J210" s="15"/>
+      <c r="J210" s="16"/>
     </row>
     <row r="211" spans="10:10">
-      <c r="J211" s="15"/>
+      <c r="J211" s="16"/>
     </row>
     <row r="212" spans="10:10">
-      <c r="J212" s="15"/>
+      <c r="J212" s="16"/>
     </row>
     <row r="213" spans="10:10">
-      <c r="J213" s="15"/>
+      <c r="J213" s="16"/>
     </row>
     <row r="214" spans="10:10">
-      <c r="J214" s="15"/>
+      <c r="J214" s="16"/>
     </row>
     <row r="215" spans="10:10">
-      <c r="J215" s="15"/>
+      <c r="J215" s="16"/>
     </row>
     <row r="216" spans="10:10">
-      <c r="J216" s="15"/>
+      <c r="J216" s="16"/>
     </row>
     <row r="217" spans="10:10">
-      <c r="J217" s="15"/>
+      <c r="J217" s="16"/>
     </row>
     <row r="218" spans="10:10">
-      <c r="J218" s="15"/>
+      <c r="J218" s="16"/>
     </row>
     <row r="219" spans="10:10">
-      <c r="J219" s="15"/>
+      <c r="J219" s="16"/>
     </row>
     <row r="220" spans="10:10">
-      <c r="J220" s="15"/>
+      <c r="J220" s="16"/>
     </row>
     <row r="221" spans="10:10">
-      <c r="J221" s="15"/>
+      <c r="J221" s="16"/>
     </row>
     <row r="222" spans="10:10">
-      <c r="J222" s="15"/>
+      <c r="J222" s="16"/>
     </row>
     <row r="223" spans="10:10">
-      <c r="J223" s="15"/>
+      <c r="J223" s="16"/>
     </row>
     <row r="224" spans="10:10">
-      <c r="J224" s="15"/>
+      <c r="J224" s="16"/>
     </row>
     <row r="225" spans="10:10">
-      <c r="J225" s="15"/>
+      <c r="J225" s="16"/>
     </row>
     <row r="226" spans="10:10">
-      <c r="J226" s="15"/>
+      <c r="J226" s="16"/>
     </row>
     <row r="227" spans="10:10">
-      <c r="J227" s="15"/>
+      <c r="J227" s="16"/>
     </row>
     <row r="228" spans="10:10">
-      <c r="J228" s="15"/>
+      <c r="J228" s="16"/>
     </row>
     <row r="229" spans="10:10">
-      <c r="J229" s="15"/>
+      <c r="J229" s="16"/>
     </row>
     <row r="230" spans="10:10">
-      <c r="J230" s="15"/>
+      <c r="J230" s="16"/>
     </row>
     <row r="231" spans="10:10">
-      <c r="J231" s="15"/>
+      <c r="J231" s="16"/>
     </row>
     <row r="232" spans="10:10">
-      <c r="J232" s="15"/>
+      <c r="J232" s="16"/>
     </row>
     <row r="233" spans="10:10">
-      <c r="J233" s="15"/>
+      <c r="J233" s="16"/>
     </row>
     <row r="234" spans="10:10">
-      <c r="J234" s="15"/>
+      <c r="J234" s="16"/>
     </row>
     <row r="235" spans="10:10">
-      <c r="J235" s="15"/>
+      <c r="J235" s="16"/>
     </row>
     <row r="236" spans="10:10">
-      <c r="J236" s="15"/>
+      <c r="J236" s="16"/>
     </row>
     <row r="237" spans="10:10">
-      <c r="J237" s="15"/>
+      <c r="J237" s="16"/>
     </row>
     <row r="238" spans="10:10">
-      <c r="J238" s="15"/>
+      <c r="J238" s="16"/>
     </row>
     <row r="239" spans="10:10">
-      <c r="J239" s="15"/>
+      <c r="J239" s="16"/>
     </row>
     <row r="240" spans="10:10">
-      <c r="J240" s="15"/>
+      <c r="J240" s="16"/>
     </row>
     <row r="241" spans="10:10">
-      <c r="J241" s="15"/>
+      <c r="J241" s="16"/>
     </row>
     <row r="242" spans="10:10">
-      <c r="J242" s="15"/>
+      <c r="J242" s="16"/>
     </row>
     <row r="243" spans="10:10">
-      <c r="J243" s="15"/>
+      <c r="J243" s="16"/>
     </row>
     <row r="244" spans="10:10">
-      <c r="J244" s="15"/>
+      <c r="J244" s="16"/>
     </row>
     <row r="245" spans="10:10">
-      <c r="J245" s="15"/>
+      <c r="J245" s="16"/>
     </row>
     <row r="246" spans="10:10">
-      <c r="J246" s="15"/>
+      <c r="J246" s="16"/>
     </row>
     <row r="247" spans="10:10">
-      <c r="J247" s="15"/>
+      <c r="J247" s="16"/>
     </row>
     <row r="248" spans="10:10">
-      <c r="J248" s="15"/>
+      <c r="J248" s="16"/>
     </row>
     <row r="249" spans="10:10">
-      <c r="J249" s="15"/>
+      <c r="J249" s="16"/>
     </row>
     <row r="250" spans="10:10">
-      <c r="J250" s="15"/>
+      <c r="J250" s="16"/>
     </row>
     <row r="251" spans="10:10">
-      <c r="J251" s="15"/>
+      <c r="J251" s="16"/>
     </row>
     <row r="252" spans="10:10">
-      <c r="J252" s="15"/>
+      <c r="J252" s="16"/>
     </row>
     <row r="253" spans="10:10">
-      <c r="J253" s="15"/>
+      <c r="J253" s="16"/>
     </row>
     <row r="254" spans="10:10">
-      <c r="J254" s="15"/>
+      <c r="J254" s="16"/>
     </row>
     <row r="255" spans="10:10">
-      <c r="J255" s="15"/>
+      <c r="J255" s="16"/>
     </row>
     <row r="256" spans="10:10">
-      <c r="J256" s="15"/>
+      <c r="J256" s="16"/>
     </row>
     <row r="257" spans="10:10">
-      <c r="J257" s="15"/>
+      <c r="J257" s="16"/>
     </row>
     <row r="258" spans="10:10">
-      <c r="J258" s="15"/>
+      <c r="J258" s="16"/>
     </row>
     <row r="259" spans="10:10">
-      <c r="J259" s="15"/>
+      <c r="J259" s="16"/>
     </row>
     <row r="260" spans="10:10">
-      <c r="J260" s="15"/>
+      <c r="J260" s="16"/>
     </row>
     <row r="261" spans="10:10">
-      <c r="J261" s="15"/>
+      <c r="J261" s="16"/>
     </row>
     <row r="262" spans="10:10">
-      <c r="J262" s="15"/>
+      <c r="J262" s="16"/>
     </row>
     <row r="263" spans="10:10">
-      <c r="J263" s="15"/>
+      <c r="J263" s="16"/>
     </row>
     <row r="264" spans="10:10">
-      <c r="J264" s="15"/>
+      <c r="J264" s="16"/>
     </row>
     <row r="265" spans="10:10">
-      <c r="J265" s="15"/>
+      <c r="J265" s="16"/>
     </row>
     <row r="266" spans="10:10">
-      <c r="J266" s="15"/>
+      <c r="J266" s="16"/>
     </row>
     <row r="267" spans="10:10">
-      <c r="J267" s="15"/>
+      <c r="J267" s="16"/>
     </row>
     <row r="268" spans="10:10">
-      <c r="J268" s="15"/>
+      <c r="J268" s="16"/>
     </row>
     <row r="269" spans="10:10">
-      <c r="J269" s="15"/>
+      <c r="J269" s="16"/>
     </row>
     <row r="270" spans="10:10">
-      <c r="J270" s="15"/>
+      <c r="J270" s="16"/>
     </row>
     <row r="271" spans="10:10">
-      <c r="J271" s="15"/>
+      <c r="J271" s="16"/>
     </row>
     <row r="272" spans="10:10">
-      <c r="J272" s="15"/>
+      <c r="J272" s="16"/>
     </row>
     <row r="273" spans="10:10">
-      <c r="J273" s="15"/>
+      <c r="J273" s="16"/>
     </row>
     <row r="274" spans="10:10">
-      <c r="J274" s="15"/>
+      <c r="J274" s="16"/>
     </row>
     <row r="275" spans="10:10">
-      <c r="J275" s="15"/>
+      <c r="J275" s="16"/>
     </row>
     <row r="276" spans="10:10">
-      <c r="J276" s="15"/>
+      <c r="J276" s="16"/>
     </row>
     <row r="277" spans="10:10">
-      <c r="J277" s="15"/>
+      <c r="J277" s="16"/>
     </row>
     <row r="278" spans="10:10">
-      <c r="J278" s="15"/>
+      <c r="J278" s="16"/>
     </row>
     <row r="279" spans="10:10">
-      <c r="J279" s="15"/>
+      <c r="J279" s="16"/>
     </row>
     <row r="280" spans="10:10">
-      <c r="J280" s="15"/>
+      <c r="J280" s="16"/>
     </row>
     <row r="281" spans="10:10">
-      <c r="J281" s="15"/>
+      <c r="J281" s="16"/>
     </row>
     <row r="282" spans="10:10">
-      <c r="J282" s="15"/>
+      <c r="J282" s="16"/>
     </row>
     <row r="283" spans="10:10">
-      <c r="J283" s="15"/>
+      <c r="J283" s="16"/>
     </row>
     <row r="284" spans="10:10">
-      <c r="J284" s="15"/>
+      <c r="J284" s="16"/>
     </row>
     <row r="285" spans="10:10">
-      <c r="J285" s="15"/>
+      <c r="J285" s="16"/>
     </row>
     <row r="286" spans="10:10">
-      <c r="J286" s="15"/>
+      <c r="J286" s="16"/>
     </row>
     <row r="287" spans="10:10">
-      <c r="J287" s="15"/>
+      <c r="J287" s="16"/>
     </row>
     <row r="288" spans="10:10">
-      <c r="J288" s="15"/>
+      <c r="J288" s="16"/>
     </row>
     <row r="289" spans="10:10">
-      <c r="J289" s="15"/>
+      <c r="J289" s="16"/>
     </row>
     <row r="290" spans="10:10">
-      <c r="J290" s="15"/>
+      <c r="J290" s="16"/>
     </row>
     <row r="291" spans="10:10">
-      <c r="J291" s="15"/>
+      <c r="J291" s="16"/>
     </row>
     <row r="292" spans="10:10">
-      <c r="J292" s="15"/>
+      <c r="J292" s="16"/>
     </row>
     <row r="293" spans="10:10">
-      <c r="J293" s="15"/>
+      <c r="J293" s="16"/>
     </row>
     <row r="294" spans="10:10">
-      <c r="J294" s="15"/>
+      <c r="J294" s="16"/>
     </row>
     <row r="295" spans="10:10">
-      <c r="J295" s="15"/>
+      <c r="J295" s="16"/>
     </row>
     <row r="296" spans="10:10">
-      <c r="J296" s="15"/>
+      <c r="J296" s="16"/>
     </row>
     <row r="297" spans="10:10">
-      <c r="J297" s="15"/>
+      <c r="J297" s="16"/>
     </row>
     <row r="298" spans="10:10">
-      <c r="J298" s="15"/>
+      <c r="J298" s="16"/>
     </row>
     <row r="299" spans="10:10">
-      <c r="J299" s="15"/>
+      <c r="J299" s="16"/>
     </row>
     <row r="300" spans="10:10">
-      <c r="J300" s="15"/>
+      <c r="J300" s="16"/>
     </row>
     <row r="301" spans="10:10">
-      <c r="J301" s="15"/>
+      <c r="J301" s="16"/>
     </row>
   </sheetData>
   <protectedRanges>

--- a/src/temp/TEMPLATE.xlsx
+++ b/src/temp/TEMPLATE.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="14340" windowHeight="14115"/>
+    <workbookView windowWidth="28800" windowHeight="14295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -176,14 +176,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="\N\8"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;₱&quot;* #,##0_-;\-&quot;₱&quot;* #,##0_-;_-&quot;₱&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -214,7 +215,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -222,6 +231,29 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -241,9 +273,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -251,22 +283,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -281,44 +298,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -326,7 +305,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -340,8 +319,37 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -380,31 +388,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,115 +430,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,13 +448,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -561,6 +551,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -607,6 +621,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -625,32 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -675,26 +689,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -713,82 +712,98 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -801,28 +816,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -831,6 +841,9 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -891,6 +904,7 @@
   </cellStyles>
   <dxfs count="1">
     <dxf>
+      <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
       <alignment horizontal="left"/>
     </dxf>
   </dxfs>
@@ -1278,14 +1292,14 @@
   <cols>
     <col min="1" max="1" width="25.4222222222222" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="13.6740740740741" customWidth="1"/>
+    <col min="3" max="3" width="14.2814814814815" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="19.2814814814815" customWidth="1"/>
     <col min="5" max="5" width="10.2814814814815" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="15.2814814814815" customWidth="1"/>
     <col min="8" max="8" width="23.8518518518519" customWidth="1"/>
     <col min="9" max="9" width="8.71111111111111" customWidth="1"/>
-    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="10" max="10" width="24" style="4" customWidth="1"/>
     <col min="11" max="11" width="26.4222222222222" customWidth="1"/>
     <col min="12" max="14" width="8.14074074074074" customWidth="1"/>
     <col min="15" max="15" width="20.1407407407407" customWidth="1"/>
@@ -1299,7 +1313,7 @@
     <col min="27" max="27" width="16.4222222222222" customWidth="1"/>
     <col min="28" max="28" width="14" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="18.7111111111111" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="9.14074074074074" style="4" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="9.14074074074074" style="5" hidden="1" customWidth="1"/>
     <col min="31" max="31" width="23.7111111111111" hidden="1" customWidth="1"/>
     <col min="32" max="32" width="16.4222222222222" hidden="1" customWidth="1"/>
     <col min="33" max="33" width="13.1407407407407" hidden="1" customWidth="1"/>
@@ -1325,272 +1339,272 @@
     <col min="57" max="58" width="12.4222222222222" hidden="1" customWidth="1"/>
     <col min="59" max="59" width="11.7111111111111" customWidth="1"/>
     <col min="60" max="60" width="11.1407407407407" customWidth="1"/>
-    <col min="61" max="61" width="15.6296296296296" customWidth="1"/>
+    <col min="61" max="61" width="13.7111111111111" hidden="1" customWidth="1"/>
     <col min="62" max="62" width="13.1407407407407" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:62">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AA1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AC1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="22" t="s">
+      <c r="AE1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="22" t="s">
+      <c r="AF1" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="22" t="s">
+      <c r="AG1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="22" t="s">
+      <c r="AH1" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="22" t="s">
+      <c r="AI1" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="22" t="s">
+      <c r="AJ1" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="22" t="s">
+      <c r="AK1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="22" t="s">
+      <c r="AL1" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="22" t="s">
+      <c r="AM1" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="22" t="s">
+      <c r="AN1" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="AO1" s="22" t="s">
+      <c r="AO1" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="AP1" s="22" t="s">
+      <c r="AP1" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="AQ1" s="22" t="s">
+      <c r="AQ1" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="AR1" s="22" t="s">
+      <c r="AR1" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="AS1" s="22" t="s">
+      <c r="AS1" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="AT1" s="22" t="s">
+      <c r="AT1" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="AU1" s="22" t="s">
+      <c r="AU1" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="AV1" s="22" t="s">
+      <c r="AV1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="AW1" s="22" t="s">
+      <c r="AW1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AX1" s="22" t="s">
+      <c r="AX1" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="AY1" s="22" t="s">
+      <c r="AY1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="AZ1" s="22" t="s">
+      <c r="AZ1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="BA1" s="22" t="s">
+      <c r="BA1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="BB1" s="22" t="s">
+      <c r="BB1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="BC1" s="22" t="s">
+      <c r="BC1" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="BD1" s="22" t="s">
+      <c r="BD1" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="BE1" s="22" t="s">
+      <c r="BE1" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="BF1" s="22" t="s">
+      <c r="BF1" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="BG1" s="22" t="s">
+      <c r="BG1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BH1" s="22" t="s">
+      <c r="BH1" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="BI1" s="22" t="s">
+      <c r="BI1" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="BJ1" s="22" t="s">
+      <c r="BJ1" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="2:62">
-      <c r="B2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+      <c r="B2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
       <c r="J2" s="16"/>
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" s="17"/>
       <c r="O2" s="17"/>
-      <c r="AE2" s="23"/>
-      <c r="AK2" s="29"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="16"/>
-      <c r="AN2" s="29"/>
-      <c r="BE2" s="29"/>
-      <c r="BF2" s="29"/>
-      <c r="BH2" s="31"/>
-      <c r="BJ2" s="29"/>
+      <c r="AE2" s="21"/>
+      <c r="AK2" s="27"/>
+      <c r="AL2" s="27"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="27"/>
+      <c r="BE2" s="27"/>
+      <c r="BF2" s="27"/>
+      <c r="BH2" s="30"/>
+      <c r="BJ2" s="27"/>
     </row>
     <row r="3" spans="2:62">
-      <c r="B3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="D3" s="7"/>
       <c r="J3" s="16"/>
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" s="17"/>
       <c r="O3" s="17"/>
-      <c r="AE3" s="23"/>
-      <c r="AK3" s="29"/>
-      <c r="AL3" s="29"/>
-      <c r="AM3" s="16"/>
-      <c r="AN3" s="29"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="29"/>
-      <c r="BH3" s="31"/>
-      <c r="BJ3" s="29"/>
+      <c r="AE3" s="21"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="27"/>
+      <c r="BE3" s="27"/>
+      <c r="BF3" s="27"/>
+      <c r="BH3" s="30"/>
+      <c r="BJ3" s="27"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="2:62">
-      <c r="B4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
+      <c r="B4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
       <c r="J4" s="18"/>
-      <c r="AD4" s="24"/>
-      <c r="BE4" s="28"/>
-      <c r="BF4" s="28"/>
-      <c r="BH4" s="27"/>
-      <c r="BJ4" s="28"/>
+      <c r="AD4" s="22"/>
+      <c r="BE4" s="26"/>
+      <c r="BF4" s="26"/>
+      <c r="BH4" s="25"/>
+      <c r="BJ4" s="26"/>
     </row>
     <row r="5" s="2" customFormat="1" spans="2:62">
-      <c r="B5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="B5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
       <c r="J5" s="19"/>
-      <c r="AD5" s="25"/>
-      <c r="AE5" s="26"/>
-      <c r="AK5" s="30"/>
-      <c r="AL5" s="30"/>
-      <c r="AN5" s="30"/>
-      <c r="BE5" s="30"/>
-      <c r="BF5" s="30"/>
-      <c r="BH5" s="32"/>
-      <c r="BJ5" s="30"/>
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="24"/>
+      <c r="AK5" s="29"/>
+      <c r="AL5" s="29"/>
+      <c r="AN5" s="29"/>
+      <c r="BE5" s="29"/>
+      <c r="BF5" s="29"/>
+      <c r="BH5" s="31"/>
+      <c r="BJ5" s="29"/>
     </row>
     <row r="6" spans="1:90">
       <c r="A6" s="1"/>
-      <c r="B6" s="7"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="20"/>
+      <c r="J6" s="16"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
@@ -1615,10 +1629,10 @@
       <c r="AN6" s="1"/>
       <c r="AR6" s="1"/>
       <c r="AS6" s="1"/>
-      <c r="BE6" s="29"/>
-      <c r="BF6" s="29"/>
-      <c r="BH6" s="31"/>
-      <c r="BJ6" s="29"/>
+      <c r="BE6" s="27"/>
+      <c r="BF6" s="27"/>
+      <c r="BH6" s="30"/>
+      <c r="BJ6" s="27"/>
       <c r="BK6" s="1"/>
       <c r="BL6" s="1"/>
       <c r="BM6" s="1"/>
@@ -1649,19 +1663,9 @@
       <c r="CL6" s="1"/>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="3:90">
-      <c r="C7" s="9"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="13"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7" s="21"/>
-      <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7"/>
-      <c r="N7"/>
-      <c r="O7"/>
+      <c r="C7" s="10"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
@@ -1672,7 +1676,6 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
-      <c r="AA7"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AE7" s="1"/>
@@ -1683,11 +1686,8 @@
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
       <c r="AL7" s="1"/>
-      <c r="AM7"/>
       <c r="AR7" s="1"/>
       <c r="AS7" s="1"/>
-      <c r="AT7"/>
-      <c r="AU7"/>
       <c r="AV7" s="1"/>
       <c r="AW7" s="1"/>
       <c r="AX7" s="1"/>
@@ -1697,12 +1697,9 @@
       <c r="BB7" s="1"/>
       <c r="BC7" s="1"/>
       <c r="BD7" s="1"/>
-      <c r="BE7" s="28"/>
-      <c r="BF7" s="28"/>
-      <c r="BG7"/>
-      <c r="BH7" s="27"/>
-      <c r="BI7"/>
-      <c r="BJ7"/>
+      <c r="BE7" s="26"/>
+      <c r="BF7" s="26"/>
+      <c r="BH7" s="25"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
       <c r="BM7" s="1"/>
@@ -1733,19 +1730,9 @@
       <c r="CL7" s="1"/>
     </row>
     <row r="8" spans="3:90">
-      <c r="C8" s="11"/>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8" s="21"/>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
-      <c r="N8"/>
-      <c r="O8"/>
+      <c r="C8" s="10"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
@@ -1756,7 +1743,6 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
-      <c r="AA8"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AE8" s="1"/>
@@ -1767,11 +1753,8 @@
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
-      <c r="AM8"/>
       <c r="AR8" s="1"/>
       <c r="AS8" s="1"/>
-      <c r="AT8"/>
-      <c r="AU8"/>
       <c r="AV8" s="1"/>
       <c r="AW8" s="1"/>
       <c r="AX8" s="1"/>
@@ -1781,12 +1764,9 @@
       <c r="BB8" s="1"/>
       <c r="BC8" s="1"/>
       <c r="BD8" s="1"/>
-      <c r="BE8" s="28"/>
-      <c r="BF8" s="28"/>
-      <c r="BG8"/>
-      <c r="BH8" s="27"/>
-      <c r="BI8"/>
-      <c r="BJ8"/>
+      <c r="BE8" s="26"/>
+      <c r="BF8" s="26"/>
+      <c r="BH8" s="25"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
       <c r="BM8" s="1"/>
@@ -1817,19 +1797,9 @@
       <c r="CL8" s="1"/>
     </row>
     <row r="9" spans="3:90">
-      <c r="C9" s="11"/>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9" s="21"/>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
-      <c r="N9"/>
-      <c r="O9"/>
+      <c r="C9" s="10"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -1840,7 +1810,6 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
-      <c r="AA9"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AE9" s="1"/>
@@ -1851,11 +1820,8 @@
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
-      <c r="AM9"/>
       <c r="AR9" s="1"/>
       <c r="AS9" s="1"/>
-      <c r="AT9"/>
-      <c r="AU9"/>
       <c r="AV9" s="1"/>
       <c r="AW9" s="1"/>
       <c r="AX9" s="1"/>
@@ -1865,12 +1831,9 @@
       <c r="BB9" s="1"/>
       <c r="BC9" s="1"/>
       <c r="BD9" s="1"/>
-      <c r="BE9" s="28"/>
-      <c r="BF9" s="28"/>
-      <c r="BG9"/>
-      <c r="BH9" s="27"/>
-      <c r="BI9"/>
-      <c r="BJ9"/>
+      <c r="BE9" s="26"/>
+      <c r="BF9" s="26"/>
+      <c r="BH9" s="25"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
       <c r="BM9" s="1"/>
@@ -1901,19 +1864,9 @@
       <c r="CL9" s="1"/>
     </row>
     <row r="10" spans="3:90">
-      <c r="C10" s="11"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10" s="21"/>
-      <c r="K10"/>
-      <c r="L10"/>
-      <c r="M10"/>
-      <c r="N10"/>
-      <c r="O10"/>
+      <c r="C10" s="10"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -1924,7 +1877,6 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-      <c r="AA10"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AE10" s="1"/>
@@ -1935,11 +1887,8 @@
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
       <c r="AL10" s="1"/>
-      <c r="AM10"/>
       <c r="AR10" s="1"/>
       <c r="AS10" s="1"/>
-      <c r="AT10"/>
-      <c r="AU10"/>
       <c r="AV10" s="1"/>
       <c r="AW10" s="1"/>
       <c r="AX10" s="1"/>
@@ -1949,12 +1898,9 @@
       <c r="BB10" s="1"/>
       <c r="BC10" s="1"/>
       <c r="BD10" s="1"/>
-      <c r="BE10" s="28"/>
-      <c r="BF10" s="28"/>
-      <c r="BG10"/>
-      <c r="BH10" s="27"/>
-      <c r="BI10"/>
-      <c r="BJ10"/>
+      <c r="BE10" s="26"/>
+      <c r="BF10" s="26"/>
+      <c r="BH10" s="25"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
       <c r="BM10" s="1"/>
@@ -1985,19 +1931,9 @@
       <c r="CL10" s="1"/>
     </row>
     <row r="11" spans="3:90">
-      <c r="C11" s="11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11" s="21"/>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
+      <c r="C11" s="10"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -2008,22 +1944,18 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
-      <c r="AA11"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AE11" s="1"/>
-      <c r="AF11" s="27"/>
+      <c r="AF11" s="25"/>
       <c r="AG11" s="1"/>
-      <c r="AH11" s="28"/>
+      <c r="AH11" s="26"/>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
-      <c r="AM11"/>
       <c r="AR11" s="1"/>
       <c r="AS11" s="1"/>
-      <c r="AT11"/>
-      <c r="AU11"/>
       <c r="AV11" s="1"/>
       <c r="AW11" s="1"/>
       <c r="AX11" s="1"/>
@@ -2033,12 +1965,9 @@
       <c r="BB11" s="1"/>
       <c r="BC11" s="1"/>
       <c r="BD11" s="1"/>
-      <c r="BE11" s="28"/>
-      <c r="BF11" s="28"/>
-      <c r="BG11"/>
-      <c r="BH11" s="27"/>
-      <c r="BI11"/>
-      <c r="BJ11"/>
+      <c r="BE11" s="26"/>
+      <c r="BF11" s="26"/>
+      <c r="BH11" s="25"/>
       <c r="BK11" s="1"/>
       <c r="BL11" s="1"/>
       <c r="BM11" s="1"/>
@@ -2069,19 +1998,9 @@
       <c r="CL11" s="1"/>
     </row>
     <row r="12" spans="3:90">
-      <c r="C12" s="11"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12" s="21"/>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
-      <c r="N12"/>
-      <c r="O12"/>
+      <c r="C12" s="10"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
@@ -2092,22 +2011,18 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
-      <c r="AA12"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AE12" s="1"/>
-      <c r="AF12" s="27"/>
+      <c r="AF12" s="25"/>
       <c r="AG12" s="1"/>
-      <c r="AH12" s="28"/>
+      <c r="AH12" s="26"/>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
       <c r="AL12" s="1"/>
-      <c r="AM12"/>
       <c r="AR12" s="1"/>
       <c r="AS12" s="1"/>
-      <c r="AT12"/>
-      <c r="AU12"/>
       <c r="AV12" s="1"/>
       <c r="AW12" s="1"/>
       <c r="AX12" s="1"/>
@@ -2117,12 +2032,9 @@
       <c r="BB12" s="1"/>
       <c r="BC12" s="1"/>
       <c r="BD12" s="1"/>
-      <c r="BE12" s="28"/>
-      <c r="BF12" s="28"/>
-      <c r="BG12"/>
-      <c r="BH12" s="27"/>
-      <c r="BI12"/>
-      <c r="BJ12"/>
+      <c r="BE12" s="26"/>
+      <c r="BF12" s="26"/>
+      <c r="BH12" s="25"/>
       <c r="BK12" s="1"/>
       <c r="BL12" s="1"/>
       <c r="BM12" s="1"/>
@@ -2153,10 +2065,9 @@
       <c r="CL12" s="1"/>
     </row>
     <row r="13" spans="3:90">
-      <c r="C13" s="11"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="J13" s="21"/>
+      <c r="C13" s="10"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
@@ -2177,11 +2088,8 @@
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
       <c r="AL13" s="1"/>
-      <c r="AM13"/>
       <c r="AR13" s="1"/>
       <c r="AS13" s="1"/>
-      <c r="AT13"/>
-      <c r="AU13"/>
       <c r="AV13" s="1"/>
       <c r="AW13" s="1"/>
       <c r="AX13" s="1"/>
@@ -2191,12 +2099,9 @@
       <c r="BB13" s="1"/>
       <c r="BC13" s="1"/>
       <c r="BD13" s="1"/>
-      <c r="BE13" s="28"/>
-      <c r="BF13" s="28"/>
-      <c r="BG13"/>
-      <c r="BH13" s="27"/>
-      <c r="BI13"/>
-      <c r="BJ13"/>
+      <c r="BE13" s="26"/>
+      <c r="BF13" s="26"/>
+      <c r="BH13" s="25"/>
       <c r="BK13" s="1"/>
       <c r="BL13" s="1"/>
       <c r="BM13" s="1"/>
@@ -2229,14 +2134,14 @@
     <row r="14" s="3" customFormat="1" spans="1:90">
       <c r="A14"/>
       <c r="B14"/>
-      <c r="C14" s="11"/>
+      <c r="C14" s="10"/>
       <c r="D14"/>
       <c r="E14"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
       <c r="H14"/>
       <c r="I14"/>
-      <c r="J14" s="21"/>
+      <c r="J14" s="4"/>
       <c r="K14"/>
       <c r="L14"/>
       <c r="M14"/>
@@ -2256,7 +2161,7 @@
       <c r="AA14"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
-      <c r="AD14" s="4"/>
+      <c r="AD14" s="5"/>
       <c r="AE14" s="1"/>
       <c r="AF14" s="1"/>
       <c r="AG14" s="1"/>
@@ -2283,10 +2188,10 @@
       <c r="BB14" s="1"/>
       <c r="BC14" s="1"/>
       <c r="BD14" s="1"/>
-      <c r="BE14" s="28"/>
-      <c r="BF14" s="28"/>
+      <c r="BE14" s="26"/>
+      <c r="BF14" s="26"/>
       <c r="BG14"/>
-      <c r="BH14" s="27"/>
+      <c r="BH14" s="25"/>
       <c r="BI14"/>
       <c r="BJ14"/>
       <c r="BK14" s="1"/>
@@ -2319,19 +2224,9 @@
       <c r="CL14" s="1"/>
     </row>
     <row r="15" spans="3:90">
-      <c r="C15" s="11"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15" s="21"/>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
+      <c r="C15" s="10"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
@@ -2342,7 +2237,6 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
-      <c r="AA15"/>
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AE15" s="1"/>
@@ -2353,11 +2247,8 @@
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
       <c r="AL15" s="1"/>
-      <c r="AM15"/>
       <c r="AR15" s="1"/>
       <c r="AS15" s="1"/>
-      <c r="AT15"/>
-      <c r="AU15"/>
       <c r="AV15" s="1"/>
       <c r="AW15" s="1"/>
       <c r="AX15" s="1"/>
@@ -2367,12 +2258,9 @@
       <c r="BB15" s="1"/>
       <c r="BC15" s="1"/>
       <c r="BD15" s="1"/>
-      <c r="BE15" s="28"/>
-      <c r="BF15" s="28"/>
-      <c r="BG15"/>
-      <c r="BH15" s="27"/>
-      <c r="BI15"/>
-      <c r="BJ15"/>
+      <c r="BE15" s="26"/>
+      <c r="BF15" s="26"/>
+      <c r="BH15" s="25"/>
       <c r="BK15" s="1"/>
       <c r="BL15" s="1"/>
       <c r="BM15" s="1"/>
@@ -2403,19 +2291,9 @@
       <c r="CL15" s="1"/>
     </row>
     <row r="16" spans="3:90">
-      <c r="C16" s="11"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16" s="21"/>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16"/>
+      <c r="C16" s="10"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -2426,7 +2304,6 @@
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
-      <c r="AA16"/>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AE16" s="1"/>
@@ -2437,11 +2314,8 @@
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
       <c r="AL16" s="1"/>
-      <c r="AM16"/>
       <c r="AR16" s="1"/>
       <c r="AS16" s="1"/>
-      <c r="AT16"/>
-      <c r="AU16"/>
       <c r="AV16" s="1"/>
       <c r="AW16" s="1"/>
       <c r="AX16" s="1"/>
@@ -2451,12 +2325,9 @@
       <c r="BB16" s="1"/>
       <c r="BC16" s="1"/>
       <c r="BD16" s="1"/>
-      <c r="BE16" s="28"/>
-      <c r="BF16" s="28"/>
-      <c r="BG16"/>
-      <c r="BH16" s="27"/>
-      <c r="BI16"/>
-      <c r="BJ16"/>
+      <c r="BE16" s="26"/>
+      <c r="BF16" s="26"/>
+      <c r="BH16" s="25"/>
       <c r="BK16" s="1"/>
       <c r="BL16" s="1"/>
       <c r="BM16" s="1"/>
@@ -2487,19 +2358,9 @@
       <c r="CL16" s="1"/>
     </row>
     <row r="17" spans="3:90">
-      <c r="C17" s="11"/>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17" s="21"/>
-      <c r="K17"/>
-      <c r="L17"/>
-      <c r="M17"/>
-      <c r="N17"/>
-      <c r="O17"/>
+      <c r="C17" s="10"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
@@ -2510,7 +2371,6 @@
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
-      <c r="AA17"/>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AE17" s="1"/>
@@ -2521,11 +2381,8 @@
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
       <c r="AL17" s="1"/>
-      <c r="AM17"/>
       <c r="AR17" s="1"/>
       <c r="AS17" s="1"/>
-      <c r="AT17"/>
-      <c r="AU17"/>
       <c r="AV17" s="1"/>
       <c r="AW17" s="1"/>
       <c r="AX17" s="1"/>
@@ -2535,12 +2392,9 @@
       <c r="BB17" s="1"/>
       <c r="BC17" s="1"/>
       <c r="BD17" s="1"/>
-      <c r="BE17" s="28"/>
-      <c r="BF17" s="28"/>
-      <c r="BG17"/>
-      <c r="BH17" s="27"/>
-      <c r="BI17"/>
-      <c r="BJ17"/>
+      <c r="BE17" s="26"/>
+      <c r="BF17" s="26"/>
+      <c r="BH17" s="25"/>
       <c r="BK17" s="1"/>
       <c r="BL17" s="1"/>
       <c r="BM17" s="1"/>
@@ -2573,14 +2427,14 @@
     <row r="18" s="3" customFormat="1" spans="1:90">
       <c r="A18"/>
       <c r="B18"/>
-      <c r="C18" s="11"/>
+      <c r="C18" s="10"/>
       <c r="D18"/>
       <c r="E18"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
       <c r="H18"/>
       <c r="I18"/>
-      <c r="J18" s="21"/>
+      <c r="J18" s="4"/>
       <c r="K18"/>
       <c r="L18"/>
       <c r="M18"/>
@@ -2600,7 +2454,7 @@
       <c r="AA18"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
-      <c r="AD18" s="4"/>
+      <c r="AD18" s="5"/>
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1"/>
@@ -2627,10 +2481,10 @@
       <c r="BB18" s="1"/>
       <c r="BC18" s="1"/>
       <c r="BD18" s="1"/>
-      <c r="BE18" s="28"/>
-      <c r="BF18" s="28"/>
+      <c r="BE18" s="26"/>
+      <c r="BF18" s="26"/>
       <c r="BG18"/>
-      <c r="BH18" s="27"/>
+      <c r="BH18" s="25"/>
       <c r="BI18"/>
       <c r="BJ18"/>
       <c r="BK18" s="1"/>
@@ -2663,19 +2517,9 @@
       <c r="CL18" s="1"/>
     </row>
     <row r="19" spans="3:90">
-      <c r="C19" s="11"/>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19" s="21"/>
-      <c r="K19"/>
-      <c r="L19"/>
-      <c r="M19"/>
-      <c r="N19"/>
-      <c r="O19"/>
+      <c r="C19" s="10"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
@@ -2686,7 +2530,6 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
-      <c r="AA19"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AE19" s="1"/>
@@ -2697,11 +2540,8 @@
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
-      <c r="AM19"/>
       <c r="AR19" s="1"/>
       <c r="AS19" s="1"/>
-      <c r="AT19"/>
-      <c r="AU19"/>
       <c r="AV19" s="1"/>
       <c r="AW19" s="1"/>
       <c r="AX19" s="1"/>
@@ -2711,12 +2551,9 @@
       <c r="BB19" s="1"/>
       <c r="BC19" s="1"/>
       <c r="BD19" s="1"/>
-      <c r="BE19" s="28"/>
-      <c r="BF19" s="28"/>
-      <c r="BG19"/>
-      <c r="BH19" s="27"/>
-      <c r="BI19"/>
-      <c r="BJ19"/>
+      <c r="BE19" s="26"/>
+      <c r="BF19" s="26"/>
+      <c r="BH19" s="25"/>
       <c r="BK19" s="1"/>
       <c r="BL19" s="1"/>
       <c r="BM19" s="1"/>
@@ -2747,19 +2584,9 @@
       <c r="CL19" s="1"/>
     </row>
     <row r="20" spans="3:90">
-      <c r="C20" s="11"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20" s="21"/>
-      <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
-      <c r="N20"/>
-      <c r="O20"/>
+      <c r="C20" s="10"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="12"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
@@ -2770,7 +2597,6 @@
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
-      <c r="AA20"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AE20" s="1"/>
@@ -2781,11 +2607,8 @@
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
       <c r="AL20" s="1"/>
-      <c r="AM20"/>
       <c r="AR20" s="1"/>
       <c r="AS20" s="1"/>
-      <c r="AT20"/>
-      <c r="AU20"/>
       <c r="AV20" s="1"/>
       <c r="AW20" s="1"/>
       <c r="AX20" s="1"/>
@@ -2795,12 +2618,9 @@
       <c r="BB20" s="1"/>
       <c r="BC20" s="1"/>
       <c r="BD20" s="1"/>
-      <c r="BE20" s="28"/>
-      <c r="BF20" s="28"/>
-      <c r="BG20"/>
-      <c r="BH20" s="27"/>
-      <c r="BI20"/>
-      <c r="BJ20"/>
+      <c r="BE20" s="26"/>
+      <c r="BF20" s="26"/>
+      <c r="BH20" s="25"/>
       <c r="BK20" s="1"/>
       <c r="BL20" s="1"/>
       <c r="BM20" s="1"/>
@@ -2831,19 +2651,9 @@
       <c r="CL20" s="1"/>
     </row>
     <row r="21" spans="3:90">
-      <c r="C21" s="11"/>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21" s="21"/>
-      <c r="K21"/>
-      <c r="L21"/>
-      <c r="M21"/>
-      <c r="N21"/>
-      <c r="O21"/>
+      <c r="C21" s="10"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="12"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
@@ -2854,7 +2664,6 @@
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
-      <c r="AA21"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AE21" s="1"/>
@@ -2865,11 +2674,8 @@
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
       <c r="AL21" s="1"/>
-      <c r="AM21"/>
       <c r="AR21" s="1"/>
       <c r="AS21" s="1"/>
-      <c r="AT21"/>
-      <c r="AU21"/>
       <c r="AV21" s="1"/>
       <c r="AW21" s="1"/>
       <c r="AX21" s="1"/>
@@ -2879,12 +2685,9 @@
       <c r="BB21" s="1"/>
       <c r="BC21" s="1"/>
       <c r="BD21" s="1"/>
-      <c r="BE21" s="28"/>
-      <c r="BF21" s="28"/>
-      <c r="BG21"/>
-      <c r="BH21" s="27"/>
-      <c r="BI21"/>
-      <c r="BJ21"/>
+      <c r="BE21" s="26"/>
+      <c r="BF21" s="26"/>
+      <c r="BH21" s="25"/>
       <c r="BK21" s="1"/>
       <c r="BL21" s="1"/>
       <c r="BM21" s="1"/>
@@ -2915,19 +2718,9 @@
       <c r="CL21" s="1"/>
     </row>
     <row r="22" spans="3:90">
-      <c r="C22" s="11"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22" s="21"/>
-      <c r="K22"/>
-      <c r="L22"/>
-      <c r="M22"/>
-      <c r="N22"/>
-      <c r="O22"/>
+      <c r="C22" s="10"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="12"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
@@ -2938,7 +2731,6 @@
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
-      <c r="AA22"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AE22" s="1"/>
@@ -2949,11 +2741,8 @@
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
       <c r="AL22" s="1"/>
-      <c r="AM22"/>
       <c r="AR22" s="1"/>
       <c r="AS22" s="1"/>
-      <c r="AT22"/>
-      <c r="AU22"/>
       <c r="AV22" s="1"/>
       <c r="AW22" s="1"/>
       <c r="AX22" s="1"/>
@@ -2963,12 +2752,9 @@
       <c r="BB22" s="1"/>
       <c r="BC22" s="1"/>
       <c r="BD22" s="1"/>
-      <c r="BE22" s="28"/>
-      <c r="BF22" s="28"/>
-      <c r="BG22"/>
-      <c r="BH22" s="27"/>
-      <c r="BI22"/>
-      <c r="BJ22"/>
+      <c r="BE22" s="26"/>
+      <c r="BF22" s="26"/>
+      <c r="BH22" s="25"/>
       <c r="BK22" s="1"/>
       <c r="BL22" s="1"/>
       <c r="BM22" s="1"/>
@@ -2999,19 +2785,9 @@
       <c r="CL22" s="1"/>
     </row>
     <row r="23" spans="3:90">
-      <c r="C23" s="11"/>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23" s="21"/>
-      <c r="K23"/>
-      <c r="L23"/>
-      <c r="M23"/>
-      <c r="N23"/>
-      <c r="O23"/>
+      <c r="C23" s="10"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="12"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
@@ -3022,7 +2798,6 @@
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
-      <c r="AA23"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AE23" s="1"/>
@@ -3033,11 +2808,8 @@
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
       <c r="AL23" s="1"/>
-      <c r="AM23"/>
       <c r="AR23" s="1"/>
       <c r="AS23" s="1"/>
-      <c r="AT23"/>
-      <c r="AU23"/>
       <c r="AV23" s="1"/>
       <c r="AW23" s="1"/>
       <c r="AX23" s="1"/>
@@ -3047,12 +2819,9 @@
       <c r="BB23" s="1"/>
       <c r="BC23" s="1"/>
       <c r="BD23" s="1"/>
-      <c r="BE23" s="28"/>
-      <c r="BF23" s="28"/>
-      <c r="BG23"/>
-      <c r="BH23" s="27"/>
-      <c r="BI23"/>
-      <c r="BJ23"/>
+      <c r="BE23" s="26"/>
+      <c r="BF23" s="26"/>
+      <c r="BH23" s="25"/>
       <c r="BK23" s="1"/>
       <c r="BL23" s="1"/>
       <c r="BM23" s="1"/>
@@ -3083,10 +2852,9 @@
       <c r="CL23" s="1"/>
     </row>
     <row r="24" spans="3:90">
-      <c r="C24" s="11"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="J24" s="21"/>
+      <c r="C24" s="10"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
@@ -3097,7 +2865,6 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
-      <c r="AA24"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AE24" s="1"/>
@@ -3108,11 +2875,8 @@
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
       <c r="AL24" s="1"/>
-      <c r="AM24"/>
       <c r="AR24" s="1"/>
       <c r="AS24" s="1"/>
-      <c r="AT24"/>
-      <c r="AU24"/>
       <c r="AV24" s="1"/>
       <c r="AW24" s="1"/>
       <c r="AX24" s="1"/>
@@ -3122,12 +2886,9 @@
       <c r="BB24" s="1"/>
       <c r="BC24" s="1"/>
       <c r="BD24" s="1"/>
-      <c r="BE24" s="28"/>
-      <c r="BF24" s="28"/>
-      <c r="BG24"/>
-      <c r="BH24" s="27"/>
-      <c r="BI24"/>
-      <c r="BJ24"/>
+      <c r="BE24" s="26"/>
+      <c r="BF24" s="26"/>
+      <c r="BH24" s="25"/>
       <c r="BK24" s="1"/>
       <c r="BL24" s="1"/>
       <c r="BM24" s="1"/>
@@ -3158,10 +2919,9 @@
       <c r="CL24" s="1"/>
     </row>
     <row r="25" spans="3:90">
-      <c r="C25" s="11"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="J25" s="21"/>
+      <c r="C25" s="10"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
@@ -3172,7 +2932,6 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
-      <c r="AA25"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AE25" s="1"/>
@@ -3183,11 +2942,8 @@
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
       <c r="AL25" s="1"/>
-      <c r="AM25"/>
       <c r="AR25" s="1"/>
       <c r="AS25" s="1"/>
-      <c r="AT25"/>
-      <c r="AU25"/>
       <c r="AV25" s="1"/>
       <c r="AW25" s="1"/>
       <c r="AX25" s="1"/>
@@ -3197,12 +2953,9 @@
       <c r="BB25" s="1"/>
       <c r="BC25" s="1"/>
       <c r="BD25" s="1"/>
-      <c r="BE25" s="28"/>
-      <c r="BF25" s="28"/>
-      <c r="BG25"/>
-      <c r="BH25" s="27"/>
-      <c r="BI25"/>
-      <c r="BJ25"/>
+      <c r="BE25" s="26"/>
+      <c r="BF25" s="26"/>
+      <c r="BH25" s="25"/>
       <c r="BK25" s="1"/>
       <c r="BL25" s="1"/>
       <c r="BM25" s="1"/>
@@ -3233,10 +2986,9 @@
       <c r="CL25" s="1"/>
     </row>
     <row r="26" spans="3:90">
-      <c r="C26" s="11"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="J26" s="21"/>
+      <c r="C26" s="10"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
@@ -3247,7 +2999,6 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
-      <c r="AA26"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AE26" s="1"/>
@@ -3258,11 +3009,8 @@
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
       <c r="AL26" s="1"/>
-      <c r="AM26"/>
       <c r="AR26" s="1"/>
       <c r="AS26" s="1"/>
-      <c r="AT26"/>
-      <c r="AU26"/>
       <c r="AV26" s="1"/>
       <c r="AW26" s="1"/>
       <c r="AX26" s="1"/>
@@ -3272,12 +3020,9 @@
       <c r="BB26" s="1"/>
       <c r="BC26" s="1"/>
       <c r="BD26" s="1"/>
-      <c r="BE26" s="28"/>
-      <c r="BF26" s="28"/>
-      <c r="BG26"/>
-      <c r="BH26" s="27"/>
-      <c r="BI26"/>
-      <c r="BJ26"/>
+      <c r="BE26" s="26"/>
+      <c r="BF26" s="26"/>
+      <c r="BH26" s="25"/>
       <c r="BK26" s="1"/>
       <c r="BL26" s="1"/>
       <c r="BM26" s="1"/>
@@ -3308,10 +3053,9 @@
       <c r="CL26" s="1"/>
     </row>
     <row r="27" spans="3:90">
-      <c r="C27" s="11"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="J27" s="21"/>
+      <c r="C27" s="10"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
@@ -3322,7 +3066,6 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
-      <c r="AA27"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AE27" s="1"/>
@@ -3333,11 +3076,8 @@
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
       <c r="AL27" s="1"/>
-      <c r="AM27"/>
       <c r="AR27" s="1"/>
       <c r="AS27" s="1"/>
-      <c r="AT27"/>
-      <c r="AU27"/>
       <c r="AV27" s="1"/>
       <c r="AW27" s="1"/>
       <c r="AX27" s="1"/>
@@ -3347,12 +3087,9 @@
       <c r="BB27" s="1"/>
       <c r="BC27" s="1"/>
       <c r="BD27" s="1"/>
-      <c r="BE27" s="28"/>
-      <c r="BF27" s="28"/>
-      <c r="BG27"/>
-      <c r="BH27" s="27"/>
-      <c r="BI27"/>
-      <c r="BJ27"/>
+      <c r="BE27" s="26"/>
+      <c r="BF27" s="26"/>
+      <c r="BH27" s="25"/>
       <c r="BK27" s="1"/>
       <c r="BL27" s="1"/>
       <c r="BM27" s="1"/>
@@ -3383,10 +3120,9 @@
       <c r="CL27" s="1"/>
     </row>
     <row r="28" spans="3:90">
-      <c r="C28" s="11"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="J28" s="21"/>
+      <c r="C28" s="10"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
@@ -3397,7 +3133,6 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
-      <c r="AA28"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
       <c r="AE28" s="1"/>
@@ -3408,11 +3143,8 @@
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
       <c r="AL28" s="1"/>
-      <c r="AM28"/>
       <c r="AR28" s="1"/>
       <c r="AS28" s="1"/>
-      <c r="AT28"/>
-      <c r="AU28"/>
       <c r="AV28" s="1"/>
       <c r="AW28" s="1"/>
       <c r="AX28" s="1"/>
@@ -3422,12 +3154,9 @@
       <c r="BB28" s="1"/>
       <c r="BC28" s="1"/>
       <c r="BD28" s="1"/>
-      <c r="BE28" s="28"/>
-      <c r="BF28" s="28"/>
-      <c r="BG28"/>
-      <c r="BH28" s="27"/>
-      <c r="BI28"/>
-      <c r="BJ28"/>
+      <c r="BE28" s="26"/>
+      <c r="BF28" s="26"/>
+      <c r="BH28" s="25"/>
       <c r="BK28" s="1"/>
       <c r="BL28" s="1"/>
       <c r="BM28" s="1"/>
@@ -3460,14 +3189,14 @@
     <row r="29" s="3" customFormat="1" spans="1:90">
       <c r="A29"/>
       <c r="B29"/>
-      <c r="C29" s="11"/>
+      <c r="C29" s="10"/>
       <c r="D29"/>
       <c r="E29"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
       <c r="H29"/>
       <c r="I29"/>
-      <c r="J29" s="21"/>
+      <c r="J29" s="4"/>
       <c r="K29"/>
       <c r="L29"/>
       <c r="M29"/>
@@ -3487,7 +3216,7 @@
       <c r="AA29"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
-      <c r="AD29" s="4"/>
+      <c r="AD29" s="5"/>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
       <c r="AG29" s="1"/>
@@ -3514,10 +3243,10 @@
       <c r="BB29" s="1"/>
       <c r="BC29" s="1"/>
       <c r="BD29" s="1"/>
-      <c r="BE29" s="28"/>
-      <c r="BF29" s="28"/>
+      <c r="BE29" s="26"/>
+      <c r="BF29" s="26"/>
       <c r="BG29"/>
-      <c r="BH29" s="27"/>
+      <c r="BH29" s="25"/>
       <c r="BI29"/>
       <c r="BJ29"/>
       <c r="BK29" s="1"/>
@@ -3550,10 +3279,9 @@
       <c r="CL29" s="1"/>
     </row>
     <row r="30" spans="3:90">
-      <c r="C30" s="11"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="J30" s="21"/>
+      <c r="C30" s="10"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
@@ -3564,7 +3292,6 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
-      <c r="AA30"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AE30" s="1"/>
@@ -3575,11 +3302,8 @@
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
       <c r="AL30" s="1"/>
-      <c r="AM30"/>
       <c r="AR30" s="1"/>
       <c r="AS30" s="1"/>
-      <c r="AT30"/>
-      <c r="AU30"/>
       <c r="AV30" s="1"/>
       <c r="AW30" s="1"/>
       <c r="AX30" s="1"/>
@@ -3589,12 +3313,9 @@
       <c r="BB30" s="1"/>
       <c r="BC30" s="1"/>
       <c r="BD30" s="1"/>
-      <c r="BE30" s="28"/>
-      <c r="BF30" s="28"/>
-      <c r="BG30"/>
-      <c r="BH30" s="27"/>
-      <c r="BI30"/>
-      <c r="BJ30"/>
+      <c r="BE30" s="26"/>
+      <c r="BF30" s="26"/>
+      <c r="BH30" s="25"/>
       <c r="BK30" s="1"/>
       <c r="BL30" s="1"/>
       <c r="BM30" s="1"/>
@@ -3625,10 +3346,9 @@
       <c r="CL30" s="1"/>
     </row>
     <row r="31" spans="3:90">
-      <c r="C31" s="11"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="J31" s="21"/>
+      <c r="C31" s="10"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
@@ -3639,7 +3359,6 @@
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
-      <c r="AA31"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AE31" s="1"/>
@@ -3650,11 +3369,8 @@
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
       <c r="AL31" s="1"/>
-      <c r="AM31"/>
       <c r="AR31" s="1"/>
       <c r="AS31" s="1"/>
-      <c r="AT31"/>
-      <c r="AU31"/>
       <c r="AV31" s="1"/>
       <c r="AW31" s="1"/>
       <c r="AX31" s="1"/>
@@ -3664,12 +3380,9 @@
       <c r="BB31" s="1"/>
       <c r="BC31" s="1"/>
       <c r="BD31" s="1"/>
-      <c r="BE31" s="28"/>
-      <c r="BF31" s="28"/>
-      <c r="BG31"/>
-      <c r="BH31" s="27"/>
-      <c r="BI31"/>
-      <c r="BJ31"/>
+      <c r="BE31" s="26"/>
+      <c r="BF31" s="26"/>
+      <c r="BH31" s="25"/>
       <c r="BK31" s="1"/>
       <c r="BL31" s="1"/>
       <c r="BM31" s="1"/>
@@ -3700,10 +3413,9 @@
       <c r="CL31" s="1"/>
     </row>
     <row r="32" spans="3:90">
-      <c r="C32" s="11"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="J32" s="21"/>
+      <c r="C32" s="10"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
@@ -3714,7 +3426,6 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
-      <c r="AA32"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AE32" s="1"/>
@@ -3725,11 +3436,8 @@
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
       <c r="AL32" s="1"/>
-      <c r="AM32"/>
       <c r="AR32" s="1"/>
       <c r="AS32" s="1"/>
-      <c r="AT32"/>
-      <c r="AU32"/>
       <c r="AV32" s="1"/>
       <c r="AW32" s="1"/>
       <c r="AX32" s="1"/>
@@ -3739,12 +3447,9 @@
       <c r="BB32" s="1"/>
       <c r="BC32" s="1"/>
       <c r="BD32" s="1"/>
-      <c r="BE32" s="28"/>
-      <c r="BF32" s="28"/>
-      <c r="BG32"/>
-      <c r="BH32" s="27"/>
-      <c r="BI32"/>
-      <c r="BJ32"/>
+      <c r="BE32" s="26"/>
+      <c r="BF32" s="26"/>
+      <c r="BH32" s="25"/>
       <c r="BK32" s="1"/>
       <c r="BL32" s="1"/>
       <c r="BM32" s="1"/>
@@ -3775,10 +3480,9 @@
       <c r="CL32" s="1"/>
     </row>
     <row r="33" spans="3:90">
-      <c r="C33" s="11"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="J33" s="21"/>
+      <c r="C33" s="10"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
@@ -3789,7 +3493,6 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
-      <c r="AA33"/>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AE33" s="1"/>
@@ -3800,11 +3503,8 @@
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
       <c r="AL33" s="1"/>
-      <c r="AM33"/>
       <c r="AR33" s="1"/>
       <c r="AS33" s="1"/>
-      <c r="AT33"/>
-      <c r="AU33"/>
       <c r="AV33" s="1"/>
       <c r="AW33" s="1"/>
       <c r="AX33" s="1"/>
@@ -3814,12 +3514,9 @@
       <c r="BB33" s="1"/>
       <c r="BC33" s="1"/>
       <c r="BD33" s="1"/>
-      <c r="BE33" s="28"/>
-      <c r="BF33" s="28"/>
-      <c r="BG33"/>
-      <c r="BH33" s="27"/>
-      <c r="BI33"/>
-      <c r="BJ33"/>
+      <c r="BE33" s="26"/>
+      <c r="BF33" s="26"/>
+      <c r="BH33" s="25"/>
       <c r="BK33" s="1"/>
       <c r="BL33" s="1"/>
       <c r="BM33" s="1"/>
@@ -3850,10 +3547,9 @@
       <c r="CL33" s="1"/>
     </row>
     <row r="34" spans="3:90">
-      <c r="C34" s="11"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="J34" s="21"/>
+      <c r="C34" s="10"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
@@ -3864,7 +3560,6 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
-      <c r="AA34"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AE34" s="1"/>
@@ -3875,11 +3570,8 @@
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
       <c r="AL34" s="1"/>
-      <c r="AM34"/>
       <c r="AR34" s="1"/>
       <c r="AS34" s="1"/>
-      <c r="AT34"/>
-      <c r="AU34"/>
       <c r="AV34" s="1"/>
       <c r="AW34" s="1"/>
       <c r="AX34" s="1"/>
@@ -3889,12 +3581,9 @@
       <c r="BB34" s="1"/>
       <c r="BC34" s="1"/>
       <c r="BD34" s="1"/>
-      <c r="BE34" s="28"/>
-      <c r="BF34" s="28"/>
-      <c r="BG34"/>
-      <c r="BH34" s="27"/>
-      <c r="BI34"/>
-      <c r="BJ34"/>
+      <c r="BE34" s="26"/>
+      <c r="BF34" s="26"/>
+      <c r="BH34" s="25"/>
       <c r="BK34" s="1"/>
       <c r="BL34" s="1"/>
       <c r="BM34" s="1"/>
@@ -3925,10 +3614,9 @@
       <c r="CL34" s="1"/>
     </row>
     <row r="35" spans="3:90">
-      <c r="C35" s="11"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="J35" s="21"/>
+      <c r="C35" s="10"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
@@ -3939,7 +3627,6 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
-      <c r="AA35"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AE35" s="1"/>
@@ -3950,11 +3637,8 @@
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
       <c r="AL35" s="1"/>
-      <c r="AM35"/>
       <c r="AR35" s="1"/>
       <c r="AS35" s="1"/>
-      <c r="AT35"/>
-      <c r="AU35"/>
       <c r="AV35" s="1"/>
       <c r="AW35" s="1"/>
       <c r="AX35" s="1"/>
@@ -3964,12 +3648,9 @@
       <c r="BB35" s="1"/>
       <c r="BC35" s="1"/>
       <c r="BD35" s="1"/>
-      <c r="BE35" s="28"/>
-      <c r="BF35" s="28"/>
-      <c r="BG35"/>
-      <c r="BH35" s="27"/>
-      <c r="BI35"/>
-      <c r="BJ35"/>
+      <c r="BE35" s="26"/>
+      <c r="BF35" s="26"/>
+      <c r="BH35" s="25"/>
       <c r="BK35" s="1"/>
       <c r="BL35" s="1"/>
       <c r="BM35" s="1"/>
@@ -4000,10 +3681,9 @@
       <c r="CL35" s="1"/>
     </row>
     <row r="36" spans="3:90">
-      <c r="C36" s="11"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="J36" s="21"/>
+      <c r="C36" s="10"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
@@ -4014,7 +3694,6 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
-      <c r="AA36"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AE36" s="1"/>
@@ -4025,11 +3704,8 @@
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
       <c r="AL36" s="1"/>
-      <c r="AM36"/>
       <c r="AR36" s="1"/>
       <c r="AS36" s="1"/>
-      <c r="AT36"/>
-      <c r="AU36"/>
       <c r="AV36" s="1"/>
       <c r="AW36" s="1"/>
       <c r="AX36" s="1"/>
@@ -4039,12 +3715,9 @@
       <c r="BB36" s="1"/>
       <c r="BC36" s="1"/>
       <c r="BD36" s="1"/>
-      <c r="BE36" s="28"/>
-      <c r="BF36" s="28"/>
-      <c r="BG36"/>
-      <c r="BH36" s="27"/>
-      <c r="BI36"/>
-      <c r="BJ36"/>
+      <c r="BE36" s="26"/>
+      <c r="BF36" s="26"/>
+      <c r="BH36" s="25"/>
       <c r="BK36" s="1"/>
       <c r="BL36" s="1"/>
       <c r="BM36" s="1"/>
@@ -4075,10 +3748,9 @@
       <c r="CL36" s="1"/>
     </row>
     <row r="37" spans="3:90">
-      <c r="C37" s="11"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="J37" s="21"/>
+      <c r="C37" s="10"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
@@ -4089,7 +3761,6 @@
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
-      <c r="AA37"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AE37" s="1"/>
@@ -4100,11 +3771,8 @@
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
       <c r="AL37" s="1"/>
-      <c r="AM37"/>
       <c r="AR37" s="1"/>
       <c r="AS37" s="1"/>
-      <c r="AT37"/>
-      <c r="AU37"/>
       <c r="AV37" s="1"/>
       <c r="AW37" s="1"/>
       <c r="AX37" s="1"/>
@@ -4114,12 +3782,9 @@
       <c r="BB37" s="1"/>
       <c r="BC37" s="1"/>
       <c r="BD37" s="1"/>
-      <c r="BE37" s="28"/>
-      <c r="BF37" s="28"/>
-      <c r="BG37"/>
-      <c r="BH37" s="27"/>
-      <c r="BI37"/>
-      <c r="BJ37"/>
+      <c r="BE37" s="26"/>
+      <c r="BF37" s="26"/>
+      <c r="BH37" s="25"/>
       <c r="BK37" s="1"/>
       <c r="BL37" s="1"/>
       <c r="BM37" s="1"/>
@@ -4150,19 +3815,9 @@
       <c r="CL37" s="1"/>
     </row>
     <row r="38" spans="3:90">
-      <c r="C38" s="11"/>
-      <c r="D38"/>
-      <c r="E38"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38"/>
-      <c r="I38"/>
-      <c r="J38" s="21"/>
-      <c r="K38"/>
-      <c r="L38"/>
-      <c r="M38"/>
-      <c r="N38"/>
-      <c r="O38"/>
+      <c r="C38" s="10"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
@@ -4173,7 +3828,6 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
-      <c r="AA38"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AE38" s="1"/>
@@ -4184,11 +3838,8 @@
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
       <c r="AL38" s="1"/>
-      <c r="AM38"/>
       <c r="AR38" s="1"/>
       <c r="AS38" s="1"/>
-      <c r="AT38"/>
-      <c r="AU38"/>
       <c r="AV38" s="1"/>
       <c r="AW38" s="1"/>
       <c r="AX38" s="1"/>
@@ -4198,12 +3849,9 @@
       <c r="BB38" s="1"/>
       <c r="BC38" s="1"/>
       <c r="BD38" s="1"/>
-      <c r="BE38" s="28"/>
-      <c r="BF38" s="28"/>
-      <c r="BG38"/>
-      <c r="BH38" s="27"/>
-      <c r="BI38"/>
-      <c r="BJ38"/>
+      <c r="BE38" s="26"/>
+      <c r="BF38" s="26"/>
+      <c r="BH38" s="25"/>
       <c r="BK38" s="1"/>
       <c r="BL38" s="1"/>
       <c r="BM38" s="1"/>
@@ -4234,19 +3882,9 @@
       <c r="CL38" s="1"/>
     </row>
     <row r="39" spans="3:90">
-      <c r="C39" s="11"/>
-      <c r="D39"/>
-      <c r="E39"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39"/>
-      <c r="I39"/>
-      <c r="J39" s="21"/>
-      <c r="K39"/>
-      <c r="L39"/>
-      <c r="M39"/>
-      <c r="N39"/>
-      <c r="O39"/>
+      <c r="C39" s="10"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
@@ -4257,7 +3895,6 @@
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
-      <c r="AA39"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AE39" s="1"/>
@@ -4268,11 +3905,8 @@
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
       <c r="AL39" s="1"/>
-      <c r="AM39"/>
       <c r="AR39" s="1"/>
       <c r="AS39" s="1"/>
-      <c r="AT39"/>
-      <c r="AU39"/>
       <c r="AV39" s="1"/>
       <c r="AW39" s="1"/>
       <c r="AX39" s="1"/>
@@ -4282,12 +3916,9 @@
       <c r="BB39" s="1"/>
       <c r="BC39" s="1"/>
       <c r="BD39" s="1"/>
-      <c r="BE39" s="28"/>
-      <c r="BF39" s="28"/>
-      <c r="BG39"/>
-      <c r="BH39" s="27"/>
-      <c r="BI39"/>
-      <c r="BJ39"/>
+      <c r="BE39" s="26"/>
+      <c r="BF39" s="26"/>
+      <c r="BH39" s="25"/>
       <c r="BK39" s="1"/>
       <c r="BL39" s="1"/>
       <c r="BM39" s="1"/>
@@ -4318,19 +3949,9 @@
       <c r="CL39" s="1"/>
     </row>
     <row r="40" spans="3:90">
-      <c r="C40" s="11"/>
-      <c r="D40"/>
-      <c r="E40"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40"/>
-      <c r="I40"/>
-      <c r="J40" s="21"/>
-      <c r="K40"/>
-      <c r="L40"/>
-      <c r="M40"/>
-      <c r="N40"/>
-      <c r="O40"/>
+      <c r="C40" s="10"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
@@ -4341,7 +3962,6 @@
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
-      <c r="AA40"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AE40" s="1"/>
@@ -4352,11 +3972,8 @@
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
       <c r="AL40" s="1"/>
-      <c r="AM40"/>
       <c r="AR40" s="1"/>
       <c r="AS40" s="1"/>
-      <c r="AT40"/>
-      <c r="AU40"/>
       <c r="AV40" s="1"/>
       <c r="AW40" s="1"/>
       <c r="AX40" s="1"/>
@@ -4366,12 +3983,9 @@
       <c r="BB40" s="1"/>
       <c r="BC40" s="1"/>
       <c r="BD40" s="1"/>
-      <c r="BE40" s="28"/>
-      <c r="BF40" s="28"/>
-      <c r="BG40"/>
-      <c r="BH40" s="27"/>
-      <c r="BI40"/>
-      <c r="BJ40"/>
+      <c r="BE40" s="26"/>
+      <c r="BF40" s="26"/>
+      <c r="BH40" s="25"/>
       <c r="BK40" s="1"/>
       <c r="BL40" s="1"/>
       <c r="BM40" s="1"/>
@@ -4402,10 +4016,9 @@
       <c r="CL40" s="1"/>
     </row>
     <row r="41" spans="3:90">
-      <c r="C41" s="11"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="J41" s="21"/>
+      <c r="C41" s="10"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
@@ -4416,7 +4029,6 @@
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
-      <c r="AA41"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AE41" s="1"/>
@@ -4427,11 +4039,8 @@
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
       <c r="AL41" s="1"/>
-      <c r="AM41"/>
       <c r="AR41" s="1"/>
       <c r="AS41" s="1"/>
-      <c r="AT41"/>
-      <c r="AU41"/>
       <c r="AV41" s="1"/>
       <c r="AW41" s="1"/>
       <c r="AX41" s="1"/>
@@ -4441,12 +4050,9 @@
       <c r="BB41" s="1"/>
       <c r="BC41" s="1"/>
       <c r="BD41" s="1"/>
-      <c r="BE41" s="28"/>
-      <c r="BF41" s="28"/>
-      <c r="BG41"/>
-      <c r="BH41" s="27"/>
-      <c r="BI41"/>
-      <c r="BJ41"/>
+      <c r="BE41" s="26"/>
+      <c r="BF41" s="26"/>
+      <c r="BH41" s="25"/>
       <c r="BK41" s="1"/>
       <c r="BL41" s="1"/>
       <c r="BM41" s="1"/>
@@ -4477,19 +4083,9 @@
       <c r="CL41" s="1"/>
     </row>
     <row r="42" spans="3:90">
-      <c r="C42" s="11"/>
-      <c r="D42"/>
-      <c r="E42"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42"/>
-      <c r="I42"/>
-      <c r="J42" s="21"/>
-      <c r="K42"/>
-      <c r="L42"/>
-      <c r="M42"/>
-      <c r="N42"/>
-      <c r="O42"/>
+      <c r="C42" s="10"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
@@ -4500,7 +4096,6 @@
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
-      <c r="AA42"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AE42" s="1"/>
@@ -4511,11 +4106,8 @@
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
       <c r="AL42" s="1"/>
-      <c r="AM42"/>
       <c r="AR42" s="1"/>
       <c r="AS42" s="1"/>
-      <c r="AT42"/>
-      <c r="AU42"/>
       <c r="AV42" s="1"/>
       <c r="AW42" s="1"/>
       <c r="AX42" s="1"/>
@@ -4525,12 +4117,9 @@
       <c r="BB42" s="1"/>
       <c r="BC42" s="1"/>
       <c r="BD42" s="1"/>
-      <c r="BE42" s="28"/>
-      <c r="BF42" s="28"/>
-      <c r="BG42"/>
-      <c r="BH42" s="27"/>
-      <c r="BI42"/>
-      <c r="BJ42"/>
+      <c r="BE42" s="26"/>
+      <c r="BF42" s="26"/>
+      <c r="BH42" s="25"/>
       <c r="BK42" s="1"/>
       <c r="BL42" s="1"/>
       <c r="BM42" s="1"/>
@@ -4561,19 +4150,9 @@
       <c r="CL42" s="1"/>
     </row>
     <row r="43" spans="3:90">
-      <c r="C43" s="11"/>
-      <c r="D43"/>
-      <c r="E43"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43"/>
-      <c r="I43"/>
-      <c r="J43" s="21"/>
-      <c r="K43"/>
-      <c r="L43"/>
-      <c r="M43"/>
-      <c r="N43"/>
-      <c r="O43"/>
+      <c r="C43" s="10"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
@@ -4584,7 +4163,6 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
-      <c r="AA43"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
       <c r="AE43" s="1"/>
@@ -4595,11 +4173,8 @@
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
       <c r="AL43" s="1"/>
-      <c r="AM43"/>
       <c r="AR43" s="1"/>
       <c r="AS43" s="1"/>
-      <c r="AT43"/>
-      <c r="AU43"/>
       <c r="AV43" s="1"/>
       <c r="AW43" s="1"/>
       <c r="AX43" s="1"/>
@@ -4609,12 +4184,9 @@
       <c r="BB43" s="1"/>
       <c r="BC43" s="1"/>
       <c r="BD43" s="1"/>
-      <c r="BE43" s="28"/>
-      <c r="BF43" s="28"/>
-      <c r="BG43"/>
-      <c r="BH43" s="27"/>
-      <c r="BI43"/>
-      <c r="BJ43"/>
+      <c r="BE43" s="26"/>
+      <c r="BF43" s="26"/>
+      <c r="BH43" s="25"/>
       <c r="BK43" s="1"/>
       <c r="BL43" s="1"/>
       <c r="BM43" s="1"/>
@@ -4645,10 +4217,9 @@
       <c r="CL43" s="1"/>
     </row>
     <row r="44" spans="3:90">
-      <c r="C44" s="11"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="J44" s="21"/>
+      <c r="C44" s="10"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
@@ -4659,7 +4230,6 @@
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
-      <c r="AA44"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AE44" s="1"/>
@@ -4670,11 +4240,8 @@
       <c r="AJ44" s="1"/>
       <c r="AK44" s="1"/>
       <c r="AL44" s="1"/>
-      <c r="AM44"/>
       <c r="AR44" s="1"/>
       <c r="AS44" s="1"/>
-      <c r="AT44"/>
-      <c r="AU44"/>
       <c r="AV44" s="1"/>
       <c r="AW44" s="1"/>
       <c r="AX44" s="1"/>
@@ -4684,12 +4251,9 @@
       <c r="BB44" s="1"/>
       <c r="BC44" s="1"/>
       <c r="BD44" s="1"/>
-      <c r="BE44" s="28"/>
-      <c r="BF44" s="28"/>
-      <c r="BG44"/>
-      <c r="BH44" s="27"/>
-      <c r="BI44"/>
-      <c r="BJ44"/>
+      <c r="BE44" s="26"/>
+      <c r="BF44" s="26"/>
+      <c r="BH44" s="25"/>
       <c r="BK44" s="1"/>
       <c r="BL44" s="1"/>
       <c r="BM44" s="1"/>
@@ -4720,19 +4284,9 @@
       <c r="CL44" s="1"/>
     </row>
     <row r="45" spans="3:90">
-      <c r="C45" s="11"/>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45"/>
-      <c r="I45"/>
-      <c r="J45" s="21"/>
-      <c r="K45"/>
-      <c r="L45"/>
-      <c r="M45"/>
-      <c r="N45"/>
-      <c r="O45"/>
+      <c r="C45" s="10"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
@@ -4743,7 +4297,6 @@
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
-      <c r="AA45"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
       <c r="AE45" s="1"/>
@@ -4754,11 +4307,8 @@
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
       <c r="AL45" s="1"/>
-      <c r="AM45"/>
       <c r="AR45" s="1"/>
       <c r="AS45" s="1"/>
-      <c r="AT45"/>
-      <c r="AU45"/>
       <c r="AV45" s="1"/>
       <c r="AW45" s="1"/>
       <c r="AX45" s="1"/>
@@ -4768,12 +4318,9 @@
       <c r="BB45" s="1"/>
       <c r="BC45" s="1"/>
       <c r="BD45" s="1"/>
-      <c r="BE45" s="28"/>
-      <c r="BF45" s="28"/>
-      <c r="BG45"/>
-      <c r="BH45" s="27"/>
-      <c r="BI45"/>
-      <c r="BJ45"/>
+      <c r="BE45" s="26"/>
+      <c r="BF45" s="26"/>
+      <c r="BH45" s="25"/>
       <c r="BK45" s="1"/>
       <c r="BL45" s="1"/>
       <c r="BM45" s="1"/>
@@ -4804,19 +4351,9 @@
       <c r="CL45" s="1"/>
     </row>
     <row r="46" spans="3:90">
-      <c r="C46" s="11"/>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46"/>
-      <c r="I46"/>
-      <c r="J46" s="21"/>
-      <c r="K46"/>
-      <c r="L46"/>
-      <c r="M46"/>
-      <c r="N46"/>
-      <c r="O46"/>
+      <c r="C46" s="10"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
@@ -4827,7 +4364,6 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
-      <c r="AA46"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
       <c r="AE46" s="1"/>
@@ -4838,11 +4374,8 @@
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
       <c r="AL46" s="1"/>
-      <c r="AM46"/>
       <c r="AR46" s="1"/>
       <c r="AS46" s="1"/>
-      <c r="AT46"/>
-      <c r="AU46"/>
       <c r="AV46" s="1"/>
       <c r="AW46" s="1"/>
       <c r="AX46" s="1"/>
@@ -4852,12 +4385,9 @@
       <c r="BB46" s="1"/>
       <c r="BC46" s="1"/>
       <c r="BD46" s="1"/>
-      <c r="BE46" s="28"/>
-      <c r="BF46" s="28"/>
-      <c r="BG46"/>
-      <c r="BH46" s="27"/>
-      <c r="BI46"/>
-      <c r="BJ46"/>
+      <c r="BE46" s="26"/>
+      <c r="BF46" s="26"/>
+      <c r="BH46" s="25"/>
       <c r="BK46" s="1"/>
       <c r="BL46" s="1"/>
       <c r="BM46" s="1"/>
@@ -4888,19 +4418,9 @@
       <c r="CL46" s="1"/>
     </row>
     <row r="47" spans="3:90">
-      <c r="C47" s="11"/>
-      <c r="D47"/>
-      <c r="E47"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47"/>
-      <c r="I47"/>
-      <c r="J47" s="21"/>
-      <c r="K47"/>
-      <c r="L47"/>
-      <c r="M47"/>
-      <c r="N47"/>
-      <c r="O47"/>
+      <c r="C47" s="10"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
@@ -4911,7 +4431,6 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
-      <c r="AA47"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
       <c r="AE47" s="1"/>
@@ -4922,11 +4441,8 @@
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
       <c r="AL47" s="1"/>
-      <c r="AM47"/>
       <c r="AR47" s="1"/>
       <c r="AS47" s="1"/>
-      <c r="AT47"/>
-      <c r="AU47"/>
       <c r="AV47" s="1"/>
       <c r="AW47" s="1"/>
       <c r="AX47" s="1"/>
@@ -4936,12 +4452,9 @@
       <c r="BB47" s="1"/>
       <c r="BC47" s="1"/>
       <c r="BD47" s="1"/>
-      <c r="BE47" s="28"/>
-      <c r="BF47" s="28"/>
-      <c r="BG47"/>
-      <c r="BH47" s="27"/>
-      <c r="BI47"/>
-      <c r="BJ47"/>
+      <c r="BE47" s="26"/>
+      <c r="BF47" s="26"/>
+      <c r="BH47" s="25"/>
       <c r="BK47" s="1"/>
       <c r="BL47" s="1"/>
       <c r="BM47" s="1"/>
@@ -4972,19 +4485,9 @@
       <c r="CL47" s="1"/>
     </row>
     <row r="48" spans="3:90">
-      <c r="C48" s="11"/>
-      <c r="D48"/>
-      <c r="E48"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48"/>
-      <c r="I48"/>
-      <c r="J48" s="21"/>
-      <c r="K48"/>
-      <c r="L48"/>
-      <c r="M48"/>
-      <c r="N48"/>
-      <c r="O48"/>
+      <c r="C48" s="10"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
@@ -4995,7 +4498,6 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
-      <c r="AA48"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AE48" s="1"/>
@@ -5006,11 +4508,8 @@
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
       <c r="AL48" s="1"/>
-      <c r="AM48"/>
       <c r="AR48" s="1"/>
       <c r="AS48" s="1"/>
-      <c r="AT48"/>
-      <c r="AU48"/>
       <c r="AV48" s="1"/>
       <c r="AW48" s="1"/>
       <c r="AX48" s="1"/>
@@ -5020,12 +4519,9 @@
       <c r="BB48" s="1"/>
       <c r="BC48" s="1"/>
       <c r="BD48" s="1"/>
-      <c r="BE48" s="28"/>
-      <c r="BF48" s="28"/>
-      <c r="BG48"/>
-      <c r="BH48" s="27"/>
-      <c r="BI48"/>
-      <c r="BJ48"/>
+      <c r="BE48" s="26"/>
+      <c r="BF48" s="26"/>
+      <c r="BH48" s="25"/>
       <c r="BK48" s="1"/>
       <c r="BL48" s="1"/>
       <c r="BM48" s="1"/>
@@ -5056,19 +4552,9 @@
       <c r="CL48" s="1"/>
     </row>
     <row r="49" spans="3:90">
-      <c r="C49" s="11"/>
-      <c r="D49"/>
-      <c r="E49"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49"/>
-      <c r="I49"/>
-      <c r="J49" s="21"/>
-      <c r="K49"/>
-      <c r="L49"/>
-      <c r="M49"/>
-      <c r="N49"/>
-      <c r="O49"/>
+      <c r="C49" s="10"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
@@ -5079,7 +4565,6 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
-      <c r="AA49"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AE49" s="1"/>
@@ -5090,11 +4575,8 @@
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
       <c r="AL49" s="1"/>
-      <c r="AM49"/>
       <c r="AR49" s="1"/>
       <c r="AS49" s="1"/>
-      <c r="AT49"/>
-      <c r="AU49"/>
       <c r="AV49" s="1"/>
       <c r="AW49" s="1"/>
       <c r="AX49" s="1"/>
@@ -5104,12 +4586,9 @@
       <c r="BB49" s="1"/>
       <c r="BC49" s="1"/>
       <c r="BD49" s="1"/>
-      <c r="BE49" s="28"/>
-      <c r="BF49" s="28"/>
-      <c r="BG49"/>
-      <c r="BH49" s="27"/>
-      <c r="BI49"/>
-      <c r="BJ49"/>
+      <c r="BE49" s="26"/>
+      <c r="BF49" s="26"/>
+      <c r="BH49" s="25"/>
       <c r="BK49" s="1"/>
       <c r="BL49" s="1"/>
       <c r="BM49" s="1"/>
@@ -5140,10 +4619,9 @@
       <c r="CL49" s="1"/>
     </row>
     <row r="50" spans="3:90">
-      <c r="C50" s="11"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="J50" s="21"/>
+      <c r="C50" s="10"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
@@ -5154,7 +4632,6 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
-      <c r="AA50"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
       <c r="AE50" s="1"/>
@@ -5165,11 +4642,8 @@
       <c r="AJ50" s="1"/>
       <c r="AK50" s="1"/>
       <c r="AL50" s="1"/>
-      <c r="AM50"/>
       <c r="AR50" s="1"/>
       <c r="AS50" s="1"/>
-      <c r="AT50"/>
-      <c r="AU50"/>
       <c r="AV50" s="1"/>
       <c r="AW50" s="1"/>
       <c r="AX50" s="1"/>
@@ -5179,12 +4653,9 @@
       <c r="BB50" s="1"/>
       <c r="BC50" s="1"/>
       <c r="BD50" s="1"/>
-      <c r="BE50" s="28"/>
-      <c r="BF50" s="28"/>
-      <c r="BG50"/>
-      <c r="BH50" s="27"/>
-      <c r="BI50"/>
-      <c r="BJ50"/>
+      <c r="BE50" s="26"/>
+      <c r="BF50" s="26"/>
+      <c r="BH50" s="25"/>
       <c r="BK50" s="1"/>
       <c r="BL50" s="1"/>
       <c r="BM50" s="1"/>
@@ -5215,19 +4686,9 @@
       <c r="CL50" s="1"/>
     </row>
     <row r="51" spans="3:90">
-      <c r="C51" s="11"/>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51"/>
-      <c r="I51"/>
-      <c r="J51" s="21"/>
-      <c r="K51"/>
-      <c r="L51"/>
-      <c r="M51"/>
-      <c r="N51"/>
-      <c r="O51"/>
+      <c r="C51" s="10"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
@@ -5238,7 +4699,6 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
-      <c r="AA51"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AE51" s="1"/>
@@ -5249,11 +4709,8 @@
       <c r="AJ51" s="1"/>
       <c r="AK51" s="1"/>
       <c r="AL51" s="1"/>
-      <c r="AM51"/>
       <c r="AR51" s="1"/>
       <c r="AS51" s="1"/>
-      <c r="AT51"/>
-      <c r="AU51"/>
       <c r="AV51" s="1"/>
       <c r="AW51" s="1"/>
       <c r="AX51" s="1"/>
@@ -5263,12 +4720,9 @@
       <c r="BB51" s="1"/>
       <c r="BC51" s="1"/>
       <c r="BD51" s="1"/>
-      <c r="BE51" s="28"/>
-      <c r="BF51" s="28"/>
-      <c r="BG51"/>
-      <c r="BH51" s="27"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
+      <c r="BE51" s="26"/>
+      <c r="BF51" s="26"/>
+      <c r="BH51" s="25"/>
       <c r="BK51" s="1"/>
       <c r="BL51" s="1"/>
       <c r="BM51" s="1"/>
@@ -5299,19 +4753,9 @@
       <c r="CL51" s="1"/>
     </row>
     <row r="52" spans="3:90">
-      <c r="C52" s="11"/>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52" s="21"/>
-      <c r="K52"/>
-      <c r="L52"/>
-      <c r="M52"/>
-      <c r="N52"/>
-      <c r="O52"/>
+      <c r="C52" s="10"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
@@ -5322,7 +4766,6 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
-      <c r="AA52"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AE52" s="1"/>
@@ -5333,11 +4776,8 @@
       <c r="AJ52" s="1"/>
       <c r="AK52" s="1"/>
       <c r="AL52" s="1"/>
-      <c r="AM52"/>
       <c r="AR52" s="1"/>
       <c r="AS52" s="1"/>
-      <c r="AT52"/>
-      <c r="AU52"/>
       <c r="AV52" s="1"/>
       <c r="AW52" s="1"/>
       <c r="AX52" s="1"/>
@@ -5347,12 +4787,9 @@
       <c r="BB52" s="1"/>
       <c r="BC52" s="1"/>
       <c r="BD52" s="1"/>
-      <c r="BE52" s="28"/>
-      <c r="BF52" s="28"/>
-      <c r="BG52"/>
-      <c r="BH52" s="27"/>
-      <c r="BI52"/>
-      <c r="BJ52"/>
+      <c r="BE52" s="26"/>
+      <c r="BF52" s="26"/>
+      <c r="BH52" s="25"/>
       <c r="BK52" s="1"/>
       <c r="BL52" s="1"/>
       <c r="BM52" s="1"/>
@@ -5383,19 +4820,9 @@
       <c r="CL52" s="1"/>
     </row>
     <row r="53" spans="3:90">
-      <c r="C53" s="11"/>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53" s="21"/>
-      <c r="K53"/>
-      <c r="L53"/>
-      <c r="M53"/>
-      <c r="N53"/>
-      <c r="O53"/>
+      <c r="C53" s="10"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
@@ -5406,7 +4833,6 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
-      <c r="AA53"/>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
       <c r="AE53" s="1"/>
@@ -5417,11 +4843,8 @@
       <c r="AJ53" s="1"/>
       <c r="AK53" s="1"/>
       <c r="AL53" s="1"/>
-      <c r="AM53"/>
       <c r="AR53" s="1"/>
       <c r="AS53" s="1"/>
-      <c r="AT53"/>
-      <c r="AU53"/>
       <c r="AV53" s="1"/>
       <c r="AW53" s="1"/>
       <c r="AX53" s="1"/>
@@ -5431,12 +4854,9 @@
       <c r="BB53" s="1"/>
       <c r="BC53" s="1"/>
       <c r="BD53" s="1"/>
-      <c r="BE53" s="28"/>
-      <c r="BF53" s="28"/>
-      <c r="BG53"/>
-      <c r="BH53" s="27"/>
-      <c r="BI53"/>
-      <c r="BJ53"/>
+      <c r="BE53" s="26"/>
+      <c r="BF53" s="26"/>
+      <c r="BH53" s="25"/>
       <c r="BK53" s="1"/>
       <c r="BL53" s="1"/>
       <c r="BM53" s="1"/>
@@ -5467,19 +4887,9 @@
       <c r="CL53" s="1"/>
     </row>
     <row r="54" spans="3:90">
-      <c r="C54" s="11"/>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54"/>
-      <c r="I54"/>
-      <c r="J54" s="21"/>
-      <c r="K54"/>
-      <c r="L54"/>
-      <c r="M54"/>
-      <c r="N54"/>
-      <c r="O54"/>
+      <c r="C54" s="10"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
@@ -5490,7 +4900,6 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
-      <c r="AA54"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AE54" s="1"/>
@@ -5501,11 +4910,8 @@
       <c r="AJ54" s="1"/>
       <c r="AK54" s="1"/>
       <c r="AL54" s="1"/>
-      <c r="AM54"/>
       <c r="AR54" s="1"/>
       <c r="AS54" s="1"/>
-      <c r="AT54"/>
-      <c r="AU54"/>
       <c r="AV54" s="1"/>
       <c r="AW54" s="1"/>
       <c r="AX54" s="1"/>
@@ -5515,12 +4921,9 @@
       <c r="BB54" s="1"/>
       <c r="BC54" s="1"/>
       <c r="BD54" s="1"/>
-      <c r="BE54" s="28"/>
-      <c r="BF54" s="28"/>
-      <c r="BG54"/>
-      <c r="BH54" s="27"/>
-      <c r="BI54"/>
-      <c r="BJ54"/>
+      <c r="BE54" s="26"/>
+      <c r="BF54" s="26"/>
+      <c r="BH54" s="25"/>
       <c r="BK54" s="1"/>
       <c r="BL54" s="1"/>
       <c r="BM54" s="1"/>
@@ -5551,19 +4954,9 @@
       <c r="CL54" s="1"/>
     </row>
     <row r="55" spans="3:90">
-      <c r="C55" s="11"/>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55"/>
-      <c r="I55"/>
-      <c r="J55" s="21"/>
-      <c r="K55"/>
-      <c r="L55"/>
-      <c r="M55"/>
-      <c r="N55"/>
-      <c r="O55"/>
+      <c r="C55" s="10"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
@@ -5574,7 +4967,6 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
-      <c r="AA55"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AE55" s="1"/>
@@ -5585,11 +4977,8 @@
       <c r="AJ55" s="1"/>
       <c r="AK55" s="1"/>
       <c r="AL55" s="1"/>
-      <c r="AM55"/>
       <c r="AR55" s="1"/>
       <c r="AS55" s="1"/>
-      <c r="AT55"/>
-      <c r="AU55"/>
       <c r="AV55" s="1"/>
       <c r="AW55" s="1"/>
       <c r="AX55" s="1"/>
@@ -5599,12 +4988,9 @@
       <c r="BB55" s="1"/>
       <c r="BC55" s="1"/>
       <c r="BD55" s="1"/>
-      <c r="BE55" s="28"/>
-      <c r="BF55" s="28"/>
-      <c r="BG55"/>
-      <c r="BH55" s="27"/>
-      <c r="BI55"/>
-      <c r="BJ55"/>
+      <c r="BE55" s="26"/>
+      <c r="BF55" s="26"/>
+      <c r="BH55" s="25"/>
       <c r="BK55" s="1"/>
       <c r="BL55" s="1"/>
       <c r="BM55" s="1"/>
@@ -5635,19 +5021,9 @@
       <c r="CL55" s="1"/>
     </row>
     <row r="56" spans="3:90">
-      <c r="C56" s="11"/>
-      <c r="D56"/>
-      <c r="E56"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56"/>
-      <c r="I56"/>
-      <c r="J56" s="21"/>
-      <c r="K56"/>
-      <c r="L56"/>
-      <c r="M56"/>
-      <c r="N56"/>
-      <c r="O56"/>
+      <c r="C56" s="10"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
@@ -5658,7 +5034,6 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
-      <c r="AA56"/>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
       <c r="AE56" s="1"/>
@@ -5669,11 +5044,8 @@
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
       <c r="AL56" s="1"/>
-      <c r="AM56"/>
       <c r="AR56" s="1"/>
       <c r="AS56" s="1"/>
-      <c r="AT56"/>
-      <c r="AU56"/>
       <c r="AV56" s="1"/>
       <c r="AW56" s="1"/>
       <c r="AX56" s="1"/>
@@ -5683,12 +5055,9 @@
       <c r="BB56" s="1"/>
       <c r="BC56" s="1"/>
       <c r="BD56" s="1"/>
-      <c r="BE56" s="28"/>
-      <c r="BF56" s="28"/>
-      <c r="BG56"/>
-      <c r="BH56" s="27"/>
-      <c r="BI56"/>
-      <c r="BJ56"/>
+      <c r="BE56" s="26"/>
+      <c r="BF56" s="26"/>
+      <c r="BH56" s="25"/>
       <c r="BK56" s="1"/>
       <c r="BL56" s="1"/>
       <c r="BM56" s="1"/>
@@ -5719,10 +5088,9 @@
       <c r="CL56" s="1"/>
     </row>
     <row r="57" spans="3:90">
-      <c r="C57" s="11"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="J57" s="21"/>
+      <c r="C57" s="10"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
@@ -5733,7 +5101,6 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
-      <c r="AA57"/>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
       <c r="AE57" s="1"/>
@@ -5744,11 +5111,8 @@
       <c r="AJ57" s="1"/>
       <c r="AK57" s="1"/>
       <c r="AL57" s="1"/>
-      <c r="AM57"/>
       <c r="AR57" s="1"/>
       <c r="AS57" s="1"/>
-      <c r="AT57"/>
-      <c r="AU57"/>
       <c r="AV57" s="1"/>
       <c r="AW57" s="1"/>
       <c r="AX57" s="1"/>
@@ -5758,12 +5122,9 @@
       <c r="BB57" s="1"/>
       <c r="BC57" s="1"/>
       <c r="BD57" s="1"/>
-      <c r="BE57" s="28"/>
-      <c r="BF57" s="28"/>
-      <c r="BG57"/>
-      <c r="BH57" s="27"/>
-      <c r="BI57"/>
-      <c r="BJ57"/>
+      <c r="BE57" s="26"/>
+      <c r="BF57" s="26"/>
+      <c r="BH57" s="25"/>
       <c r="BK57" s="1"/>
       <c r="BL57" s="1"/>
       <c r="BM57" s="1"/>
@@ -5794,19 +5155,9 @@
       <c r="CL57" s="1"/>
     </row>
     <row r="58" spans="3:90">
-      <c r="C58" s="11"/>
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58"/>
-      <c r="I58"/>
-      <c r="J58" s="21"/>
-      <c r="K58"/>
-      <c r="L58"/>
-      <c r="M58"/>
-      <c r="N58"/>
-      <c r="O58"/>
+      <c r="C58" s="10"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
@@ -5817,7 +5168,6 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
-      <c r="AA58"/>
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
       <c r="AE58" s="1"/>
@@ -5828,11 +5178,8 @@
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
       <c r="AL58" s="1"/>
-      <c r="AM58"/>
       <c r="AR58" s="1"/>
       <c r="AS58" s="1"/>
-      <c r="AT58"/>
-      <c r="AU58"/>
       <c r="AV58" s="1"/>
       <c r="AW58" s="1"/>
       <c r="AX58" s="1"/>
@@ -5842,12 +5189,9 @@
       <c r="BB58" s="1"/>
       <c r="BC58" s="1"/>
       <c r="BD58" s="1"/>
-      <c r="BE58" s="28"/>
-      <c r="BF58" s="28"/>
-      <c r="BG58"/>
-      <c r="BH58" s="27"/>
-      <c r="BI58"/>
-      <c r="BJ58"/>
+      <c r="BE58" s="26"/>
+      <c r="BF58" s="26"/>
+      <c r="BH58" s="25"/>
       <c r="BK58" s="1"/>
       <c r="BL58" s="1"/>
       <c r="BM58" s="1"/>
@@ -5878,19 +5222,9 @@
       <c r="CL58" s="1"/>
     </row>
     <row r="59" spans="3:90">
-      <c r="C59" s="11"/>
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59"/>
-      <c r="I59"/>
-      <c r="J59" s="21"/>
-      <c r="K59"/>
-      <c r="L59"/>
-      <c r="M59"/>
-      <c r="N59"/>
-      <c r="O59"/>
+      <c r="C59" s="10"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
@@ -5901,7 +5235,6 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
-      <c r="AA59"/>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
       <c r="AE59" s="1"/>
@@ -5912,11 +5245,8 @@
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
       <c r="AL59" s="1"/>
-      <c r="AM59"/>
       <c r="AR59" s="1"/>
       <c r="AS59" s="1"/>
-      <c r="AT59"/>
-      <c r="AU59"/>
       <c r="AV59" s="1"/>
       <c r="AW59" s="1"/>
       <c r="AX59" s="1"/>
@@ -5926,12 +5256,9 @@
       <c r="BB59" s="1"/>
       <c r="BC59" s="1"/>
       <c r="BD59" s="1"/>
-      <c r="BE59" s="28"/>
-      <c r="BF59" s="28"/>
-      <c r="BG59"/>
-      <c r="BH59" s="27"/>
-      <c r="BI59"/>
-      <c r="BJ59"/>
+      <c r="BE59" s="26"/>
+      <c r="BF59" s="26"/>
+      <c r="BH59" s="25"/>
       <c r="BK59" s="1"/>
       <c r="BL59" s="1"/>
       <c r="BM59" s="1"/>
@@ -5962,19 +5289,9 @@
       <c r="CL59" s="1"/>
     </row>
     <row r="60" spans="3:90">
-      <c r="C60" s="11"/>
-      <c r="D60"/>
-      <c r="E60"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60"/>
-      <c r="I60"/>
-      <c r="J60" s="21"/>
-      <c r="K60"/>
-      <c r="L60"/>
-      <c r="M60"/>
-      <c r="N60"/>
-      <c r="O60"/>
+      <c r="C60" s="10"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
@@ -5985,7 +5302,6 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
-      <c r="AA60"/>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
       <c r="AE60" s="1"/>
@@ -5996,11 +5312,8 @@
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
       <c r="AL60" s="1"/>
-      <c r="AM60"/>
       <c r="AR60" s="1"/>
       <c r="AS60" s="1"/>
-      <c r="AT60"/>
-      <c r="AU60"/>
       <c r="AV60" s="1"/>
       <c r="AW60" s="1"/>
       <c r="AX60" s="1"/>
@@ -6010,12 +5323,9 @@
       <c r="BB60" s="1"/>
       <c r="BC60" s="1"/>
       <c r="BD60" s="1"/>
-      <c r="BE60" s="28"/>
-      <c r="BF60" s="28"/>
-      <c r="BG60"/>
-      <c r="BH60" s="27"/>
-      <c r="BI60"/>
-      <c r="BJ60"/>
+      <c r="BE60" s="26"/>
+      <c r="BF60" s="26"/>
+      <c r="BH60" s="25"/>
       <c r="BK60" s="1"/>
       <c r="BL60" s="1"/>
       <c r="BM60" s="1"/>
@@ -6046,19 +5356,9 @@
       <c r="CL60" s="1"/>
     </row>
     <row r="61" spans="3:90">
-      <c r="C61" s="11"/>
-      <c r="D61"/>
-      <c r="E61"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61"/>
-      <c r="I61"/>
-      <c r="J61" s="21"/>
-      <c r="K61"/>
-      <c r="L61"/>
-      <c r="M61"/>
-      <c r="N61"/>
-      <c r="O61"/>
+      <c r="C61" s="10"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
@@ -6069,7 +5369,6 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
-      <c r="AA61"/>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
       <c r="AE61" s="1"/>
@@ -6080,11 +5379,8 @@
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
       <c r="AL61" s="1"/>
-      <c r="AM61"/>
       <c r="AR61" s="1"/>
       <c r="AS61" s="1"/>
-      <c r="AT61"/>
-      <c r="AU61"/>
       <c r="AV61" s="1"/>
       <c r="AW61" s="1"/>
       <c r="AX61" s="1"/>
@@ -6094,12 +5390,9 @@
       <c r="BB61" s="1"/>
       <c r="BC61" s="1"/>
       <c r="BD61" s="1"/>
-      <c r="BE61" s="28"/>
-      <c r="BF61" s="28"/>
-      <c r="BG61"/>
-      <c r="BH61" s="27"/>
-      <c r="BI61"/>
-      <c r="BJ61"/>
+      <c r="BE61" s="26"/>
+      <c r="BF61" s="26"/>
+      <c r="BH61" s="25"/>
       <c r="BK61" s="1"/>
       <c r="BL61" s="1"/>
       <c r="BM61" s="1"/>
@@ -6130,19 +5423,9 @@
       <c r="CL61" s="1"/>
     </row>
     <row r="62" spans="3:90">
-      <c r="C62" s="11"/>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62"/>
-      <c r="I62"/>
-      <c r="J62" s="21"/>
-      <c r="K62"/>
-      <c r="L62"/>
-      <c r="M62"/>
-      <c r="N62"/>
-      <c r="O62"/>
+      <c r="C62" s="10"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
@@ -6153,7 +5436,6 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
-      <c r="AA62"/>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
       <c r="AE62" s="1"/>
@@ -6164,11 +5446,8 @@
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
       <c r="AL62" s="1"/>
-      <c r="AM62"/>
       <c r="AR62" s="1"/>
       <c r="AS62" s="1"/>
-      <c r="AT62"/>
-      <c r="AU62"/>
       <c r="AV62" s="1"/>
       <c r="AW62" s="1"/>
       <c r="AX62" s="1"/>
@@ -6178,12 +5457,9 @@
       <c r="BB62" s="1"/>
       <c r="BC62" s="1"/>
       <c r="BD62" s="1"/>
-      <c r="BE62" s="28"/>
-      <c r="BF62" s="28"/>
-      <c r="BG62"/>
-      <c r="BH62" s="27"/>
-      <c r="BI62"/>
-      <c r="BJ62"/>
+      <c r="BE62" s="26"/>
+      <c r="BF62" s="26"/>
+      <c r="BH62" s="25"/>
       <c r="BK62" s="1"/>
       <c r="BL62" s="1"/>
       <c r="BM62" s="1"/>
@@ -6214,19 +5490,9 @@
       <c r="CL62" s="1"/>
     </row>
     <row r="63" spans="3:90">
-      <c r="C63" s="11"/>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63"/>
-      <c r="I63"/>
-      <c r="J63" s="21"/>
-      <c r="K63"/>
-      <c r="L63"/>
-      <c r="M63"/>
-      <c r="N63"/>
-      <c r="O63"/>
+      <c r="C63" s="10"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
@@ -6237,7 +5503,6 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
-      <c r="AA63"/>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
       <c r="AE63" s="1"/>
@@ -6248,11 +5513,8 @@
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
       <c r="AL63" s="1"/>
-      <c r="AM63"/>
       <c r="AR63" s="1"/>
       <c r="AS63" s="1"/>
-      <c r="AT63"/>
-      <c r="AU63"/>
       <c r="AV63" s="1"/>
       <c r="AW63" s="1"/>
       <c r="AX63" s="1"/>
@@ -6262,12 +5524,9 @@
       <c r="BB63" s="1"/>
       <c r="BC63" s="1"/>
       <c r="BD63" s="1"/>
-      <c r="BE63" s="28"/>
-      <c r="BF63" s="28"/>
-      <c r="BG63"/>
-      <c r="BH63" s="27"/>
-      <c r="BI63"/>
-      <c r="BJ63"/>
+      <c r="BE63" s="26"/>
+      <c r="BF63" s="26"/>
+      <c r="BH63" s="25"/>
       <c r="BK63" s="1"/>
       <c r="BL63" s="1"/>
       <c r="BM63" s="1"/>
@@ -6298,19 +5557,9 @@
       <c r="CL63" s="1"/>
     </row>
     <row r="64" spans="3:90">
-      <c r="C64" s="11"/>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64"/>
-      <c r="I64"/>
-      <c r="J64" s="21"/>
-      <c r="K64"/>
-      <c r="L64"/>
-      <c r="M64"/>
-      <c r="N64"/>
-      <c r="O64"/>
+      <c r="C64" s="10"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
@@ -6321,7 +5570,6 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
-      <c r="AA64"/>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
       <c r="AE64" s="1"/>
@@ -6332,11 +5580,8 @@
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
       <c r="AL64" s="1"/>
-      <c r="AM64"/>
       <c r="AR64" s="1"/>
       <c r="AS64" s="1"/>
-      <c r="AT64"/>
-      <c r="AU64"/>
       <c r="AV64" s="1"/>
       <c r="AW64" s="1"/>
       <c r="AX64" s="1"/>
@@ -6346,12 +5591,9 @@
       <c r="BB64" s="1"/>
       <c r="BC64" s="1"/>
       <c r="BD64" s="1"/>
-      <c r="BE64" s="28"/>
-      <c r="BF64" s="28"/>
-      <c r="BG64"/>
-      <c r="BH64" s="27"/>
-      <c r="BI64"/>
-      <c r="BJ64"/>
+      <c r="BE64" s="26"/>
+      <c r="BF64" s="26"/>
+      <c r="BH64" s="25"/>
       <c r="BK64" s="1"/>
       <c r="BL64" s="1"/>
       <c r="BM64" s="1"/>
@@ -6382,19 +5624,9 @@
       <c r="CL64" s="1"/>
     </row>
     <row r="65" spans="3:90">
-      <c r="C65" s="11"/>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65"/>
-      <c r="I65"/>
-      <c r="J65" s="21"/>
-      <c r="K65"/>
-      <c r="L65"/>
-      <c r="M65"/>
-      <c r="N65"/>
-      <c r="O65"/>
+      <c r="C65" s="10"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
@@ -6405,7 +5637,6 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
-      <c r="AA65"/>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
       <c r="AE65" s="1"/>
@@ -6416,11 +5647,8 @@
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
       <c r="AL65" s="1"/>
-      <c r="AM65"/>
       <c r="AR65" s="1"/>
       <c r="AS65" s="1"/>
-      <c r="AT65"/>
-      <c r="AU65"/>
       <c r="AV65" s="1"/>
       <c r="AW65" s="1"/>
       <c r="AX65" s="1"/>
@@ -6430,12 +5658,9 @@
       <c r="BB65" s="1"/>
       <c r="BC65" s="1"/>
       <c r="BD65" s="1"/>
-      <c r="BE65" s="28"/>
-      <c r="BF65" s="28"/>
-      <c r="BG65"/>
-      <c r="BH65" s="27"/>
-      <c r="BI65"/>
-      <c r="BJ65"/>
+      <c r="BE65" s="26"/>
+      <c r="BF65" s="26"/>
+      <c r="BH65" s="25"/>
       <c r="BK65" s="1"/>
       <c r="BL65" s="1"/>
       <c r="BM65" s="1"/>
@@ -6466,10 +5691,9 @@
       <c r="CL65" s="1"/>
     </row>
     <row r="66" spans="3:90">
-      <c r="C66" s="11"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="J66" s="21"/>
+      <c r="C66" s="10"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
@@ -6480,7 +5704,6 @@
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
-      <c r="AA66"/>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
       <c r="AE66" s="1"/>
@@ -6491,11 +5714,8 @@
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
       <c r="AL66" s="1"/>
-      <c r="AM66"/>
       <c r="AR66" s="1"/>
       <c r="AS66" s="1"/>
-      <c r="AT66"/>
-      <c r="AU66"/>
       <c r="AV66" s="1"/>
       <c r="AW66" s="1"/>
       <c r="AX66" s="1"/>
@@ -6505,12 +5725,9 @@
       <c r="BB66" s="1"/>
       <c r="BC66" s="1"/>
       <c r="BD66" s="1"/>
-      <c r="BE66" s="28"/>
-      <c r="BF66" s="28"/>
-      <c r="BG66"/>
-      <c r="BH66" s="27"/>
-      <c r="BI66"/>
-      <c r="BJ66"/>
+      <c r="BE66" s="26"/>
+      <c r="BF66" s="26"/>
+      <c r="BH66" s="25"/>
       <c r="BK66" s="1"/>
       <c r="BL66" s="1"/>
       <c r="BM66" s="1"/>
@@ -6541,19 +5758,9 @@
       <c r="CL66" s="1"/>
     </row>
     <row r="67" spans="3:90">
-      <c r="C67" s="11"/>
-      <c r="D67"/>
-      <c r="E67"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67"/>
-      <c r="I67"/>
-      <c r="J67" s="21"/>
-      <c r="K67"/>
-      <c r="L67"/>
-      <c r="M67"/>
-      <c r="N67"/>
-      <c r="O67"/>
+      <c r="C67" s="10"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
@@ -6564,7 +5771,6 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
-      <c r="AA67"/>
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
       <c r="AE67" s="1"/>
@@ -6575,11 +5781,8 @@
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
       <c r="AL67" s="1"/>
-      <c r="AM67"/>
       <c r="AR67" s="1"/>
       <c r="AS67" s="1"/>
-      <c r="AT67"/>
-      <c r="AU67"/>
       <c r="AV67" s="1"/>
       <c r="AW67" s="1"/>
       <c r="AX67" s="1"/>
@@ -6589,12 +5792,9 @@
       <c r="BB67" s="1"/>
       <c r="BC67" s="1"/>
       <c r="BD67" s="1"/>
-      <c r="BE67" s="28"/>
-      <c r="BF67" s="28"/>
-      <c r="BG67"/>
-      <c r="BH67" s="27"/>
-      <c r="BI67"/>
-      <c r="BJ67"/>
+      <c r="BE67" s="26"/>
+      <c r="BF67" s="26"/>
+      <c r="BH67" s="25"/>
       <c r="BK67" s="1"/>
       <c r="BL67" s="1"/>
       <c r="BM67" s="1"/>
@@ -6625,19 +5825,9 @@
       <c r="CL67" s="1"/>
     </row>
     <row r="68" spans="3:90">
-      <c r="C68" s="11"/>
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68"/>
-      <c r="I68"/>
-      <c r="J68" s="21"/>
-      <c r="K68"/>
-      <c r="L68"/>
-      <c r="M68"/>
-      <c r="N68"/>
-      <c r="O68"/>
+      <c r="C68" s="10"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
       <c r="S68" s="1"/>
@@ -6648,7 +5838,6 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
-      <c r="AA68"/>
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
       <c r="AE68" s="1"/>
@@ -6659,11 +5848,8 @@
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
       <c r="AL68" s="1"/>
-      <c r="AM68"/>
       <c r="AR68" s="1"/>
       <c r="AS68" s="1"/>
-      <c r="AT68"/>
-      <c r="AU68"/>
       <c r="AV68" s="1"/>
       <c r="AW68" s="1"/>
       <c r="AX68" s="1"/>
@@ -6673,12 +5859,9 @@
       <c r="BB68" s="1"/>
       <c r="BC68" s="1"/>
       <c r="BD68" s="1"/>
-      <c r="BE68" s="28"/>
-      <c r="BF68" s="28"/>
-      <c r="BG68"/>
-      <c r="BH68" s="27"/>
-      <c r="BI68"/>
-      <c r="BJ68"/>
+      <c r="BE68" s="26"/>
+      <c r="BF68" s="26"/>
+      <c r="BH68" s="25"/>
       <c r="BK68" s="1"/>
       <c r="BL68" s="1"/>
       <c r="BM68" s="1"/>
@@ -6709,19 +5892,9 @@
       <c r="CL68" s="1"/>
     </row>
     <row r="69" spans="3:90">
-      <c r="C69" s="11"/>
-      <c r="D69"/>
-      <c r="E69"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69"/>
-      <c r="I69"/>
-      <c r="J69" s="21"/>
-      <c r="K69"/>
-      <c r="L69"/>
-      <c r="M69"/>
-      <c r="N69"/>
-      <c r="O69"/>
+      <c r="C69" s="10"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
@@ -6732,7 +5905,6 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
-      <c r="AA69"/>
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
       <c r="AE69" s="1"/>
@@ -6743,11 +5915,8 @@
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
       <c r="AL69" s="1"/>
-      <c r="AM69"/>
       <c r="AR69" s="1"/>
       <c r="AS69" s="1"/>
-      <c r="AT69"/>
-      <c r="AU69"/>
       <c r="AV69" s="1"/>
       <c r="AW69" s="1"/>
       <c r="AX69" s="1"/>
@@ -6757,12 +5926,9 @@
       <c r="BB69" s="1"/>
       <c r="BC69" s="1"/>
       <c r="BD69" s="1"/>
-      <c r="BE69" s="28"/>
-      <c r="BF69" s="28"/>
-      <c r="BG69"/>
-      <c r="BH69" s="27"/>
-      <c r="BI69"/>
-      <c r="BJ69"/>
+      <c r="BE69" s="26"/>
+      <c r="BF69" s="26"/>
+      <c r="BH69" s="25"/>
       <c r="BK69" s="1"/>
       <c r="BL69" s="1"/>
       <c r="BM69" s="1"/>
@@ -6793,19 +5959,9 @@
       <c r="CL69" s="1"/>
     </row>
     <row r="70" spans="3:90">
-      <c r="C70" s="11"/>
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70"/>
-      <c r="I70"/>
-      <c r="J70" s="21"/>
-      <c r="K70"/>
-      <c r="L70"/>
-      <c r="M70"/>
-      <c r="N70"/>
-      <c r="O70"/>
+      <c r="C70" s="10"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
@@ -6816,7 +5972,6 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
-      <c r="AA70"/>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
       <c r="AE70" s="1"/>
@@ -6827,11 +5982,8 @@
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
       <c r="AL70" s="1"/>
-      <c r="AM70"/>
       <c r="AR70" s="1"/>
       <c r="AS70" s="1"/>
-      <c r="AT70"/>
-      <c r="AU70"/>
       <c r="AV70" s="1"/>
       <c r="AW70" s="1"/>
       <c r="AX70" s="1"/>
@@ -6841,12 +5993,9 @@
       <c r="BB70" s="1"/>
       <c r="BC70" s="1"/>
       <c r="BD70" s="1"/>
-      <c r="BE70" s="28"/>
-      <c r="BF70" s="28"/>
-      <c r="BG70"/>
-      <c r="BH70" s="27"/>
-      <c r="BI70"/>
-      <c r="BJ70"/>
+      <c r="BE70" s="26"/>
+      <c r="BF70" s="26"/>
+      <c r="BH70" s="25"/>
       <c r="BK70" s="1"/>
       <c r="BL70" s="1"/>
       <c r="BM70" s="1"/>
@@ -6877,19 +6026,9 @@
       <c r="CL70" s="1"/>
     </row>
     <row r="71" spans="3:90">
-      <c r="C71" s="11"/>
-      <c r="D71"/>
-      <c r="E71"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71"/>
-      <c r="I71"/>
-      <c r="J71" s="21"/>
-      <c r="K71"/>
-      <c r="L71"/>
-      <c r="M71"/>
-      <c r="N71"/>
-      <c r="O71"/>
+      <c r="C71" s="10"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
@@ -6900,7 +6039,6 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
-      <c r="AA71"/>
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
       <c r="AE71" s="1"/>
@@ -6911,11 +6049,8 @@
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
       <c r="AL71" s="1"/>
-      <c r="AM71"/>
       <c r="AR71" s="1"/>
       <c r="AS71" s="1"/>
-      <c r="AT71"/>
-      <c r="AU71"/>
       <c r="AV71" s="1"/>
       <c r="AW71" s="1"/>
       <c r="AX71" s="1"/>
@@ -6925,12 +6060,9 @@
       <c r="BB71" s="1"/>
       <c r="BC71" s="1"/>
       <c r="BD71" s="1"/>
-      <c r="BE71" s="28"/>
-      <c r="BF71" s="28"/>
-      <c r="BG71"/>
-      <c r="BH71" s="27"/>
-      <c r="BI71"/>
-      <c r="BJ71"/>
+      <c r="BE71" s="26"/>
+      <c r="BF71" s="26"/>
+      <c r="BH71" s="25"/>
       <c r="BK71" s="1"/>
       <c r="BL71" s="1"/>
       <c r="BM71" s="1"/>
@@ -6961,11 +6093,9 @@
       <c r="CL71" s="1"/>
     </row>
     <row r="72" spans="3:90">
-      <c r="C72" s="11"/>
-      <c r="D72"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="J72" s="21"/>
+      <c r="C72" s="10"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
@@ -6976,7 +6106,6 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
-      <c r="AA72"/>
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
       <c r="AE72" s="1"/>
@@ -6987,11 +6116,8 @@
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
       <c r="AL72" s="1"/>
-      <c r="AM72"/>
       <c r="AR72" s="1"/>
       <c r="AS72" s="1"/>
-      <c r="AT72"/>
-      <c r="AU72"/>
       <c r="AV72" s="1"/>
       <c r="AW72" s="1"/>
       <c r="AX72" s="1"/>
@@ -7001,12 +6127,9 @@
       <c r="BB72" s="1"/>
       <c r="BC72" s="1"/>
       <c r="BD72" s="1"/>
-      <c r="BE72" s="28"/>
-      <c r="BF72" s="28"/>
-      <c r="BG72"/>
-      <c r="BH72" s="27"/>
-      <c r="BI72"/>
-      <c r="BJ72"/>
+      <c r="BE72" s="26"/>
+      <c r="BF72" s="26"/>
+      <c r="BH72" s="25"/>
       <c r="BK72" s="1"/>
       <c r="BL72" s="1"/>
       <c r="BM72" s="1"/>
@@ -7037,19 +6160,9 @@
       <c r="CL72" s="1"/>
     </row>
     <row r="73" spans="3:90">
-      <c r="C73" s="11"/>
-      <c r="D73"/>
-      <c r="E73"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73"/>
-      <c r="I73"/>
-      <c r="J73" s="21"/>
-      <c r="K73"/>
-      <c r="L73"/>
-      <c r="M73"/>
-      <c r="N73"/>
-      <c r="O73"/>
+      <c r="C73" s="10"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
@@ -7060,7 +6173,6 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
-      <c r="AA73"/>
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
       <c r="AE73" s="1"/>
@@ -7071,11 +6183,8 @@
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
       <c r="AL73" s="1"/>
-      <c r="AM73"/>
       <c r="AR73" s="1"/>
       <c r="AS73" s="1"/>
-      <c r="AT73"/>
-      <c r="AU73"/>
       <c r="AV73" s="1"/>
       <c r="AW73" s="1"/>
       <c r="AX73" s="1"/>
@@ -7085,12 +6194,9 @@
       <c r="BB73" s="1"/>
       <c r="BC73" s="1"/>
       <c r="BD73" s="1"/>
-      <c r="BE73" s="28"/>
-      <c r="BF73" s="28"/>
-      <c r="BG73"/>
-      <c r="BH73" s="27"/>
-      <c r="BI73"/>
-      <c r="BJ73"/>
+      <c r="BE73" s="26"/>
+      <c r="BF73" s="26"/>
+      <c r="BH73" s="25"/>
       <c r="BK73" s="1"/>
       <c r="BL73" s="1"/>
       <c r="BM73" s="1"/>
@@ -7121,19 +6227,9 @@
       <c r="CL73" s="1"/>
     </row>
     <row r="74" spans="3:90">
-      <c r="C74" s="11"/>
-      <c r="D74"/>
-      <c r="E74"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74"/>
-      <c r="I74"/>
-      <c r="J74" s="21"/>
-      <c r="K74"/>
-      <c r="L74"/>
-      <c r="M74"/>
-      <c r="N74"/>
-      <c r="O74"/>
+      <c r="C74" s="10"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
@@ -7144,7 +6240,6 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
-      <c r="AA74"/>
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
       <c r="AE74" s="1"/>
@@ -7155,11 +6250,8 @@
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
       <c r="AL74" s="1"/>
-      <c r="AM74"/>
       <c r="AR74" s="1"/>
       <c r="AS74" s="1"/>
-      <c r="AT74"/>
-      <c r="AU74"/>
       <c r="AV74" s="1"/>
       <c r="AW74" s="1"/>
       <c r="AX74" s="1"/>
@@ -7169,12 +6261,9 @@
       <c r="BB74" s="1"/>
       <c r="BC74" s="1"/>
       <c r="BD74" s="1"/>
-      <c r="BE74" s="28"/>
-      <c r="BF74" s="28"/>
-      <c r="BG74"/>
-      <c r="BH74" s="27"/>
-      <c r="BI74"/>
-      <c r="BJ74"/>
+      <c r="BE74" s="26"/>
+      <c r="BF74" s="26"/>
+      <c r="BH74" s="25"/>
       <c r="BK74" s="1"/>
       <c r="BL74" s="1"/>
       <c r="BM74" s="1"/>
@@ -7205,19 +6294,9 @@
       <c r="CL74" s="1"/>
     </row>
     <row r="75" spans="3:90">
-      <c r="C75" s="11"/>
-      <c r="D75"/>
-      <c r="E75"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75"/>
-      <c r="I75"/>
-      <c r="J75" s="21"/>
-      <c r="K75"/>
-      <c r="L75"/>
-      <c r="M75"/>
-      <c r="N75"/>
-      <c r="O75"/>
+      <c r="C75" s="10"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
@@ -7228,7 +6307,6 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
-      <c r="AA75"/>
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
       <c r="AE75" s="1"/>
@@ -7239,11 +6317,8 @@
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
       <c r="AL75" s="1"/>
-      <c r="AM75"/>
       <c r="AR75" s="1"/>
       <c r="AS75" s="1"/>
-      <c r="AT75"/>
-      <c r="AU75"/>
       <c r="AV75" s="1"/>
       <c r="AW75" s="1"/>
       <c r="AX75" s="1"/>
@@ -7253,12 +6328,9 @@
       <c r="BB75" s="1"/>
       <c r="BC75" s="1"/>
       <c r="BD75" s="1"/>
-      <c r="BE75" s="28"/>
-      <c r="BF75" s="28"/>
-      <c r="BG75"/>
-      <c r="BH75" s="27"/>
-      <c r="BI75"/>
-      <c r="BJ75"/>
+      <c r="BE75" s="26"/>
+      <c r="BF75" s="26"/>
+      <c r="BH75" s="25"/>
       <c r="BK75" s="1"/>
       <c r="BL75" s="1"/>
       <c r="BM75" s="1"/>
@@ -7289,19 +6361,9 @@
       <c r="CL75" s="1"/>
     </row>
     <row r="76" spans="3:90">
-      <c r="C76" s="11"/>
-      <c r="D76"/>
-      <c r="E76"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76"/>
-      <c r="I76"/>
-      <c r="J76" s="21"/>
-      <c r="K76"/>
-      <c r="L76"/>
-      <c r="M76"/>
-      <c r="N76"/>
-      <c r="O76"/>
+      <c r="C76" s="10"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
@@ -7312,7 +6374,6 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
-      <c r="AA76"/>
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
       <c r="AE76" s="1"/>
@@ -7323,11 +6384,8 @@
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
       <c r="AL76" s="1"/>
-      <c r="AM76"/>
       <c r="AR76" s="1"/>
       <c r="AS76" s="1"/>
-      <c r="AT76"/>
-      <c r="AU76"/>
       <c r="AV76" s="1"/>
       <c r="AW76" s="1"/>
       <c r="AX76" s="1"/>
@@ -7337,12 +6395,9 @@
       <c r="BB76" s="1"/>
       <c r="BC76" s="1"/>
       <c r="BD76" s="1"/>
-      <c r="BE76" s="28"/>
-      <c r="BF76" s="28"/>
-      <c r="BG76"/>
-      <c r="BH76" s="27"/>
-      <c r="BI76"/>
-      <c r="BJ76"/>
+      <c r="BE76" s="26"/>
+      <c r="BF76" s="26"/>
+      <c r="BH76" s="25"/>
       <c r="BK76" s="1"/>
       <c r="BL76" s="1"/>
       <c r="BM76" s="1"/>
@@ -7373,13 +6428,13 @@
       <c r="CL76" s="1"/>
     </row>
     <row r="77" spans="3:90">
-      <c r="C77" s="11"/>
+      <c r="C77" s="10"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
-      <c r="J77" s="21"/>
+      <c r="J77" s="4"/>
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
@@ -7414,12 +6469,12 @@
       <c r="BB77" s="1"/>
       <c r="BC77" s="1"/>
       <c r="BD77" s="1"/>
-      <c r="BE77" s="28"/>
-      <c r="BF77" s="28"/>
+      <c r="BE77" s="26"/>
+      <c r="BF77" s="26"/>
       <c r="BG77" s="1"/>
-      <c r="BH77" s="27"/>
+      <c r="BH77" s="25"/>
       <c r="BI77" s="1"/>
-      <c r="BJ77" s="28"/>
+      <c r="BJ77" s="26"/>
       <c r="BK77" s="1"/>
       <c r="BL77" s="1"/>
       <c r="BM77" s="1"/>
@@ -7450,13 +6505,13 @@
       <c r="CL77" s="1"/>
     </row>
     <row r="78" spans="3:90">
-      <c r="C78" s="11"/>
+      <c r="C78" s="10"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
-      <c r="J78" s="21"/>
+      <c r="J78" s="4"/>
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
@@ -7491,12 +6546,12 @@
       <c r="BB78" s="1"/>
       <c r="BC78" s="1"/>
       <c r="BD78" s="1"/>
-      <c r="BE78" s="28"/>
-      <c r="BF78" s="28"/>
+      <c r="BE78" s="26"/>
+      <c r="BF78" s="26"/>
       <c r="BG78" s="1"/>
-      <c r="BH78" s="27"/>
+      <c r="BH78" s="25"/>
       <c r="BI78" s="1"/>
-      <c r="BJ78" s="28"/>
+      <c r="BJ78" s="26"/>
       <c r="BK78" s="1"/>
       <c r="BL78" s="1"/>
       <c r="BM78" s="1"/>
@@ -7527,13 +6582,13 @@
       <c r="CL78" s="1"/>
     </row>
     <row r="79" spans="3:90">
-      <c r="C79" s="11"/>
+      <c r="C79" s="10"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
-      <c r="J79" s="21"/>
+      <c r="J79" s="4"/>
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
@@ -7568,12 +6623,12 @@
       <c r="BB79" s="1"/>
       <c r="BC79" s="1"/>
       <c r="BD79" s="1"/>
-      <c r="BE79" s="28"/>
-      <c r="BF79" s="28"/>
+      <c r="BE79" s="26"/>
+      <c r="BF79" s="26"/>
       <c r="BG79" s="1"/>
-      <c r="BH79" s="27"/>
+      <c r="BH79" s="25"/>
       <c r="BI79" s="1"/>
-      <c r="BJ79" s="28"/>
+      <c r="BJ79" s="26"/>
       <c r="BK79" s="1"/>
       <c r="BL79" s="1"/>
       <c r="BM79" s="1"/>
@@ -7604,13 +6659,13 @@
       <c r="CL79" s="1"/>
     </row>
     <row r="80" spans="3:90">
-      <c r="C80" s="11"/>
+      <c r="C80" s="10"/>
       <c r="E80" s="1"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
-      <c r="J80" s="21"/>
+      <c r="J80" s="4"/>
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
@@ -7645,12 +6700,12 @@
       <c r="BB80" s="1"/>
       <c r="BC80" s="1"/>
       <c r="BD80" s="1"/>
-      <c r="BE80" s="28"/>
-      <c r="BF80" s="28"/>
+      <c r="BE80" s="26"/>
+      <c r="BF80" s="26"/>
       <c r="BG80" s="1"/>
-      <c r="BH80" s="27"/>
+      <c r="BH80" s="25"/>
       <c r="BI80" s="1"/>
-      <c r="BJ80" s="28"/>
+      <c r="BJ80" s="26"/>
       <c r="BK80" s="1"/>
       <c r="BL80" s="1"/>
       <c r="BM80" s="1"/>
@@ -7681,13 +6736,13 @@
       <c r="CL80" s="1"/>
     </row>
     <row r="81" spans="3:90">
-      <c r="C81" s="11"/>
+      <c r="C81" s="10"/>
       <c r="E81" s="1"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
-      <c r="J81" s="21"/>
+      <c r="J81" s="4"/>
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
@@ -7722,12 +6777,12 @@
       <c r="BB81" s="1"/>
       <c r="BC81" s="1"/>
       <c r="BD81" s="1"/>
-      <c r="BE81" s="28"/>
-      <c r="BF81" s="28"/>
+      <c r="BE81" s="26"/>
+      <c r="BF81" s="26"/>
       <c r="BG81" s="1"/>
-      <c r="BH81" s="27"/>
+      <c r="BH81" s="25"/>
       <c r="BI81" s="1"/>
-      <c r="BJ81" s="28"/>
+      <c r="BJ81" s="26"/>
       <c r="BK81" s="1"/>
       <c r="BL81" s="1"/>
       <c r="BM81" s="1"/>
@@ -7758,13 +6813,13 @@
       <c r="CL81" s="1"/>
     </row>
     <row r="82" spans="3:90">
-      <c r="C82" s="11"/>
+      <c r="C82" s="10"/>
       <c r="E82" s="1"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="21"/>
+      <c r="J82" s="4"/>
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
@@ -7799,12 +6854,12 @@
       <c r="BB82" s="1"/>
       <c r="BC82" s="1"/>
       <c r="BD82" s="1"/>
-      <c r="BE82" s="28"/>
-      <c r="BF82" s="28"/>
+      <c r="BE82" s="26"/>
+      <c r="BF82" s="26"/>
       <c r="BG82" s="1"/>
-      <c r="BH82" s="27"/>
+      <c r="BH82" s="25"/>
       <c r="BI82" s="1"/>
-      <c r="BJ82" s="28"/>
+      <c r="BJ82" s="26"/>
       <c r="BK82" s="1"/>
       <c r="BL82" s="1"/>
       <c r="BM82" s="1"/>
@@ -7835,13 +6890,13 @@
       <c r="CL82" s="1"/>
     </row>
     <row r="83" spans="3:90">
-      <c r="C83" s="11"/>
+      <c r="C83" s="10"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
-      <c r="J83" s="21"/>
+      <c r="J83" s="4"/>
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
@@ -7876,12 +6931,12 @@
       <c r="BB83" s="1"/>
       <c r="BC83" s="1"/>
       <c r="BD83" s="1"/>
-      <c r="BE83" s="28"/>
-      <c r="BF83" s="28"/>
+      <c r="BE83" s="26"/>
+      <c r="BF83" s="26"/>
       <c r="BG83" s="1"/>
-      <c r="BH83" s="27"/>
+      <c r="BH83" s="25"/>
       <c r="BI83" s="1"/>
-      <c r="BJ83" s="28"/>
+      <c r="BJ83" s="26"/>
       <c r="BK83" s="1"/>
       <c r="BL83" s="1"/>
       <c r="BM83" s="1"/>
@@ -7912,13 +6967,13 @@
       <c r="CL83" s="1"/>
     </row>
     <row r="84" spans="3:90">
-      <c r="C84" s="11"/>
+      <c r="C84" s="10"/>
       <c r="E84" s="1"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
-      <c r="J84" s="21"/>
+      <c r="J84" s="4"/>
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
@@ -7953,12 +7008,12 @@
       <c r="BB84" s="1"/>
       <c r="BC84" s="1"/>
       <c r="BD84" s="1"/>
-      <c r="BE84" s="28"/>
-      <c r="BF84" s="28"/>
+      <c r="BE84" s="26"/>
+      <c r="BF84" s="26"/>
       <c r="BG84" s="1"/>
-      <c r="BH84" s="27"/>
+      <c r="BH84" s="25"/>
       <c r="BI84" s="1"/>
-      <c r="BJ84" s="28"/>
+      <c r="BJ84" s="26"/>
       <c r="BK84" s="1"/>
       <c r="BL84" s="1"/>
       <c r="BM84" s="1"/>
@@ -7989,13 +7044,13 @@
       <c r="CL84" s="1"/>
     </row>
     <row r="85" spans="3:90">
-      <c r="C85" s="11"/>
+      <c r="C85" s="10"/>
       <c r="E85" s="1"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
-      <c r="J85" s="21"/>
+      <c r="J85" s="4"/>
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
@@ -8030,12 +7085,12 @@
       <c r="BB85" s="1"/>
       <c r="BC85" s="1"/>
       <c r="BD85" s="1"/>
-      <c r="BE85" s="28"/>
-      <c r="BF85" s="28"/>
+      <c r="BE85" s="26"/>
+      <c r="BF85" s="26"/>
       <c r="BG85" s="1"/>
-      <c r="BH85" s="27"/>
+      <c r="BH85" s="25"/>
       <c r="BI85" s="1"/>
-      <c r="BJ85" s="28"/>
+      <c r="BJ85" s="26"/>
       <c r="BK85" s="1"/>
       <c r="BL85" s="1"/>
       <c r="BM85" s="1"/>
@@ -8066,13 +7121,13 @@
       <c r="CL85" s="1"/>
     </row>
     <row r="86" spans="3:90">
-      <c r="C86" s="11"/>
+      <c r="C86" s="10"/>
       <c r="E86" s="1"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
-      <c r="J86" s="21"/>
+      <c r="J86" s="4"/>
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
@@ -8107,12 +7162,12 @@
       <c r="BB86" s="1"/>
       <c r="BC86" s="1"/>
       <c r="BD86" s="1"/>
-      <c r="BE86" s="28"/>
-      <c r="BF86" s="28"/>
+      <c r="BE86" s="26"/>
+      <c r="BF86" s="26"/>
       <c r="BG86" s="1"/>
-      <c r="BH86" s="27"/>
+      <c r="BH86" s="25"/>
       <c r="BI86" s="1"/>
-      <c r="BJ86" s="28"/>
+      <c r="BJ86" s="26"/>
       <c r="BK86" s="1"/>
       <c r="BL86" s="1"/>
       <c r="BM86" s="1"/>
@@ -8143,13 +7198,13 @@
       <c r="CL86" s="1"/>
     </row>
     <row r="87" spans="3:62">
-      <c r="C87" s="11"/>
+      <c r="C87" s="10"/>
       <c r="E87" s="1"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="13"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
-      <c r="J87" s="21"/>
+      <c r="J87" s="4"/>
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
@@ -8184,21 +7239,21 @@
       <c r="BB87" s="1"/>
       <c r="BC87" s="1"/>
       <c r="BD87" s="1"/>
-      <c r="BE87" s="28"/>
-      <c r="BF87" s="28"/>
+      <c r="BE87" s="26"/>
+      <c r="BF87" s="26"/>
       <c r="BG87" s="1"/>
-      <c r="BH87" s="27"/>
+      <c r="BH87" s="25"/>
       <c r="BI87" s="1"/>
-      <c r="BJ87" s="28"/>
+      <c r="BJ87" s="26"/>
     </row>
     <row r="88" spans="3:62">
-      <c r="C88" s="11"/>
+      <c r="C88" s="10"/>
       <c r="E88" s="1"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="13"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
-      <c r="J88" s="21"/>
+      <c r="J88" s="4"/>
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
@@ -8233,21 +7288,21 @@
       <c r="BB88" s="1"/>
       <c r="BC88" s="1"/>
       <c r="BD88" s="1"/>
-      <c r="BE88" s="28"/>
-      <c r="BF88" s="28"/>
+      <c r="BE88" s="26"/>
+      <c r="BF88" s="26"/>
       <c r="BG88" s="1"/>
-      <c r="BH88" s="27"/>
+      <c r="BH88" s="25"/>
       <c r="BI88" s="1"/>
-      <c r="BJ88" s="28"/>
+      <c r="BJ88" s="26"/>
     </row>
     <row r="89" spans="3:62">
-      <c r="C89" s="11"/>
+      <c r="C89" s="10"/>
       <c r="E89" s="1"/>
-      <c r="F89" s="13"/>
-      <c r="G89" s="13"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
-      <c r="J89" s="21"/>
+      <c r="J89" s="4"/>
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
@@ -8282,21 +7337,21 @@
       <c r="BB89" s="1"/>
       <c r="BC89" s="1"/>
       <c r="BD89" s="1"/>
-      <c r="BE89" s="28"/>
-      <c r="BF89" s="28"/>
+      <c r="BE89" s="26"/>
+      <c r="BF89" s="26"/>
       <c r="BG89" s="1"/>
-      <c r="BH89" s="27"/>
+      <c r="BH89" s="25"/>
       <c r="BI89" s="1"/>
-      <c r="BJ89" s="28"/>
+      <c r="BJ89" s="26"/>
     </row>
     <row r="90" spans="3:62">
-      <c r="C90" s="11"/>
+      <c r="C90" s="10"/>
       <c r="E90" s="1"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
-      <c r="J90" s="21"/>
+      <c r="J90" s="4"/>
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
@@ -8331,21 +7386,21 @@
       <c r="BB90" s="1"/>
       <c r="BC90" s="1"/>
       <c r="BD90" s="1"/>
-      <c r="BE90" s="28"/>
-      <c r="BF90" s="28"/>
+      <c r="BE90" s="26"/>
+      <c r="BF90" s="26"/>
       <c r="BG90" s="1"/>
-      <c r="BH90" s="27"/>
+      <c r="BH90" s="25"/>
       <c r="BI90" s="1"/>
-      <c r="BJ90" s="28"/>
+      <c r="BJ90" s="26"/>
     </row>
     <row r="91" spans="3:62">
-      <c r="C91" s="11"/>
+      <c r="C91" s="10"/>
       <c r="E91" s="1"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="13"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
-      <c r="J91" s="21"/>
+      <c r="J91" s="4"/>
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
@@ -8380,21 +7435,21 @@
       <c r="BB91" s="1"/>
       <c r="BC91" s="1"/>
       <c r="BD91" s="1"/>
-      <c r="BE91" s="28"/>
-      <c r="BF91" s="28"/>
+      <c r="BE91" s="26"/>
+      <c r="BF91" s="26"/>
       <c r="BG91" s="1"/>
-      <c r="BH91" s="27"/>
+      <c r="BH91" s="25"/>
       <c r="BI91" s="1"/>
-      <c r="BJ91" s="28"/>
+      <c r="BJ91" s="26"/>
     </row>
     <row r="92" spans="3:62">
-      <c r="C92" s="11"/>
+      <c r="C92" s="10"/>
       <c r="E92" s="1"/>
-      <c r="F92" s="13"/>
-      <c r="G92" s="13"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
-      <c r="J92" s="21"/>
+      <c r="J92" s="4"/>
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
@@ -8429,21 +7484,21 @@
       <c r="BB92" s="1"/>
       <c r="BC92" s="1"/>
       <c r="BD92" s="1"/>
-      <c r="BE92" s="28"/>
-      <c r="BF92" s="28"/>
+      <c r="BE92" s="26"/>
+      <c r="BF92" s="26"/>
       <c r="BG92" s="1"/>
-      <c r="BH92" s="27"/>
+      <c r="BH92" s="25"/>
       <c r="BI92" s="1"/>
-      <c r="BJ92" s="28"/>
+      <c r="BJ92" s="26"/>
     </row>
     <row r="93" spans="3:62">
-      <c r="C93" s="11"/>
+      <c r="C93" s="10"/>
       <c r="E93" s="1"/>
-      <c r="F93" s="13"/>
-      <c r="G93" s="13"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
-      <c r="J93" s="21"/>
+      <c r="J93" s="4"/>
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
@@ -8478,21 +7533,21 @@
       <c r="BB93" s="1"/>
       <c r="BC93" s="1"/>
       <c r="BD93" s="1"/>
-      <c r="BE93" s="28"/>
-      <c r="BF93" s="28"/>
+      <c r="BE93" s="26"/>
+      <c r="BF93" s="26"/>
       <c r="BG93" s="1"/>
-      <c r="BH93" s="27"/>
+      <c r="BH93" s="25"/>
       <c r="BI93" s="1"/>
-      <c r="BJ93" s="28"/>
+      <c r="BJ93" s="26"/>
     </row>
     <row r="94" spans="3:62">
-      <c r="C94" s="11"/>
+      <c r="C94" s="10"/>
       <c r="E94" s="1"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
-      <c r="J94" s="21"/>
+      <c r="J94" s="4"/>
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
@@ -8527,21 +7582,21 @@
       <c r="BB94" s="1"/>
       <c r="BC94" s="1"/>
       <c r="BD94" s="1"/>
-      <c r="BE94" s="28"/>
-      <c r="BF94" s="28"/>
+      <c r="BE94" s="26"/>
+      <c r="BF94" s="26"/>
       <c r="BG94" s="1"/>
-      <c r="BH94" s="27"/>
+      <c r="BH94" s="25"/>
       <c r="BI94" s="1"/>
-      <c r="BJ94" s="28"/>
+      <c r="BJ94" s="26"/>
     </row>
     <row r="95" spans="3:62">
-      <c r="C95" s="11"/>
+      <c r="C95" s="10"/>
       <c r="E95" s="1"/>
-      <c r="F95" s="13"/>
-      <c r="G95" s="13"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
-      <c r="J95" s="21"/>
+      <c r="J95" s="4"/>
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
@@ -8576,21 +7631,21 @@
       <c r="BB95" s="1"/>
       <c r="BC95" s="1"/>
       <c r="BD95" s="1"/>
-      <c r="BE95" s="28"/>
-      <c r="BF95" s="28"/>
+      <c r="BE95" s="26"/>
+      <c r="BF95" s="26"/>
       <c r="BG95" s="1"/>
-      <c r="BH95" s="27"/>
+      <c r="BH95" s="25"/>
       <c r="BI95" s="1"/>
-      <c r="BJ95" s="28"/>
+      <c r="BJ95" s="26"/>
     </row>
     <row r="96" spans="3:62">
-      <c r="C96" s="11"/>
+      <c r="C96" s="10"/>
       <c r="E96" s="1"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
-      <c r="J96" s="21"/>
+      <c r="J96" s="4"/>
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
@@ -8625,21 +7680,21 @@
       <c r="BB96" s="1"/>
       <c r="BC96" s="1"/>
       <c r="BD96" s="1"/>
-      <c r="BE96" s="28"/>
-      <c r="BF96" s="28"/>
+      <c r="BE96" s="26"/>
+      <c r="BF96" s="26"/>
       <c r="BG96" s="1"/>
-      <c r="BH96" s="27"/>
+      <c r="BH96" s="25"/>
       <c r="BI96" s="1"/>
-      <c r="BJ96" s="28"/>
+      <c r="BJ96" s="26"/>
     </row>
     <row r="97" spans="3:62">
-      <c r="C97" s="11"/>
+      <c r="C97" s="10"/>
       <c r="E97" s="1"/>
-      <c r="F97" s="13"/>
-      <c r="G97" s="13"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
-      <c r="J97" s="21"/>
+      <c r="J97" s="4"/>
       <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
@@ -8675,21 +7730,21 @@
       <c r="BB97" s="1"/>
       <c r="BC97" s="1"/>
       <c r="BD97" s="1"/>
-      <c r="BE97" s="28"/>
-      <c r="BF97" s="28"/>
+      <c r="BE97" s="26"/>
+      <c r="BF97" s="26"/>
       <c r="BG97" s="1"/>
-      <c r="BH97" s="27"/>
+      <c r="BH97" s="25"/>
       <c r="BI97" s="1"/>
-      <c r="BJ97" s="28"/>
+      <c r="BJ97" s="26"/>
     </row>
     <row r="98" spans="3:62">
-      <c r="C98" s="11"/>
+      <c r="C98" s="10"/>
       <c r="E98" s="1"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="13"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
-      <c r="J98" s="21"/>
+      <c r="J98" s="4"/>
       <c r="P98" s="1"/>
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
@@ -8725,21 +7780,21 @@
       <c r="BB98" s="1"/>
       <c r="BC98" s="1"/>
       <c r="BD98" s="1"/>
-      <c r="BE98" s="28"/>
-      <c r="BF98" s="28"/>
+      <c r="BE98" s="26"/>
+      <c r="BF98" s="26"/>
       <c r="BG98" s="1"/>
-      <c r="BH98" s="27"/>
+      <c r="BH98" s="25"/>
       <c r="BI98" s="1"/>
-      <c r="BJ98" s="28"/>
+      <c r="BJ98" s="26"/>
     </row>
     <row r="99" spans="3:62">
-      <c r="C99" s="11"/>
+      <c r="C99" s="10"/>
       <c r="E99" s="1"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="13"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
-      <c r="J99" s="21"/>
+      <c r="J99" s="4"/>
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
@@ -8775,21 +7830,21 @@
       <c r="BB99" s="1"/>
       <c r="BC99" s="1"/>
       <c r="BD99" s="1"/>
-      <c r="BE99" s="28"/>
-      <c r="BF99" s="28"/>
+      <c r="BE99" s="26"/>
+      <c r="BF99" s="26"/>
       <c r="BG99" s="1"/>
-      <c r="BH99" s="27"/>
+      <c r="BH99" s="25"/>
       <c r="BI99" s="1"/>
-      <c r="BJ99" s="28"/>
+      <c r="BJ99" s="26"/>
     </row>
     <row r="100" spans="3:62">
-      <c r="C100" s="11"/>
+      <c r="C100" s="10"/>
       <c r="E100" s="1"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="13"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
-      <c r="J100" s="21"/>
+      <c r="J100" s="4"/>
       <c r="P100" s="1"/>
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
@@ -8825,21 +7880,21 @@
       <c r="BB100" s="1"/>
       <c r="BC100" s="1"/>
       <c r="BD100" s="1"/>
-      <c r="BE100" s="28"/>
-      <c r="BF100" s="28"/>
+      <c r="BE100" s="26"/>
+      <c r="BF100" s="26"/>
       <c r="BG100" s="1"/>
-      <c r="BH100" s="27"/>
+      <c r="BH100" s="25"/>
       <c r="BI100" s="1"/>
-      <c r="BJ100" s="28"/>
+      <c r="BJ100" s="26"/>
     </row>
     <row r="101" spans="3:62">
-      <c r="C101" s="11"/>
+      <c r="C101" s="10"/>
       <c r="E101" s="1"/>
-      <c r="F101" s="13"/>
-      <c r="G101" s="13"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
-      <c r="J101" s="21"/>
+      <c r="J101" s="4"/>
       <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
@@ -8875,21 +7930,21 @@
       <c r="BB101" s="1"/>
       <c r="BC101" s="1"/>
       <c r="BD101" s="1"/>
-      <c r="BE101" s="28"/>
-      <c r="BF101" s="28"/>
+      <c r="BE101" s="26"/>
+      <c r="BF101" s="26"/>
       <c r="BG101" s="1"/>
-      <c r="BH101" s="27"/>
+      <c r="BH101" s="25"/>
       <c r="BI101" s="1"/>
-      <c r="BJ101" s="28"/>
+      <c r="BJ101" s="26"/>
     </row>
     <row r="102" spans="3:62">
-      <c r="C102" s="11"/>
+      <c r="C102" s="10"/>
       <c r="E102" s="1"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="13"/>
+      <c r="F102" s="12"/>
+      <c r="G102" s="12"/>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
-      <c r="J102" s="21"/>
+      <c r="J102" s="4"/>
       <c r="P102" s="1"/>
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
@@ -8925,21 +7980,21 @@
       <c r="BB102" s="1"/>
       <c r="BC102" s="1"/>
       <c r="BD102" s="1"/>
-      <c r="BE102" s="28"/>
-      <c r="BF102" s="28"/>
+      <c r="BE102" s="26"/>
+      <c r="BF102" s="26"/>
       <c r="BG102" s="1"/>
-      <c r="BH102" s="27"/>
+      <c r="BH102" s="25"/>
       <c r="BI102" s="1"/>
-      <c r="BJ102" s="28"/>
+      <c r="BJ102" s="26"/>
     </row>
     <row r="103" spans="3:62">
-      <c r="C103" s="11"/>
+      <c r="C103" s="10"/>
       <c r="E103" s="1"/>
-      <c r="F103" s="13"/>
-      <c r="G103" s="13"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="12"/>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
-      <c r="J103" s="21"/>
+      <c r="J103" s="4"/>
       <c r="P103" s="1"/>
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
@@ -8975,21 +8030,21 @@
       <c r="BB103" s="1"/>
       <c r="BC103" s="1"/>
       <c r="BD103" s="1"/>
-      <c r="BE103" s="28"/>
-      <c r="BF103" s="28"/>
+      <c r="BE103" s="26"/>
+      <c r="BF103" s="26"/>
       <c r="BG103" s="1"/>
-      <c r="BH103" s="27"/>
+      <c r="BH103" s="25"/>
       <c r="BI103" s="1"/>
-      <c r="BJ103" s="28"/>
+      <c r="BJ103" s="26"/>
     </row>
     <row r="104" spans="3:62">
-      <c r="C104" s="11"/>
+      <c r="C104" s="10"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="13"/>
-      <c r="G104" s="13"/>
+      <c r="F104" s="12"/>
+      <c r="G104" s="12"/>
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
-      <c r="J104" s="21"/>
+      <c r="J104" s="4"/>
       <c r="P104" s="1"/>
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
@@ -9025,21 +8080,21 @@
       <c r="BB104" s="1"/>
       <c r="BC104" s="1"/>
       <c r="BD104" s="1"/>
-      <c r="BE104" s="28"/>
-      <c r="BF104" s="28"/>
+      <c r="BE104" s="26"/>
+      <c r="BF104" s="26"/>
       <c r="BG104" s="1"/>
-      <c r="BH104" s="27"/>
+      <c r="BH104" s="25"/>
       <c r="BI104" s="1"/>
-      <c r="BJ104" s="28"/>
+      <c r="BJ104" s="26"/>
     </row>
     <row r="105" spans="3:62">
-      <c r="C105" s="11"/>
+      <c r="C105" s="10"/>
       <c r="E105" s="1"/>
-      <c r="F105" s="13"/>
-      <c r="G105" s="13"/>
+      <c r="F105" s="12"/>
+      <c r="G105" s="12"/>
       <c r="H105" s="1"/>
       <c r="I105" s="1"/>
-      <c r="J105" s="21"/>
+      <c r="J105" s="4"/>
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
@@ -9075,21 +8130,21 @@
       <c r="BB105" s="1"/>
       <c r="BC105" s="1"/>
       <c r="BD105" s="1"/>
-      <c r="BE105" s="28"/>
-      <c r="BF105" s="28"/>
+      <c r="BE105" s="26"/>
+      <c r="BF105" s="26"/>
       <c r="BG105" s="1"/>
-      <c r="BH105" s="27"/>
+      <c r="BH105" s="25"/>
       <c r="BI105" s="1"/>
-      <c r="BJ105" s="28"/>
+      <c r="BJ105" s="26"/>
     </row>
     <row r="106" spans="3:62">
-      <c r="C106" s="11"/>
+      <c r="C106" s="10"/>
       <c r="E106" s="1"/>
-      <c r="F106" s="13"/>
-      <c r="G106" s="13"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
-      <c r="J106" s="21"/>
+      <c r="J106" s="4"/>
       <c r="P106" s="1"/>
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
@@ -9125,21 +8180,21 @@
       <c r="BB106" s="1"/>
       <c r="BC106" s="1"/>
       <c r="BD106" s="1"/>
-      <c r="BE106" s="28"/>
-      <c r="BF106" s="28"/>
+      <c r="BE106" s="26"/>
+      <c r="BF106" s="26"/>
       <c r="BG106" s="1"/>
-      <c r="BH106" s="27"/>
+      <c r="BH106" s="25"/>
       <c r="BI106" s="1"/>
-      <c r="BJ106" s="28"/>
+      <c r="BJ106" s="26"/>
     </row>
     <row r="107" spans="3:62">
-      <c r="C107" s="11"/>
+      <c r="C107" s="10"/>
       <c r="E107" s="1"/>
-      <c r="F107" s="13"/>
-      <c r="G107" s="13"/>
+      <c r="F107" s="12"/>
+      <c r="G107" s="12"/>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
-      <c r="J107" s="21"/>
+      <c r="J107" s="4"/>
       <c r="P107" s="1"/>
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
@@ -9175,21 +8230,21 @@
       <c r="BB107" s="1"/>
       <c r="BC107" s="1"/>
       <c r="BD107" s="1"/>
-      <c r="BE107" s="28"/>
-      <c r="BF107" s="28"/>
+      <c r="BE107" s="26"/>
+      <c r="BF107" s="26"/>
       <c r="BG107" s="1"/>
-      <c r="BH107" s="27"/>
+      <c r="BH107" s="25"/>
       <c r="BI107" s="1"/>
-      <c r="BJ107" s="28"/>
+      <c r="BJ107" s="26"/>
     </row>
     <row r="108" spans="3:62">
-      <c r="C108" s="11"/>
+      <c r="C108" s="10"/>
       <c r="E108" s="1"/>
-      <c r="F108" s="13"/>
-      <c r="G108" s="13"/>
+      <c r="F108" s="12"/>
+      <c r="G108" s="12"/>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
-      <c r="J108" s="21"/>
+      <c r="J108" s="4"/>
       <c r="P108" s="1"/>
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
@@ -9225,21 +8280,21 @@
       <c r="BB108" s="1"/>
       <c r="BC108" s="1"/>
       <c r="BD108" s="1"/>
-      <c r="BE108" s="28"/>
-      <c r="BF108" s="28"/>
+      <c r="BE108" s="26"/>
+      <c r="BF108" s="26"/>
       <c r="BG108" s="1"/>
-      <c r="BH108" s="27"/>
+      <c r="BH108" s="25"/>
       <c r="BI108" s="1"/>
-      <c r="BJ108" s="28"/>
+      <c r="BJ108" s="26"/>
     </row>
     <row r="109" spans="3:62">
-      <c r="C109" s="11"/>
+      <c r="C109" s="10"/>
       <c r="E109" s="1"/>
-      <c r="F109" s="13"/>
-      <c r="G109" s="13"/>
+      <c r="F109" s="12"/>
+      <c r="G109" s="12"/>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
-      <c r="J109" s="21"/>
+      <c r="J109" s="4"/>
       <c r="P109" s="1"/>
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
@@ -9275,21 +8330,21 @@
       <c r="BB109" s="1"/>
       <c r="BC109" s="1"/>
       <c r="BD109" s="1"/>
-      <c r="BE109" s="28"/>
-      <c r="BF109" s="28"/>
+      <c r="BE109" s="26"/>
+      <c r="BF109" s="26"/>
       <c r="BG109" s="1"/>
-      <c r="BH109" s="27"/>
+      <c r="BH109" s="25"/>
       <c r="BI109" s="1"/>
-      <c r="BJ109" s="28"/>
+      <c r="BJ109" s="26"/>
     </row>
     <row r="110" spans="3:62">
-      <c r="C110" s="11"/>
+      <c r="C110" s="10"/>
       <c r="E110" s="1"/>
-      <c r="F110" s="13"/>
-      <c r="G110" s="13"/>
+      <c r="F110" s="12"/>
+      <c r="G110" s="12"/>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
-      <c r="J110" s="21"/>
+      <c r="J110" s="4"/>
       <c r="P110" s="1"/>
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
@@ -9325,21 +8380,21 @@
       <c r="BB110" s="1"/>
       <c r="BC110" s="1"/>
       <c r="BD110" s="1"/>
-      <c r="BE110" s="28"/>
-      <c r="BF110" s="28"/>
+      <c r="BE110" s="26"/>
+      <c r="BF110" s="26"/>
       <c r="BG110" s="1"/>
-      <c r="BH110" s="27"/>
+      <c r="BH110" s="25"/>
       <c r="BI110" s="1"/>
-      <c r="BJ110" s="28"/>
+      <c r="BJ110" s="26"/>
     </row>
     <row r="111" spans="3:62">
-      <c r="C111" s="11"/>
+      <c r="C111" s="10"/>
       <c r="E111" s="1"/>
-      <c r="F111" s="13"/>
-      <c r="G111" s="13"/>
+      <c r="F111" s="12"/>
+      <c r="G111" s="12"/>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
-      <c r="J111" s="21"/>
+      <c r="J111" s="4"/>
       <c r="P111" s="1"/>
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
@@ -9375,21 +8430,21 @@
       <c r="BB111" s="1"/>
       <c r="BC111" s="1"/>
       <c r="BD111" s="1"/>
-      <c r="BE111" s="28"/>
-      <c r="BF111" s="28"/>
+      <c r="BE111" s="26"/>
+      <c r="BF111" s="26"/>
       <c r="BG111" s="1"/>
-      <c r="BH111" s="27"/>
+      <c r="BH111" s="25"/>
       <c r="BI111" s="1"/>
-      <c r="BJ111" s="28"/>
+      <c r="BJ111" s="26"/>
     </row>
     <row r="112" spans="3:62">
-      <c r="C112" s="11"/>
+      <c r="C112" s="10"/>
       <c r="E112" s="1"/>
-      <c r="F112" s="13"/>
-      <c r="G112" s="13"/>
+      <c r="F112" s="12"/>
+      <c r="G112" s="12"/>
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
-      <c r="J112" s="21"/>
+      <c r="J112" s="4"/>
       <c r="P112" s="1"/>
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
@@ -9425,21 +8480,21 @@
       <c r="BB112" s="1"/>
       <c r="BC112" s="1"/>
       <c r="BD112" s="1"/>
-      <c r="BE112" s="28"/>
-      <c r="BF112" s="28"/>
+      <c r="BE112" s="26"/>
+      <c r="BF112" s="26"/>
       <c r="BG112" s="1"/>
-      <c r="BH112" s="27"/>
+      <c r="BH112" s="25"/>
       <c r="BI112" s="1"/>
-      <c r="BJ112" s="28"/>
+      <c r="BJ112" s="26"/>
     </row>
     <row r="113" spans="3:62">
-      <c r="C113" s="11"/>
+      <c r="C113" s="10"/>
       <c r="E113" s="1"/>
-      <c r="F113" s="13"/>
-      <c r="G113" s="13"/>
+      <c r="F113" s="12"/>
+      <c r="G113" s="12"/>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
-      <c r="J113" s="21"/>
+      <c r="J113" s="4"/>
       <c r="P113" s="1"/>
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
@@ -9475,21 +8530,21 @@
       <c r="BB113" s="1"/>
       <c r="BC113" s="1"/>
       <c r="BD113" s="1"/>
-      <c r="BE113" s="28"/>
-      <c r="BF113" s="28"/>
+      <c r="BE113" s="26"/>
+      <c r="BF113" s="26"/>
       <c r="BG113" s="1"/>
-      <c r="BH113" s="27"/>
+      <c r="BH113" s="25"/>
       <c r="BI113" s="1"/>
-      <c r="BJ113" s="28"/>
+      <c r="BJ113" s="26"/>
     </row>
     <row r="114" spans="3:62">
-      <c r="C114" s="11"/>
+      <c r="C114" s="10"/>
       <c r="E114" s="1"/>
-      <c r="F114" s="13"/>
-      <c r="G114" s="13"/>
+      <c r="F114" s="12"/>
+      <c r="G114" s="12"/>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
-      <c r="J114" s="21"/>
+      <c r="J114" s="4"/>
       <c r="P114" s="1"/>
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
@@ -9525,21 +8580,21 @@
       <c r="BB114" s="1"/>
       <c r="BC114" s="1"/>
       <c r="BD114" s="1"/>
-      <c r="BE114" s="28"/>
-      <c r="BF114" s="28"/>
+      <c r="BE114" s="26"/>
+      <c r="BF114" s="26"/>
       <c r="BG114" s="1"/>
-      <c r="BH114" s="27"/>
+      <c r="BH114" s="25"/>
       <c r="BI114" s="1"/>
-      <c r="BJ114" s="28"/>
+      <c r="BJ114" s="26"/>
     </row>
     <row r="115" spans="3:62">
-      <c r="C115" s="11"/>
+      <c r="C115" s="10"/>
       <c r="E115" s="1"/>
-      <c r="F115" s="13"/>
-      <c r="G115" s="13"/>
+      <c r="F115" s="12"/>
+      <c r="G115" s="12"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
-      <c r="J115" s="21"/>
+      <c r="J115" s="4"/>
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
@@ -9575,21 +8630,21 @@
       <c r="BB115" s="1"/>
       <c r="BC115" s="1"/>
       <c r="BD115" s="1"/>
-      <c r="BE115" s="28"/>
-      <c r="BF115" s="28"/>
+      <c r="BE115" s="26"/>
+      <c r="BF115" s="26"/>
       <c r="BG115" s="1"/>
-      <c r="BH115" s="27"/>
+      <c r="BH115" s="25"/>
       <c r="BI115" s="1"/>
-      <c r="BJ115" s="28"/>
+      <c r="BJ115" s="26"/>
     </row>
     <row r="116" spans="3:62">
-      <c r="C116" s="11"/>
+      <c r="C116" s="10"/>
       <c r="E116" s="1"/>
-      <c r="F116" s="13"/>
-      <c r="G116" s="13"/>
+      <c r="F116" s="12"/>
+      <c r="G116" s="12"/>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
-      <c r="J116" s="21"/>
+      <c r="J116" s="4"/>
       <c r="P116" s="1"/>
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
@@ -9625,21 +8680,21 @@
       <c r="BB116" s="1"/>
       <c r="BC116" s="1"/>
       <c r="BD116" s="1"/>
-      <c r="BE116" s="28"/>
-      <c r="BF116" s="28"/>
+      <c r="BE116" s="26"/>
+      <c r="BF116" s="26"/>
       <c r="BG116" s="1"/>
-      <c r="BH116" s="27"/>
+      <c r="BH116" s="25"/>
       <c r="BI116" s="1"/>
-      <c r="BJ116" s="28"/>
+      <c r="BJ116" s="26"/>
     </row>
     <row r="117" spans="3:62">
-      <c r="C117" s="11"/>
+      <c r="C117" s="10"/>
       <c r="E117" s="1"/>
-      <c r="F117" s="13"/>
-      <c r="G117" s="13"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="12"/>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
-      <c r="J117" s="21"/>
+      <c r="J117" s="4"/>
       <c r="P117" s="1"/>
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
@@ -9675,21 +8730,21 @@
       <c r="BB117" s="1"/>
       <c r="BC117" s="1"/>
       <c r="BD117" s="1"/>
-      <c r="BE117" s="28"/>
-      <c r="BF117" s="28"/>
+      <c r="BE117" s="26"/>
+      <c r="BF117" s="26"/>
       <c r="BG117" s="1"/>
-      <c r="BH117" s="27"/>
+      <c r="BH117" s="25"/>
       <c r="BI117" s="1"/>
-      <c r="BJ117" s="28"/>
+      <c r="BJ117" s="26"/>
     </row>
     <row r="118" spans="3:62">
-      <c r="C118" s="11"/>
+      <c r="C118" s="10"/>
       <c r="E118" s="1"/>
-      <c r="F118" s="13"/>
-      <c r="G118" s="13"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
-      <c r="J118" s="21"/>
+      <c r="J118" s="4"/>
       <c r="P118" s="1"/>
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
@@ -9725,21 +8780,21 @@
       <c r="BB118" s="1"/>
       <c r="BC118" s="1"/>
       <c r="BD118" s="1"/>
-      <c r="BE118" s="28"/>
-      <c r="BF118" s="28"/>
+      <c r="BE118" s="26"/>
+      <c r="BF118" s="26"/>
       <c r="BG118" s="1"/>
-      <c r="BH118" s="27"/>
+      <c r="BH118" s="25"/>
       <c r="BI118" s="1"/>
-      <c r="BJ118" s="28"/>
+      <c r="BJ118" s="26"/>
     </row>
     <row r="119" spans="3:62">
-      <c r="C119" s="11"/>
+      <c r="C119" s="10"/>
       <c r="E119" s="1"/>
-      <c r="F119" s="13"/>
-      <c r="G119" s="13"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
-      <c r="J119" s="21"/>
+      <c r="J119" s="4"/>
       <c r="P119" s="1"/>
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
@@ -9775,21 +8830,21 @@
       <c r="BB119" s="1"/>
       <c r="BC119" s="1"/>
       <c r="BD119" s="1"/>
-      <c r="BE119" s="28"/>
-      <c r="BF119" s="28"/>
+      <c r="BE119" s="26"/>
+      <c r="BF119" s="26"/>
       <c r="BG119" s="1"/>
-      <c r="BH119" s="27"/>
+      <c r="BH119" s="25"/>
       <c r="BI119" s="1"/>
-      <c r="BJ119" s="28"/>
+      <c r="BJ119" s="26"/>
     </row>
     <row r="120" spans="3:62">
-      <c r="C120" s="11"/>
+      <c r="C120" s="10"/>
       <c r="E120" s="1"/>
-      <c r="F120" s="13"/>
-      <c r="G120" s="13"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="12"/>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
-      <c r="J120" s="21"/>
+      <c r="J120" s="4"/>
       <c r="P120" s="1"/>
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
@@ -9825,21 +8880,21 @@
       <c r="BB120" s="1"/>
       <c r="BC120" s="1"/>
       <c r="BD120" s="1"/>
-      <c r="BE120" s="28"/>
-      <c r="BF120" s="28"/>
+      <c r="BE120" s="26"/>
+      <c r="BF120" s="26"/>
       <c r="BG120" s="1"/>
-      <c r="BH120" s="27"/>
+      <c r="BH120" s="25"/>
       <c r="BI120" s="1"/>
-      <c r="BJ120" s="28"/>
+      <c r="BJ120" s="26"/>
     </row>
     <row r="121" spans="3:62">
-      <c r="C121" s="11"/>
+      <c r="C121" s="10"/>
       <c r="E121" s="1"/>
-      <c r="F121" s="13"/>
-      <c r="G121" s="13"/>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12"/>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
-      <c r="J121" s="21"/>
+      <c r="J121" s="4"/>
       <c r="P121" s="1"/>
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
@@ -9875,21 +8930,21 @@
       <c r="BB121" s="1"/>
       <c r="BC121" s="1"/>
       <c r="BD121" s="1"/>
-      <c r="BE121" s="28"/>
-      <c r="BF121" s="28"/>
+      <c r="BE121" s="26"/>
+      <c r="BF121" s="26"/>
       <c r="BG121" s="1"/>
-      <c r="BH121" s="27"/>
+      <c r="BH121" s="25"/>
       <c r="BI121" s="1"/>
-      <c r="BJ121" s="28"/>
+      <c r="BJ121" s="26"/>
     </row>
     <row r="122" spans="3:62">
-      <c r="C122" s="11"/>
+      <c r="C122" s="10"/>
       <c r="E122" s="1"/>
-      <c r="F122" s="13"/>
-      <c r="G122" s="13"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
-      <c r="J122" s="21"/>
+      <c r="J122" s="4"/>
       <c r="P122" s="1"/>
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
@@ -9925,21 +8980,21 @@
       <c r="BB122" s="1"/>
       <c r="BC122" s="1"/>
       <c r="BD122" s="1"/>
-      <c r="BE122" s="28"/>
-      <c r="BF122" s="28"/>
+      <c r="BE122" s="26"/>
+      <c r="BF122" s="26"/>
       <c r="BG122" s="1"/>
-      <c r="BH122" s="27"/>
+      <c r="BH122" s="25"/>
       <c r="BI122" s="1"/>
-      <c r="BJ122" s="28"/>
+      <c r="BJ122" s="26"/>
     </row>
     <row r="123" spans="3:62">
-      <c r="C123" s="11"/>
+      <c r="C123" s="10"/>
       <c r="E123" s="1"/>
-      <c r="F123" s="13"/>
-      <c r="G123" s="13"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
-      <c r="J123" s="21"/>
+      <c r="J123" s="4"/>
       <c r="P123" s="1"/>
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
@@ -9975,21 +9030,21 @@
       <c r="BB123" s="1"/>
       <c r="BC123" s="1"/>
       <c r="BD123" s="1"/>
-      <c r="BE123" s="28"/>
-      <c r="BF123" s="28"/>
+      <c r="BE123" s="26"/>
+      <c r="BF123" s="26"/>
       <c r="BG123" s="1"/>
-      <c r="BH123" s="27"/>
+      <c r="BH123" s="25"/>
       <c r="BI123" s="1"/>
-      <c r="BJ123" s="28"/>
+      <c r="BJ123" s="26"/>
     </row>
     <row r="124" spans="3:62">
-      <c r="C124" s="11"/>
+      <c r="C124" s="10"/>
       <c r="E124" s="1"/>
-      <c r="F124" s="13"/>
-      <c r="G124" s="13"/>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12"/>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
-      <c r="J124" s="21"/>
+      <c r="J124" s="4"/>
       <c r="P124" s="1"/>
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
@@ -10025,21 +9080,21 @@
       <c r="BB124" s="1"/>
       <c r="BC124" s="1"/>
       <c r="BD124" s="1"/>
-      <c r="BE124" s="28"/>
-      <c r="BF124" s="28"/>
+      <c r="BE124" s="26"/>
+      <c r="BF124" s="26"/>
       <c r="BG124" s="1"/>
-      <c r="BH124" s="27"/>
+      <c r="BH124" s="25"/>
       <c r="BI124" s="1"/>
-      <c r="BJ124" s="28"/>
+      <c r="BJ124" s="26"/>
     </row>
     <row r="125" spans="3:62">
-      <c r="C125" s="11"/>
+      <c r="C125" s="10"/>
       <c r="E125" s="1"/>
-      <c r="F125" s="13"/>
-      <c r="G125" s="13"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="12"/>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
-      <c r="J125" s="21"/>
+      <c r="J125" s="4"/>
       <c r="P125" s="1"/>
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
@@ -10075,21 +9130,21 @@
       <c r="BB125" s="1"/>
       <c r="BC125" s="1"/>
       <c r="BD125" s="1"/>
-      <c r="BE125" s="28"/>
-      <c r="BF125" s="28"/>
+      <c r="BE125" s="26"/>
+      <c r="BF125" s="26"/>
       <c r="BG125" s="1"/>
-      <c r="BH125" s="27"/>
+      <c r="BH125" s="25"/>
       <c r="BI125" s="1"/>
-      <c r="BJ125" s="28"/>
+      <c r="BJ125" s="26"/>
     </row>
     <row r="126" spans="3:62">
-      <c r="C126" s="11"/>
+      <c r="C126" s="10"/>
       <c r="E126" s="1"/>
-      <c r="F126" s="13"/>
-      <c r="G126" s="13"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12"/>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
-      <c r="J126" s="21"/>
+      <c r="J126" s="4"/>
       <c r="P126" s="1"/>
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
@@ -10125,21 +9180,21 @@
       <c r="BB126" s="1"/>
       <c r="BC126" s="1"/>
       <c r="BD126" s="1"/>
-      <c r="BE126" s="28"/>
-      <c r="BF126" s="28"/>
+      <c r="BE126" s="26"/>
+      <c r="BF126" s="26"/>
       <c r="BG126" s="1"/>
-      <c r="BH126" s="27"/>
+      <c r="BH126" s="25"/>
       <c r="BI126" s="1"/>
-      <c r="BJ126" s="28"/>
+      <c r="BJ126" s="26"/>
     </row>
     <row r="127" spans="3:62">
-      <c r="C127" s="11"/>
+      <c r="C127" s="10"/>
       <c r="E127" s="1"/>
-      <c r="F127" s="13"/>
-      <c r="G127" s="13"/>
+      <c r="F127" s="12"/>
+      <c r="G127" s="12"/>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
-      <c r="J127" s="21"/>
+      <c r="J127" s="4"/>
       <c r="P127" s="1"/>
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
@@ -10175,21 +9230,21 @@
       <c r="BB127" s="1"/>
       <c r="BC127" s="1"/>
       <c r="BD127" s="1"/>
-      <c r="BE127" s="28"/>
-      <c r="BF127" s="28"/>
+      <c r="BE127" s="26"/>
+      <c r="BF127" s="26"/>
       <c r="BG127" s="1"/>
-      <c r="BH127" s="27"/>
+      <c r="BH127" s="25"/>
       <c r="BI127" s="1"/>
-      <c r="BJ127" s="28"/>
+      <c r="BJ127" s="26"/>
     </row>
     <row r="128" spans="3:62">
-      <c r="C128" s="11"/>
+      <c r="C128" s="10"/>
       <c r="E128" s="1"/>
-      <c r="F128" s="13"/>
-      <c r="G128" s="13"/>
+      <c r="F128" s="12"/>
+      <c r="G128" s="12"/>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
-      <c r="J128" s="21"/>
+      <c r="J128" s="4"/>
       <c r="P128" s="1"/>
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
@@ -10225,21 +9280,21 @@
       <c r="BB128" s="1"/>
       <c r="BC128" s="1"/>
       <c r="BD128" s="1"/>
-      <c r="BE128" s="28"/>
-      <c r="BF128" s="28"/>
+      <c r="BE128" s="26"/>
+      <c r="BF128" s="26"/>
       <c r="BG128" s="1"/>
-      <c r="BH128" s="27"/>
+      <c r="BH128" s="25"/>
       <c r="BI128" s="1"/>
-      <c r="BJ128" s="28"/>
+      <c r="BJ128" s="26"/>
     </row>
     <row r="129" spans="3:62">
-      <c r="C129" s="11"/>
+      <c r="C129" s="10"/>
       <c r="E129" s="1"/>
-      <c r="F129" s="13"/>
-      <c r="G129" s="13"/>
+      <c r="F129" s="12"/>
+      <c r="G129" s="12"/>
       <c r="H129" s="1"/>
       <c r="I129" s="1"/>
-      <c r="J129" s="21"/>
+      <c r="J129" s="4"/>
       <c r="P129" s="1"/>
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
@@ -10275,21 +9330,21 @@
       <c r="BB129" s="1"/>
       <c r="BC129" s="1"/>
       <c r="BD129" s="1"/>
-      <c r="BE129" s="28"/>
-      <c r="BF129" s="28"/>
+      <c r="BE129" s="26"/>
+      <c r="BF129" s="26"/>
       <c r="BG129" s="1"/>
-      <c r="BH129" s="27"/>
+      <c r="BH129" s="25"/>
       <c r="BI129" s="1"/>
-      <c r="BJ129" s="28"/>
+      <c r="BJ129" s="26"/>
     </row>
     <row r="130" spans="3:62">
-      <c r="C130" s="11"/>
+      <c r="C130" s="10"/>
       <c r="E130" s="1"/>
-      <c r="F130" s="13"/>
-      <c r="G130" s="13"/>
+      <c r="F130" s="12"/>
+      <c r="G130" s="12"/>
       <c r="H130" s="1"/>
       <c r="I130" s="1"/>
-      <c r="J130" s="21"/>
+      <c r="J130" s="4"/>
       <c r="P130" s="1"/>
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
@@ -10325,21 +9380,21 @@
       <c r="BB130" s="1"/>
       <c r="BC130" s="1"/>
       <c r="BD130" s="1"/>
-      <c r="BE130" s="28"/>
-      <c r="BF130" s="28"/>
+      <c r="BE130" s="26"/>
+      <c r="BF130" s="26"/>
       <c r="BG130" s="1"/>
-      <c r="BH130" s="27"/>
+      <c r="BH130" s="25"/>
       <c r="BI130" s="1"/>
-      <c r="BJ130" s="28"/>
+      <c r="BJ130" s="26"/>
     </row>
     <row r="131" spans="3:62">
-      <c r="C131" s="11"/>
+      <c r="C131" s="10"/>
       <c r="E131" s="1"/>
-      <c r="F131" s="13"/>
-      <c r="G131" s="13"/>
+      <c r="F131" s="12"/>
+      <c r="G131" s="12"/>
       <c r="H131" s="1"/>
       <c r="I131" s="1"/>
-      <c r="J131" s="21"/>
+      <c r="J131" s="4"/>
       <c r="P131" s="1"/>
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
@@ -10375,21 +9430,21 @@
       <c r="BB131" s="1"/>
       <c r="BC131" s="1"/>
       <c r="BD131" s="1"/>
-      <c r="BE131" s="28"/>
-      <c r="BF131" s="28"/>
+      <c r="BE131" s="26"/>
+      <c r="BF131" s="26"/>
       <c r="BG131" s="1"/>
-      <c r="BH131" s="27"/>
+      <c r="BH131" s="25"/>
       <c r="BI131" s="1"/>
-      <c r="BJ131" s="28"/>
+      <c r="BJ131" s="26"/>
     </row>
     <row r="132" spans="3:62">
-      <c r="C132" s="11"/>
+      <c r="C132" s="10"/>
       <c r="E132" s="1"/>
-      <c r="F132" s="13"/>
-      <c r="G132" s="13"/>
+      <c r="F132" s="12"/>
+      <c r="G132" s="12"/>
       <c r="H132" s="1"/>
       <c r="I132" s="1"/>
-      <c r="J132" s="21"/>
+      <c r="J132" s="4"/>
       <c r="P132" s="1"/>
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
@@ -10425,21 +9480,21 @@
       <c r="BB132" s="1"/>
       <c r="BC132" s="1"/>
       <c r="BD132" s="1"/>
-      <c r="BE132" s="28"/>
-      <c r="BF132" s="28"/>
+      <c r="BE132" s="26"/>
+      <c r="BF132" s="26"/>
       <c r="BG132" s="1"/>
-      <c r="BH132" s="27"/>
+      <c r="BH132" s="25"/>
       <c r="BI132" s="1"/>
-      <c r="BJ132" s="28"/>
+      <c r="BJ132" s="26"/>
     </row>
     <row r="133" spans="3:62">
-      <c r="C133" s="11"/>
+      <c r="C133" s="10"/>
       <c r="E133" s="1"/>
-      <c r="F133" s="13"/>
-      <c r="G133" s="13"/>
+      <c r="F133" s="12"/>
+      <c r="G133" s="12"/>
       <c r="H133" s="1"/>
       <c r="I133" s="1"/>
-      <c r="J133" s="21"/>
+      <c r="J133" s="4"/>
       <c r="P133" s="1"/>
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
@@ -10475,21 +9530,21 @@
       <c r="BB133" s="1"/>
       <c r="BC133" s="1"/>
       <c r="BD133" s="1"/>
-      <c r="BE133" s="28"/>
-      <c r="BF133" s="28"/>
+      <c r="BE133" s="26"/>
+      <c r="BF133" s="26"/>
       <c r="BG133" s="1"/>
-      <c r="BH133" s="27"/>
+      <c r="BH133" s="25"/>
       <c r="BI133" s="1"/>
-      <c r="BJ133" s="28"/>
+      <c r="BJ133" s="26"/>
     </row>
     <row r="134" spans="3:62">
-      <c r="C134" s="11"/>
+      <c r="C134" s="10"/>
       <c r="E134" s="1"/>
-      <c r="F134" s="13"/>
-      <c r="G134" s="13"/>
+      <c r="F134" s="12"/>
+      <c r="G134" s="12"/>
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
-      <c r="J134" s="21"/>
+      <c r="J134" s="4"/>
       <c r="P134" s="1"/>
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
@@ -10525,21 +9580,21 @@
       <c r="BB134" s="1"/>
       <c r="BC134" s="1"/>
       <c r="BD134" s="1"/>
-      <c r="BE134" s="28"/>
-      <c r="BF134" s="28"/>
+      <c r="BE134" s="26"/>
+      <c r="BF134" s="26"/>
       <c r="BG134" s="1"/>
-      <c r="BH134" s="27"/>
+      <c r="BH134" s="25"/>
       <c r="BI134" s="1"/>
-      <c r="BJ134" s="28"/>
+      <c r="BJ134" s="26"/>
     </row>
     <row r="135" spans="3:62">
-      <c r="C135" s="11"/>
+      <c r="C135" s="10"/>
       <c r="E135" s="1"/>
-      <c r="F135" s="13"/>
-      <c r="G135" s="13"/>
+      <c r="F135" s="12"/>
+      <c r="G135" s="12"/>
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
-      <c r="J135" s="21"/>
+      <c r="J135" s="4"/>
       <c r="P135" s="1"/>
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
@@ -10575,21 +9630,21 @@
       <c r="BB135" s="1"/>
       <c r="BC135" s="1"/>
       <c r="BD135" s="1"/>
-      <c r="BE135" s="28"/>
-      <c r="BF135" s="28"/>
+      <c r="BE135" s="26"/>
+      <c r="BF135" s="26"/>
       <c r="BG135" s="1"/>
-      <c r="BH135" s="27"/>
+      <c r="BH135" s="25"/>
       <c r="BI135" s="1"/>
-      <c r="BJ135" s="28"/>
+      <c r="BJ135" s="26"/>
     </row>
     <row r="136" spans="3:62">
-      <c r="C136" s="11"/>
+      <c r="C136" s="10"/>
       <c r="E136" s="1"/>
-      <c r="F136" s="13"/>
-      <c r="G136" s="13"/>
+      <c r="F136" s="12"/>
+      <c r="G136" s="12"/>
       <c r="H136" s="1"/>
       <c r="I136" s="1"/>
-      <c r="J136" s="21"/>
+      <c r="J136" s="4"/>
       <c r="AA136" s="1"/>
       <c r="AU136" s="1"/>
       <c r="AV136" s="1"/>
@@ -10601,21 +9656,21 @@
       <c r="BB136" s="1"/>
       <c r="BC136" s="1"/>
       <c r="BD136" s="1"/>
-      <c r="BE136" s="28"/>
-      <c r="BF136" s="28"/>
+      <c r="BE136" s="26"/>
+      <c r="BF136" s="26"/>
       <c r="BG136" s="1"/>
-      <c r="BH136" s="27"/>
+      <c r="BH136" s="25"/>
       <c r="BI136" s="1"/>
-      <c r="BJ136" s="28"/>
+      <c r="BJ136" s="26"/>
     </row>
     <row r="137" spans="3:62">
-      <c r="C137" s="11"/>
+      <c r="C137" s="10"/>
       <c r="E137" s="1"/>
-      <c r="F137" s="13"/>
-      <c r="G137" s="13"/>
+      <c r="F137" s="12"/>
+      <c r="G137" s="12"/>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
-      <c r="J137" s="21"/>
+      <c r="J137" s="4"/>
       <c r="AA137" s="1"/>
       <c r="AU137" s="1"/>
       <c r="AV137" s="1"/>
@@ -10627,21 +9682,21 @@
       <c r="BB137" s="1"/>
       <c r="BC137" s="1"/>
       <c r="BD137" s="1"/>
-      <c r="BE137" s="28"/>
-      <c r="BF137" s="28"/>
+      <c r="BE137" s="26"/>
+      <c r="BF137" s="26"/>
       <c r="BG137" s="1"/>
-      <c r="BH137" s="27"/>
+      <c r="BH137" s="25"/>
       <c r="BI137" s="1"/>
-      <c r="BJ137" s="28"/>
+      <c r="BJ137" s="26"/>
     </row>
     <row r="138" spans="3:62">
-      <c r="C138" s="11"/>
+      <c r="C138" s="10"/>
       <c r="E138" s="1"/>
-      <c r="F138" s="13"/>
-      <c r="G138" s="13"/>
+      <c r="F138" s="12"/>
+      <c r="G138" s="12"/>
       <c r="H138" s="1"/>
       <c r="I138" s="1"/>
-      <c r="J138" s="21"/>
+      <c r="J138" s="4"/>
       <c r="AA138" s="1"/>
       <c r="AU138" s="1"/>
       <c r="AV138" s="1"/>
@@ -10653,21 +9708,21 @@
       <c r="BB138" s="1"/>
       <c r="BC138" s="1"/>
       <c r="BD138" s="1"/>
-      <c r="BE138" s="28"/>
-      <c r="BF138" s="28"/>
+      <c r="BE138" s="26"/>
+      <c r="BF138" s="26"/>
       <c r="BG138" s="1"/>
-      <c r="BH138" s="27"/>
+      <c r="BH138" s="25"/>
       <c r="BI138" s="1"/>
-      <c r="BJ138" s="28"/>
+      <c r="BJ138" s="26"/>
     </row>
     <row r="139" spans="3:62">
-      <c r="C139" s="11"/>
+      <c r="C139" s="10"/>
       <c r="E139" s="1"/>
-      <c r="F139" s="13"/>
-      <c r="G139" s="13"/>
+      <c r="F139" s="12"/>
+      <c r="G139" s="12"/>
       <c r="H139" s="1"/>
       <c r="I139" s="1"/>
-      <c r="J139" s="21"/>
+      <c r="J139" s="4"/>
       <c r="AA139" s="1"/>
       <c r="AU139" s="1"/>
       <c r="AV139" s="1"/>
@@ -10679,21 +9734,21 @@
       <c r="BB139" s="1"/>
       <c r="BC139" s="1"/>
       <c r="BD139" s="1"/>
-      <c r="BE139" s="28"/>
-      <c r="BF139" s="28"/>
+      <c r="BE139" s="26"/>
+      <c r="BF139" s="26"/>
       <c r="BG139" s="1"/>
-      <c r="BH139" s="27"/>
+      <c r="BH139" s="25"/>
       <c r="BI139" s="1"/>
-      <c r="BJ139" s="28"/>
+      <c r="BJ139" s="26"/>
     </row>
     <row r="140" spans="3:62">
-      <c r="C140" s="11"/>
+      <c r="C140" s="10"/>
       <c r="E140" s="1"/>
-      <c r="F140" s="13"/>
-      <c r="G140" s="13"/>
+      <c r="F140" s="12"/>
+      <c r="G140" s="12"/>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
-      <c r="J140" s="21"/>
+      <c r="J140" s="4"/>
       <c r="AA140" s="1"/>
       <c r="AU140" s="1"/>
       <c r="AV140" s="1"/>
@@ -10705,21 +9760,21 @@
       <c r="BB140" s="1"/>
       <c r="BC140" s="1"/>
       <c r="BD140" s="1"/>
-      <c r="BE140" s="28"/>
-      <c r="BF140" s="28"/>
+      <c r="BE140" s="26"/>
+      <c r="BF140" s="26"/>
       <c r="BG140" s="1"/>
-      <c r="BH140" s="27"/>
+      <c r="BH140" s="25"/>
       <c r="BI140" s="1"/>
-      <c r="BJ140" s="28"/>
+      <c r="BJ140" s="26"/>
     </row>
     <row r="141" spans="3:62">
-      <c r="C141" s="11"/>
+      <c r="C141" s="10"/>
       <c r="E141" s="1"/>
-      <c r="F141" s="13"/>
-      <c r="G141" s="13"/>
+      <c r="F141" s="12"/>
+      <c r="G141" s="12"/>
       <c r="H141" s="1"/>
       <c r="I141" s="1"/>
-      <c r="J141" s="21"/>
+      <c r="J141" s="4"/>
       <c r="AA141" s="1"/>
       <c r="AU141" s="1"/>
       <c r="AV141" s="1"/>
@@ -10731,21 +9786,21 @@
       <c r="BB141" s="1"/>
       <c r="BC141" s="1"/>
       <c r="BD141" s="1"/>
-      <c r="BE141" s="28"/>
-      <c r="BF141" s="28"/>
+      <c r="BE141" s="26"/>
+      <c r="BF141" s="26"/>
       <c r="BG141" s="1"/>
-      <c r="BH141" s="27"/>
+      <c r="BH141" s="25"/>
       <c r="BI141" s="1"/>
-      <c r="BJ141" s="28"/>
+      <c r="BJ141" s="26"/>
     </row>
     <row r="142" spans="3:62">
-      <c r="C142" s="11"/>
+      <c r="C142" s="10"/>
       <c r="E142" s="1"/>
-      <c r="F142" s="13"/>
-      <c r="G142" s="13"/>
+      <c r="F142" s="12"/>
+      <c r="G142" s="12"/>
       <c r="H142" s="1"/>
       <c r="I142" s="1"/>
-      <c r="J142" s="21"/>
+      <c r="J142" s="4"/>
       <c r="AA142" s="1"/>
       <c r="AU142" s="1"/>
       <c r="AV142" s="1"/>
@@ -10757,21 +9812,21 @@
       <c r="BB142" s="1"/>
       <c r="BC142" s="1"/>
       <c r="BD142" s="1"/>
-      <c r="BE142" s="28"/>
-      <c r="BF142" s="28"/>
+      <c r="BE142" s="26"/>
+      <c r="BF142" s="26"/>
       <c r="BG142" s="1"/>
-      <c r="BH142" s="27"/>
+      <c r="BH142" s="25"/>
       <c r="BI142" s="1"/>
-      <c r="BJ142" s="28"/>
+      <c r="BJ142" s="26"/>
     </row>
     <row r="143" spans="3:62">
-      <c r="C143" s="11"/>
+      <c r="C143" s="10"/>
       <c r="E143" s="1"/>
-      <c r="F143" s="13"/>
-      <c r="G143" s="13"/>
+      <c r="F143" s="12"/>
+      <c r="G143" s="12"/>
       <c r="H143" s="1"/>
       <c r="I143" s="1"/>
-      <c r="J143" s="21"/>
+      <c r="J143" s="4"/>
       <c r="AA143" s="1"/>
       <c r="AU143" s="1"/>
       <c r="AV143" s="1"/>
@@ -10783,21 +9838,21 @@
       <c r="BB143" s="1"/>
       <c r="BC143" s="1"/>
       <c r="BD143" s="1"/>
-      <c r="BE143" s="28"/>
-      <c r="BF143" s="28"/>
+      <c r="BE143" s="26"/>
+      <c r="BF143" s="26"/>
       <c r="BG143" s="1"/>
-      <c r="BH143" s="27"/>
+      <c r="BH143" s="25"/>
       <c r="BI143" s="1"/>
-      <c r="BJ143" s="28"/>
+      <c r="BJ143" s="26"/>
     </row>
     <row r="144" spans="3:62">
-      <c r="C144" s="11"/>
+      <c r="C144" s="10"/>
       <c r="E144" s="1"/>
-      <c r="F144" s="13"/>
-      <c r="G144" s="13"/>
+      <c r="F144" s="12"/>
+      <c r="G144" s="12"/>
       <c r="H144" s="1"/>
       <c r="I144" s="1"/>
-      <c r="J144" s="21"/>
+      <c r="J144" s="4"/>
       <c r="AA144" s="1"/>
       <c r="AU144" s="1"/>
       <c r="AV144" s="1"/>
@@ -10809,21 +9864,21 @@
       <c r="BB144" s="1"/>
       <c r="BC144" s="1"/>
       <c r="BD144" s="1"/>
-      <c r="BE144" s="28"/>
-      <c r="BF144" s="28"/>
+      <c r="BE144" s="26"/>
+      <c r="BF144" s="26"/>
       <c r="BG144" s="1"/>
-      <c r="BH144" s="27"/>
+      <c r="BH144" s="25"/>
       <c r="BI144" s="1"/>
-      <c r="BJ144" s="28"/>
+      <c r="BJ144" s="26"/>
     </row>
     <row r="145" spans="3:62">
-      <c r="C145" s="11"/>
+      <c r="C145" s="10"/>
       <c r="E145" s="1"/>
-      <c r="F145" s="13"/>
-      <c r="G145" s="13"/>
+      <c r="F145" s="12"/>
+      <c r="G145" s="12"/>
       <c r="H145" s="1"/>
       <c r="I145" s="1"/>
-      <c r="J145" s="21"/>
+      <c r="J145" s="4"/>
       <c r="AA145" s="1"/>
       <c r="AU145" s="1"/>
       <c r="AV145" s="1"/>
@@ -10835,21 +9890,21 @@
       <c r="BB145" s="1"/>
       <c r="BC145" s="1"/>
       <c r="BD145" s="1"/>
-      <c r="BE145" s="28"/>
-      <c r="BF145" s="28"/>
+      <c r="BE145" s="26"/>
+      <c r="BF145" s="26"/>
       <c r="BG145" s="1"/>
-      <c r="BH145" s="27"/>
+      <c r="BH145" s="25"/>
       <c r="BI145" s="1"/>
-      <c r="BJ145" s="28"/>
+      <c r="BJ145" s="26"/>
     </row>
     <row r="146" spans="3:62">
-      <c r="C146" s="11"/>
+      <c r="C146" s="10"/>
       <c r="E146" s="1"/>
-      <c r="F146" s="13"/>
-      <c r="G146" s="13"/>
+      <c r="F146" s="12"/>
+      <c r="G146" s="12"/>
       <c r="H146" s="1"/>
       <c r="I146" s="1"/>
-      <c r="J146" s="21"/>
+      <c r="J146" s="4"/>
       <c r="AA146" s="1"/>
       <c r="AU146" s="1"/>
       <c r="AV146" s="1"/>
@@ -10861,21 +9916,21 @@
       <c r="BB146" s="1"/>
       <c r="BC146" s="1"/>
       <c r="BD146" s="1"/>
-      <c r="BE146" s="28"/>
-      <c r="BF146" s="28"/>
+      <c r="BE146" s="26"/>
+      <c r="BF146" s="26"/>
       <c r="BG146" s="1"/>
-      <c r="BH146" s="27"/>
+      <c r="BH146" s="25"/>
       <c r="BI146" s="1"/>
-      <c r="BJ146" s="28"/>
+      <c r="BJ146" s="26"/>
     </row>
     <row r="147" spans="3:62">
-      <c r="C147" s="11"/>
+      <c r="C147" s="10"/>
       <c r="E147" s="1"/>
-      <c r="F147" s="13"/>
-      <c r="G147" s="13"/>
+      <c r="F147" s="12"/>
+      <c r="G147" s="12"/>
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
-      <c r="J147" s="21"/>
+      <c r="J147" s="4"/>
       <c r="AA147" s="1"/>
       <c r="AU147" s="1"/>
       <c r="AV147" s="1"/>
@@ -10887,21 +9942,21 @@
       <c r="BB147" s="1"/>
       <c r="BC147" s="1"/>
       <c r="BD147" s="1"/>
-      <c r="BE147" s="28"/>
-      <c r="BF147" s="28"/>
+      <c r="BE147" s="26"/>
+      <c r="BF147" s="26"/>
       <c r="BG147" s="1"/>
-      <c r="BH147" s="27"/>
+      <c r="BH147" s="25"/>
       <c r="BI147" s="1"/>
-      <c r="BJ147" s="28"/>
+      <c r="BJ147" s="26"/>
     </row>
     <row r="148" spans="3:62">
-      <c r="C148" s="11"/>
+      <c r="C148" s="10"/>
       <c r="E148" s="1"/>
-      <c r="F148" s="13"/>
-      <c r="G148" s="13"/>
+      <c r="F148" s="12"/>
+      <c r="G148" s="12"/>
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
-      <c r="J148" s="21"/>
+      <c r="J148" s="4"/>
       <c r="AA148" s="1"/>
       <c r="AU148" s="1"/>
       <c r="AV148" s="1"/>
@@ -10913,21 +9968,21 @@
       <c r="BB148" s="1"/>
       <c r="BC148" s="1"/>
       <c r="BD148" s="1"/>
-      <c r="BE148" s="28"/>
-      <c r="BF148" s="28"/>
+      <c r="BE148" s="26"/>
+      <c r="BF148" s="26"/>
       <c r="BG148" s="1"/>
-      <c r="BH148" s="27"/>
+      <c r="BH148" s="25"/>
       <c r="BI148" s="1"/>
-      <c r="BJ148" s="28"/>
+      <c r="BJ148" s="26"/>
     </row>
     <row r="149" spans="3:62">
-      <c r="C149" s="11"/>
+      <c r="C149" s="10"/>
       <c r="E149" s="1"/>
-      <c r="F149" s="13"/>
-      <c r="G149" s="13"/>
+      <c r="F149" s="12"/>
+      <c r="G149" s="12"/>
       <c r="H149" s="1"/>
       <c r="I149" s="1"/>
-      <c r="J149" s="21"/>
+      <c r="J149" s="4"/>
       <c r="AA149" s="1"/>
       <c r="AU149" s="1"/>
       <c r="AV149" s="1"/>
@@ -10939,21 +9994,21 @@
       <c r="BB149" s="1"/>
       <c r="BC149" s="1"/>
       <c r="BD149" s="1"/>
-      <c r="BE149" s="28"/>
-      <c r="BF149" s="28"/>
+      <c r="BE149" s="26"/>
+      <c r="BF149" s="26"/>
       <c r="BG149" s="1"/>
-      <c r="BH149" s="27"/>
+      <c r="BH149" s="25"/>
       <c r="BI149" s="1"/>
-      <c r="BJ149" s="28"/>
+      <c r="BJ149" s="26"/>
     </row>
     <row r="150" spans="3:62">
-      <c r="C150" s="11"/>
+      <c r="C150" s="10"/>
       <c r="E150" s="1"/>
-      <c r="F150" s="13"/>
-      <c r="G150" s="13"/>
+      <c r="F150" s="12"/>
+      <c r="G150" s="12"/>
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
-      <c r="J150" s="21"/>
+      <c r="J150" s="4"/>
       <c r="AA150" s="1"/>
       <c r="AU150" s="1"/>
       <c r="AV150" s="1"/>
@@ -10965,21 +10020,21 @@
       <c r="BB150" s="1"/>
       <c r="BC150" s="1"/>
       <c r="BD150" s="1"/>
-      <c r="BE150" s="28"/>
-      <c r="BF150" s="28"/>
+      <c r="BE150" s="26"/>
+      <c r="BF150" s="26"/>
       <c r="BG150" s="1"/>
-      <c r="BH150" s="27"/>
+      <c r="BH150" s="25"/>
       <c r="BI150" s="1"/>
-      <c r="BJ150" s="28"/>
+      <c r="BJ150" s="26"/>
     </row>
     <row r="151" spans="3:62">
-      <c r="C151" s="11"/>
+      <c r="C151" s="10"/>
       <c r="E151" s="1"/>
-      <c r="F151" s="13"/>
-      <c r="G151" s="13"/>
+      <c r="F151" s="12"/>
+      <c r="G151" s="12"/>
       <c r="H151" s="1"/>
       <c r="I151" s="1"/>
-      <c r="J151" s="21"/>
+      <c r="J151" s="4"/>
       <c r="AA151" s="1"/>
       <c r="AU151" s="1"/>
       <c r="AV151" s="1"/>
@@ -10991,21 +10046,21 @@
       <c r="BB151" s="1"/>
       <c r="BC151" s="1"/>
       <c r="BD151" s="1"/>
-      <c r="BE151" s="28"/>
-      <c r="BF151" s="28"/>
+      <c r="BE151" s="26"/>
+      <c r="BF151" s="26"/>
       <c r="BG151" s="1"/>
-      <c r="BH151" s="27"/>
+      <c r="BH151" s="25"/>
       <c r="BI151" s="1"/>
-      <c r="BJ151" s="28"/>
+      <c r="BJ151" s="26"/>
     </row>
     <row r="152" spans="3:62">
-      <c r="C152" s="11"/>
+      <c r="C152" s="10"/>
       <c r="E152" s="1"/>
-      <c r="F152" s="13"/>
-      <c r="G152" s="13"/>
+      <c r="F152" s="12"/>
+      <c r="G152" s="12"/>
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
-      <c r="J152" s="21"/>
+      <c r="J152" s="4"/>
       <c r="AA152" s="1"/>
       <c r="AU152" s="1"/>
       <c r="AV152" s="1"/>
@@ -11017,21 +10072,21 @@
       <c r="BB152" s="1"/>
       <c r="BC152" s="1"/>
       <c r="BD152" s="1"/>
-      <c r="BE152" s="28"/>
-      <c r="BF152" s="28"/>
+      <c r="BE152" s="26"/>
+      <c r="BF152" s="26"/>
       <c r="BG152" s="1"/>
-      <c r="BH152" s="27"/>
+      <c r="BH152" s="25"/>
       <c r="BI152" s="1"/>
-      <c r="BJ152" s="28"/>
+      <c r="BJ152" s="26"/>
     </row>
     <row r="153" spans="3:62">
-      <c r="C153" s="11"/>
+      <c r="C153" s="10"/>
       <c r="E153" s="1"/>
-      <c r="F153" s="13"/>
-      <c r="G153" s="13"/>
+      <c r="F153" s="12"/>
+      <c r="G153" s="12"/>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
-      <c r="J153" s="21"/>
+      <c r="J153" s="4"/>
       <c r="AA153" s="1"/>
       <c r="AU153" s="1"/>
       <c r="AV153" s="1"/>
@@ -11043,21 +10098,21 @@
       <c r="BB153" s="1"/>
       <c r="BC153" s="1"/>
       <c r="BD153" s="1"/>
-      <c r="BE153" s="28"/>
-      <c r="BF153" s="28"/>
+      <c r="BE153" s="26"/>
+      <c r="BF153" s="26"/>
       <c r="BG153" s="1"/>
-      <c r="BH153" s="27"/>
+      <c r="BH153" s="25"/>
       <c r="BI153" s="1"/>
-      <c r="BJ153" s="28"/>
+      <c r="BJ153" s="26"/>
     </row>
     <row r="154" spans="3:62">
-      <c r="C154" s="11"/>
+      <c r="C154" s="10"/>
       <c r="E154" s="1"/>
-      <c r="F154" s="13"/>
-      <c r="G154" s="13"/>
+      <c r="F154" s="12"/>
+      <c r="G154" s="12"/>
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
-      <c r="J154" s="21"/>
+      <c r="J154" s="4"/>
       <c r="AA154" s="1"/>
       <c r="AU154" s="1"/>
       <c r="AV154" s="1"/>
@@ -11069,21 +10124,21 @@
       <c r="BB154" s="1"/>
       <c r="BC154" s="1"/>
       <c r="BD154" s="1"/>
-      <c r="BE154" s="28"/>
-      <c r="BF154" s="28"/>
+      <c r="BE154" s="26"/>
+      <c r="BF154" s="26"/>
       <c r="BG154" s="1"/>
-      <c r="BH154" s="27"/>
+      <c r="BH154" s="25"/>
       <c r="BI154" s="1"/>
-      <c r="BJ154" s="28"/>
+      <c r="BJ154" s="26"/>
     </row>
     <row r="155" spans="3:62">
-      <c r="C155" s="11"/>
+      <c r="C155" s="10"/>
       <c r="E155" s="1"/>
-      <c r="F155" s="13"/>
-      <c r="G155" s="13"/>
+      <c r="F155" s="12"/>
+      <c r="G155" s="12"/>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
-      <c r="J155" s="21"/>
+      <c r="J155" s="4"/>
       <c r="AA155" s="1"/>
       <c r="AU155" s="1"/>
       <c r="AV155" s="1"/>
@@ -11095,21 +10150,21 @@
       <c r="BB155" s="1"/>
       <c r="BC155" s="1"/>
       <c r="BD155" s="1"/>
-      <c r="BE155" s="28"/>
-      <c r="BF155" s="28"/>
+      <c r="BE155" s="26"/>
+      <c r="BF155" s="26"/>
       <c r="BG155" s="1"/>
-      <c r="BH155" s="27"/>
+      <c r="BH155" s="25"/>
       <c r="BI155" s="1"/>
-      <c r="BJ155" s="28"/>
+      <c r="BJ155" s="26"/>
     </row>
     <row r="156" spans="3:62">
-      <c r="C156" s="11"/>
+      <c r="C156" s="10"/>
       <c r="E156" s="1"/>
-      <c r="F156" s="13"/>
-      <c r="G156" s="13"/>
+      <c r="F156" s="12"/>
+      <c r="G156" s="12"/>
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
-      <c r="J156" s="21"/>
+      <c r="J156" s="4"/>
       <c r="AA156" s="1"/>
       <c r="AU156" s="1"/>
       <c r="AV156" s="1"/>
@@ -11121,21 +10176,21 @@
       <c r="BB156" s="1"/>
       <c r="BC156" s="1"/>
       <c r="BD156" s="1"/>
-      <c r="BE156" s="28"/>
-      <c r="BF156" s="28"/>
+      <c r="BE156" s="26"/>
+      <c r="BF156" s="26"/>
       <c r="BG156" s="1"/>
-      <c r="BH156" s="27"/>
+      <c r="BH156" s="25"/>
       <c r="BI156" s="1"/>
-      <c r="BJ156" s="28"/>
+      <c r="BJ156" s="26"/>
     </row>
     <row r="157" ht="14.25" customHeight="1" spans="3:62">
-      <c r="C157" s="11"/>
+      <c r="C157" s="10"/>
       <c r="E157" s="1"/>
-      <c r="F157" s="13"/>
-      <c r="G157" s="13"/>
+      <c r="F157" s="12"/>
+      <c r="G157" s="12"/>
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
-      <c r="J157" s="21"/>
+      <c r="J157" s="4"/>
       <c r="AA157" s="1"/>
       <c r="AU157" s="1"/>
       <c r="AV157" s="1"/>
@@ -11147,21 +10202,21 @@
       <c r="BB157" s="1"/>
       <c r="BC157" s="1"/>
       <c r="BD157" s="1"/>
-      <c r="BE157" s="28"/>
-      <c r="BF157" s="28"/>
+      <c r="BE157" s="26"/>
+      <c r="BF157" s="26"/>
       <c r="BG157" s="1"/>
-      <c r="BH157" s="27"/>
+      <c r="BH157" s="25"/>
       <c r="BI157" s="1"/>
-      <c r="BJ157" s="28"/>
+      <c r="BJ157" s="26"/>
     </row>
     <row r="158" spans="3:62">
-      <c r="C158" s="11"/>
+      <c r="C158" s="10"/>
       <c r="E158" s="1"/>
-      <c r="F158" s="13"/>
-      <c r="G158" s="13"/>
+      <c r="F158" s="12"/>
+      <c r="G158" s="12"/>
       <c r="H158" s="1"/>
       <c r="I158" s="1"/>
-      <c r="J158" s="21"/>
+      <c r="J158" s="4"/>
       <c r="AA158" s="1"/>
       <c r="AU158" s="1"/>
       <c r="AV158" s="1"/>
@@ -11173,21 +10228,21 @@
       <c r="BB158" s="1"/>
       <c r="BC158" s="1"/>
       <c r="BD158" s="1"/>
-      <c r="BE158" s="28"/>
-      <c r="BF158" s="28"/>
+      <c r="BE158" s="26"/>
+      <c r="BF158" s="26"/>
       <c r="BG158" s="1"/>
-      <c r="BH158" s="27"/>
+      <c r="BH158" s="25"/>
       <c r="BI158" s="1"/>
-      <c r="BJ158" s="28"/>
+      <c r="BJ158" s="26"/>
     </row>
     <row r="159" spans="3:62">
-      <c r="C159" s="11"/>
+      <c r="C159" s="10"/>
       <c r="E159" s="1"/>
-      <c r="F159" s="13"/>
-      <c r="G159" s="13"/>
+      <c r="F159" s="12"/>
+      <c r="G159" s="12"/>
       <c r="H159" s="1"/>
       <c r="I159" s="1"/>
-      <c r="J159" s="21"/>
+      <c r="J159" s="4"/>
       <c r="AA159" s="1"/>
       <c r="AU159" s="1"/>
       <c r="AV159" s="1"/>
@@ -11199,21 +10254,21 @@
       <c r="BB159" s="1"/>
       <c r="BC159" s="1"/>
       <c r="BD159" s="1"/>
-      <c r="BE159" s="28"/>
-      <c r="BF159" s="28"/>
+      <c r="BE159" s="26"/>
+      <c r="BF159" s="26"/>
       <c r="BG159" s="1"/>
-      <c r="BH159" s="27"/>
+      <c r="BH159" s="25"/>
       <c r="BI159" s="1"/>
-      <c r="BJ159" s="28"/>
+      <c r="BJ159" s="26"/>
     </row>
     <row r="160" spans="3:62">
-      <c r="C160" s="11"/>
+      <c r="C160" s="10"/>
       <c r="E160" s="1"/>
-      <c r="F160" s="13"/>
-      <c r="G160" s="13"/>
+      <c r="F160" s="12"/>
+      <c r="G160" s="12"/>
       <c r="H160" s="1"/>
       <c r="I160" s="1"/>
-      <c r="J160" s="21"/>
+      <c r="J160" s="4"/>
       <c r="AA160" s="1"/>
       <c r="AU160" s="1"/>
       <c r="AV160" s="1"/>
@@ -11225,21 +10280,21 @@
       <c r="BB160" s="1"/>
       <c r="BC160" s="1"/>
       <c r="BD160" s="1"/>
-      <c r="BE160" s="28"/>
-      <c r="BF160" s="28"/>
+      <c r="BE160" s="26"/>
+      <c r="BF160" s="26"/>
       <c r="BG160" s="1"/>
-      <c r="BH160" s="27"/>
+      <c r="BH160" s="25"/>
       <c r="BI160" s="1"/>
-      <c r="BJ160" s="28"/>
+      <c r="BJ160" s="26"/>
     </row>
     <row r="161" spans="3:62">
-      <c r="C161" s="11"/>
+      <c r="C161" s="10"/>
       <c r="E161" s="1"/>
-      <c r="F161" s="13"/>
-      <c r="G161" s="13"/>
+      <c r="F161" s="12"/>
+      <c r="G161" s="12"/>
       <c r="H161" s="1"/>
       <c r="I161" s="1"/>
-      <c r="J161" s="21"/>
+      <c r="J161" s="4"/>
       <c r="AA161" s="1"/>
       <c r="AU161" s="1"/>
       <c r="AV161" s="1"/>
@@ -11251,21 +10306,21 @@
       <c r="BB161" s="1"/>
       <c r="BC161" s="1"/>
       <c r="BD161" s="1"/>
-      <c r="BE161" s="28"/>
-      <c r="BF161" s="28"/>
+      <c r="BE161" s="26"/>
+      <c r="BF161" s="26"/>
       <c r="BG161" s="1"/>
-      <c r="BH161" s="27"/>
+      <c r="BH161" s="25"/>
       <c r="BI161" s="1"/>
-      <c r="BJ161" s="28"/>
+      <c r="BJ161" s="26"/>
     </row>
     <row r="162" ht="15.75" customHeight="1" spans="3:62">
-      <c r="C162" s="11"/>
+      <c r="C162" s="10"/>
       <c r="E162" s="1"/>
-      <c r="F162" s="13"/>
-      <c r="G162" s="13"/>
+      <c r="F162" s="12"/>
+      <c r="G162" s="12"/>
       <c r="H162" s="1"/>
       <c r="I162" s="1"/>
-      <c r="J162" s="21"/>
+      <c r="J162" s="4"/>
       <c r="AA162" s="1"/>
       <c r="AU162" s="1"/>
       <c r="AV162" s="1"/>
@@ -11277,21 +10332,21 @@
       <c r="BB162" s="1"/>
       <c r="BC162" s="1"/>
       <c r="BD162" s="1"/>
-      <c r="BE162" s="28"/>
-      <c r="BF162" s="28"/>
+      <c r="BE162" s="26"/>
+      <c r="BF162" s="26"/>
       <c r="BG162" s="1"/>
-      <c r="BH162" s="27"/>
+      <c r="BH162" s="25"/>
       <c r="BI162" s="1"/>
-      <c r="BJ162" s="28"/>
+      <c r="BJ162" s="26"/>
     </row>
     <row r="163" ht="14.25" customHeight="1" spans="3:62">
-      <c r="C163" s="11"/>
+      <c r="C163" s="10"/>
       <c r="E163" s="1"/>
-      <c r="F163" s="13"/>
-      <c r="G163" s="13"/>
+      <c r="F163" s="12"/>
+      <c r="G163" s="12"/>
       <c r="H163" s="1"/>
       <c r="I163" s="1"/>
-      <c r="J163" s="21"/>
+      <c r="J163" s="4"/>
       <c r="AA163" s="1"/>
       <c r="AU163" s="1"/>
       <c r="AV163" s="1"/>
@@ -11303,21 +10358,21 @@
       <c r="BB163" s="1"/>
       <c r="BC163" s="1"/>
       <c r="BD163" s="1"/>
-      <c r="BE163" s="28"/>
-      <c r="BF163" s="28"/>
+      <c r="BE163" s="26"/>
+      <c r="BF163" s="26"/>
       <c r="BG163" s="1"/>
-      <c r="BH163" s="27"/>
+      <c r="BH163" s="25"/>
       <c r="BI163" s="1"/>
-      <c r="BJ163" s="28"/>
+      <c r="BJ163" s="26"/>
     </row>
     <row r="164" spans="3:62">
-      <c r="C164" s="11"/>
+      <c r="C164" s="10"/>
       <c r="E164" s="1"/>
-      <c r="F164" s="13"/>
-      <c r="G164" s="13"/>
+      <c r="F164" s="12"/>
+      <c r="G164" s="12"/>
       <c r="H164" s="1"/>
       <c r="I164" s="1"/>
-      <c r="J164" s="21"/>
+      <c r="J164" s="4"/>
       <c r="AA164" s="1"/>
       <c r="AU164" s="1"/>
       <c r="AV164" s="1"/>
@@ -11329,21 +10384,21 @@
       <c r="BB164" s="1"/>
       <c r="BC164" s="1"/>
       <c r="BD164" s="1"/>
-      <c r="BE164" s="28"/>
-      <c r="BF164" s="28"/>
+      <c r="BE164" s="26"/>
+      <c r="BF164" s="26"/>
       <c r="BG164" s="1"/>
-      <c r="BH164" s="27"/>
+      <c r="BH164" s="25"/>
       <c r="BI164" s="1"/>
-      <c r="BJ164" s="28"/>
+      <c r="BJ164" s="26"/>
     </row>
     <row r="165" spans="3:62">
-      <c r="C165" s="11"/>
+      <c r="C165" s="10"/>
       <c r="E165" s="1"/>
-      <c r="F165" s="13"/>
-      <c r="G165" s="13"/>
+      <c r="F165" s="12"/>
+      <c r="G165" s="12"/>
       <c r="H165" s="1"/>
       <c r="I165" s="1"/>
-      <c r="J165" s="21"/>
+      <c r="J165" s="4"/>
       <c r="AA165" s="1"/>
       <c r="AU165" s="1"/>
       <c r="AV165" s="1"/>
@@ -11355,24 +10410,24 @@
       <c r="BB165" s="1"/>
       <c r="BC165" s="1"/>
       <c r="BD165" s="1"/>
-      <c r="BE165" s="28"/>
-      <c r="BF165" s="28"/>
+      <c r="BE165" s="26"/>
+      <c r="BF165" s="26"/>
       <c r="BG165" s="1"/>
-      <c r="BH165" s="27"/>
+      <c r="BH165" s="25"/>
       <c r="BI165" s="1"/>
-      <c r="BJ165" s="28"/>
+      <c r="BJ165" s="26"/>
     </row>
     <row r="166" spans="1:62">
       <c r="A166" s="1"/>
-      <c r="B166" s="7"/>
+      <c r="B166" s="8"/>
       <c r="C166" s="1"/>
-      <c r="D166" s="7"/>
+      <c r="D166" s="8"/>
       <c r="E166" s="1"/>
-      <c r="F166" s="13"/>
-      <c r="G166" s="13"/>
+      <c r="F166" s="12"/>
+      <c r="G166" s="12"/>
       <c r="H166" s="1"/>
       <c r="I166" s="1"/>
-      <c r="J166" s="20"/>
+      <c r="J166" s="16"/>
       <c r="AO166" s="1"/>
       <c r="AP166" s="1"/>
       <c r="AU166" s="1"/>
@@ -11385,24 +10440,24 @@
       <c r="BB166" s="1"/>
       <c r="BC166" s="1"/>
       <c r="BD166" s="1"/>
-      <c r="BE166" s="28"/>
-      <c r="BF166" s="28"/>
+      <c r="BE166" s="26"/>
+      <c r="BF166" s="26"/>
       <c r="BG166" s="1"/>
-      <c r="BH166" s="27"/>
+      <c r="BH166" s="25"/>
       <c r="BI166" s="1"/>
-      <c r="BJ166" s="28"/>
+      <c r="BJ166" s="26"/>
     </row>
     <row r="167" spans="1:62">
       <c r="A167" s="1"/>
-      <c r="B167" s="7"/>
+      <c r="B167" s="8"/>
       <c r="C167" s="1"/>
-      <c r="D167" s="7"/>
+      <c r="D167" s="8"/>
       <c r="E167" s="1"/>
-      <c r="F167" s="13"/>
-      <c r="G167" s="13"/>
+      <c r="F167" s="12"/>
+      <c r="G167" s="12"/>
       <c r="H167" s="1"/>
       <c r="I167" s="1"/>
-      <c r="J167" s="20"/>
+      <c r="J167" s="16"/>
       <c r="AO167" s="1"/>
       <c r="AP167" s="1"/>
       <c r="AU167" s="1"/>
@@ -11415,23 +10470,23 @@
       <c r="BB167" s="1"/>
       <c r="BC167" s="1"/>
       <c r="BD167" s="1"/>
-      <c r="BE167" s="28"/>
-      <c r="BF167" s="28"/>
+      <c r="BE167" s="26"/>
+      <c r="BF167" s="26"/>
       <c r="BG167" s="1"/>
-      <c r="BH167" s="27"/>
+      <c r="BH167" s="25"/>
       <c r="BI167" s="1"/>
-      <c r="BJ167" s="28"/>
+      <c r="BJ167" s="26"/>
     </row>
     <row r="168" spans="2:62">
-      <c r="B168" s="7"/>
+      <c r="B168" s="8"/>
       <c r="C168" s="1"/>
-      <c r="D168" s="7"/>
+      <c r="D168" s="8"/>
       <c r="E168" s="1"/>
-      <c r="F168" s="13"/>
-      <c r="G168" s="13"/>
+      <c r="F168" s="12"/>
+      <c r="G168" s="12"/>
       <c r="H168" s="1"/>
       <c r="I168" s="1"/>
-      <c r="J168" s="20"/>
+      <c r="J168" s="16"/>
       <c r="AO168" s="1"/>
       <c r="AP168" s="1"/>
       <c r="AU168" s="1"/>
@@ -11444,24 +10499,24 @@
       <c r="BB168" s="1"/>
       <c r="BC168" s="1"/>
       <c r="BD168" s="1"/>
-      <c r="BE168" s="28"/>
-      <c r="BF168" s="28"/>
+      <c r="BE168" s="26"/>
+      <c r="BF168" s="26"/>
       <c r="BG168" s="1"/>
-      <c r="BH168" s="27"/>
+      <c r="BH168" s="25"/>
       <c r="BI168" s="1"/>
-      <c r="BJ168" s="28"/>
+      <c r="BJ168" s="26"/>
     </row>
     <row r="169" spans="1:62">
       <c r="A169" s="1"/>
-      <c r="B169" s="7"/>
+      <c r="B169" s="8"/>
       <c r="C169" s="1"/>
-      <c r="D169" s="7"/>
+      <c r="D169" s="8"/>
       <c r="E169" s="1"/>
-      <c r="F169" s="13"/>
-      <c r="G169" s="13"/>
+      <c r="F169" s="12"/>
+      <c r="G169" s="12"/>
       <c r="H169" s="1"/>
       <c r="I169" s="1"/>
-      <c r="J169" s="20"/>
+      <c r="J169" s="16"/>
       <c r="AO169" s="1"/>
       <c r="AP169" s="1"/>
       <c r="AU169" s="1"/>
@@ -11474,24 +10529,24 @@
       <c r="BB169" s="1"/>
       <c r="BC169" s="1"/>
       <c r="BD169" s="1"/>
-      <c r="BE169" s="28"/>
-      <c r="BF169" s="28"/>
+      <c r="BE169" s="26"/>
+      <c r="BF169" s="26"/>
       <c r="BG169" s="1"/>
-      <c r="BH169" s="27"/>
+      <c r="BH169" s="25"/>
       <c r="BI169" s="1"/>
-      <c r="BJ169" s="28"/>
+      <c r="BJ169" s="26"/>
     </row>
     <row r="170" spans="1:62">
       <c r="A170" s="1"/>
-      <c r="B170" s="7"/>
+      <c r="B170" s="8"/>
       <c r="C170" s="1"/>
-      <c r="D170" s="7"/>
+      <c r="D170" s="8"/>
       <c r="E170" s="1"/>
-      <c r="F170" s="13"/>
-      <c r="G170" s="13"/>
+      <c r="F170" s="12"/>
+      <c r="G170" s="12"/>
       <c r="H170" s="1"/>
       <c r="I170" s="1"/>
-      <c r="J170" s="20"/>
+      <c r="J170" s="16"/>
       <c r="AO170" s="1"/>
       <c r="AP170" s="1"/>
       <c r="AU170" s="1"/>
@@ -11504,24 +10559,24 @@
       <c r="BB170" s="1"/>
       <c r="BC170" s="1"/>
       <c r="BD170" s="1"/>
-      <c r="BE170" s="28"/>
-      <c r="BF170" s="28"/>
+      <c r="BE170" s="26"/>
+      <c r="BF170" s="26"/>
       <c r="BG170" s="1"/>
-      <c r="BH170" s="27"/>
+      <c r="BH170" s="25"/>
       <c r="BI170" s="1"/>
-      <c r="BJ170" s="28"/>
+      <c r="BJ170" s="26"/>
     </row>
     <row r="171" spans="1:62">
       <c r="A171" s="1"/>
-      <c r="B171" s="7"/>
+      <c r="B171" s="8"/>
       <c r="C171" s="1"/>
-      <c r="D171" s="7"/>
+      <c r="D171" s="8"/>
       <c r="E171" s="1"/>
-      <c r="F171" s="13"/>
-      <c r="G171" s="13"/>
+      <c r="F171" s="12"/>
+      <c r="G171" s="12"/>
       <c r="H171" s="1"/>
       <c r="I171" s="1"/>
-      <c r="J171" s="20"/>
+      <c r="J171" s="16"/>
       <c r="AO171" s="1"/>
       <c r="AP171" s="1"/>
       <c r="AU171" s="1"/>
@@ -11534,24 +10589,24 @@
       <c r="BB171" s="1"/>
       <c r="BC171" s="1"/>
       <c r="BD171" s="1"/>
-      <c r="BE171" s="28"/>
-      <c r="BF171" s="28"/>
+      <c r="BE171" s="26"/>
+      <c r="BF171" s="26"/>
       <c r="BG171" s="1"/>
-      <c r="BH171" s="27"/>
+      <c r="BH171" s="25"/>
       <c r="BI171" s="1"/>
-      <c r="BJ171" s="28"/>
+      <c r="BJ171" s="26"/>
     </row>
     <row r="172" spans="1:62">
       <c r="A172" s="1"/>
-      <c r="B172" s="7"/>
+      <c r="B172" s="8"/>
       <c r="C172" s="1"/>
-      <c r="D172" s="7"/>
+      <c r="D172" s="8"/>
       <c r="E172" s="1"/>
-      <c r="F172" s="13"/>
-      <c r="G172" s="13"/>
+      <c r="F172" s="12"/>
+      <c r="G172" s="12"/>
       <c r="H172" s="1"/>
       <c r="I172" s="1"/>
-      <c r="J172" s="20"/>
+      <c r="J172" s="16"/>
       <c r="AO172" s="1"/>
       <c r="AP172" s="1"/>
       <c r="AU172" s="1"/>
@@ -11564,24 +10619,24 @@
       <c r="BB172" s="1"/>
       <c r="BC172" s="1"/>
       <c r="BD172" s="1"/>
-      <c r="BE172" s="28"/>
-      <c r="BF172" s="28"/>
+      <c r="BE172" s="26"/>
+      <c r="BF172" s="26"/>
       <c r="BG172" s="1"/>
-      <c r="BH172" s="27"/>
+      <c r="BH172" s="25"/>
       <c r="BI172" s="1"/>
-      <c r="BJ172" s="28"/>
+      <c r="BJ172" s="26"/>
     </row>
     <row r="173" spans="1:62">
       <c r="A173" s="1"/>
-      <c r="B173" s="7"/>
+      <c r="B173" s="8"/>
       <c r="C173" s="1"/>
-      <c r="D173" s="7"/>
+      <c r="D173" s="8"/>
       <c r="E173" s="1"/>
-      <c r="F173" s="13"/>
-      <c r="G173" s="13"/>
+      <c r="F173" s="12"/>
+      <c r="G173" s="12"/>
       <c r="H173" s="1"/>
       <c r="I173" s="1"/>
-      <c r="J173" s="20"/>
+      <c r="J173" s="16"/>
       <c r="AO173" s="1"/>
       <c r="AP173" s="1"/>
       <c r="AU173" s="1"/>
@@ -11594,24 +10649,24 @@
       <c r="BB173" s="1"/>
       <c r="BC173" s="1"/>
       <c r="BD173" s="1"/>
-      <c r="BE173" s="28"/>
-      <c r="BF173" s="28"/>
+      <c r="BE173" s="26"/>
+      <c r="BF173" s="26"/>
       <c r="BG173" s="1"/>
-      <c r="BH173" s="27"/>
+      <c r="BH173" s="25"/>
       <c r="BI173" s="1"/>
-      <c r="BJ173" s="28"/>
+      <c r="BJ173" s="26"/>
     </row>
     <row r="174" spans="1:62">
       <c r="A174" s="1"/>
-      <c r="B174" s="7"/>
+      <c r="B174" s="8"/>
       <c r="C174" s="1"/>
-      <c r="D174" s="7"/>
+      <c r="D174" s="8"/>
       <c r="E174" s="1"/>
-      <c r="F174" s="13"/>
-      <c r="G174" s="13"/>
+      <c r="F174" s="12"/>
+      <c r="G174" s="12"/>
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
-      <c r="J174" s="20"/>
+      <c r="J174" s="16"/>
       <c r="AO174" s="1"/>
       <c r="AP174" s="1"/>
       <c r="AU174" s="1"/>
@@ -11624,24 +10679,24 @@
       <c r="BB174" s="1"/>
       <c r="BC174" s="1"/>
       <c r="BD174" s="1"/>
-      <c r="BE174" s="28"/>
-      <c r="BF174" s="28"/>
+      <c r="BE174" s="26"/>
+      <c r="BF174" s="26"/>
       <c r="BG174" s="1"/>
-      <c r="BH174" s="27"/>
+      <c r="BH174" s="25"/>
       <c r="BI174" s="1"/>
-      <c r="BJ174" s="28"/>
+      <c r="BJ174" s="26"/>
     </row>
     <row r="175" spans="1:62">
       <c r="A175" s="1"/>
-      <c r="B175" s="7"/>
+      <c r="B175" s="8"/>
       <c r="C175" s="1"/>
-      <c r="D175" s="7"/>
+      <c r="D175" s="8"/>
       <c r="E175" s="1"/>
-      <c r="F175" s="13"/>
-      <c r="G175" s="13"/>
+      <c r="F175" s="12"/>
+      <c r="G175" s="12"/>
       <c r="H175" s="1"/>
       <c r="I175" s="1"/>
-      <c r="J175" s="20"/>
+      <c r="J175" s="16"/>
       <c r="AO175" s="1"/>
       <c r="AP175" s="1"/>
       <c r="AU175" s="1"/>
@@ -11654,24 +10709,24 @@
       <c r="BB175" s="1"/>
       <c r="BC175" s="1"/>
       <c r="BD175" s="1"/>
-      <c r="BE175" s="28"/>
-      <c r="BF175" s="28"/>
+      <c r="BE175" s="26"/>
+      <c r="BF175" s="26"/>
       <c r="BG175" s="1"/>
-      <c r="BH175" s="27"/>
+      <c r="BH175" s="25"/>
       <c r="BI175" s="1"/>
-      <c r="BJ175" s="28"/>
+      <c r="BJ175" s="26"/>
     </row>
     <row r="176" spans="1:62">
       <c r="A176" s="1"/>
-      <c r="B176" s="7"/>
+      <c r="B176" s="8"/>
       <c r="C176" s="1"/>
-      <c r="D176" s="7"/>
+      <c r="D176" s="8"/>
       <c r="E176" s="1"/>
-      <c r="F176" s="13"/>
-      <c r="G176" s="13"/>
+      <c r="F176" s="12"/>
+      <c r="G176" s="12"/>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
-      <c r="J176" s="20"/>
+      <c r="J176" s="16"/>
       <c r="AO176" s="1"/>
       <c r="AP176" s="1"/>
       <c r="AU176" s="1"/>
@@ -11684,24 +10739,24 @@
       <c r="BB176" s="1"/>
       <c r="BC176" s="1"/>
       <c r="BD176" s="1"/>
-      <c r="BE176" s="28"/>
-      <c r="BF176" s="28"/>
+      <c r="BE176" s="26"/>
+      <c r="BF176" s="26"/>
       <c r="BG176" s="1"/>
-      <c r="BH176" s="27"/>
+      <c r="BH176" s="25"/>
       <c r="BI176" s="1"/>
-      <c r="BJ176" s="28"/>
+      <c r="BJ176" s="26"/>
     </row>
     <row r="177" spans="1:62">
       <c r="A177" s="1"/>
-      <c r="B177" s="7"/>
+      <c r="B177" s="8"/>
       <c r="C177" s="1"/>
-      <c r="D177" s="7"/>
+      <c r="D177" s="8"/>
       <c r="E177" s="1"/>
-      <c r="F177" s="13"/>
-      <c r="G177" s="13"/>
+      <c r="F177" s="12"/>
+      <c r="G177" s="12"/>
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
-      <c r="J177" s="20"/>
+      <c r="J177" s="16"/>
       <c r="AO177" s="1"/>
       <c r="AP177" s="1"/>
       <c r="AU177" s="1"/>
@@ -11714,24 +10769,24 @@
       <c r="BB177" s="1"/>
       <c r="BC177" s="1"/>
       <c r="BD177" s="1"/>
-      <c r="BE177" s="28"/>
-      <c r="BF177" s="28"/>
+      <c r="BE177" s="26"/>
+      <c r="BF177" s="26"/>
       <c r="BG177" s="1"/>
-      <c r="BH177" s="27"/>
+      <c r="BH177" s="25"/>
       <c r="BI177" s="1"/>
-      <c r="BJ177" s="28"/>
+      <c r="BJ177" s="26"/>
     </row>
     <row r="178" spans="1:62">
       <c r="A178" s="1"/>
-      <c r="B178" s="7"/>
+      <c r="B178" s="8"/>
       <c r="C178" s="1"/>
-      <c r="D178" s="7"/>
+      <c r="D178" s="8"/>
       <c r="E178" s="1"/>
-      <c r="F178" s="13"/>
-      <c r="G178" s="13"/>
+      <c r="F178" s="12"/>
+      <c r="G178" s="12"/>
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
-      <c r="J178" s="20"/>
+      <c r="J178" s="16"/>
       <c r="AO178" s="1"/>
       <c r="AP178" s="1"/>
       <c r="AU178" s="1"/>
@@ -11744,24 +10799,24 @@
       <c r="BB178" s="1"/>
       <c r="BC178" s="1"/>
       <c r="BD178" s="1"/>
-      <c r="BE178" s="28"/>
-      <c r="BF178" s="28"/>
+      <c r="BE178" s="26"/>
+      <c r="BF178" s="26"/>
       <c r="BG178" s="1"/>
-      <c r="BH178" s="27"/>
+      <c r="BH178" s="25"/>
       <c r="BI178" s="1"/>
-      <c r="BJ178" s="28"/>
+      <c r="BJ178" s="26"/>
     </row>
     <row r="179" spans="1:62">
       <c r="A179" s="1"/>
-      <c r="B179" s="7"/>
+      <c r="B179" s="8"/>
       <c r="C179" s="1"/>
-      <c r="D179" s="7"/>
+      <c r="D179" s="8"/>
       <c r="E179" s="1"/>
-      <c r="F179" s="13"/>
-      <c r="G179" s="13"/>
+      <c r="F179" s="12"/>
+      <c r="G179" s="12"/>
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
-      <c r="J179" s="20"/>
+      <c r="J179" s="16"/>
       <c r="AO179" s="1"/>
       <c r="AP179" s="1"/>
       <c r="AU179" s="1"/>
@@ -11774,24 +10829,24 @@
       <c r="BB179" s="1"/>
       <c r="BC179" s="1"/>
       <c r="BD179" s="1"/>
-      <c r="BE179" s="28"/>
-      <c r="BF179" s="28"/>
+      <c r="BE179" s="26"/>
+      <c r="BF179" s="26"/>
       <c r="BG179" s="1"/>
-      <c r="BH179" s="27"/>
+      <c r="BH179" s="25"/>
       <c r="BI179" s="1"/>
-      <c r="BJ179" s="28"/>
+      <c r="BJ179" s="26"/>
     </row>
     <row r="180" spans="1:62">
       <c r="A180" s="1"/>
-      <c r="B180" s="7"/>
+      <c r="B180" s="8"/>
       <c r="C180" s="1"/>
-      <c r="D180" s="7"/>
+      <c r="D180" s="8"/>
       <c r="E180" s="1"/>
-      <c r="F180" s="13"/>
-      <c r="G180" s="13"/>
+      <c r="F180" s="12"/>
+      <c r="G180" s="12"/>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
-      <c r="J180" s="20"/>
+      <c r="J180" s="16"/>
       <c r="AO180" s="1"/>
       <c r="AP180" s="1"/>
       <c r="AU180" s="1"/>
@@ -11804,24 +10859,24 @@
       <c r="BB180" s="1"/>
       <c r="BC180" s="1"/>
       <c r="BD180" s="1"/>
-      <c r="BE180" s="28"/>
-      <c r="BF180" s="28"/>
+      <c r="BE180" s="26"/>
+      <c r="BF180" s="26"/>
       <c r="BG180" s="1"/>
-      <c r="BH180" s="27"/>
+      <c r="BH180" s="25"/>
       <c r="BI180" s="1"/>
-      <c r="BJ180" s="28"/>
+      <c r="BJ180" s="26"/>
     </row>
     <row r="181" spans="1:62">
       <c r="A181" s="1"/>
-      <c r="B181" s="7"/>
+      <c r="B181" s="8"/>
       <c r="C181" s="1"/>
-      <c r="D181" s="7"/>
+      <c r="D181" s="8"/>
       <c r="E181" s="1"/>
-      <c r="F181" s="13"/>
-      <c r="G181" s="13"/>
+      <c r="F181" s="12"/>
+      <c r="G181" s="12"/>
       <c r="H181" s="1"/>
       <c r="I181" s="1"/>
-      <c r="J181" s="20"/>
+      <c r="J181" s="16"/>
       <c r="AO181" s="1"/>
       <c r="AP181" s="1"/>
       <c r="AU181" s="1"/>
@@ -11834,24 +10889,24 @@
       <c r="BB181" s="1"/>
       <c r="BC181" s="1"/>
       <c r="BD181" s="1"/>
-      <c r="BE181" s="28"/>
-      <c r="BF181" s="28"/>
+      <c r="BE181" s="26"/>
+      <c r="BF181" s="26"/>
       <c r="BG181" s="1"/>
-      <c r="BH181" s="27"/>
+      <c r="BH181" s="25"/>
       <c r="BI181" s="1"/>
-      <c r="BJ181" s="28"/>
+      <c r="BJ181" s="26"/>
     </row>
     <row r="182" spans="1:62">
       <c r="A182" s="1"/>
-      <c r="B182" s="7"/>
+      <c r="B182" s="8"/>
       <c r="C182" s="1"/>
-      <c r="D182" s="7"/>
+      <c r="D182" s="8"/>
       <c r="E182" s="1"/>
-      <c r="F182" s="13"/>
-      <c r="G182" s="13"/>
+      <c r="F182" s="12"/>
+      <c r="G182" s="12"/>
       <c r="H182" s="1"/>
       <c r="I182" s="1"/>
-      <c r="J182" s="20"/>
+      <c r="J182" s="16"/>
       <c r="AO182" s="1"/>
       <c r="AP182" s="1"/>
       <c r="AU182" s="1"/>
@@ -11864,24 +10919,24 @@
       <c r="BB182" s="1"/>
       <c r="BC182" s="1"/>
       <c r="BD182" s="1"/>
-      <c r="BE182" s="28"/>
-      <c r="BF182" s="28"/>
+      <c r="BE182" s="26"/>
+      <c r="BF182" s="26"/>
       <c r="BG182" s="1"/>
-      <c r="BH182" s="27"/>
+      <c r="BH182" s="25"/>
       <c r="BI182" s="1"/>
-      <c r="BJ182" s="28"/>
+      <c r="BJ182" s="26"/>
     </row>
     <row r="183" spans="1:62">
       <c r="A183" s="1"/>
-      <c r="B183" s="7"/>
+      <c r="B183" s="8"/>
       <c r="C183" s="1"/>
-      <c r="D183" s="7"/>
+      <c r="D183" s="8"/>
       <c r="E183" s="1"/>
-      <c r="F183" s="13"/>
-      <c r="G183" s="13"/>
+      <c r="F183" s="12"/>
+      <c r="G183" s="12"/>
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
-      <c r="J183" s="20"/>
+      <c r="J183" s="16"/>
       <c r="AO183" s="1"/>
       <c r="AP183" s="1"/>
       <c r="AU183" s="1"/>
@@ -11894,24 +10949,24 @@
       <c r="BB183" s="1"/>
       <c r="BC183" s="1"/>
       <c r="BD183" s="1"/>
-      <c r="BE183" s="28"/>
-      <c r="BF183" s="28"/>
+      <c r="BE183" s="26"/>
+      <c r="BF183" s="26"/>
       <c r="BG183" s="1"/>
-      <c r="BH183" s="27"/>
+      <c r="BH183" s="25"/>
       <c r="BI183" s="1"/>
-      <c r="BJ183" s="28"/>
+      <c r="BJ183" s="26"/>
     </row>
     <row r="184" spans="1:62">
       <c r="A184" s="1"/>
-      <c r="B184" s="7"/>
+      <c r="B184" s="8"/>
       <c r="C184" s="1"/>
-      <c r="D184" s="7"/>
+      <c r="D184" s="8"/>
       <c r="E184" s="1"/>
-      <c r="F184" s="13"/>
-      <c r="G184" s="13"/>
+      <c r="F184" s="12"/>
+      <c r="G184" s="12"/>
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
-      <c r="J184" s="20"/>
+      <c r="J184" s="16"/>
       <c r="AO184" s="1"/>
       <c r="AP184" s="1"/>
       <c r="AU184" s="1"/>
@@ -11924,24 +10979,24 @@
       <c r="BB184" s="1"/>
       <c r="BC184" s="1"/>
       <c r="BD184" s="1"/>
-      <c r="BE184" s="28"/>
-      <c r="BF184" s="28"/>
+      <c r="BE184" s="26"/>
+      <c r="BF184" s="26"/>
       <c r="BG184" s="1"/>
-      <c r="BH184" s="27"/>
+      <c r="BH184" s="25"/>
       <c r="BI184" s="1"/>
-      <c r="BJ184" s="28"/>
+      <c r="BJ184" s="26"/>
     </row>
     <row r="185" spans="1:62">
       <c r="A185" s="1"/>
-      <c r="B185" s="7"/>
+      <c r="B185" s="8"/>
       <c r="C185" s="1"/>
-      <c r="D185" s="7"/>
+      <c r="D185" s="8"/>
       <c r="E185" s="1"/>
-      <c r="F185" s="13"/>
-      <c r="G185" s="13"/>
+      <c r="F185" s="12"/>
+      <c r="G185" s="12"/>
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
-      <c r="J185" s="20"/>
+      <c r="J185" s="16"/>
       <c r="AO185" s="1"/>
       <c r="AP185" s="1"/>
       <c r="AU185" s="1"/>
@@ -11954,24 +11009,24 @@
       <c r="BB185" s="1"/>
       <c r="BC185" s="1"/>
       <c r="BD185" s="1"/>
-      <c r="BE185" s="28"/>
-      <c r="BF185" s="28"/>
+      <c r="BE185" s="26"/>
+      <c r="BF185" s="26"/>
       <c r="BG185" s="1"/>
-      <c r="BH185" s="27"/>
+      <c r="BH185" s="25"/>
       <c r="BI185" s="1"/>
-      <c r="BJ185" s="28"/>
+      <c r="BJ185" s="26"/>
     </row>
     <row r="186" spans="1:62">
       <c r="A186" s="1"/>
-      <c r="B186" s="7"/>
+      <c r="B186" s="8"/>
       <c r="C186" s="1"/>
-      <c r="D186" s="7"/>
+      <c r="D186" s="8"/>
       <c r="E186" s="1"/>
-      <c r="F186" s="13"/>
-      <c r="G186" s="13"/>
+      <c r="F186" s="12"/>
+      <c r="G186" s="12"/>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
-      <c r="J186" s="20"/>
+      <c r="J186" s="16"/>
       <c r="AO186" s="1"/>
       <c r="AP186" s="1"/>
       <c r="AU186" s="1"/>
@@ -11984,24 +11039,24 @@
       <c r="BB186" s="1"/>
       <c r="BC186" s="1"/>
       <c r="BD186" s="1"/>
-      <c r="BE186" s="28"/>
-      <c r="BF186" s="28"/>
+      <c r="BE186" s="26"/>
+      <c r="BF186" s="26"/>
       <c r="BG186" s="1"/>
-      <c r="BH186" s="27"/>
+      <c r="BH186" s="25"/>
       <c r="BI186" s="1"/>
-      <c r="BJ186" s="28"/>
+      <c r="BJ186" s="26"/>
     </row>
     <row r="187" spans="1:62">
       <c r="A187" s="1"/>
-      <c r="B187" s="7"/>
+      <c r="B187" s="8"/>
       <c r="C187" s="1"/>
-      <c r="D187" s="7"/>
+      <c r="D187" s="8"/>
       <c r="E187" s="1"/>
-      <c r="F187" s="13"/>
-      <c r="G187" s="13"/>
+      <c r="F187" s="12"/>
+      <c r="G187" s="12"/>
       <c r="H187" s="1"/>
       <c r="I187" s="1"/>
-      <c r="J187" s="20"/>
+      <c r="J187" s="16"/>
       <c r="AO187" s="1"/>
       <c r="AP187" s="1"/>
       <c r="AU187" s="1"/>
@@ -12014,24 +11069,24 @@
       <c r="BB187" s="1"/>
       <c r="BC187" s="1"/>
       <c r="BD187" s="1"/>
-      <c r="BE187" s="28"/>
-      <c r="BF187" s="28"/>
+      <c r="BE187" s="26"/>
+      <c r="BF187" s="26"/>
       <c r="BG187" s="1"/>
-      <c r="BH187" s="27"/>
+      <c r="BH187" s="25"/>
       <c r="BI187" s="1"/>
-      <c r="BJ187" s="28"/>
+      <c r="BJ187" s="26"/>
     </row>
     <row r="188" spans="1:62">
       <c r="A188" s="1"/>
-      <c r="B188" s="7"/>
+      <c r="B188" s="8"/>
       <c r="C188" s="1"/>
-      <c r="D188" s="7"/>
+      <c r="D188" s="8"/>
       <c r="E188" s="1"/>
-      <c r="F188" s="13"/>
-      <c r="G188" s="13"/>
+      <c r="F188" s="12"/>
+      <c r="G188" s="12"/>
       <c r="H188" s="1"/>
       <c r="I188" s="1"/>
-      <c r="J188" s="20"/>
+      <c r="J188" s="16"/>
       <c r="AO188" s="1"/>
       <c r="AP188" s="1"/>
       <c r="AU188" s="1"/>
@@ -12044,24 +11099,24 @@
       <c r="BB188" s="1"/>
       <c r="BC188" s="1"/>
       <c r="BD188" s="1"/>
-      <c r="BE188" s="28"/>
-      <c r="BF188" s="28"/>
+      <c r="BE188" s="26"/>
+      <c r="BF188" s="26"/>
       <c r="BG188" s="1"/>
-      <c r="BH188" s="27"/>
+      <c r="BH188" s="25"/>
       <c r="BI188" s="1"/>
-      <c r="BJ188" s="28"/>
+      <c r="BJ188" s="26"/>
     </row>
     <row r="189" spans="1:62">
       <c r="A189" s="1"/>
-      <c r="B189" s="7"/>
+      <c r="B189" s="8"/>
       <c r="C189" s="1"/>
-      <c r="D189" s="7"/>
+      <c r="D189" s="8"/>
       <c r="E189" s="1"/>
-      <c r="F189" s="13"/>
-      <c r="G189" s="13"/>
+      <c r="F189" s="12"/>
+      <c r="G189" s="12"/>
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
-      <c r="J189" s="20"/>
+      <c r="J189" s="16"/>
       <c r="AO189" s="1"/>
       <c r="AP189" s="1"/>
       <c r="AU189" s="1"/>
@@ -12074,24 +11129,24 @@
       <c r="BB189" s="1"/>
       <c r="BC189" s="1"/>
       <c r="BD189" s="1"/>
-      <c r="BE189" s="28"/>
-      <c r="BF189" s="28"/>
+      <c r="BE189" s="26"/>
+      <c r="BF189" s="26"/>
       <c r="BG189" s="1"/>
-      <c r="BH189" s="27"/>
+      <c r="BH189" s="25"/>
       <c r="BI189" s="1"/>
-      <c r="BJ189" s="28"/>
+      <c r="BJ189" s="26"/>
     </row>
     <row r="190" spans="1:62">
       <c r="A190" s="1"/>
-      <c r="B190" s="7"/>
+      <c r="B190" s="8"/>
       <c r="C190" s="1"/>
-      <c r="D190" s="7"/>
+      <c r="D190" s="8"/>
       <c r="E190" s="1"/>
-      <c r="F190" s="13"/>
-      <c r="G190" s="13"/>
+      <c r="F190" s="12"/>
+      <c r="G190" s="12"/>
       <c r="H190" s="1"/>
       <c r="I190" s="1"/>
-      <c r="J190" s="20"/>
+      <c r="J190" s="16"/>
       <c r="AO190" s="1"/>
       <c r="AP190" s="1"/>
       <c r="AU190" s="1"/>
@@ -12104,24 +11159,24 @@
       <c r="BB190" s="1"/>
       <c r="BC190" s="1"/>
       <c r="BD190" s="1"/>
-      <c r="BE190" s="28"/>
-      <c r="BF190" s="28"/>
+      <c r="BE190" s="26"/>
+      <c r="BF190" s="26"/>
       <c r="BG190" s="1"/>
-      <c r="BH190" s="27"/>
+      <c r="BH190" s="25"/>
       <c r="BI190" s="1"/>
-      <c r="BJ190" s="28"/>
+      <c r="BJ190" s="26"/>
     </row>
     <row r="191" spans="1:62">
       <c r="A191" s="1"/>
-      <c r="B191" s="7"/>
+      <c r="B191" s="8"/>
       <c r="C191" s="1"/>
-      <c r="D191" s="7"/>
+      <c r="D191" s="8"/>
       <c r="E191" s="1"/>
-      <c r="F191" s="13"/>
-      <c r="G191" s="13"/>
+      <c r="F191" s="12"/>
+      <c r="G191" s="12"/>
       <c r="H191" s="1"/>
       <c r="I191" s="1"/>
-      <c r="J191" s="20"/>
+      <c r="J191" s="16"/>
       <c r="AO191" s="1"/>
       <c r="AP191" s="1"/>
       <c r="AU191" s="1"/>
@@ -12134,24 +11189,24 @@
       <c r="BB191" s="1"/>
       <c r="BC191" s="1"/>
       <c r="BD191" s="1"/>
-      <c r="BE191" s="28"/>
-      <c r="BF191" s="28"/>
+      <c r="BE191" s="26"/>
+      <c r="BF191" s="26"/>
       <c r="BG191" s="1"/>
-      <c r="BH191" s="27"/>
+      <c r="BH191" s="25"/>
       <c r="BI191" s="1"/>
-      <c r="BJ191" s="28"/>
+      <c r="BJ191" s="26"/>
     </row>
     <row r="192" spans="1:62">
       <c r="A192" s="1"/>
-      <c r="B192" s="7"/>
+      <c r="B192" s="8"/>
       <c r="C192" s="1"/>
-      <c r="D192" s="7"/>
+      <c r="D192" s="8"/>
       <c r="E192" s="1"/>
-      <c r="F192" s="13"/>
-      <c r="G192" s="13"/>
+      <c r="F192" s="12"/>
+      <c r="G192" s="12"/>
       <c r="H192" s="1"/>
       <c r="I192" s="1"/>
-      <c r="J192" s="20"/>
+      <c r="J192" s="16"/>
       <c r="AO192" s="1"/>
       <c r="AP192" s="1"/>
       <c r="AU192" s="1"/>
@@ -12164,24 +11219,24 @@
       <c r="BB192" s="1"/>
       <c r="BC192" s="1"/>
       <c r="BD192" s="1"/>
-      <c r="BE192" s="28"/>
-      <c r="BF192" s="28"/>
+      <c r="BE192" s="26"/>
+      <c r="BF192" s="26"/>
       <c r="BG192" s="1"/>
-      <c r="BH192" s="27"/>
+      <c r="BH192" s="25"/>
       <c r="BI192" s="1"/>
-      <c r="BJ192" s="28"/>
+      <c r="BJ192" s="26"/>
     </row>
     <row r="193" spans="1:62">
       <c r="A193" s="1"/>
-      <c r="B193" s="7"/>
+      <c r="B193" s="8"/>
       <c r="C193" s="1"/>
-      <c r="D193" s="7"/>
+      <c r="D193" s="8"/>
       <c r="E193" s="1"/>
-      <c r="F193" s="13"/>
-      <c r="G193" s="13"/>
+      <c r="F193" s="12"/>
+      <c r="G193" s="12"/>
       <c r="H193" s="1"/>
       <c r="I193" s="1"/>
-      <c r="J193" s="20"/>
+      <c r="J193" s="16"/>
       <c r="AO193" s="1"/>
       <c r="AP193" s="1"/>
       <c r="AU193" s="1"/>
@@ -12194,24 +11249,24 @@
       <c r="BB193" s="1"/>
       <c r="BC193" s="1"/>
       <c r="BD193" s="1"/>
-      <c r="BE193" s="28"/>
-      <c r="BF193" s="28"/>
+      <c r="BE193" s="26"/>
+      <c r="BF193" s="26"/>
       <c r="BG193" s="1"/>
-      <c r="BH193" s="27"/>
+      <c r="BH193" s="25"/>
       <c r="BI193" s="1"/>
-      <c r="BJ193" s="28"/>
+      <c r="BJ193" s="26"/>
     </row>
     <row r="194" spans="1:62">
       <c r="A194" s="1"/>
-      <c r="B194" s="7"/>
+      <c r="B194" s="8"/>
       <c r="C194" s="1"/>
-      <c r="D194" s="7"/>
+      <c r="D194" s="8"/>
       <c r="E194" s="1"/>
-      <c r="F194" s="13"/>
-      <c r="G194" s="13"/>
+      <c r="F194" s="12"/>
+      <c r="G194" s="12"/>
       <c r="H194" s="1"/>
       <c r="I194" s="1"/>
-      <c r="J194" s="20"/>
+      <c r="J194" s="16"/>
       <c r="AO194" s="1"/>
       <c r="AP194" s="1"/>
       <c r="AU194" s="1"/>
@@ -12224,24 +11279,24 @@
       <c r="BB194" s="1"/>
       <c r="BC194" s="1"/>
       <c r="BD194" s="1"/>
-      <c r="BE194" s="28"/>
-      <c r="BF194" s="28"/>
+      <c r="BE194" s="26"/>
+      <c r="BF194" s="26"/>
       <c r="BG194" s="1"/>
-      <c r="BH194" s="27"/>
+      <c r="BH194" s="25"/>
       <c r="BI194" s="1"/>
-      <c r="BJ194" s="28"/>
+      <c r="BJ194" s="26"/>
     </row>
     <row r="195" spans="1:62">
       <c r="A195" s="1"/>
-      <c r="B195" s="7"/>
+      <c r="B195" s="8"/>
       <c r="C195" s="1"/>
-      <c r="D195" s="7"/>
+      <c r="D195" s="8"/>
       <c r="E195" s="1"/>
-      <c r="F195" s="13"/>
-      <c r="G195" s="13"/>
+      <c r="F195" s="12"/>
+      <c r="G195" s="12"/>
       <c r="H195" s="1"/>
       <c r="I195" s="1"/>
-      <c r="J195" s="20"/>
+      <c r="J195" s="16"/>
       <c r="AO195" s="1"/>
       <c r="AP195" s="1"/>
       <c r="AU195" s="1"/>
@@ -12254,24 +11309,24 @@
       <c r="BB195" s="1"/>
       <c r="BC195" s="1"/>
       <c r="BD195" s="1"/>
-      <c r="BE195" s="28"/>
-      <c r="BF195" s="28"/>
+      <c r="BE195" s="26"/>
+      <c r="BF195" s="26"/>
       <c r="BG195" s="1"/>
-      <c r="BH195" s="27"/>
+      <c r="BH195" s="25"/>
       <c r="BI195" s="1"/>
-      <c r="BJ195" s="28"/>
+      <c r="BJ195" s="26"/>
     </row>
     <row r="196" spans="1:62">
       <c r="A196" s="1"/>
-      <c r="B196" s="7"/>
+      <c r="B196" s="8"/>
       <c r="C196" s="1"/>
-      <c r="D196" s="7"/>
+      <c r="D196" s="8"/>
       <c r="E196" s="1"/>
-      <c r="F196" s="13"/>
-      <c r="G196" s="13"/>
+      <c r="F196" s="12"/>
+      <c r="G196" s="12"/>
       <c r="H196" s="1"/>
       <c r="I196" s="1"/>
-      <c r="J196" s="20"/>
+      <c r="J196" s="16"/>
       <c r="AO196" s="1"/>
       <c r="AP196" s="1"/>
       <c r="AU196" s="1"/>
@@ -12284,24 +11339,24 @@
       <c r="BB196" s="1"/>
       <c r="BC196" s="1"/>
       <c r="BD196" s="1"/>
-      <c r="BE196" s="28"/>
-      <c r="BF196" s="28"/>
+      <c r="BE196" s="26"/>
+      <c r="BF196" s="26"/>
       <c r="BG196" s="1"/>
-      <c r="BH196" s="27"/>
+      <c r="BH196" s="25"/>
       <c r="BI196" s="1"/>
-      <c r="BJ196" s="28"/>
+      <c r="BJ196" s="26"/>
     </row>
     <row r="197" spans="1:62">
       <c r="A197" s="1"/>
-      <c r="B197" s="7"/>
+      <c r="B197" s="8"/>
       <c r="C197" s="1"/>
-      <c r="D197" s="7"/>
+      <c r="D197" s="8"/>
       <c r="E197" s="1"/>
-      <c r="F197" s="13"/>
-      <c r="G197" s="13"/>
+      <c r="F197" s="12"/>
+      <c r="G197" s="12"/>
       <c r="H197" s="1"/>
       <c r="I197" s="1"/>
-      <c r="J197" s="20"/>
+      <c r="J197" s="16"/>
       <c r="AO197" s="1"/>
       <c r="AP197" s="1"/>
       <c r="AU197" s="1"/>
@@ -12314,24 +11369,24 @@
       <c r="BB197" s="1"/>
       <c r="BC197" s="1"/>
       <c r="BD197" s="1"/>
-      <c r="BE197" s="28"/>
-      <c r="BF197" s="28"/>
+      <c r="BE197" s="26"/>
+      <c r="BF197" s="26"/>
       <c r="BG197" s="1"/>
-      <c r="BH197" s="27"/>
+      <c r="BH197" s="25"/>
       <c r="BI197" s="1"/>
-      <c r="BJ197" s="28"/>
+      <c r="BJ197" s="26"/>
     </row>
     <row r="198" spans="1:62">
       <c r="A198" s="1"/>
-      <c r="B198" s="7"/>
+      <c r="B198" s="8"/>
       <c r="C198" s="1"/>
-      <c r="D198" s="7"/>
+      <c r="D198" s="8"/>
       <c r="E198" s="1"/>
-      <c r="F198" s="13"/>
-      <c r="G198" s="13"/>
+      <c r="F198" s="12"/>
+      <c r="G198" s="12"/>
       <c r="H198" s="1"/>
       <c r="I198" s="1"/>
-      <c r="J198" s="20"/>
+      <c r="J198" s="16"/>
       <c r="AO198" s="1"/>
       <c r="AP198" s="1"/>
       <c r="AU198" s="1"/>
@@ -12344,23 +11399,23 @@
       <c r="BB198" s="1"/>
       <c r="BC198" s="1"/>
       <c r="BD198" s="1"/>
-      <c r="BE198" s="28"/>
-      <c r="BF198" s="28"/>
+      <c r="BE198" s="26"/>
+      <c r="BF198" s="26"/>
       <c r="BG198" s="1"/>
-      <c r="BH198" s="27"/>
+      <c r="BH198" s="25"/>
       <c r="BI198" s="1"/>
-      <c r="BJ198" s="28"/>
+      <c r="BJ198" s="26"/>
     </row>
     <row r="199" spans="2:62">
-      <c r="B199" s="7"/>
+      <c r="B199" s="8"/>
       <c r="C199" s="1"/>
-      <c r="D199" s="7"/>
+      <c r="D199" s="8"/>
       <c r="E199" s="1"/>
-      <c r="F199" s="13"/>
-      <c r="G199" s="13"/>
+      <c r="F199" s="12"/>
+      <c r="G199" s="12"/>
       <c r="H199" s="1"/>
       <c r="I199" s="1"/>
-      <c r="J199" s="20"/>
+      <c r="J199" s="16"/>
       <c r="AO199" s="1"/>
       <c r="AP199" s="1"/>
       <c r="AU199" s="1"/>
@@ -12373,12 +11428,12 @@
       <c r="BB199" s="1"/>
       <c r="BC199" s="1"/>
       <c r="BD199" s="1"/>
-      <c r="BE199" s="28"/>
-      <c r="BF199" s="28"/>
+      <c r="BE199" s="26"/>
+      <c r="BF199" s="26"/>
       <c r="BG199" s="1"/>
-      <c r="BH199" s="27"/>
+      <c r="BH199" s="25"/>
       <c r="BI199" s="1"/>
-      <c r="BJ199" s="28"/>
+      <c r="BJ199" s="26"/>
     </row>
     <row r="200" spans="10:10">
       <c r="J200" s="16"/>
